--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="C2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="D2">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="E2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="F2">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="G2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="H2">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="I2">
-        <v>663</v>
+        <v>677</v>
       </c>
       <c r="J2">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="K2">
-        <v>807</v>
+        <v>832</v>
       </c>
       <c r="L2">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="M2">
-        <v>594</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="C3">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D3">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="E3">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="F3">
-        <v>699</v>
+        <v>718</v>
       </c>
       <c r="G3">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="H3">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="I3">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="J3">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="K3">
-        <v>761</v>
+        <v>778</v>
       </c>
       <c r="L3">
+        <v>674</v>
+      </c>
+      <c r="M3">
         <v>661</v>
-      </c>
-      <c r="M3">
-        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C4">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D4">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E4">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F4">
+        <v>283</v>
+      </c>
+      <c r="G4">
         <v>280</v>
       </c>
-      <c r="G4">
-        <v>273</v>
-      </c>
       <c r="H4">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I4">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J4">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="K4">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L4">
+        <v>205</v>
+      </c>
+      <c r="M4">
         <v>202</v>
-      </c>
-      <c r="M4">
-        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,28 +994,28 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D5">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>64</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>80</v>
       </c>
       <c r="J5">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K5">
         <v>46</v>
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="C6">
-        <v>1359</v>
+        <v>1385</v>
       </c>
       <c r="D6">
-        <v>1493</v>
+        <v>1517</v>
       </c>
       <c r="E6">
-        <v>1191</v>
+        <v>1216</v>
       </c>
       <c r="F6">
-        <v>872</v>
+        <v>894</v>
       </c>
       <c r="G6">
-        <v>1023</v>
+        <v>1043</v>
       </c>
       <c r="H6">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="I6">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="J6">
-        <v>1206</v>
+        <v>1228</v>
       </c>
       <c r="K6">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="L6">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="M6">
-        <v>511</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2354</v>
+        <v>2400</v>
       </c>
       <c r="C7">
-        <v>2905</v>
+        <v>2969</v>
       </c>
       <c r="D7">
-        <v>3235</v>
+        <v>3305</v>
       </c>
       <c r="E7">
-        <v>2753</v>
+        <v>2812</v>
       </c>
       <c r="F7">
-        <v>2509</v>
+        <v>2578</v>
       </c>
       <c r="G7">
-        <v>2749</v>
+        <v>2804</v>
       </c>
       <c r="H7">
-        <v>2546</v>
+        <v>2583</v>
       </c>
       <c r="I7">
-        <v>2609</v>
+        <v>2679</v>
       </c>
       <c r="J7">
-        <v>3104</v>
+        <v>3167</v>
       </c>
       <c r="K7">
-        <v>2892</v>
+        <v>2957</v>
       </c>
       <c r="L7">
-        <v>2294</v>
+        <v>2333</v>
       </c>
       <c r="M7">
-        <v>1996</v>
+        <v>2041</v>
       </c>
     </row>
   </sheetData>
@@ -1201,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -1239,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1255,6 +1255,9 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>2</v>
       </c>
@@ -1331,19 +1334,19 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>8</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1504,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -1525,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2">
         <v>9</v>
@@ -1539,28 +1542,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -1583,7 +1586,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1592,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1601,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1635,7 +1638,7 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>53</v>
@@ -1659,7 +1662,7 @@
         <v>19</v>
       </c>
       <c r="K6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1673,34 +1676,34 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>44</v>
+      </c>
+      <c r="D7">
+        <v>80</v>
+      </c>
+      <c r="E7">
         <v>37</v>
       </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>78</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
-      </c>
       <c r="F7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>23</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>31</v>
       </c>
       <c r="K7">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L7">
         <v>28</v>
@@ -1780,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>38</v>
@@ -1789,22 +1792,22 @@
         <v>45</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G2">
         <v>42</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K2">
         <v>46</v>
@@ -1813,7 +1816,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1824,37 +1827,37 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>57</v>
       </c>
       <c r="G3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1877,7 +1880,7 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1906,7 +1909,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -1921,7 +1924,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1944,28 +1947,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D6">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E6">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F6">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>58</v>
       </c>
       <c r="I6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -1974,7 +1977,7 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M6">
         <v>38</v>
@@ -1985,40 +1988,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C7">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E7">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L7">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M7">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2092,16 +2095,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>14</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -2119,13 +2122,13 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>13</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2133,13 +2136,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>17</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>14</v>
@@ -2148,7 +2151,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>16</v>
@@ -2157,16 +2160,16 @@
         <v>17</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K3">
         <v>15</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2277,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6">
         <v>11</v>
@@ -2288,22 +2291,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>60</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7">
         <v>48</v>
       </c>
       <c r="G7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7">
         <v>44</v>
@@ -2312,16 +2315,16 @@
         <v>52</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2395,19 +2398,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2">
         <v>27</v>
@@ -2419,16 +2422,16 @@
         <v>27</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2445,31 +2448,31 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>45</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J3">
         <v>35</v>
       </c>
       <c r="K3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L3">
         <v>34</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2477,13 +2480,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -2492,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -2524,13 +2527,13 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2565,22 +2568,22 @@
         <v>63</v>
       </c>
       <c r="E6">
+        <v>54</v>
+      </c>
+      <c r="F6">
         <v>53</v>
       </c>
-      <c r="F6">
-        <v>52</v>
-      </c>
       <c r="G6">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H6">
         <v>39</v>
       </c>
       <c r="I6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K6">
         <v>38</v>
@@ -2597,40 +2600,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M7">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2707,7 +2710,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -2722,7 +2725,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>15</v>
@@ -2737,7 +2740,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2748,7 +2751,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>17</v>
@@ -2763,7 +2766,7 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -2772,13 +2775,13 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2859,7 +2862,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -2874,16 +2877,16 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <v>7</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>16</v>
@@ -2892,7 +2895,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2900,10 +2903,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>61</v>
@@ -2915,25 +2918,25 @@
         <v>49</v>
       </c>
       <c r="G7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3007,10 +3010,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -3034,13 +3037,13 @@
         <v>28</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>22</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3060,10 +3063,10 @@
         <v>31</v>
       </c>
       <c r="F3">
+        <v>26</v>
+      </c>
+      <c r="G3">
         <v>25</v>
-      </c>
-      <c r="G3">
-        <v>23</v>
       </c>
       <c r="H3">
         <v>39</v>
@@ -3075,7 +3078,7 @@
         <v>34</v>
       </c>
       <c r="K3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3">
         <v>20</v>
@@ -3107,7 +3110,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -3133,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3165,10 +3168,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -3177,7 +3180,7 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -3186,16 +3189,16 @@
         <v>16</v>
       </c>
       <c r="I6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J6">
         <v>40</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -3206,40 +3209,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7">
         <v>86</v>
       </c>
       <c r="F7">
+        <v>86</v>
+      </c>
+      <c r="G7">
+        <v>74</v>
+      </c>
+      <c r="H7">
         <v>84</v>
       </c>
-      <c r="G7">
-        <v>72</v>
-      </c>
-      <c r="H7">
-        <v>83</v>
-      </c>
       <c r="I7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7">
         <v>108</v>
       </c>
       <c r="K7">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3369,7 @@
         <v>14</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -3375,19 +3378,19 @@
         <v>14</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <v>21</v>
       </c>
       <c r="K3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>10</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3465,7 +3468,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -3483,19 +3486,19 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L6">
         <v>16</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3506,7 +3509,7 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7">
         <v>68</v>
@@ -3515,7 +3518,7 @@
         <v>62</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>42</v>
@@ -3524,19 +3527,19 @@
         <v>40</v>
       </c>
       <c r="I7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L7">
         <v>43</v>
       </c>
       <c r="M7">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3613,13 +3616,13 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>7</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>9</v>
@@ -3631,7 +3634,7 @@
         <v>14</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <v>12</v>
@@ -3643,7 +3646,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3651,13 +3654,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -3666,7 +3669,7 @@
         <v>19</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>18</v>
@@ -3675,13 +3678,13 @@
         <v>16</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3">
         <v>17</v>
       </c>
       <c r="L3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3">
         <v>15</v>
@@ -3765,7 +3768,7 @@
         <v>27</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -3780,7 +3783,7 @@
         <v>19</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>14</v>
@@ -3789,7 +3792,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -3803,40 +3806,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>47</v>
       </c>
       <c r="G7">
+        <v>59</v>
+      </c>
+      <c r="H7">
+        <v>55</v>
+      </c>
+      <c r="I7">
         <v>58</v>
       </c>
-      <c r="H7">
-        <v>54</v>
-      </c>
-      <c r="I7">
-        <v>56</v>
-      </c>
       <c r="J7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3910,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4052,7 +4055,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -4177,10 +4180,10 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2">
         <v>22</v>
@@ -4189,10 +4192,10 @@
         <v>22</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4200,7 +4203,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -4244,7 +4247,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -4326,13 +4329,13 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>17</v>
@@ -4350,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="K6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6">
         <v>15</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4364,31 +4367,31 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I7">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K7">
         <v>83</v>
@@ -4405,40 +4408,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E8">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F8">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G8">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H8">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I8">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L8">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M8">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4467,13 +4470,13 @@
         <v>18</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9">
         <v>13</v>
@@ -4493,7 +4496,7 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>35</v>
@@ -4502,16 +4505,16 @@
         <v>17</v>
       </c>
       <c r="G10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H10">
         <v>28</v>
       </c>
       <c r="I10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10">
         <v>18</v>
@@ -4520,7 +4523,7 @@
         <v>12</v>
       </c>
       <c r="M10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4528,7 +4531,7 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>47</v>
@@ -4537,19 +4540,19 @@
         <v>64</v>
       </c>
       <c r="E11">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H11">
         <v>41</v>
       </c>
       <c r="I11">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J11">
         <v>39</v>
@@ -4558,7 +4561,7 @@
         <v>63</v>
       </c>
       <c r="L11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M11">
         <v>30</v>
@@ -4613,7 +4616,7 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -4648,7 +4651,7 @@
         <v>11</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>17</v>
@@ -4666,7 +4669,7 @@
         <v>14</v>
       </c>
       <c r="I14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14">
         <v>15</v>
@@ -4689,7 +4692,7 @@
         <v>23</v>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>40</v>
@@ -4707,7 +4710,7 @@
         <v>25</v>
       </c>
       <c r="I15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J15">
         <v>36</v>
@@ -4716,7 +4719,7 @@
         <v>18</v>
       </c>
       <c r="L15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M15">
         <v>23</v>
@@ -4780,7 +4783,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -4806,13 +4809,13 @@
         <v>11</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18">
         <v>16</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>12</v>
@@ -4824,10 +4827,10 @@
         <v>25</v>
       </c>
       <c r="J18">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18">
         <v>16</v>
@@ -4841,37 +4844,37 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F19">
+        <v>75</v>
+      </c>
+      <c r="G19">
+        <v>86</v>
+      </c>
+      <c r="H19">
+        <v>68</v>
+      </c>
+      <c r="I19">
+        <v>68</v>
+      </c>
+      <c r="J19">
+        <v>101</v>
+      </c>
+      <c r="K19">
         <v>72</v>
       </c>
-      <c r="G19">
-        <v>82</v>
-      </c>
-      <c r="H19">
-        <v>66</v>
-      </c>
-      <c r="I19">
-        <v>66</v>
-      </c>
-      <c r="J19">
-        <v>98</v>
-      </c>
-      <c r="K19">
-        <v>71</v>
-      </c>
       <c r="L19">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M19">
         <v>74</v>
@@ -4882,40 +4885,40 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E20">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F20">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G20">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H20">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I20">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J20">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K20">
         <v>69</v>
       </c>
       <c r="L20">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M20">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4944,13 +4947,13 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J21">
         <v>4</v>
       </c>
       <c r="K21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -4967,7 +4970,7 @@
         <v>11</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -4976,7 +4979,7 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>9</v>
@@ -4991,7 +4994,7 @@
         <v>4</v>
       </c>
       <c r="K22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -5005,13 +5008,13 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23">
         <v>22</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23">
         <v>37</v>
@@ -5029,10 +5032,10 @@
         <v>29</v>
       </c>
       <c r="J23">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L23">
         <v>26</v>
@@ -5064,13 +5067,13 @@
         <v>11</v>
       </c>
       <c r="H24">
+        <v>11</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
         <v>10</v>
-      </c>
-      <c r="I24">
-        <v>3</v>
-      </c>
-      <c r="J24">
-        <v>9</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -5087,7 +5090,7 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -5099,7 +5102,7 @@
         <v>14</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>9</v>
@@ -5114,13 +5117,13 @@
         <v>16</v>
       </c>
       <c r="K25">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L25">
         <v>11</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5172,7 +5175,7 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27">
         <v>18</v>
@@ -5181,7 +5184,7 @@
         <v>21</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27">
         <v>25</v>
@@ -5193,16 +5196,16 @@
         <v>28</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27">
         <v>35</v>
       </c>
       <c r="L27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M27">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5233,40 +5236,40 @@
         <v>35</v>
       </c>
       <c r="B29">
+        <v>144</v>
+      </c>
+      <c r="C29">
+        <v>195</v>
+      </c>
+      <c r="D29">
+        <v>196</v>
+      </c>
+      <c r="E29">
         <v>138</v>
       </c>
-      <c r="C29">
-        <v>189</v>
-      </c>
-      <c r="D29">
-        <v>193</v>
-      </c>
-      <c r="E29">
-        <v>134</v>
-      </c>
       <c r="F29">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G29">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H29">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I29">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J29">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="K29">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L29">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M29">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5274,7 +5277,7 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -5318,19 +5321,19 @@
         <v>22</v>
       </c>
       <c r="C31">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31">
         <v>16</v>
@@ -5377,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32">
         <v>7</v>
@@ -5397,40 +5400,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C33">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D33">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E33">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F33">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G33">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H33">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J33">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K33">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L33">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M33">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5450,7 +5453,7 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>15</v>
@@ -5459,10 +5462,10 @@
         <v>12</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34">
         <v>19</v>
@@ -5488,7 +5491,7 @@
         <v>5</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -5520,19 +5523,19 @@
         <v>42</v>
       </c>
       <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="C36">
         <v>30</v>
       </c>
-      <c r="C36">
-        <v>28</v>
-      </c>
       <c r="D36">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F36">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G36">
         <v>27</v>
@@ -5544,13 +5547,13 @@
         <v>37</v>
       </c>
       <c r="J36">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K36">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M36">
         <v>22</v>
@@ -5561,40 +5564,40 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C37">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D37">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E37">
         <v>86</v>
       </c>
       <c r="F37">
+        <v>86</v>
+      </c>
+      <c r="G37">
+        <v>74</v>
+      </c>
+      <c r="H37">
         <v>84</v>
       </c>
-      <c r="G37">
-        <v>72</v>
-      </c>
-      <c r="H37">
-        <v>83</v>
-      </c>
       <c r="I37">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J37">
         <v>108</v>
       </c>
       <c r="K37">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L37">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M37">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5716,13 +5719,13 @@
         <v>18</v>
       </c>
       <c r="E41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F41">
         <v>10</v>
       </c>
       <c r="G41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H41">
         <v>9</v>
@@ -5731,13 +5734,13 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M41">
         <v>8</v>
@@ -5751,37 +5754,37 @@
         <v>99</v>
       </c>
       <c r="C42">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D42">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F42">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>98</v>
       </c>
       <c r="H42">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I42">
         <v>69</v>
       </c>
       <c r="J42">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K42">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L42">
         <v>80</v>
       </c>
       <c r="M42">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5801,7 +5804,7 @@
         <v>17</v>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G43">
         <v>23</v>
@@ -5810,13 +5813,13 @@
         <v>20</v>
       </c>
       <c r="I43">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J43">
         <v>38</v>
       </c>
       <c r="K43">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L43">
         <v>17</v>
@@ -5830,19 +5833,19 @@
         <v>50</v>
       </c>
       <c r="B44">
+        <v>27</v>
+      </c>
+      <c r="C44">
+        <v>24</v>
+      </c>
+      <c r="D44">
         <v>26</v>
-      </c>
-      <c r="C44">
-        <v>23</v>
-      </c>
-      <c r="D44">
-        <v>24</v>
       </c>
       <c r="E44">
         <v>36</v>
       </c>
       <c r="F44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G44">
         <v>29</v>
@@ -5863,7 +5866,7 @@
         <v>15</v>
       </c>
       <c r="M44">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -5927,7 +5930,7 @@
         <v>3</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H46">
         <v>15</v>
@@ -5939,13 +5942,13 @@
         <v>9</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L46">
         <v>7</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -5953,7 +5956,7 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47">
         <v>19</v>
@@ -5974,7 +5977,7 @@
         <v>23</v>
       </c>
       <c r="I47">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J47">
         <v>29</v>
@@ -6006,28 +6009,28 @@
         <v>30</v>
       </c>
       <c r="F48">
+        <v>26</v>
+      </c>
+      <c r="G48">
         <v>25</v>
       </c>
-      <c r="G48">
+      <c r="H48">
+        <v>34</v>
+      </c>
+      <c r="I48">
         <v>23</v>
       </c>
-      <c r="H48">
-        <v>33</v>
-      </c>
-      <c r="I48">
-        <v>22</v>
-      </c>
       <c r="J48">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L48">
         <v>38</v>
       </c>
       <c r="M48">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6041,31 +6044,31 @@
         <v>18</v>
       </c>
       <c r="D49">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G49">
         <v>18</v>
       </c>
       <c r="H49">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I49">
         <v>9</v>
       </c>
       <c r="J49">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K49">
         <v>19</v>
       </c>
       <c r="L49">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M49">
         <v>13</v>
@@ -6094,13 +6097,13 @@
         <v>13</v>
       </c>
       <c r="H50">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I50">
         <v>9</v>
       </c>
       <c r="J50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K50">
         <v>11</v>
@@ -6123,22 +6126,22 @@
         <v>26</v>
       </c>
       <c r="D51">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E51">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F51">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G51">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H51">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I51">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J51">
         <v>39</v>
@@ -6161,16 +6164,16 @@
         <v>35</v>
       </c>
       <c r="C52">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D52">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E52">
         <v>64</v>
       </c>
       <c r="F52">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G52">
         <v>48</v>
@@ -6179,7 +6182,7 @@
         <v>46</v>
       </c>
       <c r="I52">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J52">
         <v>69</v>
@@ -6191,7 +6194,7 @@
         <v>45</v>
       </c>
       <c r="M52">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6199,34 +6202,34 @@
         <v>59</v>
       </c>
       <c r="B53">
+        <v>38</v>
+      </c>
+      <c r="C53">
+        <v>44</v>
+      </c>
+      <c r="D53">
+        <v>80</v>
+      </c>
+      <c r="E53">
         <v>37</v>
       </c>
-      <c r="C53">
-        <v>41</v>
-      </c>
-      <c r="D53">
-        <v>78</v>
-      </c>
-      <c r="E53">
-        <v>36</v>
-      </c>
       <c r="F53">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G53">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H53">
         <v>23</v>
       </c>
       <c r="I53">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J53">
         <v>31</v>
       </c>
       <c r="K53">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L53">
         <v>28</v>
@@ -6243,13 +6246,13 @@
         <v>40</v>
       </c>
       <c r="C54">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D54">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E54">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F54">
         <v>48</v>
@@ -6264,16 +6267,16 @@
         <v>61</v>
       </c>
       <c r="J54">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K54">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L54">
         <v>46</v>
       </c>
       <c r="M54">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6290,7 +6293,7 @@
         <v>25</v>
       </c>
       <c r="E55">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F55">
         <v>22</v>
@@ -6305,13 +6308,13 @@
         <v>29</v>
       </c>
       <c r="J55">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K55">
         <v>30</v>
       </c>
       <c r="L55">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M55">
         <v>23</v>
@@ -6328,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56">
         <v>8</v>
@@ -6387,10 +6390,10 @@
         <v>9</v>
       </c>
       <c r="J57">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L57">
         <v>15</v>
@@ -6451,7 +6454,7 @@
         <v>3</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59">
         <v>2</v>
@@ -6489,25 +6492,25 @@
         <v>14</v>
       </c>
       <c r="G60">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H60">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I60">
         <v>11</v>
       </c>
       <c r="J60">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K60">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L60">
         <v>16</v>
       </c>
       <c r="M60">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6527,7 +6530,7 @@
         <v>2</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -6576,7 +6579,7 @@
         <v>133</v>
       </c>
       <c r="C63">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D63">
         <v>82</v>
@@ -6588,16 +6591,16 @@
         <v>55</v>
       </c>
       <c r="G63">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63">
         <v>41</v>
       </c>
       <c r="I63">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J63">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K63">
         <v>31</v>
@@ -6606,7 +6609,7 @@
         <v>10</v>
       </c>
       <c r="M63">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6617,31 +6620,31 @@
         <v>19</v>
       </c>
       <c r="C64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D64">
         <v>10</v>
       </c>
       <c r="E64">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F64">
         <v>12</v>
       </c>
       <c r="G64">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H64">
         <v>13</v>
       </c>
       <c r="I64">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J64">
         <v>18</v>
       </c>
       <c r="K64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L64">
         <v>21</v>
@@ -6658,7 +6661,7 @@
         <v>45</v>
       </c>
       <c r="C65">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D65">
         <v>68</v>
@@ -6667,7 +6670,7 @@
         <v>62</v>
       </c>
       <c r="F65">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G65">
         <v>42</v>
@@ -6676,19 +6679,19 @@
         <v>40</v>
       </c>
       <c r="I65">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J65">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K65">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L65">
         <v>43</v>
       </c>
       <c r="M65">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6711,7 +6714,7 @@
         <v>5</v>
       </c>
       <c r="G66">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H66">
         <v>8</v>
@@ -6720,7 +6723,7 @@
         <v>4</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K66">
         <v>13</v>
@@ -6734,37 +6737,37 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C67">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D67">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E67">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F67">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G67">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H67">
         <v>92</v>
       </c>
       <c r="I67">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J67">
         <v>114</v>
       </c>
       <c r="K67">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L67">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M67">
         <v>59</v>
@@ -6775,7 +6778,7 @@
         <v>74</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>6</v>
@@ -6790,7 +6793,7 @@
         <v>3</v>
       </c>
       <c r="G68">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H68">
         <v>3</v>
@@ -6837,19 +6840,19 @@
         <v>2</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J69">
         <v>8</v>
       </c>
       <c r="K69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L69">
         <v>7</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6936,7 +6939,7 @@
         <v>78</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72">
         <v>11</v>
@@ -6948,7 +6951,7 @@
         <v>16</v>
       </c>
       <c r="F72">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G72">
         <v>14</v>
@@ -6980,19 +6983,19 @@
         <v>16</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D73">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E73">
         <v>30</v>
       </c>
       <c r="F73">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G73">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H73">
         <v>30</v>
@@ -7001,7 +7004,7 @@
         <v>28</v>
       </c>
       <c r="J73">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K73">
         <v>32</v>
@@ -7080,7 +7083,7 @@
         <v>5</v>
       </c>
       <c r="J75">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K75">
         <v>8</v>
@@ -7106,10 +7109,10 @@
         <v>26</v>
       </c>
       <c r="E76">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F76">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G76">
         <v>42</v>
@@ -7118,19 +7121,19 @@
         <v>24</v>
       </c>
       <c r="I76">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J76">
         <v>52</v>
       </c>
       <c r="K76">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L76">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M76">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7150,7 +7153,7 @@
         <v>18</v>
       </c>
       <c r="F77">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77">
         <v>21</v>
@@ -7179,16 +7182,16 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C78">
+        <v>38</v>
+      </c>
+      <c r="D78">
         <v>37</v>
       </c>
-      <c r="D78">
-        <v>34</v>
-      </c>
       <c r="E78">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -7200,10 +7203,10 @@
         <v>41</v>
       </c>
       <c r="I78">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J78">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K78">
         <v>40</v>
@@ -7212,7 +7215,7 @@
         <v>23</v>
       </c>
       <c r="M78">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7220,40 +7223,40 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C79">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D79">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E79">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F79">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G79">
         <v>89</v>
       </c>
       <c r="H79">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I79">
+        <v>75</v>
+      </c>
+      <c r="J79">
+        <v>99</v>
+      </c>
+      <c r="K79">
+        <v>77</v>
+      </c>
+      <c r="L79">
         <v>73</v>
       </c>
-      <c r="J79">
-        <v>97</v>
-      </c>
-      <c r="K79">
-        <v>75</v>
-      </c>
-      <c r="L79">
-        <v>72</v>
-      </c>
       <c r="M79">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7282,7 +7285,7 @@
         <v>3</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J80">
         <v>10</v>
@@ -7326,7 +7329,7 @@
         <v>3</v>
       </c>
       <c r="K81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81">
         <v>1</v>
@@ -7378,22 +7381,22 @@
         <v>89</v>
       </c>
       <c r="B83">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C83">
         <v>60</v>
       </c>
       <c r="D83">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E83">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F83">
         <v>48</v>
       </c>
       <c r="G83">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H83">
         <v>44</v>
@@ -7402,16 +7405,16 @@
         <v>52</v>
       </c>
       <c r="J83">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K83">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L83">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M83">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7419,7 +7422,7 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C84">
         <v>22</v>
@@ -7434,19 +7437,19 @@
         <v>19</v>
       </c>
       <c r="G84">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84">
         <v>22</v>
       </c>
       <c r="I84">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J84">
         <v>35</v>
       </c>
       <c r="K84">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L84">
         <v>20</v>
@@ -7460,40 +7463,40 @@
         <v>91</v>
       </c>
       <c r="B85">
+        <v>123</v>
+      </c>
+      <c r="C85">
+        <v>86</v>
+      </c>
+      <c r="D85">
+        <v>127</v>
+      </c>
+      <c r="E85">
+        <v>95</v>
+      </c>
+      <c r="F85">
         <v>120</v>
       </c>
-      <c r="C85">
-        <v>83</v>
-      </c>
-      <c r="D85">
-        <v>120</v>
-      </c>
-      <c r="E85">
-        <v>92</v>
-      </c>
-      <c r="F85">
-        <v>119</v>
-      </c>
       <c r="G85">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H85">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I85">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J85">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K85">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L85">
         <v>107</v>
       </c>
       <c r="M85">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7525,7 +7528,7 @@
         <v>13</v>
       </c>
       <c r="J86">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K86">
         <v>21</v>
@@ -7554,7 +7557,7 @@
         <v>14</v>
       </c>
       <c r="F87">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G87">
         <v>6</v>
@@ -7572,7 +7575,7 @@
         <v>2</v>
       </c>
       <c r="L87">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M87">
         <v>5</v>
@@ -7589,7 +7592,7 @@
         <v>36</v>
       </c>
       <c r="D88">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E88">
         <v>33</v>
@@ -7604,7 +7607,7 @@
         <v>26</v>
       </c>
       <c r="I88">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J88">
         <v>24</v>
@@ -7613,10 +7616,10 @@
         <v>38</v>
       </c>
       <c r="L88">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M88">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7636,7 +7639,7 @@
         <v>26</v>
       </c>
       <c r="F89">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G89">
         <v>38</v>
@@ -7651,10 +7654,10 @@
         <v>39</v>
       </c>
       <c r="K89">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L89">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M89">
         <v>28</v>
@@ -7668,16 +7671,16 @@
         <v>25</v>
       </c>
       <c r="C90">
+        <v>42</v>
+      </c>
+      <c r="D90">
         <v>38</v>
       </c>
-      <c r="D90">
-        <v>37</v>
-      </c>
       <c r="E90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G90">
         <v>25</v>
@@ -7686,16 +7689,16 @@
         <v>25</v>
       </c>
       <c r="I90">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J90">
         <v>38</v>
       </c>
       <c r="K90">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M90">
         <v>24</v>
@@ -7706,40 +7709,40 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C91">
         <v>40</v>
       </c>
       <c r="D91">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E91">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F91">
         <v>28</v>
       </c>
       <c r="G91">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H91">
         <v>20</v>
       </c>
       <c r="I91">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J91">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K91">
         <v>28</v>
       </c>
       <c r="L91">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M91">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7753,13 +7756,13 @@
         <v>8</v>
       </c>
       <c r="D92">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E92">
         <v>12</v>
       </c>
       <c r="F92">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G92">
         <v>13</v>
@@ -7803,7 +7806,7 @@
         <v>9</v>
       </c>
       <c r="G93">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H93">
         <v>10</v>
@@ -7818,7 +7821,7 @@
         <v>9</v>
       </c>
       <c r="L93">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M93">
         <v>12</v>
@@ -7838,10 +7841,10 @@
         <v>23</v>
       </c>
       <c r="E94">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F94">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G94">
         <v>18</v>
@@ -7850,19 +7853,19 @@
         <v>13</v>
       </c>
       <c r="I94">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J94">
         <v>18</v>
       </c>
       <c r="K94">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L94">
         <v>30</v>
       </c>
       <c r="M94">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7870,10 +7873,10 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C95">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D95">
         <v>61</v>
@@ -7885,25 +7888,25 @@
         <v>49</v>
       </c>
       <c r="G95">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H95">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I95">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J95">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K95">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L95">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M95">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7914,19 +7917,19 @@
         <v>20</v>
       </c>
       <c r="C96">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D96">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E96">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F96">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G96">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H96">
         <v>20</v>
@@ -7935,13 +7938,13 @@
         <v>31</v>
       </c>
       <c r="J96">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K96">
         <v>45</v>
       </c>
       <c r="L96">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M96">
         <v>21</v>
@@ -7961,7 +7964,7 @@
         <v>28</v>
       </c>
       <c r="E97">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F97">
         <v>18</v>
@@ -7970,13 +7973,13 @@
         <v>12</v>
       </c>
       <c r="H97">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J97">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K97">
         <v>22</v>
@@ -7993,13 +7996,13 @@
         <v>104</v>
       </c>
       <c r="B98">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98">
         <v>12</v>
       </c>
       <c r="D98">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E98">
         <v>17</v>
@@ -8014,7 +8017,7 @@
         <v>16</v>
       </c>
       <c r="I98">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98">
         <v>21</v>
@@ -8023,7 +8026,7 @@
         <v>18</v>
       </c>
       <c r="L98">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M98">
         <v>14</v>
@@ -8034,40 +8037,40 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C99">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D99">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E99">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F99">
         <v>47</v>
       </c>
       <c r="G99">
+        <v>59</v>
+      </c>
+      <c r="H99">
+        <v>55</v>
+      </c>
+      <c r="I99">
         <v>58</v>
       </c>
-      <c r="H99">
-        <v>54</v>
-      </c>
-      <c r="I99">
-        <v>56</v>
-      </c>
       <c r="J99">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K99">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L99">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M99">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8075,7 +8078,7 @@
         <v>106</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -8096,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K100">
         <v>4</v>
@@ -8105,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -8113,40 +8116,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2354</v>
+        <v>2400</v>
       </c>
       <c r="C101">
-        <v>2905</v>
+        <v>2969</v>
       </c>
       <c r="D101">
-        <v>3235</v>
+        <v>3305</v>
       </c>
       <c r="E101">
-        <v>2753</v>
+        <v>2812</v>
       </c>
       <c r="F101">
-        <v>2509</v>
+        <v>2578</v>
       </c>
       <c r="G101">
-        <v>2749</v>
+        <v>2804</v>
       </c>
       <c r="H101">
-        <v>2546</v>
+        <v>2583</v>
       </c>
       <c r="I101">
-        <v>2609</v>
+        <v>2679</v>
       </c>
       <c r="J101">
-        <v>3104</v>
+        <v>3167</v>
       </c>
       <c r="K101">
-        <v>2892</v>
+        <v>2957</v>
       </c>
       <c r="L101">
-        <v>2294</v>
+        <v>2333</v>
       </c>
       <c r="M101">
-        <v>1996</v>
+        <v>2041</v>
       </c>
     </row>
   </sheetData>
@@ -8334,7 +8337,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -8366,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -8378,7 +8381,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -8471,13 +8474,13 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>16</v>
@@ -8512,19 +8515,19 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -8628,7 +8631,7 @@
         <v>26</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
         <v>30</v>
@@ -8637,16 +8640,16 @@
         <v>25</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2">
         <v>22</v>
       </c>
       <c r="K2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -8657,34 +8660,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>52</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>38</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3">
         <v>26</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>49</v>
       </c>
       <c r="K3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>20</v>
@@ -8745,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -8780,19 +8783,19 @@
         <v>41</v>
       </c>
       <c r="C6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6">
         <v>34</v>
@@ -8804,10 +8807,10 @@
         <v>35</v>
       </c>
       <c r="K6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M6">
         <v>16</v>
@@ -8818,37 +8821,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H7">
         <v>92</v>
       </c>
       <c r="I7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J7">
         <v>114</v>
       </c>
       <c r="K7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M7">
         <v>59</v>
@@ -8940,7 +8943,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -8987,7 +8990,7 @@
         <v>9</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -9007,7 +9010,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -9080,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -9094,7 +9097,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -9109,19 +9112,19 @@
         <v>19</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7">
         <v>22</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>35</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -9207,7 +9210,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -9225,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -9244,8 +9247,11 @@
       <c r="D3">
         <v>5</v>
       </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -9285,17 +9291,20 @@
       <c r="G4">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -9361,31 +9370,31 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>18</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>9</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7">
         <v>19</v>
       </c>
       <c r="L7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M7">
         <v>13</v>
@@ -9468,10 +9477,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -9489,7 +9498,7 @@
         <v>16</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2">
         <v>16</v>
@@ -9509,10 +9518,10 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -9536,7 +9545,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9550,10 +9559,10 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -9605,13 +9614,13 @@
         <v>25</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>21</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6">
         <v>26</v>
@@ -9626,16 +9635,16 @@
         <v>30</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>21</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9646,13 +9655,13 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F7">
         <v>48</v>
@@ -9667,16 +9676,16 @@
         <v>61</v>
       </c>
       <c r="J7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L7">
         <v>46</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -9750,28 +9759,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>32</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2">
         <v>39</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2">
         <v>48</v>
@@ -9780,10 +9789,10 @@
         <v>37</v>
       </c>
       <c r="L2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9791,37 +9800,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>37</v>
       </c>
       <c r="F3">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>57</v>
       </c>
       <c r="H3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I3">
+        <v>46</v>
+      </c>
+      <c r="J3">
+        <v>54</v>
+      </c>
+      <c r="K3">
         <v>45</v>
       </c>
-      <c r="J3">
-        <v>52</v>
-      </c>
-      <c r="K3">
-        <v>44</v>
-      </c>
       <c r="L3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3">
         <v>39</v>
@@ -9832,10 +9841,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>14</v>
@@ -9917,28 +9926,28 @@
         <v>51</v>
       </c>
       <c r="C6">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D6">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F6">
         <v>37</v>
       </c>
       <c r="G6">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K6">
         <v>58</v>
@@ -9947,7 +9956,7 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9955,40 +9964,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>144</v>
+      </c>
+      <c r="C7">
+        <v>195</v>
+      </c>
+      <c r="D7">
+        <v>196</v>
+      </c>
+      <c r="E7">
         <v>138</v>
       </c>
-      <c r="C7">
-        <v>189</v>
-      </c>
-      <c r="D7">
-        <v>193</v>
-      </c>
-      <c r="E7">
-        <v>134</v>
-      </c>
       <c r="F7">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G7">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J7">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="K7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -10115,7 +10124,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -10127,7 +10136,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4</v>
@@ -10159,10 +10168,10 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -10177,7 +10186,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10211,19 +10220,19 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>20</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>11</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -10249,28 +10258,28 @@
         <v>30</v>
       </c>
       <c r="F7">
+        <v>26</v>
+      </c>
+      <c r="G7">
         <v>25</v>
       </c>
-      <c r="G7">
+      <c r="H7">
+        <v>34</v>
+      </c>
+      <c r="I7">
         <v>23</v>
       </c>
-      <c r="H7">
-        <v>33</v>
-      </c>
-      <c r="I7">
-        <v>22</v>
-      </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>38</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -10353,22 +10362,22 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -10385,10 +10394,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -10397,10 +10406,10 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3">
         <v>22</v>
@@ -10415,7 +10424,7 @@
         <v>25</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3">
         <v>24</v>
@@ -10438,7 +10447,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>7</v>
@@ -10450,10 +10459,10 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -10482,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -10511,16 +10520,16 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>23</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H6">
         <v>25</v>
@@ -10535,7 +10544,7 @@
         <v>22</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6">
         <v>22</v>
@@ -10546,37 +10555,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7">
+        <v>86</v>
+      </c>
+      <c r="H7">
+        <v>68</v>
+      </c>
+      <c r="I7">
+        <v>68</v>
+      </c>
+      <c r="J7">
+        <v>101</v>
+      </c>
+      <c r="K7">
         <v>72</v>
       </c>
-      <c r="G7">
-        <v>82</v>
-      </c>
-      <c r="H7">
-        <v>66</v>
-      </c>
-      <c r="I7">
-        <v>66</v>
-      </c>
-      <c r="J7">
-        <v>98</v>
-      </c>
-      <c r="K7">
-        <v>71</v>
-      </c>
       <c r="L7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M7">
         <v>74</v>
@@ -10653,7 +10662,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -10665,7 +10674,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>6</v>
@@ -10799,10 +10808,10 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>21</v>
@@ -10829,7 +10838,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10837,19 +10846,19 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
         <v>26</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>24</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>29</v>
@@ -10870,7 +10879,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -10956,7 +10965,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>6</v>
@@ -10971,13 +10980,13 @@
         <v>5</v>
       </c>
       <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
         <v>7</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11006,7 +11015,7 @@
         <v>6</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>13</v>
@@ -11053,7 +11062,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -11084,10 +11093,10 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>23</v>
@@ -11125,10 +11134,10 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>42</v>
@@ -11137,19 +11146,19 @@
         <v>24</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>52</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -11226,7 +11235,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -11345,7 +11354,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -11363,7 +11372,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -11383,7 +11392,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -11401,7 +11410,7 @@
         <v>14</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>15</v>
@@ -11493,7 +11502,7 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -11531,7 +11540,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -11561,7 +11570,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11578,7 +11587,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -11621,7 +11630,7 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -11639,7 +11648,7 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -11656,13 +11665,13 @@
         <v>26</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -11680,13 +11689,13 @@
         <v>26</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>15</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -11775,7 +11784,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -11787,7 +11796,7 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -11831,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -11891,7 +11900,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -11906,7 +11915,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -11932,13 +11941,13 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>10</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -11947,13 +11956,13 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -12033,13 +12042,13 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>27</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -12057,7 +12066,7 @@
         <v>21</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>18</v>
@@ -12074,10 +12083,10 @@
         <v>23</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>27</v>
@@ -12098,13 +12107,13 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3">
         <v>15</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12115,7 +12124,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -12130,13 +12139,13 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -12194,22 +12203,22 @@
         <v>52</v>
       </c>
       <c r="C6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>36</v>
       </c>
       <c r="H6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -12235,37 +12244,37 @@
         <v>99</v>
       </c>
       <c r="C7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>98</v>
       </c>
       <c r="H7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I7">
         <v>69</v>
       </c>
       <c r="J7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L7">
         <v>80</v>
       </c>
       <c r="M7">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -12334,7 +12343,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -12423,7 +12432,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -12536,7 +12545,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -12595,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12655,7 +12664,7 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -12664,16 +12673,16 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>13</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -12696,7 +12705,7 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -12705,16 +12714,16 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H7">
         <v>28</v>
       </c>
       <c r="I7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>18</v>
@@ -12723,7 +12732,7 @@
         <v>12</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -12797,7 +12806,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -12830,7 +12839,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12844,10 +12853,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -12859,10 +12868,10 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3">
         <v>10</v>
@@ -12900,7 +12909,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -12934,10 +12943,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -12972,16 +12981,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7">
+        <v>38</v>
+      </c>
+      <c r="D7">
         <v>37</v>
       </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
       <c r="E7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>25</v>
@@ -12993,10 +13002,10 @@
         <v>41</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7">
         <v>40</v>
@@ -13005,7 +13014,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -13103,7 +13112,7 @@
         <v>9</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>11</v>
@@ -13167,7 +13176,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -13204,6 +13213,9 @@
       <c r="G5">
         <v>2</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
       <c r="K5">
         <v>1</v>
       </c>
@@ -13246,7 +13258,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -13266,7 +13278,7 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>22</v>
@@ -13281,13 +13293,13 @@
         <v>29</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K7">
         <v>30</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>23</v>
@@ -13484,10 +13496,10 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -13519,13 +13531,13 @@
         <v>11</v>
       </c>
       <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <v>10</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>9</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -13620,7 +13632,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -13635,7 +13647,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13655,7 +13667,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -13762,7 +13774,7 @@
         <v>3</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>15</v>
@@ -13774,13 +13786,13 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13860,7 +13872,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -13878,7 +13890,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>11</v>
@@ -13991,7 +14003,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -14015,10 +14027,10 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -14032,13 +14044,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>22</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>37</v>
@@ -14056,10 +14068,10 @@
         <v>29</v>
       </c>
       <c r="J7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>26</v>
@@ -14142,7 +14154,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -14186,10 +14198,10 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -14251,7 +14263,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -14267,6 +14279,9 @@
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>1</v>
       </c>
@@ -14291,10 +14306,10 @@
         <v>25</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -14303,7 +14318,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>21</v>
@@ -14323,19 +14338,19 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>20</v>
@@ -14344,13 +14359,13 @@
         <v>31</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7">
         <v>45</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
         <v>21</v>
@@ -14427,7 +14442,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -14448,7 +14463,7 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -14460,7 +14475,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14474,7 +14489,7 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>13</v>
@@ -14483,7 +14498,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -14492,7 +14507,7 @@
         <v>12</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -14501,7 +14516,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14564,7 +14579,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -14585,7 +14600,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -14596,40 +14611,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>40</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K7">
         <v>28</v>
       </c>
       <c r="L7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -14718,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -14813,13 +14828,13 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -14854,13 +14869,13 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J7">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -14946,13 +14961,13 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
         <v>24</v>
@@ -14961,13 +14976,13 @@
         <v>29</v>
       </c>
       <c r="I2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2">
         <v>28</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2">
         <v>23</v>
@@ -14981,10 +14996,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>14</v>
@@ -15011,7 +15026,7 @@
         <v>27</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3">
         <v>21</v>
@@ -15107,7 +15122,7 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>28</v>
@@ -15119,13 +15134,13 @@
         <v>35</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K6">
         <v>20</v>
@@ -15134,7 +15149,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15142,40 +15157,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7">
         <v>89</v>
       </c>
       <c r="H7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I7">
+        <v>75</v>
+      </c>
+      <c r="J7">
+        <v>99</v>
+      </c>
+      <c r="K7">
+        <v>77</v>
+      </c>
+      <c r="L7">
         <v>73</v>
       </c>
-      <c r="J7">
-        <v>97</v>
-      </c>
-      <c r="K7">
-        <v>75</v>
-      </c>
-      <c r="L7">
-        <v>72</v>
-      </c>
       <c r="M7">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -15261,7 +15276,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -15296,7 +15311,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -15383,7 +15398,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -15401,13 +15416,13 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>8</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -15424,31 +15439,31 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H7">
         <v>13</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>18</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7">
         <v>21</v>
@@ -15534,7 +15549,7 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>21</v>
@@ -15546,10 +15561,10 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2">
         <v>17</v>
@@ -15561,7 +15576,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15569,28 +15584,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>19</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3">
         <v>13</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3">
         <v>21</v>
@@ -15686,10 +15701,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>31</v>
@@ -15698,25 +15713,25 @@
         <v>44</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6">
         <v>16</v>
       </c>
       <c r="I6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6">
         <v>32</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -15727,40 +15742,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F7">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K7">
         <v>69</v>
       </c>
       <c r="L7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M7">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -15846,7 +15861,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -15902,7 +15917,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -15928,7 +15943,7 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -15956,7 +15971,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -15997,13 +16012,13 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>16</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -16015,10 +16030,10 @@
         <v>25</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7">
         <v>16</v>
@@ -16126,7 +16141,7 @@
         <v>5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -16207,7 +16222,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -16305,7 +16320,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -16317,7 +16332,7 @@
         <v>8</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <v>12</v>
@@ -16334,7 +16349,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -16343,7 +16358,7 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -16358,10 +16373,10 @@
         <v>8</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -16416,7 +16431,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -16439,19 +16454,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>12</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -16466,10 +16481,10 @@
         <v>22</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -16480,19 +16495,19 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
         <v>30</v>
       </c>
-      <c r="C7">
-        <v>28</v>
-      </c>
       <c r="D7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7">
         <v>27</v>
@@ -16504,13 +16519,13 @@
         <v>37</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7">
         <v>22</v>
@@ -16643,7 +16658,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -16658,7 +16673,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -16765,7 +16780,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7">
         <v>10</v>
@@ -16780,7 +16795,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -16856,7 +16871,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -16905,6 +16920,9 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
       <c r="C6">
         <v>4</v>
       </c>
@@ -16922,6 +16940,9 @@
       </c>
       <c r="J6">
         <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -16929,7 +16950,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -16950,7 +16971,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -16959,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -17033,31 +17054,31 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>29</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>27</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>25</v>
       </c>
       <c r="J2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2">
         <v>35</v>
@@ -17074,7 +17095,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>27</v>
@@ -17083,10 +17104,10 @@
         <v>39</v>
       </c>
       <c r="E3">
+        <v>23</v>
+      </c>
+      <c r="F3">
         <v>22</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
       </c>
       <c r="G3">
         <v>28</v>
@@ -17095,7 +17116,7 @@
         <v>25</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>34</v>
@@ -17168,7 +17189,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -17194,13 +17215,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>62</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>38</v>
@@ -17212,10 +17233,10 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J6">
         <v>26</v>
@@ -17235,31 +17256,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I7">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K7">
         <v>83</v>
@@ -17401,7 +17422,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>6</v>
@@ -17429,6 +17450,9 @@
       <c r="G4">
         <v>2</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>2</v>
       </c>
@@ -17476,7 +17500,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -17517,7 +17541,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>15</v>
@@ -17526,10 +17550,10 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>19</v>
@@ -17636,7 +17660,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -17661,6 +17685,9 @@
       <c r="E3">
         <v>3</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>3</v>
       </c>
@@ -17737,7 +17764,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -17749,7 +17776,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -17761,7 +17788,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17778,10 +17805,10 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -17790,19 +17817,19 @@
         <v>13</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>18</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L7">
         <v>30</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -17903,7 +17930,7 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -17917,7 +17944,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -17975,6 +18002,9 @@
       <c r="K4">
         <v>2</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -18006,6 +18036,9 @@
       <c r="E6">
         <v>6</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
       <c r="G6">
         <v>1</v>
       </c>
@@ -18030,7 +18063,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>11</v>
@@ -18042,7 +18075,7 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>9</v>
@@ -18057,13 +18090,13 @@
         <v>16</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L7">
         <v>11</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18137,7 +18170,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -18199,7 +18232,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -18292,7 +18325,7 @@
         <v>14</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>18</v>
@@ -18312,7 +18345,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>19</v>
@@ -18333,7 +18366,7 @@
         <v>23</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7">
         <v>29</v>
@@ -18440,7 +18473,7 @@
         <v>9</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>10</v>
@@ -18463,7 +18496,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -18487,7 +18520,7 @@
         <v>11</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -18603,7 +18636,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -18621,7 +18654,7 @@
         <v>25</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>36</v>
@@ -18630,7 +18663,7 @@
         <v>18</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7">
         <v>23</v>
@@ -18713,7 +18746,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -18814,7 +18847,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -18835,7 +18868,7 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>11</v>
@@ -18844,7 +18877,7 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -18855,13 +18888,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -18876,7 +18909,7 @@
         <v>16</v>
       </c>
       <c r="I7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <v>21</v>
@@ -18885,7 +18918,7 @@
         <v>18</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -19024,7 +19057,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -19108,7 +19141,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -19149,13 +19182,13 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <v>9</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>11</v>
@@ -19645,7 +19678,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -19709,7 +19742,7 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -19735,7 +19768,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -19744,7 +19777,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>13</v>
@@ -19833,19 +19866,19 @@
         <v>18</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>15</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -19854,7 +19887,7 @@
         <v>20</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <v>10</v>
@@ -19895,7 +19928,7 @@
         <v>13</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -19973,7 +20006,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>24</v>
@@ -20014,7 +20047,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>47</v>
@@ -20023,19 +20056,19 @@
         <v>64</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7">
         <v>41</v>
       </c>
       <c r="I7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>39</v>
@@ -20044,7 +20077,7 @@
         <v>63</v>
       </c>
       <c r="L7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M7">
         <v>30</v>
@@ -20172,7 +20205,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -20210,7 +20243,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -20332,10 +20365,10 @@
         <v>5</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -20457,7 +20490,7 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -20498,13 +20531,13 @@
         <v>18</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -20596,7 +20629,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -20608,7 +20641,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>10</v>
@@ -20628,10 +20661,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -20640,7 +20673,7 @@
         <v>7</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>11</v>
@@ -20721,10 +20754,10 @@
         <v>18</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -20753,19 +20786,19 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>30</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>30</v>
@@ -20774,7 +20807,7 @@
         <v>28</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7">
         <v>32</v>
@@ -20958,7 +20991,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -20996,7 +21029,7 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -21103,10 +21136,10 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>9</v>
@@ -21115,10 +21148,10 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21272,10 +21305,10 @@
         <v>25</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>22</v>
@@ -21284,10 +21317,10 @@
         <v>22</v>
       </c>
       <c r="L7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -21376,13 +21409,13 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -21489,7 +21522,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -21501,7 +21534,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J6">
         <v>13</v>
@@ -21530,7 +21563,7 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>18</v>
@@ -21539,13 +21572,13 @@
         <v>12</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>22</v>
@@ -21640,7 +21673,7 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -21735,7 +21768,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -21776,13 +21809,13 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>12</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -22123,10 +22156,10 @@
         <v>8</v>
       </c>
       <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
         <v>8</v>
-      </c>
-      <c r="M2">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22155,7 +22188,7 @@
         <v>6</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -22189,6 +22222,9 @@
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -22236,7 +22272,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -22277,7 +22313,7 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>33</v>
@@ -22292,7 +22328,7 @@
         <v>26</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -22301,10 +22337,10 @@
         <v>38</v>
       </c>
       <c r="L7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -22482,7 +22518,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -22517,7 +22553,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -22633,7 +22669,7 @@
         <v>6</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -22755,7 +22791,7 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -22770,7 +22806,7 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -22796,7 +22832,7 @@
         <v>26</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
         <v>38</v>
@@ -22811,10 +22847,10 @@
         <v>39</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7">
         <v>28</v>
@@ -23164,7 +23200,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -23185,10 +23221,10 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23208,7 +23244,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -23218,6 +23254,9 @@
       </c>
       <c r="I4">
         <v>5</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -23289,7 +23328,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>18</v>
@@ -23298,7 +23337,7 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -23310,16 +23349,16 @@
         <v>28</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7">
         <v>35</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -23490,7 +23529,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -23572,7 +23611,7 @@
         <v>13</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>21</v>
@@ -23673,7 +23712,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -23714,7 +23753,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -23742,6 +23781,9 @@
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>2</v>
       </c>
@@ -23818,7 +23860,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>8</v>
@@ -23904,7 +23946,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -23913,7 +23955,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -23928,7 +23970,7 @@
         <v>8</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -23948,10 +23990,10 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>11</v>
@@ -24018,7 +24060,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -24050,7 +24092,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -24059,7 +24101,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -24068,16 +24110,16 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>19</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -24091,16 +24133,16 @@
         <v>25</v>
       </c>
       <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
         <v>38</v>
       </c>
-      <c r="D7">
-        <v>37</v>
-      </c>
       <c r="E7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -24109,16 +24151,16 @@
         <v>25</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>38</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -24213,7 +24255,7 @@
         <v>6</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -24257,7 +24299,7 @@
         <v>11</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>15</v>
@@ -24283,7 +24325,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -24341,13 +24383,13 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>15</v>
@@ -24379,22 +24421,22 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7">
         <v>39</v>
@@ -24517,6 +24559,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -24562,7 +24607,7 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -24622,7 +24667,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -24637,7 +24682,7 @@
         <v>3</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -24860,10 +24905,10 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -24898,10 +24943,10 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>15</v>
@@ -25046,7 +25091,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -25062,11 +25107,17 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -25106,7 +25157,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -25124,7 +25175,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25147,25 +25198,25 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
         <v>11</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7">
         <v>16</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -25248,7 +25299,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -25379,13 +25430,13 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>24</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -25411,7 +25462,7 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>23</v>
@@ -25420,13 +25471,13 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7">
         <v>38</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>17</v>
@@ -25506,16 +25557,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -25524,16 +25575,16 @@
         <v>22</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2">
         <v>33</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L2">
         <v>28</v>
@@ -25547,31 +25598,31 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>24</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>45</v>
       </c>
       <c r="H3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3">
         <v>45</v>
@@ -25603,7 +25654,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -25621,7 +25672,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -25635,7 +25686,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -25670,13 +25721,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6">
         <v>31</v>
@@ -25691,7 +25742,7 @@
         <v>40</v>
       </c>
       <c r="I6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6">
         <v>42</v>
@@ -25703,7 +25754,7 @@
         <v>21</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25711,40 +25762,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>123</v>
+      </c>
+      <c r="C7">
+        <v>86</v>
+      </c>
+      <c r="D7">
+        <v>127</v>
+      </c>
+      <c r="E7">
+        <v>95</v>
+      </c>
+      <c r="F7">
         <v>120</v>
       </c>
-      <c r="C7">
-        <v>83</v>
-      </c>
-      <c r="D7">
-        <v>120</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="F7">
-        <v>119</v>
-      </c>
       <c r="G7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L7">
         <v>107</v>
       </c>
       <c r="M7">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -25821,7 +25872,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -25906,7 +25957,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -25934,7 +25985,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -25960,7 +26011,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -25969,7 +26020,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>9</v>
@@ -25984,7 +26035,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -26345,7 +26396,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -26400,7 +26451,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -26441,7 +26492,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -26453,7 +26504,7 @@
         <v>16</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -26802,7 +26853,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -26927,7 +26978,7 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>21</v>
@@ -27227,6 +27278,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -27303,7 +27357,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -27454,7 +27508,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -27565,7 +27619,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -27687,7 +27741,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -27719,7 +27773,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -28052,7 +28106,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -28082,7 +28136,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28137,7 +28191,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -28164,7 +28218,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -28219,7 +28273,7 @@
         <v>23</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>15</v>
@@ -28228,7 +28282,7 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6">
         <v>28</v>
@@ -28251,16 +28305,16 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7">
         <v>64</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>48</v>
@@ -28269,7 +28323,7 @@
         <v>46</v>
       </c>
       <c r="I7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J7">
         <v>69</v>
@@ -28281,7 +28335,7 @@
         <v>45</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -28390,7 +28444,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -28468,7 +28522,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -28824,7 +28878,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -28834,6 +28888,9 @@
       </c>
       <c r="J2">
         <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -28951,7 +29008,7 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -28969,7 +29026,7 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -29126,6 +29183,9 @@
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>2</v>
       </c>
@@ -29159,7 +29219,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -29943,7 +30003,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -29975,7 +30035,7 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>1</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>670</v>
       </c>
       <c r="M2">
-        <v>612</v>
+        <v>633</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>674</v>
       </c>
       <c r="M3">
-        <v>661</v>
+        <v>696</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>205</v>
       </c>
       <c r="M4">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>730</v>
       </c>
       <c r="M6">
-        <v>524</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>2333</v>
       </c>
       <c r="M7">
-        <v>2041</v>
+        <v>2114</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1534,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1709,7 +1709,7 @@
         <v>28</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1816,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1857,7 +1857,7 @@
         <v>42</v>
       </c>
       <c r="M3">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2021,7 +2021,7 @@
         <v>136</v>
       </c>
       <c r="M7">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2128,7 +2128,7 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2324,7 +2324,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2431,7 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2472,7 +2472,7 @@
         <v>34</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2513,7 +2513,7 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2633,7 +2633,7 @@
         <v>99</v>
       </c>
       <c r="M7">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2740,7 +2740,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2781,7 +2781,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2936,7 +2936,7 @@
         <v>30</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3084,7 +3084,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3242,7 +3242,7 @@
         <v>76</v>
       </c>
       <c r="M7">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3687,7 +3687,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3839,7 +3839,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4047,7 +4047,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4088,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4195,7 +4195,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4277,7 +4277,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4318,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4400,7 +4400,7 @@
         <v>78</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4441,7 +4441,7 @@
         <v>136</v>
       </c>
       <c r="M8">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4681,7 +4681,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4722,7 +4722,7 @@
         <v>18</v>
       </c>
       <c r="M15">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4877,7 +4877,7 @@
         <v>77</v>
       </c>
       <c r="M19">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4918,7 +4918,7 @@
         <v>59</v>
       </c>
       <c r="M20">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5000,7 +5000,7 @@
         <v>7</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5041,7 +5041,7 @@
         <v>26</v>
       </c>
       <c r="M23">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5205,7 +5205,7 @@
         <v>28</v>
       </c>
       <c r="M27">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5269,7 +5269,7 @@
         <v>118</v>
       </c>
       <c r="M29">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5310,7 +5310,7 @@
         <v>15</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5433,7 +5433,7 @@
         <v>99</v>
       </c>
       <c r="M33">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5556,7 +5556,7 @@
         <v>42</v>
       </c>
       <c r="M36">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5597,7 +5597,7 @@
         <v>76</v>
       </c>
       <c r="M37">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5784,7 +5784,7 @@
         <v>80</v>
       </c>
       <c r="M42">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5825,7 +5825,7 @@
         <v>17</v>
       </c>
       <c r="M43">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6071,7 +6071,7 @@
         <v>16</v>
       </c>
       <c r="M49">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6194,7 +6194,7 @@
         <v>45</v>
       </c>
       <c r="M52">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6235,7 +6235,7 @@
         <v>28</v>
       </c>
       <c r="M53">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6276,7 +6276,7 @@
         <v>46</v>
       </c>
       <c r="M54">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6317,7 +6317,7 @@
         <v>26</v>
       </c>
       <c r="M55">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6609,7 +6609,7 @@
         <v>10</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6770,7 +6770,7 @@
         <v>79</v>
       </c>
       <c r="M67">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6811,7 +6811,7 @@
         <v>5</v>
       </c>
       <c r="M68">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -7133,7 +7133,7 @@
         <v>32</v>
       </c>
       <c r="M76">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7215,7 +7215,7 @@
         <v>23</v>
       </c>
       <c r="M78">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7256,7 +7256,7 @@
         <v>73</v>
       </c>
       <c r="M79">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7414,7 +7414,7 @@
         <v>47</v>
       </c>
       <c r="M83">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7455,7 +7455,7 @@
         <v>20</v>
       </c>
       <c r="M84">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7496,7 +7496,7 @@
         <v>107</v>
       </c>
       <c r="M85">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7537,7 +7537,7 @@
         <v>16</v>
       </c>
       <c r="M86">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7619,7 +7619,7 @@
         <v>38</v>
       </c>
       <c r="M88">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7660,7 +7660,7 @@
         <v>28</v>
       </c>
       <c r="M89">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7742,7 +7742,7 @@
         <v>35</v>
       </c>
       <c r="M91">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7906,7 +7906,7 @@
         <v>30</v>
       </c>
       <c r="M95">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7988,7 +7988,7 @@
         <v>28</v>
       </c>
       <c r="M97">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8029,7 +8029,7 @@
         <v>19</v>
       </c>
       <c r="M98">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -8070,7 +8070,7 @@
         <v>41</v>
       </c>
       <c r="M99">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8149,7 +8149,7 @@
         <v>2333</v>
       </c>
       <c r="M101">
-        <v>2041</v>
+        <v>2114</v>
       </c>
     </row>
   </sheetData>
@@ -8652,7 +8652,7 @@
         <v>23</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8813,7 +8813,7 @@
         <v>24</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8854,7 +8854,7 @@
         <v>79</v>
       </c>
       <c r="M7">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -9002,7 +9002,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9130,7 +9130,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -9231,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9269,7 +9269,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9356,7 +9356,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9397,7 +9397,7 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -9545,7 +9545,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9644,7 +9644,7 @@
         <v>21</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9685,7 +9685,7 @@
         <v>46</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -9792,7 +9792,7 @@
         <v>40</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9833,7 +9833,7 @@
         <v>36</v>
       </c>
       <c r="M3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9997,7 +9997,7 @@
         <v>118</v>
       </c>
       <c r="M7">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -10427,7 +10427,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10588,7 +10588,7 @@
         <v>77</v>
       </c>
       <c r="M7">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -11027,7 +11027,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11158,7 +11158,7 @@
         <v>32</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -11303,7 +11303,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11422,7 +11422,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -12072,7 +12072,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12233,7 +12233,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12274,7 +12274,7 @@
         <v>80</v>
       </c>
       <c r="M7">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -12880,7 +12880,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13014,7 +13014,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -13162,7 +13162,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13302,7 +13302,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -14036,7 +14036,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14077,7 +14077,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -14225,7 +14225,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14327,7 +14327,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14475,7 +14475,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14516,7 +14516,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14644,7 +14644,7 @@
         <v>35</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -15149,7 +15149,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15190,7 +15190,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -15576,7 +15576,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15775,7 +15775,7 @@
         <v>59</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -16382,7 +16382,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16528,7 +16528,7 @@
         <v>42</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -17087,7 +17087,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17248,7 +17248,7 @@
         <v>26</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17289,7 +17289,7 @@
         <v>78</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -18485,7 +18485,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18666,7 +18666,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -18880,7 +18880,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18921,7 +18921,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -21192,7 +21192,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21320,7 +21320,7 @@
         <v>14</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -21424,7 +21424,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21459,7 +21459,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21546,7 +21546,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21587,7 +21587,7 @@
         <v>28</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -22159,7 +22159,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22200,7 +22200,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22299,7 +22299,7 @@
         <v>17</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22340,7 +22340,7 @@
         <v>38</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -22672,7 +22672,7 @@
         <v>11</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22853,7 +22853,7 @@
         <v>28</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -22986,7 +22986,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23082,7 +23082,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -23189,7 +23189,7 @@
         <v>8</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23317,7 +23317,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23358,7 +23358,7 @@
         <v>28</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -23497,7 +23497,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23620,7 +23620,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -24590,7 +24590,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24700,7 +24700,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -25361,7 +25361,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25483,7 +25483,7 @@
         <v>17</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -25590,7 +25590,7 @@
         <v>28</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25631,7 +25631,7 @@
         <v>47</v>
       </c>
       <c r="M3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25795,7 +25795,7 @@
         <v>107</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -25937,7 +25937,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26041,7 +26041,7 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -28136,7 +28136,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28177,7 +28177,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28335,7 +28335,7 @@
         <v>45</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -28511,7 +28511,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28552,7 +28552,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="D2">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="E2">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="F2">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="G2">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="H2">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="I2">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="J2">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="K2">
-        <v>871</v>
+        <v>888</v>
       </c>
       <c r="L2">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="M2">
-        <v>655</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C3">
+        <v>793</v>
+      </c>
+      <c r="D3">
+        <v>829</v>
+      </c>
+      <c r="E3">
+        <v>745</v>
+      </c>
+      <c r="F3">
         <v>777</v>
       </c>
-      <c r="D3">
-        <v>816</v>
-      </c>
-      <c r="E3">
-        <v>725</v>
-      </c>
-      <c r="F3">
-        <v>757</v>
-      </c>
       <c r="G3">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="H3">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="I3">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="J3">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K3">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="L3">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="M3">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C4">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D4">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E4">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F4">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G4">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H4">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I4">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J4">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K4">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="L4">
+        <v>214</v>
+      </c>
+      <c r="M4">
         <v>212</v>
-      </c>
-      <c r="M4">
-        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,34 +994,34 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5">
+        <v>67</v>
+      </c>
+      <c r="F5">
+        <v>42</v>
+      </c>
+      <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5">
+        <v>78</v>
+      </c>
+      <c r="I5">
+        <v>82</v>
+      </c>
+      <c r="J5">
         <v>66</v>
       </c>
-      <c r="F5">
-        <v>41</v>
-      </c>
-      <c r="G5">
-        <v>59</v>
-      </c>
-      <c r="H5">
-        <v>77</v>
-      </c>
-      <c r="I5">
-        <v>81</v>
-      </c>
-      <c r="J5">
-        <v>64</v>
-      </c>
       <c r="K5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M5">
         <v>43</v>
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1079</v>
+      </c>
+      <c r="C6">
+        <v>1456</v>
+      </c>
+      <c r="D6">
+        <v>1604</v>
+      </c>
+      <c r="E6">
+        <v>1302</v>
+      </c>
+      <c r="F6">
+        <v>940</v>
+      </c>
+      <c r="G6">
+        <v>1105</v>
+      </c>
+      <c r="H6">
+        <v>1026</v>
+      </c>
+      <c r="I6">
         <v>1065</v>
       </c>
-      <c r="C6">
-        <v>1436</v>
-      </c>
-      <c r="D6">
-        <v>1574</v>
-      </c>
-      <c r="E6">
-        <v>1274</v>
-      </c>
-      <c r="F6">
-        <v>921</v>
-      </c>
-      <c r="G6">
-        <v>1086</v>
-      </c>
-      <c r="H6">
-        <v>1003</v>
-      </c>
-      <c r="I6">
-        <v>1055</v>
-      </c>
       <c r="J6">
-        <v>1264</v>
+        <v>1280</v>
       </c>
       <c r="K6">
-        <v>1121</v>
+        <v>1143</v>
       </c>
       <c r="L6">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="M6">
-        <v>551</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2469</v>
+        <v>2504</v>
       </c>
       <c r="C7">
-        <v>3088</v>
+        <v>3139</v>
       </c>
       <c r="D7">
-        <v>3435</v>
+        <v>3498</v>
       </c>
       <c r="E7">
-        <v>2964</v>
+        <v>3025</v>
       </c>
       <c r="F7">
-        <v>2685</v>
+        <v>2747</v>
       </c>
       <c r="G7">
-        <v>2921</v>
+        <v>2971</v>
       </c>
       <c r="H7">
-        <v>2686</v>
+        <v>2740</v>
       </c>
       <c r="I7">
-        <v>2806</v>
+        <v>2856</v>
       </c>
       <c r="J7">
-        <v>3280</v>
+        <v>3328</v>
       </c>
       <c r="K7">
-        <v>3079</v>
+        <v>3143</v>
       </c>
       <c r="L7">
-        <v>2440</v>
+        <v>2494</v>
       </c>
       <c r="M7">
-        <v>2179</v>
+        <v>2230</v>
       </c>
     </row>
   </sheetData>
@@ -1186,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1262,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1319,7 +1319,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1340,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1356,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1364,45 +1364,56 @@
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="1">
         <v>2021</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="F1" s="1">
         <v>2024</v>
       </c>
-      <c r="E1" s="1">
+      <c r="G1" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1412,8 +1423,11 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1427,6 +1441,12 @@
         <v>1</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
     </row>
@@ -1501,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -1519,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -1635,13 +1655,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>19</v>
@@ -1665,7 +1685,7 @@
         <v>20</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1676,13 +1696,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>46</v>
       </c>
       <c r="D7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>39</v>
@@ -1694,7 +1714,7 @@
         <v>31</v>
       </c>
       <c r="H7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>31</v>
@@ -1706,7 +1726,7 @@
         <v>40</v>
       </c>
       <c r="L7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M7">
         <v>22</v>
@@ -1783,40 +1803,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>41</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2">
         <v>44</v>
       </c>
       <c r="F2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>43</v>
       </c>
       <c r="H2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I2">
+        <v>50</v>
+      </c>
+      <c r="J2">
+        <v>63</v>
+      </c>
+      <c r="K2">
         <v>48</v>
       </c>
-      <c r="J2">
-        <v>62</v>
-      </c>
-      <c r="K2">
-        <v>47</v>
-      </c>
       <c r="L2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1827,13 +1847,13 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>58</v>
@@ -1848,16 +1868,16 @@
         <v>47</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1877,16 +1897,16 @@
         <v>12</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>11</v>
@@ -1924,7 +1944,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1950,31 +1970,31 @@
         <v>75</v>
       </c>
       <c r="C6">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I6">
         <v>52</v>
       </c>
       <c r="J6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K6">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L6">
         <v>45</v>
@@ -1988,40 +2008,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M7">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2118,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>21</v>
@@ -2119,13 +2139,13 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>32</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2">
         <v>15</v>
@@ -2139,7 +2159,7 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -2148,10 +2168,10 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <v>16</v>
@@ -2160,13 +2180,13 @@
         <v>17</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3">
         <v>15</v>
       </c>
       <c r="L3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>23</v>
@@ -2210,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2250,16 +2270,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>19</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>16</v>
@@ -2280,7 +2300,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <v>11</v>
@@ -2291,22 +2311,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>72</v>
       </c>
       <c r="E7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7">
         <v>47</v>
@@ -2315,16 +2335,16 @@
         <v>53</v>
       </c>
       <c r="J7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K7">
         <v>56</v>
       </c>
       <c r="L7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M7">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2424,22 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>34</v>
       </c>
       <c r="F2">
+        <v>28</v>
+      </c>
+      <c r="G2">
+        <v>29</v>
+      </c>
+      <c r="H2">
         <v>27</v>
       </c>
-      <c r="G2">
-        <v>28</v>
-      </c>
-      <c r="H2">
-        <v>26</v>
-      </c>
       <c r="I2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <v>30</v>
@@ -2439,7 +2459,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>54</v>
@@ -2448,10 +2468,10 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F3">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>51</v>
@@ -2466,13 +2486,13 @@
         <v>36</v>
       </c>
       <c r="K3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2489,10 +2509,10 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -2507,13 +2527,13 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2559,37 +2579,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6">
         <v>65</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K6">
         <v>39</v>
       </c>
       <c r="L6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M6">
         <v>25</v>
@@ -2600,40 +2620,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E7">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F7">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H7">
+        <v>131</v>
+      </c>
+      <c r="I7">
+        <v>125</v>
+      </c>
+      <c r="J7">
+        <v>138</v>
+      </c>
+      <c r="K7">
         <v>129</v>
       </c>
-      <c r="I7">
-        <v>123</v>
-      </c>
-      <c r="J7">
-        <v>136</v>
-      </c>
-      <c r="K7">
-        <v>127</v>
-      </c>
       <c r="L7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M7">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2719,19 +2739,19 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>16</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2">
         <v>17</v>
       </c>
       <c r="J2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2">
         <v>18</v>
@@ -2754,13 +2774,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>18</v>
@@ -2781,7 +2801,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2886,7 +2906,7 @@
         <v>11</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6">
         <v>17</v>
@@ -2909,25 +2929,25 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>43</v>
       </c>
       <c r="F7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>60</v>
       </c>
       <c r="H7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7">
         <v>47</v>
       </c>
       <c r="J7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K7">
         <v>51</v>
@@ -2936,7 +2956,7 @@
         <v>32</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3013,10 +3033,10 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>27</v>
@@ -3031,10 +3051,10 @@
         <v>25</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2">
         <v>22</v>
@@ -3043,7 +3063,7 @@
         <v>24</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3084,7 +3104,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3107,7 +3127,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3125,7 +3145,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3171,22 +3191,22 @@
         <v>39</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>25</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>29</v>
@@ -3195,13 +3215,13 @@
         <v>41</v>
       </c>
       <c r="K6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3212,37 +3232,37 @@
         <v>86</v>
       </c>
       <c r="C7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F7">
         <v>91</v>
       </c>
       <c r="G7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3337,7 +3357,7 @@
         <v>14</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>21</v>
@@ -3349,7 +3369,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3360,7 +3380,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>23</v>
@@ -3372,7 +3392,7 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>14</v>
@@ -3416,10 +3436,10 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -3451,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -3477,22 +3497,22 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6">
         <v>11</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <v>35</v>
       </c>
       <c r="K6">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L6">
         <v>16</v>
@@ -3509,7 +3529,7 @@
         <v>47</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7">
         <v>71</v>
@@ -3518,28 +3538,28 @@
         <v>67</v>
       </c>
       <c r="F7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K7">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L7">
         <v>46</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3628,10 +3648,10 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>20</v>
@@ -3666,13 +3686,13 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>22</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>16</v>
@@ -3687,7 +3707,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3707,7 +3727,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -3771,7 +3791,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -3789,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>18</v>
@@ -3798,7 +3818,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3812,25 +3832,25 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7">
         <v>42</v>
       </c>
       <c r="F7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I7">
         <v>60</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7">
         <v>60</v>
@@ -3839,7 +3859,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3916,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -3925,7 +3945,7 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -3978,7 +3998,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -4014,7 +4034,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -4055,10 +4075,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -4067,7 +4087,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -4082,7 +4102,7 @@
         <v>12</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>15</v>
@@ -4165,7 +4185,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>28</v>
@@ -4186,16 +4206,16 @@
         <v>28</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2">
         <v>22</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4221,7 +4241,7 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4250,7 +4270,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -4291,7 +4311,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -4332,7 +4352,7 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>28</v>
@@ -4347,7 +4367,7 @@
         <v>15</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>28</v>
@@ -4359,7 +4379,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4370,37 +4390,37 @@
         <v>98</v>
       </c>
       <c r="C7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G7">
         <v>83</v>
       </c>
       <c r="H7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4408,40 +4428,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C8">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D8">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E8">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F8">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G8">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I8">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J8">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K8">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L8">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M8">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4458,19 +4478,19 @@
         <v>20</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9">
         <v>18</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9">
         <v>24</v>
@@ -4505,7 +4525,7 @@
         <v>17</v>
       </c>
       <c r="G10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10">
         <v>28</v>
@@ -4523,7 +4543,7 @@
         <v>13</v>
       </c>
       <c r="M10">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4534,13 +4554,13 @@
         <v>44</v>
       </c>
       <c r="C11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11">
         <v>66</v>
       </c>
       <c r="E11">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F11">
         <v>46</v>
@@ -4552,16 +4572,16 @@
         <v>44</v>
       </c>
       <c r="I11">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J11">
         <v>39</v>
       </c>
       <c r="K11">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L11">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M11">
         <v>32</v>
@@ -4651,13 +4671,13 @@
         <v>11</v>
       </c>
       <c r="C14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>19</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14">
         <v>8</v>
@@ -4692,22 +4712,22 @@
         <v>25</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <v>43</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>25</v>
       </c>
       <c r="G15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I15">
         <v>38</v>
@@ -4716,7 +4736,7 @@
         <v>37</v>
       </c>
       <c r="K15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L15">
         <v>18</v>
@@ -4742,7 +4762,7 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>11</v>
@@ -4780,10 +4800,13 @@
         <v>4</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -4795,7 +4818,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4833,7 +4856,7 @@
         <v>23</v>
       </c>
       <c r="L18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M18">
         <v>17</v>
@@ -4844,34 +4867,34 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G19">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I19">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J19">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K19">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L19">
         <v>81</v>
@@ -4885,7 +4908,7 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20">
         <v>70</v>
@@ -4894,31 +4917,31 @@
         <v>79</v>
       </c>
       <c r="E20">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F20">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G20">
         <v>65</v>
       </c>
       <c r="H20">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20">
         <v>85</v>
       </c>
       <c r="J20">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K20">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L20">
         <v>62</v>
       </c>
       <c r="M20">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4929,7 +4952,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -4947,10 +4970,10 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -4959,7 +4982,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4970,7 +4993,7 @@
         <v>11</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -5023,7 +5046,7 @@
         <v>22</v>
       </c>
       <c r="G23">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H23">
         <v>23</v>
@@ -5035,13 +5058,13 @@
         <v>31</v>
       </c>
       <c r="K23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L23">
         <v>26</v>
       </c>
       <c r="M23">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5055,13 +5078,13 @@
         <v>26</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>12</v>
@@ -5073,16 +5096,16 @@
         <v>4</v>
       </c>
       <c r="J24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K24">
         <v>9</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5099,7 +5122,7 @@
         <v>17</v>
       </c>
       <c r="E25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25">
         <v>7</v>
@@ -5178,31 +5201,31 @@
         <v>20</v>
       </c>
       <c r="D27">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E27">
         <v>23</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H27">
         <v>20</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J27">
         <v>14</v>
       </c>
       <c r="K27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L27">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M27">
         <v>25</v>
@@ -5236,40 +5259,40 @@
         <v>35</v>
       </c>
       <c r="B29">
+        <v>149</v>
+      </c>
+      <c r="C29">
+        <v>205</v>
+      </c>
+      <c r="D29">
+        <v>209</v>
+      </c>
+      <c r="E29">
         <v>147</v>
       </c>
-      <c r="C29">
-        <v>204</v>
-      </c>
-      <c r="D29">
-        <v>202</v>
-      </c>
-      <c r="E29">
-        <v>145</v>
-      </c>
       <c r="F29">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G29">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H29">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I29">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J29">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K29">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L29">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M29">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5277,10 +5300,10 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>17</v>
@@ -5289,7 +5312,7 @@
         <v>9</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>11</v>
@@ -5304,7 +5327,7 @@
         <v>12</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>15</v>
@@ -5321,7 +5344,7 @@
         <v>22</v>
       </c>
       <c r="C31">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D31">
         <v>41</v>
@@ -5330,7 +5353,7 @@
         <v>18</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G31">
         <v>20</v>
@@ -5345,7 +5368,7 @@
         <v>22</v>
       </c>
       <c r="K31">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L31">
         <v>28</v>
@@ -5400,40 +5423,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D33">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E33">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F33">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G33">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H33">
+        <v>131</v>
+      </c>
+      <c r="I33">
+        <v>125</v>
+      </c>
+      <c r="J33">
+        <v>138</v>
+      </c>
+      <c r="K33">
         <v>129</v>
       </c>
-      <c r="I33">
-        <v>123</v>
-      </c>
-      <c r="J33">
-        <v>136</v>
-      </c>
-      <c r="K33">
-        <v>127</v>
-      </c>
       <c r="L33">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M33">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5447,7 +5470,7 @@
         <v>14</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>9</v>
@@ -5465,7 +5488,7 @@
         <v>7</v>
       </c>
       <c r="J34">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K34">
         <v>21</v>
@@ -5506,7 +5529,7 @@
         <v>2</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>5</v>
@@ -5523,7 +5546,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36">
         <v>31</v>
@@ -5532,16 +5555,16 @@
         <v>28</v>
       </c>
       <c r="E36">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36">
         <v>35</v>
       </c>
       <c r="G36">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I36">
         <v>38</v>
@@ -5550,10 +5573,10 @@
         <v>49</v>
       </c>
       <c r="K36">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M36">
         <v>25</v>
@@ -5567,37 +5590,37 @@
         <v>86</v>
       </c>
       <c r="C37">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D37">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E37">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F37">
         <v>91</v>
       </c>
       <c r="G37">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H37">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I37">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J37">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K37">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L37">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M37">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5620,7 +5643,7 @@
         <v>1</v>
       </c>
       <c r="K38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>3</v>
@@ -5646,7 +5669,7 @@
         <v>3</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39">
         <v>2</v>
@@ -5719,10 +5742,10 @@
         <v>19</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <v>15</v>
@@ -5731,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41">
         <v>23</v>
@@ -5743,7 +5766,7 @@
         <v>11</v>
       </c>
       <c r="M41">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5751,40 +5774,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C42">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D42">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E42">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F42">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G42">
         <v>101</v>
       </c>
       <c r="H42">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I42">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J42">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K42">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L42">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M42">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5807,25 +5830,25 @@
         <v>23</v>
       </c>
       <c r="G43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H43">
         <v>22</v>
       </c>
       <c r="I43">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J43">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K43">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L43">
         <v>18</v>
       </c>
       <c r="M43">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5833,13 +5856,13 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>26</v>
       </c>
       <c r="D44">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E44">
         <v>37</v>
@@ -5848,13 +5871,13 @@
         <v>16</v>
       </c>
       <c r="G44">
+        <v>33</v>
+      </c>
+      <c r="H44">
         <v>32</v>
       </c>
-      <c r="H44">
-        <v>31</v>
-      </c>
       <c r="I44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J44">
         <v>26</v>
@@ -5939,7 +5962,7 @@
         <v>7</v>
       </c>
       <c r="J46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K46">
         <v>6</v>
@@ -5974,7 +5997,7 @@
         <v>14</v>
       </c>
       <c r="H47">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I47">
         <v>18</v>
@@ -5983,10 +6006,10 @@
         <v>30</v>
       </c>
       <c r="K47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M47">
         <v>15</v>
@@ -5997,7 +6020,7 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -6009,10 +6032,10 @@
         <v>30</v>
       </c>
       <c r="F48">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G48">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H48">
         <v>34</v>
@@ -6027,10 +6050,10 @@
         <v>27</v>
       </c>
       <c r="L48">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M48">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6088,7 +6111,7 @@
         <v>23</v>
       </c>
       <c r="E50">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F50">
         <v>18</v>
@@ -6109,7 +6132,7 @@
         <v>12</v>
       </c>
       <c r="L50">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M50">
         <v>10</v>
@@ -6129,7 +6152,7 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F51">
         <v>35</v>
@@ -6138,22 +6161,22 @@
         <v>23</v>
       </c>
       <c r="H51">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J51">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K51">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L51">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M51">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6161,31 +6184,31 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C52">
         <v>97</v>
       </c>
       <c r="D52">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E52">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F52">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G52">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H52">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I52">
         <v>61</v>
       </c>
       <c r="J52">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K52">
         <v>80</v>
@@ -6202,13 +6225,13 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C53">
         <v>46</v>
       </c>
       <c r="D53">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E53">
         <v>39</v>
@@ -6220,7 +6243,7 @@
         <v>31</v>
       </c>
       <c r="H53">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I53">
         <v>31</v>
@@ -6232,7 +6255,7 @@
         <v>40</v>
       </c>
       <c r="L53">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M53">
         <v>22</v>
@@ -6243,28 +6266,28 @@
         <v>60</v>
       </c>
       <c r="B54">
+        <v>43</v>
+      </c>
+      <c r="C54">
         <v>41</v>
       </c>
-      <c r="C54">
-        <v>40</v>
-      </c>
       <c r="D54">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E54">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F54">
         <v>51</v>
       </c>
       <c r="G54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H54">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J54">
         <v>63</v>
@@ -6276,7 +6299,7 @@
         <v>47</v>
       </c>
       <c r="M54">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6287,10 +6310,10 @@
         <v>16</v>
       </c>
       <c r="C55">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D55">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E55">
         <v>27</v>
@@ -6302,13 +6325,13 @@
         <v>30</v>
       </c>
       <c r="H55">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I55">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K55">
         <v>31</v>
@@ -6317,7 +6340,7 @@
         <v>26</v>
       </c>
       <c r="M55">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6346,13 +6369,13 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J56">
         <v>2</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -6387,7 +6410,7 @@
         <v>12</v>
       </c>
       <c r="I57">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J57">
         <v>12</v>
@@ -6410,12 +6433,15 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
         <v>1</v>
       </c>
       <c r="I58">
@@ -6486,16 +6512,16 @@
         <v>32</v>
       </c>
       <c r="E60">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F60">
         <v>15</v>
       </c>
       <c r="G60">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I60">
         <v>12</v>
@@ -6504,7 +6530,7 @@
         <v>19</v>
       </c>
       <c r="K60">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L60">
         <v>16</v>
@@ -6558,6 +6584,12 @@
       <c r="A62" s="2" t="s">
         <v>68</v>
       </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
       <c r="H62">
         <v>1</v>
       </c>
@@ -6579,19 +6611,19 @@
         <v>134</v>
       </c>
       <c r="C63">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D63">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E63">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F63">
         <v>55</v>
       </c>
       <c r="G63">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H63">
         <v>42</v>
@@ -6609,7 +6641,7 @@
         <v>10</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6617,7 +6649,7 @@
         <v>70</v>
       </c>
       <c r="B64">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C64">
         <v>20</v>
@@ -6650,7 +6682,7 @@
         <v>22</v>
       </c>
       <c r="M64">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6661,7 +6693,7 @@
         <v>47</v>
       </c>
       <c r="C65">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D65">
         <v>71</v>
@@ -6670,28 +6702,28 @@
         <v>67</v>
       </c>
       <c r="F65">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G65">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H65">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I65">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J65">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K65">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L65">
         <v>46</v>
       </c>
       <c r="M65">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6699,7 +6731,7 @@
         <v>72</v>
       </c>
       <c r="B66">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C66">
         <v>8</v>
@@ -6717,7 +6749,7 @@
         <v>11</v>
       </c>
       <c r="H66">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I66">
         <v>4</v>
@@ -6740,37 +6772,37 @@
         <v>96</v>
       </c>
       <c r="C67">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D67">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E67">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F67">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G67">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H67">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I67">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J67">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K67">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L67">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M67">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6778,10 +6810,10 @@
         <v>74</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>9</v>
@@ -6825,7 +6857,7 @@
         <v>3</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -6846,7 +6878,7 @@
         <v>8</v>
       </c>
       <c r="K69">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L69">
         <v>7</v>
@@ -6863,7 +6895,7 @@
         <v>2</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -6916,7 +6948,7 @@
         <v>5</v>
       </c>
       <c r="H71">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I71">
         <v>4</v>
@@ -6925,7 +6957,7 @@
         <v>13</v>
       </c>
       <c r="K71">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L71">
         <v>8</v>
@@ -6948,13 +6980,13 @@
         <v>12</v>
       </c>
       <c r="E72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F72">
         <v>15</v>
       </c>
       <c r="G72">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H72">
         <v>8</v>
@@ -6966,13 +6998,13 @@
         <v>13</v>
       </c>
       <c r="K72">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L72">
         <v>10</v>
       </c>
       <c r="M72">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -6992,7 +7024,7 @@
         <v>31</v>
       </c>
       <c r="F73">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G73">
         <v>25</v>
@@ -7036,7 +7068,7 @@
         <v>6</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>3</v>
@@ -7080,7 +7112,7 @@
         <v>9</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75">
         <v>15</v>
@@ -7092,7 +7124,7 @@
         <v>10</v>
       </c>
       <c r="M75">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7100,7 +7132,7 @@
         <v>82</v>
       </c>
       <c r="B76">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C76">
         <v>31</v>
@@ -7109,19 +7141,19 @@
         <v>29</v>
       </c>
       <c r="E76">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F76">
+        <v>43</v>
+      </c>
+      <c r="G76">
+        <v>48</v>
+      </c>
+      <c r="H76">
+        <v>26</v>
+      </c>
+      <c r="I76">
         <v>41</v>
-      </c>
-      <c r="G76">
-        <v>45</v>
-      </c>
-      <c r="H76">
-        <v>25</v>
-      </c>
-      <c r="I76">
-        <v>40</v>
       </c>
       <c r="J76">
         <v>54</v>
@@ -7130,7 +7162,7 @@
         <v>47</v>
       </c>
       <c r="L76">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M76">
         <v>32</v>
@@ -7141,16 +7173,16 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C77">
         <v>21</v>
       </c>
       <c r="D77">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F77">
         <v>14</v>
@@ -7162,16 +7194,16 @@
         <v>12</v>
       </c>
       <c r="I77">
+        <v>21</v>
+      </c>
+      <c r="J77">
+        <v>28</v>
+      </c>
+      <c r="K77">
         <v>20</v>
       </c>
-      <c r="J77">
-        <v>27</v>
-      </c>
-      <c r="K77">
+      <c r="L77">
         <v>18</v>
-      </c>
-      <c r="L77">
-        <v>17</v>
       </c>
       <c r="M77">
         <v>21</v>
@@ -7182,40 +7214,40 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C78">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D78">
         <v>37</v>
       </c>
       <c r="E78">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F78">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G78">
         <v>45</v>
       </c>
       <c r="H78">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I78">
         <v>35</v>
       </c>
       <c r="J78">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K78">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L78">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M78">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7223,40 +7255,40 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C79">
         <v>97</v>
       </c>
       <c r="D79">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E79">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F79">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G79">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H79">
         <v>95</v>
       </c>
       <c r="I79">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J79">
         <v>101</v>
       </c>
       <c r="K79">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M79">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7273,10 +7305,10 @@
         <v>10</v>
       </c>
       <c r="E80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G80">
         <v>10</v>
@@ -7294,7 +7326,7 @@
         <v>10</v>
       </c>
       <c r="L80">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M80">
         <v>9</v>
@@ -7370,7 +7402,7 @@
         <v>3</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82">
         <v>3</v>
@@ -7381,22 +7413,22 @@
         <v>89</v>
       </c>
       <c r="B83">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C83">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D83">
         <v>72</v>
       </c>
       <c r="E83">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F83">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G83">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H83">
         <v>47</v>
@@ -7405,16 +7437,16 @@
         <v>53</v>
       </c>
       <c r="J83">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K83">
         <v>56</v>
       </c>
       <c r="L83">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M83">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7422,7 +7454,7 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C84">
         <v>22</v>
@@ -7437,19 +7469,19 @@
         <v>21</v>
       </c>
       <c r="G84">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H84">
         <v>22</v>
       </c>
       <c r="I84">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J84">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K84">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L84">
         <v>21</v>
@@ -7463,34 +7495,34 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C85">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D85">
         <v>132</v>
       </c>
       <c r="E85">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F85">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G85">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H85">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I85">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J85">
         <v>130</v>
       </c>
       <c r="K85">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L85">
         <v>116</v>
@@ -7522,7 +7554,7 @@
         <v>19</v>
       </c>
       <c r="H86">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I86">
         <v>13</v>
@@ -7534,10 +7566,10 @@
         <v>22</v>
       </c>
       <c r="L86">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M86">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7551,7 +7583,7 @@
         <v>6</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E87">
         <v>15</v>
@@ -7569,7 +7601,7 @@
         <v>3</v>
       </c>
       <c r="J87">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K87">
         <v>2</v>
@@ -7586,28 +7618,28 @@
         <v>94</v>
       </c>
       <c r="B88">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C88">
         <v>37</v>
       </c>
       <c r="D88">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E88">
         <v>36</v>
       </c>
       <c r="F88">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G88">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H88">
         <v>28</v>
       </c>
       <c r="I88">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J88">
         <v>25</v>
@@ -7627,25 +7659,25 @@
         <v>95</v>
       </c>
       <c r="B89">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C89">
         <v>29</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E89">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F89">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G89">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H89">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I89">
         <v>24</v>
@@ -7671,13 +7703,13 @@
         <v>25</v>
       </c>
       <c r="C90">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D90">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E90">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F90">
         <v>33</v>
@@ -7695,13 +7727,13 @@
         <v>38</v>
       </c>
       <c r="K90">
+        <v>27</v>
+      </c>
+      <c r="L90">
+        <v>22</v>
+      </c>
+      <c r="M90">
         <v>26</v>
-      </c>
-      <c r="L90">
-        <v>20</v>
-      </c>
-      <c r="M90">
-        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7712,7 +7744,7 @@
         <v>30</v>
       </c>
       <c r="C91">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D91">
         <v>41</v>
@@ -7724,22 +7756,22 @@
         <v>28</v>
       </c>
       <c r="G91">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H91">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I91">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J91">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K91">
         <v>29</v>
       </c>
       <c r="L91">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M91">
         <v>33</v>
@@ -7768,7 +7800,7 @@
         <v>13</v>
       </c>
       <c r="H92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I92">
         <v>9</v>
@@ -7777,7 +7809,7 @@
         <v>7</v>
       </c>
       <c r="K92">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L92">
         <v>5</v>
@@ -7797,7 +7829,7 @@
         <v>22</v>
       </c>
       <c r="D93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E93">
         <v>17</v>
@@ -7818,7 +7850,7 @@
         <v>16</v>
       </c>
       <c r="K93">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L93">
         <v>13</v>
@@ -7835,7 +7867,7 @@
         <v>9</v>
       </c>
       <c r="C94">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D94">
         <v>24</v>
@@ -7844,7 +7876,7 @@
         <v>27</v>
       </c>
       <c r="F94">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G94">
         <v>18</v>
@@ -7862,7 +7894,7 @@
         <v>41</v>
       </c>
       <c r="L94">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M94">
         <v>28</v>
@@ -7879,25 +7911,25 @@
         <v>42</v>
       </c>
       <c r="D95">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E95">
         <v>43</v>
       </c>
       <c r="F95">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G95">
         <v>60</v>
       </c>
       <c r="H95">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I95">
         <v>47</v>
       </c>
       <c r="J95">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K95">
         <v>51</v>
@@ -7906,7 +7938,7 @@
         <v>32</v>
       </c>
       <c r="M95">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7914,7 +7946,7 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C96">
         <v>32</v>
@@ -7923,28 +7955,28 @@
         <v>31</v>
       </c>
       <c r="E96">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F96">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G96">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H96">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I96">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J96">
         <v>36</v>
       </c>
       <c r="K96">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L96">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M96">
         <v>22</v>
@@ -7961,7 +7993,7 @@
         <v>28</v>
       </c>
       <c r="D97">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E97">
         <v>20</v>
@@ -7982,13 +8014,13 @@
         <v>18</v>
       </c>
       <c r="K97">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L97">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M97">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8008,10 +8040,10 @@
         <v>19</v>
       </c>
       <c r="F98">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G98">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H98">
         <v>16</v>
@@ -8020,7 +8052,7 @@
         <v>17</v>
       </c>
       <c r="J98">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K98">
         <v>19</v>
@@ -8043,25 +8075,25 @@
         <v>40</v>
       </c>
       <c r="D99">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E99">
         <v>42</v>
       </c>
       <c r="F99">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G99">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H99">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I99">
         <v>60</v>
       </c>
       <c r="J99">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K99">
         <v>60</v>
@@ -8070,7 +8102,7 @@
         <v>41</v>
       </c>
       <c r="M99">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8116,40 +8148,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2469</v>
+        <v>2504</v>
       </c>
       <c r="C101">
-        <v>3088</v>
+        <v>3139</v>
       </c>
       <c r="D101">
-        <v>3435</v>
+        <v>3498</v>
       </c>
       <c r="E101">
-        <v>2964</v>
+        <v>3025</v>
       </c>
       <c r="F101">
-        <v>2685</v>
+        <v>2747</v>
       </c>
       <c r="G101">
-        <v>2921</v>
+        <v>2971</v>
       </c>
       <c r="H101">
-        <v>2686</v>
+        <v>2740</v>
       </c>
       <c r="I101">
-        <v>2806</v>
+        <v>2856</v>
       </c>
       <c r="J101">
-        <v>3280</v>
+        <v>3328</v>
       </c>
       <c r="K101">
-        <v>3079</v>
+        <v>3143</v>
       </c>
       <c r="L101">
-        <v>2440</v>
+        <v>2494</v>
       </c>
       <c r="M101">
-        <v>2179</v>
+        <v>2230</v>
       </c>
     </row>
   </sheetData>
@@ -8328,7 +8360,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -8393,7 +8425,7 @@
         <v>6</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -8456,6 +8488,9 @@
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>1</v>
       </c>
@@ -8474,7 +8509,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -8498,7 +8533,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>13</v>
@@ -8515,7 +8550,7 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -8524,7 +8559,7 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>20</v>
@@ -8539,7 +8574,7 @@
         <v>22</v>
       </c>
       <c r="K7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7">
         <v>28</v>
@@ -8622,19 +8657,19 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>23</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>29</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>26</v>
@@ -8643,13 +8678,13 @@
         <v>28</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2">
         <v>21</v>
@@ -8669,7 +8704,7 @@
         <v>54</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>41</v>
@@ -8678,22 +8713,22 @@
         <v>37</v>
       </c>
       <c r="H3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3">
         <v>23</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8783,22 +8818,22 @@
         <v>41</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>34</v>
@@ -8807,13 +8842,13 @@
         <v>37</v>
       </c>
       <c r="K6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8824,37 +8859,37 @@
         <v>96</v>
       </c>
       <c r="C7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -8949,13 +8984,13 @@
         <v>3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>11</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -8969,7 +9004,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -8990,7 +9025,7 @@
         <v>9</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -9074,7 +9109,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -9083,7 +9118,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -9100,7 +9135,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -9115,19 +9150,19 @@
         <v>21</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>22</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>21</v>
@@ -9486,7 +9521,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -9518,7 +9553,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -9539,7 +9574,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -9551,7 +9586,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9605,6 +9640,9 @@
       <c r="F5">
         <v>1</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="K5">
         <v>2</v>
       </c>
@@ -9617,16 +9655,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>29</v>
@@ -9635,7 +9673,7 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>31</v>
@@ -9658,28 +9696,28 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>43</v>
+      </c>
+      <c r="C7">
         <v>41</v>
       </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
       <c r="D7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>51</v>
       </c>
       <c r="G7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J7">
         <v>63</v>
@@ -9691,7 +9729,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -9771,25 +9809,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H2">
         <v>49</v>
       </c>
       <c r="I2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2">
         <v>38</v>
@@ -9798,7 +9836,7 @@
         <v>43</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9809,37 +9847,37 @@
         <v>52</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9847,7 +9885,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -9874,13 +9912,13 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>9</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9894,7 +9932,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -9909,7 +9947,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -9929,19 +9967,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>85</v>
       </c>
       <c r="D6">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E6">
         <v>53</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>63</v>
@@ -9950,19 +9988,19 @@
         <v>43</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9970,40 +10008,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>149</v>
+      </c>
+      <c r="C7">
+        <v>205</v>
+      </c>
+      <c r="D7">
+        <v>209</v>
+      </c>
+      <c r="E7">
         <v>147</v>
       </c>
-      <c r="C7">
-        <v>204</v>
-      </c>
-      <c r="D7">
-        <v>202</v>
-      </c>
-      <c r="E7">
-        <v>145</v>
-      </c>
       <c r="F7">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M7">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10089,7 +10127,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -10118,7 +10156,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -10133,7 +10171,7 @@
         <v>8</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -10151,7 +10189,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10192,7 +10230,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10241,7 +10279,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6">
         <v>17</v>
@@ -10252,7 +10290,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>47</v>
@@ -10264,10 +10302,10 @@
         <v>30</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7">
         <v>34</v>
@@ -10282,10 +10320,10 @@
         <v>27</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -10365,28 +10403,28 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
       <c r="F2">
+        <v>23</v>
+      </c>
+      <c r="G2">
         <v>22</v>
       </c>
-      <c r="G2">
-        <v>21</v>
-      </c>
       <c r="H2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2">
         <v>27</v>
@@ -10403,13 +10441,13 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>21</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>29</v>
@@ -10421,19 +10459,19 @@
         <v>22</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>31</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3">
         <v>21</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10520,7 +10558,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -10538,7 +10576,7 @@
         <v>32</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -10547,13 +10585,13 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6">
         <v>27</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10561,34 +10599,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K7">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L7">
         <v>81</v>
@@ -10668,13 +10706,13 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
         <v>7</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -10683,7 +10721,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -10730,7 +10768,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -10814,7 +10852,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -10832,7 +10870,7 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -10855,13 +10893,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>26</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>37</v>
@@ -10870,13 +10908,13 @@
         <v>16</v>
       </c>
       <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
         <v>32</v>
       </c>
-      <c r="H7">
-        <v>31</v>
-      </c>
       <c r="I7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7">
         <v>26</v>
@@ -10971,7 +11009,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -11003,7 +11041,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -11056,22 +11094,22 @@
         <v>5</v>
       </c>
       <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
         <v>8</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>6</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>6</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -11105,13 +11143,13 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>17</v>
@@ -11134,7 +11172,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -11143,19 +11181,19 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
+        <v>43</v>
+      </c>
+      <c r="G7">
+        <v>48</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
         <v>41</v>
-      </c>
-      <c r="G7">
-        <v>45</v>
-      </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7">
-        <v>40</v>
       </c>
       <c r="J7">
         <v>54</v>
@@ -11164,7 +11202,7 @@
         <v>47</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -11285,13 +11323,13 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>6</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -11375,7 +11413,7 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -11407,13 +11445,13 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>19</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -11532,7 +11570,7 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>7</v>
@@ -11544,7 +11582,7 @@
         <v>8</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11642,7 +11680,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>17</v>
@@ -11683,7 +11721,7 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -11698,7 +11736,7 @@
         <v>15</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7">
         <v>28</v>
@@ -11710,7 +11748,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -11817,7 +11855,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11834,7 +11872,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -11924,7 +11962,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -11933,7 +11971,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -11962,10 +12000,10 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>15</v>
@@ -11974,7 +12012,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7">
         <v>23</v>
@@ -11986,7 +12024,7 @@
         <v>11</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -12063,16 +12101,16 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>23</v>
+      </c>
+      <c r="F2">
         <v>29</v>
-      </c>
-      <c r="E2">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>28</v>
       </c>
       <c r="G2">
         <v>21</v>
@@ -12081,13 +12119,13 @@
         <v>25</v>
       </c>
       <c r="I2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J2">
         <v>21</v>
       </c>
       <c r="K2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2">
         <v>19</v>
@@ -12101,16 +12139,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>24</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -12119,22 +12157,22 @@
         <v>31</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>23</v>
       </c>
       <c r="K3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3">
         <v>16</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12142,7 +12180,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -12160,13 +12198,13 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>3</v>
@@ -12224,10 +12262,10 @@
         <v>52</v>
       </c>
       <c r="C6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>53</v>
@@ -12251,7 +12289,7 @@
         <v>40</v>
       </c>
       <c r="L6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M6">
         <v>19</v>
@@ -12262,40 +12300,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D7">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G7">
         <v>101</v>
       </c>
       <c r="H7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -12587,7 +12625,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12610,7 +12648,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -12738,7 +12776,7 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>28</v>
@@ -12756,7 +12794,7 @@
         <v>13</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -12857,10 +12895,10 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2">
         <v>8</v>
@@ -12889,7 +12927,7 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -12930,7 +12968,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -12945,7 +12983,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12958,25 +12996,28 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>14</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -12988,13 +13029,13 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>14</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -13005,40 +13046,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>37</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>45</v>
       </c>
       <c r="H7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7">
         <v>35</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -13115,7 +13156,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -13130,7 +13171,7 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -13156,7 +13197,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -13258,7 +13299,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -13273,10 +13314,10 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <v>11</v>
@@ -13285,7 +13326,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13296,10 +13337,10 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>27</v>
@@ -13311,13 +13352,13 @@
         <v>30</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7">
         <v>31</v>
@@ -13326,7 +13367,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -13421,7 +13462,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -13450,7 +13491,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -13462,13 +13503,13 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13519,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -13543,7 +13584,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13557,13 +13598,13 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -13575,16 +13616,16 @@
         <v>4</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <v>9</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -13710,6 +13751,9 @@
       <c r="I3">
         <v>3</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>2</v>
       </c>
@@ -13830,7 +13874,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -13940,7 +13984,7 @@
         <v>9</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -13987,7 +14031,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14065,7 +14109,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -14106,7 +14150,7 @@
         <v>22</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7">
         <v>23</v>
@@ -14118,13 +14162,13 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>26</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -14216,7 +14260,7 @@
         <v>9</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>5</v>
@@ -14228,7 +14272,7 @@
         <v>17</v>
       </c>
       <c r="L2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M2">
         <v>8</v>
@@ -14251,10 +14295,10 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -14280,7 +14324,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -14350,28 +14394,28 @@
         <v>15</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -14382,7 +14426,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -14391,28 +14435,28 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>36</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M7">
         <v>22</v>
@@ -14507,7 +14551,7 @@
         <v>6</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2">
         <v>13</v>
@@ -14545,22 +14589,22 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3">
         <v>6</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3">
         <v>10</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3">
         <v>16</v>
@@ -14620,7 +14664,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>22</v>
@@ -14661,7 +14705,7 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -14673,22 +14717,22 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7">
         <v>29</v>
       </c>
       <c r="L7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7">
         <v>33</v>
@@ -14777,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -14857,7 +14901,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -14878,7 +14922,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -14887,7 +14931,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14898,7 +14942,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -14916,10 +14960,10 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -14928,7 +14972,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15002,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -15014,10 +15058,10 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>29</v>
@@ -15029,13 +15073,13 @@
         <v>28</v>
       </c>
       <c r="K2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15049,22 +15093,22 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
+        <v>28</v>
+      </c>
+      <c r="G3">
         <v>27</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
       </c>
       <c r="H3">
         <v>31</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3">
         <v>31</v>
@@ -15111,7 +15155,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -15169,10 +15213,10 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>18</v>
@@ -15190,7 +15234,7 @@
         <v>32</v>
       </c>
       <c r="K6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -15204,40 +15248,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>97</v>
       </c>
       <c r="D7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7">
         <v>95</v>
       </c>
       <c r="I7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7">
         <v>101</v>
       </c>
       <c r="K7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M7">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -15445,7 +15489,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -15478,7 +15522,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15486,7 +15530,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -15519,7 +15563,7 @@
         <v>22</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -15593,7 +15637,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -15611,7 +15655,7 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2">
         <v>21</v>
@@ -15620,7 +15664,7 @@
         <v>17</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -15646,7 +15690,7 @@
         <v>22</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>17</v>
@@ -15658,7 +15702,7 @@
         <v>25</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3">
         <v>21</v>
@@ -15687,7 +15731,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -15708,7 +15752,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15760,10 +15804,10 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>34</v>
@@ -15775,7 +15819,7 @@
         <v>31</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K6">
         <v>32</v>
@@ -15792,7 +15836,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>70</v>
@@ -15801,31 +15845,31 @@
         <v>79</v>
       </c>
       <c r="E7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F7">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G7">
         <v>65</v>
       </c>
       <c r="H7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7">
         <v>85</v>
       </c>
       <c r="J7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L7">
         <v>62</v>
       </c>
       <c r="M7">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -15970,7 +16014,7 @@
         <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -16086,7 +16130,7 @@
         <v>23</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7">
         <v>17</v>
@@ -16099,7 +16143,7 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16114,9 +16158,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16142,19 +16187,22 @@
         <v>2021</v>
       </c>
       <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16167,11 +16215,17 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -16194,16 +16248,19 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -16216,14 +16273,14 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -16242,17 +16299,20 @@
       <c r="H5">
         <v>5</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -16272,22 +16332,25 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16361,7 +16424,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -16376,7 +16439,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>13</v>
@@ -16388,10 +16451,10 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>8</v>
@@ -16411,7 +16474,7 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -16420,7 +16483,7 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -16442,6 +16505,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="C4">
         <v>2</v>
       </c>
@@ -16548,7 +16614,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -16557,16 +16623,16 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>35</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7">
         <v>38</v>
@@ -16575,10 +16641,10 @@
         <v>49</v>
       </c>
       <c r="K7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7">
         <v>25</v>
@@ -16661,7 +16727,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -16804,7 +16870,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -16824,7 +16890,7 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -16845,7 +16911,7 @@
         <v>16</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -17113,37 +17179,37 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
         <v>17</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2">
         <v>37</v>
       </c>
       <c r="L2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17157,13 +17223,13 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>30</v>
@@ -17172,7 +17238,7 @@
         <v>26</v>
       </c>
       <c r="I3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J3">
         <v>35</v>
@@ -17184,7 +17250,7 @@
         <v>28</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17210,7 +17276,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -17219,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -17233,7 +17299,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -17274,31 +17340,31 @@
         <v>49</v>
       </c>
       <c r="C6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
         <v>23</v>
       </c>
       <c r="H6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I6">
         <v>28</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L6">
         <v>26</v>
@@ -17315,37 +17381,37 @@
         <v>98</v>
       </c>
       <c r="C7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G7">
         <v>83</v>
       </c>
       <c r="H7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -17550,7 +17616,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -17568,7 +17634,7 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -17591,7 +17657,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -17609,7 +17675,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
         <v>21</v>
@@ -17692,7 +17758,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -17701,7 +17767,7 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -17719,7 +17785,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -17855,7 +17921,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>24</v>
@@ -17864,7 +17930,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -17882,7 +17948,7 @@
         <v>41</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7">
         <v>28</v>
@@ -17968,7 +18034,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -18128,7 +18194,7 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -18256,7 +18322,7 @@
         <v>6</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -18294,7 +18360,7 @@
         <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -18378,7 +18444,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -18419,7 +18485,7 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>18</v>
@@ -18428,10 +18494,10 @@
         <v>30</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7">
         <v>15</v>
@@ -18535,7 +18601,7 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -18558,13 +18624,13 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -18590,7 +18656,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -18614,7 +18680,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -18666,7 +18732,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>20</v>
@@ -18692,22 +18758,22 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7">
         <v>43</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>38</v>
@@ -18716,7 +18782,7 @@
         <v>37</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -18817,7 +18883,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -18915,10 +18981,10 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>11</v>
@@ -18956,10 +19022,10 @@
         <v>19</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -18968,7 +19034,7 @@
         <v>17</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K7">
         <v>19</v>
@@ -19060,7 +19126,7 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -19078,7 +19144,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -19209,7 +19275,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -19229,7 +19295,7 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>18</v>
@@ -19250,7 +19316,7 @@
         <v>12</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -19567,7 +19633,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -19599,7 +19665,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -19780,7 +19846,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -19798,7 +19864,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -19812,7 +19878,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -19830,7 +19896,7 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -19919,7 +19985,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>19</v>
@@ -19937,7 +20003,7 @@
         <v>16</v>
       </c>
       <c r="I2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -19984,10 +20050,10 @@
         <v>11</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -20074,7 +20140,7 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>20</v>
@@ -20092,7 +20158,7 @@
         <v>13</v>
       </c>
       <c r="K6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6">
         <v>13</v>
@@ -20109,13 +20175,13 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>66</v>
       </c>
       <c r="E7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7">
         <v>46</v>
@@ -20127,16 +20193,16 @@
         <v>44</v>
       </c>
       <c r="I7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>39</v>
       </c>
       <c r="K7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -20233,7 +20299,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -20323,7 +20389,7 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -20418,7 +20484,7 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -20456,19 +20522,19 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>5</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -20590,19 +20656,19 @@
         <v>20</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7">
         <v>18</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -20741,7 +20807,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -20869,7 +20935,7 @@
         <v>31</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -21216,13 +21282,13 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -21236,7 +21302,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -21266,7 +21332,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21314,6 +21380,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -21323,7 +21392,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>21</v>
@@ -21364,7 +21433,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>28</v>
@@ -21385,16 +21454,16 @@
         <v>28</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>22</v>
       </c>
       <c r="L7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -21527,7 +21596,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -21568,7 +21637,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -21596,7 +21665,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>16</v>
@@ -21620,7 +21689,7 @@
         <v>14</v>
       </c>
       <c r="L6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -21637,7 +21706,7 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -21658,13 +21727,13 @@
         <v>18</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -21857,7 +21926,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -21866,7 +21935,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -21898,7 +21967,7 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -21907,7 +21976,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -21986,7 +22055,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -22102,7 +22171,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -22218,7 +22287,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -22250,7 +22319,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -22265,7 +22334,7 @@
         <v>6</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -22285,7 +22354,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -22355,7 +22424,7 @@
         <v>19</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -22384,28 +22453,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>37</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7">
         <v>28</v>
       </c>
       <c r="I7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J7">
         <v>25</v>
@@ -22734,7 +22803,7 @@
         <v>6</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -22763,7 +22832,7 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -22798,7 +22867,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -22813,7 +22882,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -22865,13 +22934,13 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -22897,25 +22966,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>29</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>24</v>
@@ -23097,7 +23166,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -23135,7 +23204,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -23242,7 +23311,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -23251,22 +23320,22 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
         <v>10</v>
-      </c>
-      <c r="L2">
-        <v>9</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -23289,7 +23358,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>7</v>
@@ -23298,7 +23367,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>10</v>
@@ -23318,7 +23387,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -23379,7 +23448,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>13</v>
@@ -23411,31 +23480,31 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>23</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>14</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7">
         <v>25</v>
@@ -23580,7 +23649,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23606,7 +23675,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -23621,7 +23690,7 @@
         <v>13</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23659,7 +23728,7 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -23688,7 +23757,7 @@
         <v>19</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -23700,10 +23769,10 @@
         <v>22</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -23845,7 +23914,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23911,7 +23980,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -23946,7 +24015,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>15</v>
@@ -23958,7 +24027,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -24062,7 +24131,7 @@
         <v>9</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -24079,7 +24148,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -24103,7 +24172,7 @@
         <v>8</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -24181,13 +24250,13 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -24205,13 +24274,13 @@
         <v>19</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>2</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24222,13 +24291,13 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>33</v>
@@ -24246,13 +24315,13 @@
         <v>38</v>
       </c>
       <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
         <v>26</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -24353,7 +24422,7 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>11</v>
@@ -24388,19 +24457,19 @@
         <v>11</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3">
         <v>11</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24417,7 +24486,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -24454,6 +24523,9 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="M5">
         <v>2</v>
       </c>
@@ -24481,7 +24553,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>13</v>
@@ -24513,7 +24585,7 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>35</v>
@@ -24522,22 +24594,22 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -24652,7 +24724,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -24724,7 +24796,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -24759,10 +24831,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -24881,7 +24953,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -25035,7 +25107,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -25177,10 +25249,10 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -25189,7 +25261,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -25249,7 +25321,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -25267,7 +25339,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -25290,16 +25362,16 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>15</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -25308,7 +25380,7 @@
         <v>19</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>16</v>
@@ -25406,19 +25478,19 @@
         <v>3</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25441,7 +25513,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -25534,7 +25606,7 @@
         <v>18</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <v>14</v>
@@ -25566,25 +25638,25 @@
         <v>23</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7">
         <v>22</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>18</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -25658,7 +25730,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>18</v>
@@ -25667,7 +25739,7 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -25702,22 +25774,22 @@
         <v>33</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>41</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>47</v>
       </c>
       <c r="H3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I3">
         <v>51</v>
@@ -25726,7 +25798,7 @@
         <v>42</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L3">
         <v>52</v>
@@ -25822,10 +25894,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>52</v>
@@ -25834,22 +25906,22 @@
         <v>32</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>40</v>
       </c>
       <c r="I6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6">
         <v>42</v>
       </c>
       <c r="K6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6">
         <v>23</v>
@@ -25863,34 +25935,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>132</v>
       </c>
       <c r="E7">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J7">
         <v>130</v>
       </c>
       <c r="K7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L7">
         <v>116</v>
@@ -26011,7 +26083,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -26115,7 +26187,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -26237,7 +26309,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -26326,7 +26398,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -26367,7 +26439,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -26376,7 +26448,7 @@
         <v>13</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -26483,7 +26555,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26547,7 +26619,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -26567,13 +26639,13 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -26585,7 +26657,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -26608,13 +26680,13 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>15</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -26626,13 +26698,13 @@
         <v>13</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L6">
         <v>10</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -26740,7 +26812,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -26798,7 +26870,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -26833,7 +26905,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -26937,7 +27009,7 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -26951,13 +27023,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>11</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -26972,7 +27044,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>7</v>
@@ -26981,7 +27053,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -27021,7 +27093,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -27062,7 +27134,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -27079,16 +27151,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>21</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>14</v>
@@ -27100,16 +27172,16 @@
         <v>12</v>
       </c>
       <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>28</v>
+      </c>
+      <c r="K7">
         <v>20</v>
       </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
+      <c r="L7">
         <v>18</v>
-      </c>
-      <c r="L7">
-        <v>17</v>
       </c>
       <c r="M7">
         <v>21</v>
@@ -27450,13 +27522,13 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -27491,13 +27563,13 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -27595,7 +27667,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -27618,7 +27690,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -27636,7 +27708,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -27688,7 +27760,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -27726,10 +27798,10 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -27747,7 +27819,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -27830,7 +27902,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -27913,7 +27985,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -28243,7 +28315,7 @@
         <v>19</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -28272,7 +28344,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -28281,7 +28353,7 @@
         <v>17</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>17</v>
@@ -28296,7 +28368,7 @@
         <v>21</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3">
         <v>15</v>
@@ -28331,7 +28403,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -28395,7 +28467,7 @@
         <v>48</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -28404,10 +28476,10 @@
         <v>24</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6">
         <v>15</v>
@@ -28430,31 +28502,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>97</v>
       </c>
       <c r="D7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I7">
         <v>61</v>
       </c>
       <c r="J7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K7">
         <v>80</v>
@@ -28574,6 +28646,9 @@
       <c r="C3">
         <v>2</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>2</v>
       </c>
@@ -28653,7 +28728,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -29047,7 +29122,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -29095,7 +29170,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -29133,7 +29208,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -29151,7 +29226,7 @@
         <v>3</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -29443,7 +29518,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -29552,7 +29627,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -29577,7 +29652,7 @@
 
 <file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -29589,9 +29664,10 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -29608,47 +29684,50 @@
         <v>2019</v>
       </c>
       <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2025</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="I3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -29656,7 +29735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -29669,11 +29748,14 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -29681,7 +29763,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -29696,9 +29778,12 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -29786,6 +29871,9 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>2</v>
       </c>
@@ -29827,7 +29915,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -29951,7 +30039,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -29986,7 +30074,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>3</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>722</v>
       </c>
       <c r="M2">
-        <v>668</v>
+        <v>684</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>734</v>
       </c>
       <c r="M3">
-        <v>744</v>
+        <v>752</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -974,7 +974,7 @@
         <v>219</v>
       </c>
       <c r="J4">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K4">
         <v>230</v>
@@ -983,7 +983,7 @@
         <v>214</v>
       </c>
       <c r="M4">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>55</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>769</v>
       </c>
       <c r="M6">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1097,7 +1097,7 @@
         <v>2856</v>
       </c>
       <c r="J7">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="K7">
         <v>3143</v>
@@ -1106,7 +1106,7 @@
         <v>2494</v>
       </c>
       <c r="M7">
-        <v>2230</v>
+        <v>2264</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1836,7 @@
         <v>40</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1877,7 +1877,7 @@
         <v>49</v>
       </c>
       <c r="M3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2041,7 +2041,7 @@
         <v>149</v>
       </c>
       <c r="M7">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +2148,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2189,7 +2189,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2344,7 +2344,7 @@
         <v>52</v>
       </c>
       <c r="M7">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2451,7 +2451,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2653,7 +2653,7 @@
         <v>104</v>
       </c>
       <c r="M7">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2841,6 +2841,9 @@
       <c r="L4">
         <v>3</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -2956,7 +2959,7 @@
         <v>32</v>
       </c>
       <c r="M7">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3518,7 +3521,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3559,7 +3562,7 @@
         <v>46</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3707,7 +3710,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3859,7 +3862,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4215,7 +4218,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4420,7 +4423,7 @@
         <v>82</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4461,7 +4464,7 @@
         <v>149</v>
       </c>
       <c r="M8">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4941,7 +4944,7 @@
         <v>62</v>
       </c>
       <c r="M20">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5064,7 +5067,7 @@
         <v>26</v>
       </c>
       <c r="M23">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5105,7 +5108,7 @@
         <v>4</v>
       </c>
       <c r="M24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5228,7 +5231,7 @@
         <v>32</v>
       </c>
       <c r="M27">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5292,7 +5295,7 @@
         <v>126</v>
       </c>
       <c r="M29">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5456,7 +5459,7 @@
         <v>104</v>
       </c>
       <c r="M33">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5579,7 +5582,7 @@
         <v>44</v>
       </c>
       <c r="M36">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5807,7 +5810,7 @@
         <v>86</v>
       </c>
       <c r="M42">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6053,7 +6056,7 @@
         <v>40</v>
       </c>
       <c r="M48">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6299,7 +6302,7 @@
         <v>47</v>
       </c>
       <c r="M54">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6340,7 +6343,7 @@
         <v>26</v>
       </c>
       <c r="M55">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6495,7 +6498,7 @@
         <v>2</v>
       </c>
       <c r="M59">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -6641,7 +6644,7 @@
         <v>10</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6723,7 +6726,7 @@
         <v>46</v>
       </c>
       <c r="M65">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6802,7 +6805,7 @@
         <v>89</v>
       </c>
       <c r="M67">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6843,7 +6846,7 @@
         <v>5</v>
       </c>
       <c r="M68">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6922,7 +6925,7 @@
         <v>8</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6963,7 +6966,7 @@
         <v>8</v>
       </c>
       <c r="M71">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7083,7 +7086,7 @@
         <v>2</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -7206,7 +7209,7 @@
         <v>18</v>
       </c>
       <c r="M77">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7247,7 +7250,7 @@
         <v>31</v>
       </c>
       <c r="M78">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7446,7 +7449,7 @@
         <v>52</v>
       </c>
       <c r="M83">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7692,7 +7695,7 @@
         <v>30</v>
       </c>
       <c r="M89">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7938,7 +7941,7 @@
         <v>32</v>
       </c>
       <c r="M95">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7970,7 +7973,7 @@
         <v>35</v>
       </c>
       <c r="J96">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K96">
         <v>49</v>
@@ -8102,7 +8105,7 @@
         <v>41</v>
       </c>
       <c r="M99">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8172,7 +8175,7 @@
         <v>2856</v>
       </c>
       <c r="J101">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="K101">
         <v>3143</v>
@@ -8181,7 +8184,7 @@
         <v>2494</v>
       </c>
       <c r="M101">
-        <v>2230</v>
+        <v>2264</v>
       </c>
     </row>
   </sheetData>
@@ -8728,7 +8731,7 @@
         <v>23</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8889,7 +8892,7 @@
         <v>89</v>
       </c>
       <c r="M7">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -9545,7 +9548,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9729,7 +9732,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -9836,7 +9839,7 @@
         <v>43</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9877,7 +9880,7 @@
         <v>39</v>
       </c>
       <c r="M3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10000,7 +10003,7 @@
         <v>34</v>
       </c>
       <c r="M6">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10041,7 +10044,7 @@
         <v>126</v>
       </c>
       <c r="M7">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -10148,7 +10151,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10323,7 +10326,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -12172,7 +12175,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12333,7 +12336,7 @@
         <v>86</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -12901,7 +12904,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13079,7 +13082,7 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13186,7 +13189,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13326,7 +13329,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13367,7 +13370,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -13538,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13625,7 +13628,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -13990,7 +13993,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14168,7 +14171,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -14348,7 +14351,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -14450,7 +14453,7 @@
         <v>35</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7">
         <v>49</v>
@@ -15828,7 +15831,7 @@
         <v>22</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15869,7 +15872,7 @@
         <v>62</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -16457,7 +16460,7 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16647,7 +16650,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -17209,7 +17212,7 @@
         <v>21</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17250,7 +17253,7 @@
         <v>28</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17411,7 +17414,7 @@
         <v>82</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -21143,7 +21146,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21184,7 +21187,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -21332,7 +21335,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21463,7 +21466,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -22081,6 +22084,9 @@
       <c r="K2">
         <v>3</v>
       </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
@@ -22198,7 +22204,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -22818,7 +22824,7 @@
         <v>11</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22999,7 +23005,7 @@
         <v>30</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -23373,7 +23379,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23507,7 +23513,7 @@
         <v>32</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -24751,7 +24757,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24864,7 +24870,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -26372,7 +26378,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -26454,7 +26460,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -27104,6 +27110,9 @@
       <c r="L5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -27184,7 +27193,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -29993,6 +30002,9 @@
       <c r="K2">
         <v>2</v>
       </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
@@ -30089,7 +30101,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="107">
   <si>
     <t>crime_category</t>
   </si>
@@ -901,7 +901,7 @@
         <v>778</v>
       </c>
       <c r="M2">
-        <v>741</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>802</v>
       </c>
       <c r="M3">
-        <v>808</v>
+        <v>828</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>228</v>
       </c>
       <c r="M4">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>56</v>
       </c>
       <c r="M5">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>842</v>
       </c>
       <c r="M6">
-        <v>610</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>2706</v>
       </c>
       <c r="M7">
-        <v>2431</v>
+        <v>2488</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +1893,7 @@
         <v>52</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2016,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2057,7 +2057,7 @@
         <v>166</v>
       </c>
       <c r="M7">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2205,7 +2205,7 @@
         <v>21</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2322,7 +2322,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2363,7 +2363,7 @@
         <v>54</v>
       </c>
       <c r="M7">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2511,7 @@
         <v>39</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2675,7 +2675,7 @@
         <v>114</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2782,7 +2782,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2940,7 +2940,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2981,7 +2981,7 @@
         <v>37</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3394,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3549,7 +3549,7 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3590,7 +3590,7 @@
         <v>56</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3849,7 +3849,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3890,7 +3890,7 @@
         <v>43</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4287,7 +4287,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4369,7 +4369,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4451,7 +4451,7 @@
         <v>87</v>
       </c>
       <c r="M7">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4492,7 +4492,7 @@
         <v>166</v>
       </c>
       <c r="M8">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4656,7 +4656,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4934,7 +4934,7 @@
         <v>86</v>
       </c>
       <c r="M19">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5016,7 +5016,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5180,7 +5180,7 @@
         <v>13</v>
       </c>
       <c r="M25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5326,7 +5326,7 @@
         <v>136</v>
       </c>
       <c r="M29">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5408,7 +5408,7 @@
         <v>29</v>
       </c>
       <c r="M31">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5490,7 +5490,7 @@
         <v>114</v>
       </c>
       <c r="M33">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5613,7 +5613,7 @@
         <v>49</v>
       </c>
       <c r="M36">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5844,7 +5844,7 @@
         <v>90</v>
       </c>
       <c r="M42">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5885,7 +5885,7 @@
         <v>19</v>
       </c>
       <c r="M43">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5926,7 +5926,7 @@
         <v>17</v>
       </c>
       <c r="M44">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6049,7 +6049,7 @@
         <v>22</v>
       </c>
       <c r="M47">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6090,7 +6090,7 @@
         <v>44</v>
       </c>
       <c r="M48">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6172,7 +6172,7 @@
         <v>21</v>
       </c>
       <c r="M50">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6254,7 +6254,7 @@
         <v>51</v>
       </c>
       <c r="M52">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6336,7 +6336,7 @@
         <v>51</v>
       </c>
       <c r="M54">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6576,7 +6576,7 @@
         <v>18</v>
       </c>
       <c r="M60">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6684,7 +6684,7 @@
         <v>12</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6766,7 +6766,7 @@
         <v>56</v>
       </c>
       <c r="M65">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6845,7 +6845,7 @@
         <v>96</v>
       </c>
       <c r="M67">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7170,7 +7170,7 @@
         <v>10</v>
       </c>
       <c r="M75">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7211,7 +7211,7 @@
         <v>35</v>
       </c>
       <c r="M76">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7334,7 +7334,7 @@
         <v>81</v>
       </c>
       <c r="M79">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7492,7 +7492,7 @@
         <v>54</v>
       </c>
       <c r="M83">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7574,7 +7574,7 @@
         <v>129</v>
       </c>
       <c r="M85">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7738,7 +7738,7 @@
         <v>34</v>
       </c>
       <c r="M89">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7943,7 +7943,7 @@
         <v>34</v>
       </c>
       <c r="M94">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7984,7 +7984,7 @@
         <v>37</v>
       </c>
       <c r="M95">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8066,7 +8066,7 @@
         <v>34</v>
       </c>
       <c r="M97">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8148,7 +8148,7 @@
         <v>43</v>
       </c>
       <c r="M99">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8230,7 +8230,7 @@
         <v>2706</v>
       </c>
       <c r="M101">
-        <v>2431</v>
+        <v>2488</v>
       </c>
     </row>
   </sheetData>
@@ -8480,7 +8480,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8629,7 +8629,7 @@
         <v>29</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -8736,7 +8736,7 @@
         <v>26</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8777,7 +8777,7 @@
         <v>26</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8897,7 +8897,7 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8938,7 +8938,7 @@
         <v>96</v>
       </c>
       <c r="M7">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -9638,7 +9638,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9781,7 +9781,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -9888,7 +9888,7 @@
         <v>46</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10052,7 +10052,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10093,7 +10093,7 @@
         <v>136</v>
       </c>
       <c r="M7">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -10334,7 +10334,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10375,7 +10375,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -10482,7 +10482,7 @@
         <v>28</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10523,7 +10523,7 @@
         <v>23</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10687,7 +10687,7 @@
         <v>86</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -10794,7 +10794,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10981,7 +10981,7 @@
         <v>17</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -11219,7 +11219,7 @@
         <v>18</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11260,7 +11260,7 @@
         <v>35</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -12239,7 +12239,7 @@
         <v>17</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12280,7 +12280,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12359,7 +12359,7 @@
         <v>42</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12400,7 +12400,7 @@
         <v>90</v>
       </c>
       <c r="M7">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -15016,7 +15016,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15057,7 +15057,7 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15164,7 +15164,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15366,7 +15366,7 @@
         <v>81</v>
       </c>
       <c r="M7">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -16598,7 +16598,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16750,7 +16750,7 @@
         <v>49</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -17325,7 +17325,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17407,7 +17407,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17527,7 +17527,7 @@
         <v>87</v>
       </c>
       <c r="M7">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -17907,7 +17907,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17948,7 +17948,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17977,7 +17977,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18070,7 +18070,7 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -18260,6 +18260,9 @@
       <c r="K5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -18337,7 +18340,7 @@
         <v>13</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -18485,7 +18488,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18619,7 +18622,7 @@
         <v>22</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -18764,7 +18767,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18866,7 +18869,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19403,7 +19406,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19444,7 +19447,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -21826,7 +21829,7 @@
         <v>27</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21867,7 +21870,7 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -22964,7 +22967,7 @@
         <v>11</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23005,7 +23008,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23148,7 +23151,7 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -23255,7 +23258,7 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23293,7 +23296,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23350,6 +23353,9 @@
       <c r="L5">
         <v>2</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -23389,7 +23395,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -24034,7 +24040,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24188,7 +24194,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -25431,7 +25437,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25553,7 +25559,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -25657,7 +25663,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25826,7 +25832,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -25974,7 +25980,7 @@
         <v>58</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26138,7 +26144,7 @@
         <v>129</v>
       </c>
       <c r="M7">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -28020,10 +28026,10 @@
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -28112,50 +28118,26 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -28167,28 +28149,60 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
       <c r="M6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -28535,7 +28549,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28576,7 +28590,7 @@
         <v>14</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28734,7 +28748,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -29090,7 +29104,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29203,7 +29217,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="D2">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="E2">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="F2">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="G2">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="H2">
-        <v>808</v>
+        <v>824</v>
       </c>
       <c r="I2">
-        <v>823</v>
+        <v>836</v>
       </c>
       <c r="J2">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="K2">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="L2">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="M2">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="C3">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="D3">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="E3">
-        <v>847</v>
+        <v>869</v>
       </c>
       <c r="F3">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="G3">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="H3">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="I3">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="J3">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="K3">
-        <v>943</v>
+        <v>961</v>
       </c>
       <c r="L3">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="M3">
-        <v>848</v>
+        <v>858</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>326</v>
+      </c>
+      <c r="C4">
+        <v>290</v>
+      </c>
+      <c r="D4">
+        <v>356</v>
+      </c>
+      <c r="E4">
+        <v>310</v>
+      </c>
+      <c r="F4">
+        <v>325</v>
+      </c>
+      <c r="G4">
         <v>324</v>
       </c>
-      <c r="C4">
-        <v>287</v>
-      </c>
-      <c r="D4">
-        <v>352</v>
-      </c>
-      <c r="E4">
-        <v>307</v>
-      </c>
-      <c r="F4">
-        <v>322</v>
-      </c>
-      <c r="G4">
-        <v>321</v>
-      </c>
       <c r="H4">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I4">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="J4">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K4">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="L4">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="M4">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,25 +994,25 @@
         <v>47</v>
       </c>
       <c r="C5">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D5">
         <v>99</v>
       </c>
       <c r="E5">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F5">
         <v>46</v>
       </c>
       <c r="G5">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>74</v>
@@ -1024,7 +1024,7 @@
         <v>59</v>
       </c>
       <c r="M5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1172</v>
+        <v>1187</v>
       </c>
       <c r="C6">
-        <v>1618</v>
+        <v>1639</v>
       </c>
       <c r="D6">
-        <v>1749</v>
+        <v>1768</v>
       </c>
       <c r="E6">
-        <v>1430</v>
+        <v>1456</v>
       </c>
       <c r="F6">
-        <v>1063</v>
+        <v>1086</v>
       </c>
       <c r="G6">
-        <v>1253</v>
+        <v>1271</v>
       </c>
       <c r="H6">
-        <v>1121</v>
+        <v>1141</v>
       </c>
       <c r="I6">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="J6">
-        <v>1380</v>
+        <v>1396</v>
       </c>
       <c r="K6">
-        <v>1287</v>
+        <v>1306</v>
       </c>
       <c r="L6">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="M6">
-        <v>627</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2741</v>
+        <v>2781</v>
       </c>
       <c r="C7">
-        <v>3530</v>
+        <v>3577</v>
       </c>
       <c r="D7">
-        <v>3888</v>
+        <v>3934</v>
       </c>
       <c r="E7">
-        <v>3384</v>
+        <v>3447</v>
       </c>
       <c r="F7">
-        <v>3072</v>
+        <v>3120</v>
       </c>
       <c r="G7">
-        <v>3346</v>
+        <v>3392</v>
       </c>
       <c r="H7">
-        <v>3072</v>
+        <v>3125</v>
       </c>
       <c r="I7">
-        <v>3231</v>
+        <v>3284</v>
       </c>
       <c r="J7">
-        <v>3651</v>
+        <v>3705</v>
       </c>
       <c r="K7">
-        <v>3549</v>
+        <v>3598</v>
       </c>
       <c r="L7">
-        <v>2828</v>
+        <v>2874</v>
       </c>
       <c r="M7">
-        <v>2526</v>
+        <v>2563</v>
       </c>
     </row>
   </sheetData>
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -1349,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1596,10 +1596,10 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -1695,7 +1695,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>18</v>
@@ -1730,13 +1730,13 @@
         <v>43</v>
       </c>
       <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>35</v>
+      </c>
+      <c r="H7">
         <v>29</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>27</v>
       </c>
       <c r="I7">
         <v>38</v>
@@ -1745,7 +1745,7 @@
         <v>33</v>
       </c>
       <c r="K7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7">
         <v>37</v>
@@ -1828,7 +1828,7 @@
         <v>41</v>
       </c>
       <c r="C2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>59</v>
@@ -1837,25 +1837,25 @@
         <v>49</v>
       </c>
       <c r="F2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>57</v>
       </c>
       <c r="I2">
+        <v>59</v>
+      </c>
+      <c r="J2">
+        <v>71</v>
+      </c>
+      <c r="K2">
         <v>58</v>
       </c>
-      <c r="J2">
-        <v>70</v>
-      </c>
-      <c r="K2">
-        <v>57</v>
-      </c>
       <c r="L2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M2">
         <v>55</v>
@@ -1875,31 +1875,31 @@
         <v>70</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H3">
         <v>57</v>
       </c>
       <c r="I3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1928,7 +1928,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4">
         <v>14</v>
@@ -1951,7 +1951,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>14</v>
@@ -1981,7 +1981,7 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1992,7 +1992,7 @@
         <v>79</v>
       </c>
       <c r="C6">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D6">
         <v>127</v>
@@ -2001,25 +2001,25 @@
         <v>113</v>
       </c>
       <c r="F6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6">
         <v>121</v>
       </c>
       <c r="H6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K6">
         <v>68</v>
       </c>
       <c r="L6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6">
         <v>41</v>
@@ -2033,37 +2033,37 @@
         <v>173</v>
       </c>
       <c r="C7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D7">
         <v>290</v>
       </c>
       <c r="E7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M7">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2158,10 +2158,10 @@
         <v>19</v>
       </c>
       <c r="I2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2">
         <v>33</v>
@@ -2199,16 +2199,16 @@
         <v>21</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3">
         <v>19</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3">
         <v>26</v>
@@ -2310,7 +2310,7 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>16</v>
@@ -2351,22 +2351,22 @@
         <v>57</v>
       </c>
       <c r="G7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7">
         <v>63</v>
       </c>
       <c r="I7">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K7">
         <v>63</v>
       </c>
       <c r="L7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M7">
         <v>59</v>
@@ -2443,7 +2443,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>27</v>
@@ -2452,10 +2452,10 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
         <v>31</v>
@@ -2467,16 +2467,16 @@
         <v>33</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2493,28 +2493,28 @@
         <v>48</v>
       </c>
       <c r="E3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3">
         <v>57</v>
       </c>
       <c r="G3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M3">
         <v>29</v>
@@ -2531,7 +2531,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -2607,34 +2607,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6">
         <v>62</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H6">
         <v>45</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J6">
         <v>70</v>
       </c>
       <c r="K6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6">
         <v>47</v>
@@ -2648,40 +2648,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E7">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M7">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2764,7 +2764,7 @@
         <v>11</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -2785,7 +2785,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2">
         <v>15</v>
@@ -2805,7 +2805,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         <v>19</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3">
         <v>17</v>
@@ -2934,7 +2934,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>21</v>
@@ -2963,7 +2963,7 @@
         <v>66</v>
       </c>
       <c r="E7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F7">
         <v>54</v>
@@ -2972,10 +2972,10 @@
         <v>65</v>
       </c>
       <c r="H7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J7">
         <v>69</v>
@@ -2984,7 +2984,7 @@
         <v>60</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7">
         <v>41</v>
@@ -3079,19 +3079,19 @@
         <v>25</v>
       </c>
       <c r="H2">
+        <v>29</v>
+      </c>
+      <c r="I2">
+        <v>32</v>
+      </c>
+      <c r="J2">
+        <v>35</v>
+      </c>
+      <c r="K2">
         <v>26</v>
       </c>
-      <c r="I2">
-        <v>31</v>
-      </c>
-      <c r="J2">
-        <v>33</v>
-      </c>
-      <c r="K2">
-        <v>25</v>
-      </c>
       <c r="L2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2">
         <v>30</v>
@@ -3114,16 +3114,16 @@
         <v>34</v>
       </c>
       <c r="F3">
+        <v>32</v>
+      </c>
+      <c r="G3">
         <v>31</v>
       </c>
-      <c r="G3">
-        <v>29</v>
-      </c>
       <c r="H3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>41</v>
@@ -3132,10 +3132,10 @@
         <v>37</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>45</v>
@@ -3260,10 +3260,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7">
         <v>142</v>
@@ -3272,28 +3272,28 @@
         <v>105</v>
       </c>
       <c r="F7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I7">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M7">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3379,22 +3379,22 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>14</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2">
         <v>18</v>
@@ -3414,10 +3414,10 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -3426,7 +3426,7 @@
         <v>12</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>24</v>
@@ -3455,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -3470,7 +3470,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -3543,7 +3543,7 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>41</v>
@@ -3569,28 +3569,28 @@
         <v>74</v>
       </c>
       <c r="D7">
+        <v>83</v>
+      </c>
+      <c r="E7">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>55</v>
+      </c>
+      <c r="G7">
+        <v>54</v>
+      </c>
+      <c r="H7">
+        <v>53</v>
+      </c>
+      <c r="I7">
         <v>81</v>
       </c>
-      <c r="E7">
-        <v>74</v>
-      </c>
-      <c r="F7">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>53</v>
-      </c>
-      <c r="H7">
-        <v>51</v>
-      </c>
-      <c r="I7">
-        <v>78</v>
-      </c>
       <c r="J7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>58</v>
@@ -3711,10 +3711,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>26</v>
@@ -3741,7 +3741,7 @@
         <v>18</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <v>23</v>
@@ -3764,10 +3764,10 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3776,7 +3776,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>3</v>
@@ -3796,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -3822,7 +3822,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -3846,7 +3846,7 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>19</v>
@@ -3855,7 +3855,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3863,22 +3863,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>78</v>
       </c>
       <c r="E7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>65</v>
@@ -3887,16 +3887,16 @@
         <v>61</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K7">
         <v>62</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M7">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4029,7 +4029,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -4089,7 +4089,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -4104,7 +4104,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4130,10 +4130,10 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7">
         <v>14</v>
@@ -4145,7 +4145,7 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4222,34 +4222,34 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>17</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>30</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2">
         <v>31</v>
       </c>
       <c r="K2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2">
         <v>23</v>
@@ -4272,7 +4272,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -4284,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -4357,7 +4357,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -4375,7 +4375,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4386,7 +4386,7 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>52</v>
@@ -4424,40 +4424,40 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7">
+        <v>110</v>
+      </c>
+      <c r="I7">
         <v>109</v>
-      </c>
-      <c r="I7">
-        <v>106</v>
       </c>
       <c r="J7">
         <v>98</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L7">
         <v>93</v>
       </c>
       <c r="M7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4468,37 +4468,37 @@
         <v>173</v>
       </c>
       <c r="C8">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D8">
         <v>290</v>
       </c>
       <c r="E8">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F8">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I8">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J8">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K8">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L8">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M8">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4509,10 +4509,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9">
         <v>14</v>
@@ -4533,13 +4533,13 @@
         <v>25</v>
       </c>
       <c r="K9">
+        <v>18</v>
+      </c>
+      <c r="L9">
         <v>17</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>16</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4547,19 +4547,19 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>32</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>30</v>
@@ -4568,7 +4568,7 @@
         <v>28</v>
       </c>
       <c r="I10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10">
         <v>24</v>
@@ -4591,13 +4591,13 @@
         <v>50</v>
       </c>
       <c r="C11">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11">
         <v>71</v>
       </c>
       <c r="E11">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F11">
         <v>51</v>
@@ -4609,13 +4609,13 @@
         <v>46</v>
       </c>
       <c r="I11">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K11">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L11">
         <v>46</v>
@@ -4717,10 +4717,10 @@
         <v>16</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H14">
         <v>16</v>
@@ -4735,7 +4735,7 @@
         <v>17</v>
       </c>
       <c r="L14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>12</v>
@@ -4749,10 +4749,10 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E15">
         <v>41</v>
@@ -4770,10 +4770,10 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15">
         <v>20</v>
@@ -4825,10 +4825,10 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -4843,7 +4843,7 @@
         <v>11</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17">
         <v>3</v>
@@ -4872,13 +4872,13 @@
         <v>14</v>
       </c>
       <c r="D18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E18">
         <v>19</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>12</v>
@@ -4896,7 +4896,7 @@
         <v>28</v>
       </c>
       <c r="L18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M18">
         <v>18</v>
@@ -4907,40 +4907,40 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19">
         <v>92</v>
       </c>
       <c r="E19">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G19">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H19">
         <v>80</v>
       </c>
       <c r="I19">
+        <v>87</v>
+      </c>
+      <c r="J19">
+        <v>123</v>
+      </c>
+      <c r="K19">
+        <v>94</v>
+      </c>
+      <c r="L19">
+        <v>92</v>
+      </c>
+      <c r="M19">
         <v>86</v>
-      </c>
-      <c r="J19">
-        <v>122</v>
-      </c>
-      <c r="K19">
-        <v>93</v>
-      </c>
-      <c r="L19">
-        <v>91</v>
-      </c>
-      <c r="M19">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4948,25 +4948,25 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E20">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F20">
         <v>109</v>
       </c>
       <c r="G20">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H20">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I20">
         <v>90</v>
@@ -4975,13 +4975,13 @@
         <v>81</v>
       </c>
       <c r="K20">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L20">
         <v>77</v>
       </c>
       <c r="M20">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4995,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -5039,7 +5039,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>9</v>
@@ -5074,7 +5074,7 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>48</v>
@@ -5083,7 +5083,7 @@
         <v>39</v>
       </c>
       <c r="F23">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23">
         <v>40</v>
@@ -5092,7 +5092,7 @@
         <v>25</v>
       </c>
       <c r="I23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23">
         <v>33</v>
@@ -5104,7 +5104,7 @@
         <v>28</v>
       </c>
       <c r="M23">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5115,7 +5115,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -5159,10 +5159,10 @@
         <v>12</v>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -5177,7 +5177,7 @@
         <v>18</v>
       </c>
       <c r="J25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K25">
         <v>17</v>
@@ -5203,7 +5203,7 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -5218,7 +5218,7 @@
         <v>4</v>
       </c>
       <c r="J26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -5235,7 +5235,7 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27">
         <v>24</v>
@@ -5244,10 +5244,10 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G27">
         <v>29</v>
@@ -5256,7 +5256,7 @@
         <v>24</v>
       </c>
       <c r="I27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J27">
         <v>16</v>
@@ -5268,7 +5268,7 @@
         <v>34</v>
       </c>
       <c r="M27">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5302,40 +5302,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C29">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D29">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E29">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F29">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G29">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H29">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I29">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="J29">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K29">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L29">
         <v>137</v>
       </c>
       <c r="M29">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5361,10 +5361,10 @@
         <v>11</v>
       </c>
       <c r="H30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30">
         <v>14</v>
@@ -5376,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="M30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5390,22 +5390,22 @@
         <v>54</v>
       </c>
       <c r="D31">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31">
         <v>35</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H31">
         <v>19</v>
       </c>
       <c r="I31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J31">
         <v>24</v>
@@ -5414,7 +5414,7 @@
         <v>38</v>
       </c>
       <c r="L31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M31">
         <v>28</v>
@@ -5452,7 +5452,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -5466,40 +5466,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C33">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D33">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E33">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F33">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G33">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H33">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I33">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J33">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K33">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L33">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M33">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5507,7 +5507,7 @@
         <v>40</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>16</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="J34">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K34">
         <v>22</v>
@@ -5563,7 +5563,7 @@
         <v>3</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -5589,7 +5589,7 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <v>38</v>
@@ -5604,10 +5604,10 @@
         <v>39</v>
       </c>
       <c r="G36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I36">
         <v>44</v>
@@ -5619,7 +5619,7 @@
         <v>43</v>
       </c>
       <c r="L36">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M36">
         <v>29</v>
@@ -5630,10 +5630,10 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D37">
         <v>142</v>
@@ -5642,28 +5642,28 @@
         <v>105</v>
       </c>
       <c r="F37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G37">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H37">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I37">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J37">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K37">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L37">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M37">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5738,10 +5738,10 @@
         <v>46</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -5756,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="H40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>3</v>
@@ -5820,40 +5820,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C42">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D42">
         <v>163</v>
       </c>
       <c r="E42">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F42">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G42">
         <v>111</v>
       </c>
       <c r="H42">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I42">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J42">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K42">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L42">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M42">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5861,7 +5861,7 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C43">
         <v>14</v>
@@ -5920,7 +5920,7 @@
         <v>37</v>
       </c>
       <c r="H44">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I44">
         <v>26</v>
@@ -5929,13 +5929,13 @@
         <v>27</v>
       </c>
       <c r="K44">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L44">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M44">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6002,7 +6002,7 @@
         <v>12</v>
       </c>
       <c r="H46">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I46">
         <v>8</v>
@@ -6031,13 +6031,13 @@
         <v>22</v>
       </c>
       <c r="D47">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E47">
         <v>18</v>
       </c>
       <c r="F47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G47">
         <v>14</v>
@@ -6046,10 +6046,10 @@
         <v>27</v>
       </c>
       <c r="I47">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J47">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K47">
         <v>25</v>
@@ -6058,7 +6058,7 @@
         <v>24</v>
       </c>
       <c r="M47">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6069,25 +6069,25 @@
         <v>22</v>
       </c>
       <c r="C48">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D48">
         <v>34</v>
       </c>
       <c r="E48">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F48">
         <v>31</v>
       </c>
       <c r="G48">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H48">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I48">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J48">
         <v>23</v>
@@ -6096,7 +6096,7 @@
         <v>34</v>
       </c>
       <c r="L48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M48">
         <v>39</v>
@@ -6116,13 +6116,13 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F49">
         <v>13</v>
       </c>
       <c r="G49">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H49">
         <v>11</v>
@@ -6160,10 +6160,10 @@
         <v>19</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50">
         <v>14</v>
@@ -6175,10 +6175,10 @@
         <v>21</v>
       </c>
       <c r="K50">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M50">
         <v>11</v>
@@ -6195,16 +6195,16 @@
         <v>32</v>
       </c>
       <c r="D51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E51">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F51">
         <v>36</v>
       </c>
       <c r="G51">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H51">
         <v>43</v>
@@ -6219,7 +6219,7 @@
         <v>49</v>
       </c>
       <c r="L51">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M51">
         <v>31</v>
@@ -6230,13 +6230,13 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C52">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D52">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E52">
         <v>76</v>
@@ -6245,25 +6245,25 @@
         <v>64</v>
       </c>
       <c r="G52">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H52">
         <v>56</v>
       </c>
       <c r="I52">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J52">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K52">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L52">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M52">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6283,13 +6283,13 @@
         <v>43</v>
       </c>
       <c r="F53">
+        <v>30</v>
+      </c>
+      <c r="G53">
+        <v>35</v>
+      </c>
+      <c r="H53">
         <v>29</v>
-      </c>
-      <c r="G53">
-        <v>34</v>
-      </c>
-      <c r="H53">
-        <v>27</v>
       </c>
       <c r="I53">
         <v>38</v>
@@ -6298,7 +6298,7 @@
         <v>33</v>
       </c>
       <c r="K53">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L53">
         <v>37</v>
@@ -6315,19 +6315,19 @@
         <v>44</v>
       </c>
       <c r="C54">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D54">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E54">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F54">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G54">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H54">
         <v>32</v>
@@ -6336,16 +6336,16 @@
         <v>73</v>
       </c>
       <c r="J54">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K54">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L54">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M54">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6359,13 +6359,13 @@
         <v>26</v>
       </c>
       <c r="D55">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E55">
         <v>36</v>
       </c>
       <c r="F55">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G55">
         <v>32</v>
@@ -6377,13 +6377,13 @@
         <v>36</v>
       </c>
       <c r="J55">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K55">
         <v>32</v>
       </c>
       <c r="L55">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M55">
         <v>35</v>
@@ -6409,7 +6409,7 @@
         <v>5</v>
       </c>
       <c r="G56">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H56">
         <v>2</v>
@@ -6441,7 +6441,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E57">
         <v>11</v>
@@ -6459,10 +6459,10 @@
         <v>11</v>
       </c>
       <c r="J57">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L57">
         <v>16</v>
@@ -6514,7 +6514,7 @@
         <v>3</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D59">
         <v>8</v>
@@ -6532,7 +6532,7 @@
         <v>4</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J59">
         <v>6</v>
@@ -6561,16 +6561,16 @@
         <v>33</v>
       </c>
       <c r="E60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F60">
         <v>16</v>
       </c>
       <c r="G60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H60">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I60">
         <v>13</v>
@@ -6579,7 +6579,7 @@
         <v>20</v>
       </c>
       <c r="K60">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L60">
         <v>18</v>
@@ -6608,7 +6608,7 @@
         <v>3</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -6620,7 +6620,7 @@
         <v>6</v>
       </c>
       <c r="K61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L61">
         <v>2</v>
@@ -6660,7 +6660,7 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C63">
         <v>72</v>
@@ -6678,7 +6678,7 @@
         <v>53</v>
       </c>
       <c r="H63">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I63">
         <v>40</v>
@@ -6690,10 +6690,10 @@
         <v>32</v>
       </c>
       <c r="L63">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6701,7 +6701,7 @@
         <v>70</v>
       </c>
       <c r="B64">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C64">
         <v>23</v>
@@ -6722,7 +6722,7 @@
         <v>16</v>
       </c>
       <c r="I64">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J64">
         <v>20</v>
@@ -6748,28 +6748,28 @@
         <v>74</v>
       </c>
       <c r="D65">
+        <v>83</v>
+      </c>
+      <c r="E65">
+        <v>75</v>
+      </c>
+      <c r="F65">
+        <v>55</v>
+      </c>
+      <c r="G65">
+        <v>54</v>
+      </c>
+      <c r="H65">
+        <v>53</v>
+      </c>
+      <c r="I65">
         <v>81</v>
       </c>
-      <c r="E65">
-        <v>74</v>
-      </c>
-      <c r="F65">
-        <v>54</v>
-      </c>
-      <c r="G65">
-        <v>53</v>
-      </c>
-      <c r="H65">
-        <v>51</v>
-      </c>
-      <c r="I65">
-        <v>78</v>
-      </c>
       <c r="J65">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K65">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L65">
         <v>58</v>
@@ -6824,37 +6824,37 @@
         <v>104</v>
       </c>
       <c r="C67">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D67">
         <v>155</v>
       </c>
       <c r="E67">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F67">
         <v>122</v>
       </c>
       <c r="G67">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H67">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I67">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J67">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K67">
         <v>146</v>
       </c>
       <c r="L67">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M67">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6930,7 +6930,7 @@
         <v>8</v>
       </c>
       <c r="K69">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L69">
         <v>7</v>
@@ -6968,7 +6968,7 @@
         <v>9</v>
       </c>
       <c r="K70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L70">
         <v>10</v>
@@ -6997,13 +6997,13 @@
         <v>8</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H71">
         <v>16</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71">
         <v>14</v>
@@ -7032,16 +7032,16 @@
         <v>13</v>
       </c>
       <c r="E72">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F72">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G72">
         <v>18</v>
       </c>
       <c r="H72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I72">
         <v>9</v>
@@ -7050,7 +7050,7 @@
         <v>14</v>
       </c>
       <c r="K72">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L72">
         <v>12</v>
@@ -7067,10 +7067,10 @@
         <v>19</v>
       </c>
       <c r="C73">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D73">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E73">
         <v>34</v>
@@ -7079,7 +7079,7 @@
         <v>33</v>
       </c>
       <c r="G73">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H73">
         <v>34</v>
@@ -7088,16 +7088,16 @@
         <v>34</v>
       </c>
       <c r="J73">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K73">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L73">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M73">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7138,7 +7138,7 @@
         <v>2</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -7158,7 +7158,7 @@
         <v>9</v>
       </c>
       <c r="F75">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -7176,10 +7176,10 @@
         <v>10</v>
       </c>
       <c r="L75">
+        <v>12</v>
+      </c>
+      <c r="M75">
         <v>11</v>
-      </c>
-      <c r="M75">
-        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7187,7 +7187,7 @@
         <v>82</v>
       </c>
       <c r="B76">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C76">
         <v>43</v>
@@ -7205,22 +7205,22 @@
         <v>56</v>
       </c>
       <c r="H76">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I76">
         <v>48</v>
       </c>
       <c r="J76">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K76">
         <v>50</v>
       </c>
       <c r="L76">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M76">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7231,7 +7231,7 @@
         <v>14</v>
       </c>
       <c r="C77">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D77">
         <v>20</v>
@@ -7275,34 +7275,34 @@
         <v>47</v>
       </c>
       <c r="D78">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E78">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F78">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G78">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H78">
         <v>51</v>
       </c>
       <c r="I78">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J78">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K78">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L78">
         <v>39</v>
       </c>
       <c r="M78">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7310,13 +7310,13 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C79">
         <v>103</v>
       </c>
       <c r="D79">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E79">
         <v>86</v>
@@ -7325,7 +7325,7 @@
         <v>88</v>
       </c>
       <c r="G79">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H79">
         <v>110</v>
@@ -7334,16 +7334,16 @@
         <v>87</v>
       </c>
       <c r="J79">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K79">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L79">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M79">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7357,13 +7357,13 @@
         <v>8</v>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E80">
         <v>10</v>
       </c>
       <c r="F80">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G80">
         <v>12</v>
@@ -7378,13 +7378,13 @@
         <v>10</v>
       </c>
       <c r="K80">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L80">
         <v>11</v>
       </c>
       <c r="M80">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7442,7 +7442,7 @@
         <v>7</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G82">
         <v>5</v>
@@ -7483,22 +7483,22 @@
         <v>57</v>
       </c>
       <c r="G83">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H83">
         <v>63</v>
       </c>
       <c r="I83">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J83">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K83">
         <v>63</v>
       </c>
       <c r="L83">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M83">
         <v>59</v>
@@ -7509,19 +7509,19 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84">
         <v>26</v>
       </c>
       <c r="D84">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E84">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F84">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G84">
         <v>29</v>
@@ -7553,34 +7553,34 @@
         <v>136</v>
       </c>
       <c r="C85">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D85">
+        <v>150</v>
+      </c>
+      <c r="E85">
+        <v>115</v>
+      </c>
+      <c r="F85">
         <v>146</v>
-      </c>
-      <c r="E85">
-        <v>113</v>
-      </c>
-      <c r="F85">
-        <v>143</v>
       </c>
       <c r="G85">
         <v>145</v>
       </c>
       <c r="H85">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I85">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J85">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K85">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L85">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M85">
         <v>128</v>
@@ -7606,10 +7606,10 @@
         <v>18</v>
       </c>
       <c r="G86">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H86">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I86">
         <v>16</v>
@@ -7673,7 +7673,7 @@
         <v>94</v>
       </c>
       <c r="B88">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C88">
         <v>41</v>
@@ -7685,10 +7685,10 @@
         <v>38</v>
       </c>
       <c r="F88">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G88">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H88">
         <v>32</v>
@@ -7697,10 +7697,10 @@
         <v>26</v>
       </c>
       <c r="J88">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K88">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L88">
         <v>42</v>
@@ -7726,13 +7726,13 @@
         <v>27</v>
       </c>
       <c r="F89">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G89">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H89">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I89">
         <v>26</v>
@@ -7741,7 +7741,7 @@
         <v>44</v>
       </c>
       <c r="K89">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L89">
         <v>36</v>
@@ -7755,19 +7755,19 @@
         <v>96</v>
       </c>
       <c r="B90">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C90">
         <v>55</v>
       </c>
       <c r="D90">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E90">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F90">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G90">
         <v>30</v>
@@ -7776,10 +7776,10 @@
         <v>35</v>
       </c>
       <c r="I90">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J90">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K90">
         <v>30</v>
@@ -7796,10 +7796,10 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C91">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D91">
         <v>50</v>
@@ -7814,16 +7814,16 @@
         <v>40</v>
       </c>
       <c r="H91">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L91">
         <v>38</v>
@@ -7855,13 +7855,13 @@
         <v>13</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I92">
         <v>10</v>
       </c>
       <c r="J92">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K92">
         <v>15</v>
@@ -7878,7 +7878,7 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93">
         <v>23</v>
@@ -7925,10 +7925,10 @@
         <v>21</v>
       </c>
       <c r="D94">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E94">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F94">
         <v>19</v>
@@ -7937,19 +7937,19 @@
         <v>24</v>
       </c>
       <c r="H94">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I94">
         <v>29</v>
       </c>
       <c r="J94">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K94">
         <v>42</v>
       </c>
       <c r="L94">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M94">
         <v>30</v>
@@ -7969,7 +7969,7 @@
         <v>66</v>
       </c>
       <c r="E95">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F95">
         <v>54</v>
@@ -7978,10 +7978,10 @@
         <v>65</v>
       </c>
       <c r="H95">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I95">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J95">
         <v>69</v>
@@ -7990,7 +7990,7 @@
         <v>60</v>
       </c>
       <c r="L95">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M95">
         <v>41</v>
@@ -8001,7 +8001,7 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C96">
         <v>36</v>
@@ -8010,25 +8010,25 @@
         <v>34</v>
       </c>
       <c r="E96">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F96">
         <v>35</v>
       </c>
       <c r="G96">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H96">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I96">
         <v>36</v>
       </c>
       <c r="J96">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K96">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L96">
         <v>26</v>
@@ -8060,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="H97">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I97">
         <v>35</v>
@@ -8086,16 +8086,16 @@
         <v>16</v>
       </c>
       <c r="C98">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D98">
         <v>29</v>
       </c>
       <c r="E98">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F98">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G98">
         <v>15</v>
@@ -8124,22 +8124,22 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C99">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D99">
         <v>78</v>
       </c>
       <c r="E99">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F99">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G99">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H99">
         <v>65</v>
@@ -8148,16 +8148,16 @@
         <v>61</v>
       </c>
       <c r="J99">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K99">
         <v>62</v>
       </c>
       <c r="L99">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M99">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8174,7 +8174,7 @@
         <v>5</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -8192,7 +8192,7 @@
         <v>5</v>
       </c>
       <c r="K100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8206,40 +8206,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2741</v>
+        <v>2781</v>
       </c>
       <c r="C101">
-        <v>3530</v>
+        <v>3577</v>
       </c>
       <c r="D101">
-        <v>3888</v>
+        <v>3934</v>
       </c>
       <c r="E101">
-        <v>3384</v>
+        <v>3447</v>
       </c>
       <c r="F101">
-        <v>3072</v>
+        <v>3120</v>
       </c>
       <c r="G101">
-        <v>3346</v>
+        <v>3392</v>
       </c>
       <c r="H101">
-        <v>3072</v>
+        <v>3125</v>
       </c>
       <c r="I101">
-        <v>3231</v>
+        <v>3284</v>
       </c>
       <c r="J101">
-        <v>3651</v>
+        <v>3705</v>
       </c>
       <c r="K101">
-        <v>3549</v>
+        <v>3598</v>
       </c>
       <c r="L101">
-        <v>2828</v>
+        <v>2874</v>
       </c>
       <c r="M101">
-        <v>2526</v>
+        <v>2563</v>
       </c>
     </row>
   </sheetData>
@@ -8436,7 +8436,7 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>14</v>
@@ -8445,7 +8445,7 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>8</v>
@@ -8570,16 +8570,16 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>19</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -8611,22 +8611,22 @@
         <v>54</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>35</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7">
         <v>19</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -8635,7 +8635,7 @@
         <v>38</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M7">
         <v>28</v>
@@ -8721,7 +8721,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>33</v>
@@ -8730,22 +8730,22 @@
         <v>38</v>
       </c>
       <c r="H2">
+        <v>36</v>
+      </c>
+      <c r="I2">
         <v>33</v>
       </c>
-      <c r="I2">
-        <v>32</v>
-      </c>
       <c r="J2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2">
         <v>43</v>
       </c>
       <c r="L2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8756,19 +8756,19 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3">
         <v>57</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>48</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>28</v>
@@ -8783,10 +8783,10 @@
         <v>43</v>
       </c>
       <c r="L3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8818,7 +8818,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -8838,7 +8838,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -8876,13 +8876,13 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6">
         <v>61</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6">
         <v>35</v>
@@ -8894,10 +8894,10 @@
         <v>47</v>
       </c>
       <c r="I6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>49</v>
@@ -8906,7 +8906,7 @@
         <v>35</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8917,37 +8917,37 @@
         <v>104</v>
       </c>
       <c r="C7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D7">
         <v>155</v>
       </c>
       <c r="E7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F7">
         <v>122</v>
       </c>
       <c r="G7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K7">
         <v>146</v>
       </c>
       <c r="L7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M7">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -9068,13 +9068,13 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>12</v>
@@ -9152,7 +9152,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>13</v>
@@ -9193,19 +9193,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>26</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7">
         <v>29</v>
@@ -9353,7 +9353,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -9382,7 +9382,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -9434,7 +9434,7 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -9475,13 +9475,13 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>13</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>11</v>
@@ -9588,7 +9588,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -9661,7 +9661,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -9679,7 +9679,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -9719,16 +9719,16 @@
         <v>27</v>
       </c>
       <c r="C6">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>56</v>
+      </c>
+      <c r="F6">
         <v>34</v>
-      </c>
-      <c r="D6">
-        <v>27</v>
-      </c>
-      <c r="E6">
-        <v>54</v>
-      </c>
-      <c r="F6">
-        <v>32</v>
       </c>
       <c r="G6">
         <v>35</v>
@@ -9740,16 +9740,16 @@
         <v>35</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9760,19 +9760,19 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7">
         <v>32</v>
@@ -9781,16 +9781,16 @@
         <v>73</v>
       </c>
       <c r="J7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K7">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -9864,28 +9864,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>45</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J2">
         <v>54</v>
@@ -9905,31 +9905,31 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>70</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K3">
         <v>48</v>
@@ -9938,7 +9938,7 @@
         <v>45</v>
       </c>
       <c r="M3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9949,7 +9949,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>15</v>
@@ -9996,7 +9996,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10028,34 +10028,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>93</v>
       </c>
       <c r="D6">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6">
         <v>58</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6">
         <v>49</v>
       </c>
       <c r="I6">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J6">
         <v>50</v>
       </c>
       <c r="K6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6">
         <v>36</v>
@@ -10069,40 +10069,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D7">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F7">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="J7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L7">
         <v>137</v>
       </c>
       <c r="M7">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -10191,7 +10191,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -10226,7 +10226,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>8</v>
@@ -10235,7 +10235,7 @@
         <v>5</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>5</v>
@@ -10273,7 +10273,7 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -10313,7 +10313,7 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -10331,7 +10331,7 @@
         <v>21</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <v>11</v>
@@ -10340,7 +10340,7 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
         <v>19</v>
@@ -10354,25 +10354,25 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>34</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>31</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>23</v>
@@ -10381,7 +10381,7 @@
         <v>34</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M7">
         <v>39</v>
@@ -10461,7 +10461,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>27</v>
@@ -10485,7 +10485,7 @@
         <v>23</v>
       </c>
       <c r="K2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2">
         <v>29</v>
@@ -10499,7 +10499,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -10529,7 +10529,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3">
         <v>32</v>
@@ -10573,7 +10573,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10590,7 +10590,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -10625,7 +10625,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
         <v>34</v>
@@ -10634,19 +10634,19 @@
         <v>26</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>28</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K6">
         <v>26</v>
@@ -10655,7 +10655,7 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10663,40 +10663,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D7">
         <v>92</v>
       </c>
       <c r="E7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H7">
         <v>80</v>
       </c>
       <c r="I7">
+        <v>87</v>
+      </c>
+      <c r="J7">
+        <v>123</v>
+      </c>
+      <c r="K7">
+        <v>94</v>
+      </c>
+      <c r="L7">
+        <v>92</v>
+      </c>
+      <c r="M7">
         <v>86</v>
-      </c>
-      <c r="J7">
-        <v>122</v>
-      </c>
-      <c r="K7">
-        <v>93</v>
-      </c>
-      <c r="L7">
-        <v>91</v>
-      </c>
-      <c r="M7">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -10838,7 +10838,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -10934,7 +10934,7 @@
         <v>16</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -10946,10 +10946,10 @@
         <v>16</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10975,7 +10975,7 @@
         <v>37</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
         <v>26</v>
@@ -10984,13 +10984,13 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -11082,13 +11082,13 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>7</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -11105,7 +11105,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -11173,7 +11173,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -11228,10 +11228,10 @@
         <v>28</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11239,7 +11239,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>43</v>
@@ -11257,22 +11257,22 @@
         <v>56</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I7">
         <v>48</v>
       </c>
       <c r="J7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K7">
         <v>50</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -11358,7 +11358,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -11451,6 +11451,9 @@
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
       <c r="M4">
         <v>2</v>
       </c>
@@ -11492,7 +11495,7 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -11527,10 +11530,10 @@
         <v>16</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -11545,7 +11548,7 @@
         <v>17</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -11753,7 +11756,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -11794,7 +11797,7 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>52</v>
@@ -12195,19 +12198,19 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2">
+        <v>29</v>
+      </c>
+      <c r="J2">
         <v>28</v>
-      </c>
-      <c r="J2">
-        <v>27</v>
       </c>
       <c r="K2">
         <v>25</v>
       </c>
       <c r="L2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -12221,25 +12224,25 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>29</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <v>35</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>23</v>
@@ -12251,7 +12254,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12338,10 +12341,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>86</v>
@@ -12356,7 +12359,7 @@
         <v>42</v>
       </c>
       <c r="H6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I6">
         <v>25</v>
@@ -12365,7 +12368,7 @@
         <v>96</v>
       </c>
       <c r="K6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L6">
         <v>43</v>
@@ -12379,40 +12382,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D7">
         <v>163</v>
       </c>
       <c r="E7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G7">
         <v>111</v>
       </c>
       <c r="H7">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M7">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -12691,7 +12694,7 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -12703,7 +12706,7 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -12723,7 +12726,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -12732,7 +12735,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -12813,16 +12816,16 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>23</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -12851,19 +12854,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>30</v>
@@ -12872,7 +12875,7 @@
         <v>28</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -12973,16 +12976,16 @@
         <v>8</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>7</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2">
         <v>18</v>
@@ -13067,13 +13070,13 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13104,28 +13107,28 @@
         <v>22</v>
       </c>
       <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>26</v>
+      </c>
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
       <c r="G6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H6">
         <v>31</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>13</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>13</v>
@@ -13145,34 +13148,34 @@
         <v>47</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>51</v>
       </c>
       <c r="I7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L7">
         <v>39</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -13293,7 +13296,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -13337,7 +13340,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -13413,13 +13416,13 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6">
         <v>12</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -13436,13 +13439,13 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7">
         <v>32</v>
@@ -13454,13 +13457,13 @@
         <v>36</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M7">
         <v>35</v>
@@ -13659,7 +13662,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -13697,7 +13700,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -13935,7 +13938,7 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -13976,7 +13979,7 @@
         <v>12</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -14086,7 +14089,7 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>10</v>
@@ -14118,7 +14121,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -14205,7 +14208,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -14223,7 +14226,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6">
         <v>11</v>
@@ -14235,7 +14238,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14246,7 +14249,7 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>48</v>
@@ -14255,7 +14258,7 @@
         <v>39</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>40</v>
@@ -14264,7 +14267,7 @@
         <v>25</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>33</v>
@@ -14276,7 +14279,7 @@
         <v>28</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -14374,7 +14377,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>19</v>
@@ -14391,7 +14394,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -14400,13 +14403,13 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>7</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -14432,7 +14435,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -14450,13 +14453,13 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -14520,7 +14523,7 @@
         <v>13</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -14534,7 +14537,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -14543,25 +14546,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>35</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7">
         <v>26</v>
@@ -14641,7 +14644,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -14665,7 +14668,7 @@
         <v>15</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <v>15</v>
@@ -14685,7 +14688,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -14706,7 +14709,7 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3">
         <v>12</v>
@@ -14737,6 +14740,9 @@
       <c r="J4">
         <v>3</v>
       </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
       <c r="L4">
         <v>5</v>
       </c>
@@ -14757,6 +14763,9 @@
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>2</v>
       </c>
@@ -14778,7 +14787,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>27</v>
@@ -14816,10 +14825,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -14834,16 +14843,16 @@
         <v>40</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7">
         <v>38</v>
@@ -15021,7 +15030,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -15062,7 +15071,7 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -15163,7 +15172,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>26</v>
@@ -15178,7 +15187,7 @@
         <v>31</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2">
         <v>35</v>
@@ -15187,13 +15196,13 @@
         <v>26</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2">
         <v>18</v>
@@ -15228,7 +15237,7 @@
         <v>26</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3">
         <v>33</v>
@@ -15237,7 +15246,7 @@
         <v>30</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15324,13 +15333,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>40</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>34</v>
@@ -15354,10 +15363,10 @@
         <v>23</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15365,13 +15374,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>103</v>
       </c>
       <c r="D7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7">
         <v>86</v>
@@ -15380,7 +15389,7 @@
         <v>88</v>
       </c>
       <c r="G7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -15389,16 +15398,16 @@
         <v>87</v>
       </c>
       <c r="J7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -15513,7 +15522,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -15565,6 +15574,9 @@
       <c r="G4">
         <v>5</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>3</v>
       </c>
@@ -15647,7 +15659,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>23</v>
@@ -15668,7 +15680,7 @@
         <v>16</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>20</v>
@@ -15757,13 +15769,13 @@
         <v>18</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>29</v>
@@ -15772,7 +15784,7 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2">
         <v>22</v>
@@ -15804,16 +15816,16 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>22</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>25</v>
@@ -15822,7 +15834,7 @@
         <v>26</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3">
         <v>20</v>
@@ -15869,7 +15881,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15915,13 +15927,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>53</v>
@@ -15942,7 +15954,7 @@
         <v>26</v>
       </c>
       <c r="K6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6">
         <v>30</v>
@@ -15956,25 +15968,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F7">
         <v>109</v>
       </c>
       <c r="G7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>90</v>
@@ -15983,13 +15995,13 @@
         <v>81</v>
       </c>
       <c r="K7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L7">
         <v>77</v>
       </c>
       <c r="M7">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -16110,13 +16122,13 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -16134,7 +16146,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -16188,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -16229,13 +16241,13 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>19</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -16253,7 +16265,7 @@
         <v>28</v>
       </c>
       <c r="L7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7">
         <v>18</v>
@@ -16330,7 +16342,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -16377,7 +16389,7 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -16425,6 +16437,9 @@
       <c r="B5">
         <v>2</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5">
         <v>1</v>
       </c>
@@ -16455,10 +16470,10 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -16473,7 +16488,7 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -16562,7 +16577,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -16580,7 +16595,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2">
         <v>9</v>
@@ -16592,7 +16607,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -16659,7 +16674,7 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -16755,7 +16770,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>38</v>
@@ -16770,10 +16785,10 @@
         <v>39</v>
       </c>
       <c r="G7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7">
         <v>44</v>
@@ -16785,7 +16800,7 @@
         <v>43</v>
       </c>
       <c r="L7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M7">
         <v>29</v>
@@ -16862,7 +16877,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -17025,7 +17040,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>23</v>
@@ -17206,7 +17221,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -17218,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -17241,7 +17256,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -17259,7 +17274,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -17339,7 +17354,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>16</v>
@@ -17351,16 +17366,16 @@
         <v>30</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>39</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2">
         <v>29</v>
@@ -17383,22 +17398,22 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>32</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3">
         <v>29</v>
@@ -17407,13 +17422,13 @@
         <v>37</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3">
         <v>33</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17430,10 +17445,10 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>9</v>
@@ -17442,7 +17457,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -17503,25 +17518,25 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6">
         <v>48</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>36</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>27</v>
       </c>
       <c r="I6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6">
         <v>30</v>
@@ -17541,40 +17556,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7">
+        <v>110</v>
+      </c>
+      <c r="I7">
         <v>109</v>
-      </c>
-      <c r="I7">
-        <v>106</v>
       </c>
       <c r="J7">
         <v>98</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L7">
         <v>93</v>
       </c>
       <c r="M7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -17648,7 +17663,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -17672,7 +17687,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -17817,7 +17832,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -17841,7 +17856,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7">
         <v>22</v>
@@ -17927,7 +17942,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -17945,7 +17960,7 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>15</v>
@@ -17986,7 +18001,7 @@
         <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>5</v>
@@ -18024,7 +18039,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -18055,7 +18070,7 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -18064,7 +18079,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -18076,7 +18091,7 @@
         <v>18</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M6">
         <v>11</v>
@@ -18093,10 +18108,10 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>19</v>
@@ -18105,19 +18120,19 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>29</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>42</v>
       </c>
       <c r="L7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M7">
         <v>30</v>
@@ -18244,7 +18259,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -18325,7 +18340,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -18343,7 +18358,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -18363,10 +18378,10 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -18381,7 +18396,7 @@
         <v>18</v>
       </c>
       <c r="J7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7">
         <v>17</v>
@@ -18511,7 +18526,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -18567,7 +18582,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -18577,6 +18592,9 @@
       </c>
       <c r="L4">
         <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18613,7 +18631,7 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -18622,10 +18640,10 @@
         <v>16</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -18648,13 +18666,13 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>18</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>14</v>
@@ -18663,10 +18681,10 @@
         <v>27</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7">
         <v>25</v>
@@ -18675,7 +18693,7 @@
         <v>24</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -18755,7 +18773,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -18793,7 +18811,7 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -18816,6 +18834,9 @@
       <c r="J3">
         <v>11</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>11</v>
       </c>
@@ -18913,7 +18934,7 @@
         <v>21</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>13</v>
@@ -18933,10 +18954,10 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>41</v>
@@ -18954,10 +18975,10 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -19089,6 +19110,9 @@
       <c r="E3">
         <v>3</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>1</v>
       </c>
@@ -19156,13 +19180,13 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>15</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -19197,16 +19221,16 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>29</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>15</v>
@@ -19351,7 +19375,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -19369,7 +19393,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -19407,7 +19431,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -19447,7 +19471,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -19485,10 +19509,10 @@
         <v>19</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>14</v>
@@ -19500,10 +19524,10 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7">
         <v>11</v>
@@ -19583,7 +19607,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -19637,7 +19661,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -19678,7 +19702,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -19693,7 +19717,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -20199,7 +20223,7 @@
         <v>17</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2">
         <v>12</v>
@@ -20330,13 +20354,13 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>34</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -20351,10 +20375,10 @@
         <v>12</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -20371,13 +20395,13 @@
         <v>50</v>
       </c>
       <c r="C7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>71</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>51</v>
@@ -20389,13 +20413,13 @@
         <v>46</v>
       </c>
       <c r="I7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L7">
         <v>46</v>
@@ -20541,7 +20565,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -20579,7 +20603,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -20674,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -20701,7 +20725,7 @@
         <v>7</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -20739,7 +20763,7 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -20779,6 +20803,9 @@
       <c r="L4">
         <v>2</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -20814,7 +20841,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -20852,10 +20879,10 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -20876,13 +20903,13 @@
         <v>25</v>
       </c>
       <c r="K7">
+        <v>18</v>
+      </c>
+      <c r="L7">
         <v>17</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>16</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -20959,10 +20986,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -20971,7 +20998,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -20986,10 +21013,10 @@
         <v>12</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21021,7 +21048,7 @@
         <v>13</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -21090,7 +21117,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -21114,7 +21141,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -21131,10 +21158,10 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>34</v>
@@ -21143,7 +21170,7 @@
         <v>33</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7">
         <v>34</v>
@@ -21152,16 +21179,16 @@
         <v>34</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -21238,7 +21265,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -21250,7 +21277,7 @@
         <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -21284,6 +21311,9 @@
       <c r="H3">
         <v>2</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -21365,7 +21395,7 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -21383,7 +21413,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -21484,7 +21514,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -21499,7 +21529,7 @@
         <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -21513,7 +21543,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -21591,6 +21621,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>1</v>
       </c>
@@ -21609,7 +21642,7 @@
         <v>22</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -21621,13 +21654,13 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -21644,34 +21677,34 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>17</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>30</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>31</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7">
         <v>23</v>
@@ -21891,7 +21924,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6">
         <v>26</v>
@@ -21932,7 +21965,7 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7">
         <v>35</v>
@@ -22039,7 +22072,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -22067,6 +22100,9 @@
       <c r="G3">
         <v>3</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3">
         <v>2</v>
       </c>
@@ -22146,7 +22182,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -22181,13 +22217,13 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7">
         <v>15</v>
@@ -22345,7 +22381,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -22409,7 +22445,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -22489,7 +22525,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>11</v>
@@ -22530,7 +22566,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -22542,10 +22578,10 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -22557,7 +22593,7 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3">
         <v>12</v>
@@ -22656,10 +22692,10 @@
         <v>13</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6">
         <v>18</v>
@@ -22673,7 +22709,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>41</v>
@@ -22685,10 +22721,10 @@
         <v>38</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>32</v>
@@ -22697,10 +22733,10 @@
         <v>26</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L7">
         <v>42</v>
@@ -22833,7 +22869,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -22931,7 +22967,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -23064,7 +23100,7 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -23111,7 +23147,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -23169,7 +23205,7 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -23181,7 +23217,7 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -23207,13 +23243,13 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7">
         <v>26</v>
@@ -23222,7 +23258,7 @@
         <v>44</v>
       </c>
       <c r="K7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L7">
         <v>36</v>
@@ -23413,7 +23449,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -23431,7 +23467,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -23454,7 +23490,7 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -23472,7 +23508,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -23579,7 +23615,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23599,7 +23635,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -23680,7 +23716,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -23689,7 +23725,7 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -23701,7 +23737,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -23721,7 +23757,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -23730,10 +23766,10 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7">
         <v>29</v>
@@ -23742,7 +23778,7 @@
         <v>24</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>16</v>
@@ -23754,7 +23790,7 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -23922,7 +23958,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>11</v>
@@ -23960,7 +23996,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -24001,10 +24037,10 @@
         <v>18</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -24120,7 +24156,7 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -24164,7 +24200,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24227,7 +24263,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -24262,7 +24298,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -24280,10 +24316,10 @@
         <v>10</v>
       </c>
       <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
         <v>11</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -24366,7 +24402,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -24381,7 +24417,7 @@
         <v>11</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>10</v>
@@ -24398,13 +24434,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -24492,7 +24528,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -24515,13 +24551,13 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -24550,19 +24586,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>55</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
         <v>30</v>
@@ -24571,10 +24607,10 @@
         <v>35</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -24663,7 +24699,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -24672,7 +24708,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>11</v>
@@ -24687,7 +24723,7 @@
         <v>12</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -24809,13 +24845,13 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>21</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6">
         <v>19</v>
@@ -24847,16 +24883,16 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>36</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>43</v>
@@ -24871,7 +24907,7 @@
         <v>49</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7">
         <v>31</v>
@@ -25206,7 +25242,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -25262,7 +25298,7 @@
         <v>6</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -25343,10 +25379,10 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -25363,7 +25399,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>11</v>
@@ -25381,10 +25417,10 @@
         <v>11</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>16</v>
@@ -25482,7 +25518,7 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -25548,6 +25584,9 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -25604,7 +25643,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -25616,7 +25655,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -25639,16 +25678,16 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>13</v>
@@ -25657,7 +25696,7 @@
         <v>20</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -25737,7 +25776,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -25903,7 +25942,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -26016,10 +26055,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>33</v>
@@ -26028,19 +26067,19 @@
         <v>30</v>
       </c>
       <c r="H2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>39</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K2">
         <v>69</v>
       </c>
       <c r="L2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2">
         <v>38</v>
@@ -26054,13 +26093,13 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>50</v>
@@ -26072,13 +26111,13 @@
         <v>57</v>
       </c>
       <c r="I3">
+        <v>58</v>
+      </c>
+      <c r="J3">
+        <v>50</v>
+      </c>
+      <c r="K3">
         <v>57</v>
-      </c>
-      <c r="J3">
-        <v>49</v>
-      </c>
-      <c r="K3">
-        <v>56</v>
       </c>
       <c r="L3">
         <v>63</v>
@@ -26122,7 +26161,7 @@
         <v>11</v>
       </c>
       <c r="L4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -26180,19 +26219,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>36</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>47</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I6">
         <v>52</v>
@@ -26218,34 +26257,34 @@
         <v>136</v>
       </c>
       <c r="C7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>115</v>
+      </c>
+      <c r="F7">
         <v>146</v>
-      </c>
-      <c r="E7">
-        <v>113</v>
-      </c>
-      <c r="F7">
-        <v>143</v>
       </c>
       <c r="G7">
         <v>145</v>
       </c>
       <c r="H7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M7">
         <v>128</v>
@@ -26372,7 +26411,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -26444,7 +26483,7 @@
         <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -26479,7 +26518,7 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -26615,7 +26654,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -26643,6 +26682,9 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -26722,13 +26764,13 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>16</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>14</v>
@@ -26901,6 +26943,9 @@
       <c r="G4">
         <v>2</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>2</v>
       </c>
@@ -26928,10 +26973,10 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -26946,7 +26991,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -26969,16 +27014,16 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>18</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -26987,7 +27032,7 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -27147,7 +27192,7 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -27182,7 +27227,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -27414,7 +27459,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -27455,7 +27500,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -27826,7 +27871,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -27867,7 +27912,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -28053,7 +28098,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -28067,13 +28112,13 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -28085,7 +28130,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -28105,13 +28150,13 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -28126,13 +28171,13 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>11</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -28209,7 +28254,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -28279,6 +28324,9 @@
       <c r="I6">
         <v>1</v>
       </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
       <c r="M6">
         <v>1</v>
       </c>
@@ -28300,7 +28348,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -28312,7 +28360,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -28398,7 +28446,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -28436,7 +28484,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -28516,6 +28564,9 @@
       <c r="G6">
         <v>1</v>
       </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
       <c r="J6">
         <v>2</v>
       </c>
@@ -28531,10 +28582,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -28549,7 +28600,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>3</v>
@@ -28662,10 +28713,10 @@
         <v>13</v>
       </c>
       <c r="J2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>18</v>
@@ -28682,7 +28733,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>22</v>
@@ -28694,22 +28745,22 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3">
+        <v>16</v>
+      </c>
+      <c r="L3">
         <v>15</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
       </c>
       <c r="M3">
         <v>15</v>
@@ -28723,7 +28774,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -28802,13 +28853,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>49</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -28823,7 +28874,7 @@
         <v>26</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <v>31</v>
@@ -28835,7 +28886,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -28843,13 +28894,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E7">
         <v>76</v>
@@ -28858,25 +28909,25 @@
         <v>64</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7">
         <v>56</v>
       </c>
       <c r="I7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -28955,6 +29006,9 @@
       <c r="C2">
         <v>3</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>3</v>
       </c>
@@ -29072,7 +29126,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -29686,7 +29740,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -29709,7 +29763,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -29790,7 +29844,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -29802,7 +29856,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -30169,7 +30223,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30210,7 +30264,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C2">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="D2">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="E2">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="F2">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="G2">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="H2">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="I2">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="J2">
-        <v>933</v>
+        <v>949</v>
       </c>
       <c r="K2">
-        <v>1011</v>
+        <v>1038</v>
       </c>
       <c r="L2">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="M2">
-        <v>770</v>
+        <v>784</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="C3">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="D3">
-        <v>962</v>
+        <v>975</v>
       </c>
       <c r="E3">
-        <v>869</v>
+        <v>892</v>
       </c>
       <c r="F3">
+        <v>903</v>
+      </c>
+      <c r="G3">
+        <v>980</v>
+      </c>
+      <c r="H3">
+        <v>867</v>
+      </c>
+      <c r="I3">
         <v>887</v>
       </c>
-      <c r="G3">
-        <v>966</v>
-      </c>
-      <c r="H3">
-        <v>852</v>
-      </c>
-      <c r="I3">
-        <v>877</v>
-      </c>
       <c r="J3">
-        <v>1020</v>
+        <v>1042</v>
       </c>
       <c r="K3">
-        <v>961</v>
+        <v>983</v>
       </c>
       <c r="L3">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="M3">
-        <v>858</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>330</v>
+      </c>
+      <c r="C4">
+        <v>292</v>
+      </c>
+      <c r="D4">
+        <v>361</v>
+      </c>
+      <c r="E4">
+        <v>318</v>
+      </c>
+      <c r="F4">
         <v>326</v>
       </c>
-      <c r="C4">
-        <v>290</v>
-      </c>
-      <c r="D4">
-        <v>356</v>
-      </c>
-      <c r="E4">
-        <v>310</v>
-      </c>
-      <c r="F4">
-        <v>325</v>
-      </c>
       <c r="G4">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H4">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I4">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="J4">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K4">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="L4">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M4">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -991,40 +991,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>99</v>
       </c>
       <c r="D5">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1187</v>
+        <v>1206</v>
       </c>
       <c r="C6">
-        <v>1639</v>
+        <v>1652</v>
       </c>
       <c r="D6">
-        <v>1768</v>
+        <v>1792</v>
       </c>
       <c r="E6">
-        <v>1456</v>
+        <v>1485</v>
       </c>
       <c r="F6">
-        <v>1086</v>
+        <v>1102</v>
       </c>
       <c r="G6">
-        <v>1271</v>
+        <v>1289</v>
       </c>
       <c r="H6">
-        <v>1141</v>
+        <v>1159</v>
       </c>
       <c r="I6">
-        <v>1225</v>
+        <v>1241</v>
       </c>
       <c r="J6">
-        <v>1396</v>
+        <v>1418</v>
       </c>
       <c r="K6">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="L6">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="M6">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2781</v>
+        <v>2829</v>
       </c>
       <c r="C7">
-        <v>3577</v>
+        <v>3628</v>
       </c>
       <c r="D7">
-        <v>3934</v>
+        <v>3988</v>
       </c>
       <c r="E7">
-        <v>3447</v>
+        <v>3529</v>
       </c>
       <c r="F7">
-        <v>3120</v>
+        <v>3161</v>
       </c>
       <c r="G7">
-        <v>3392</v>
+        <v>3439</v>
       </c>
       <c r="H7">
-        <v>3125</v>
+        <v>3179</v>
       </c>
       <c r="I7">
-        <v>3284</v>
+        <v>3328</v>
       </c>
       <c r="J7">
-        <v>3705</v>
+        <v>3770</v>
       </c>
       <c r="K7">
-        <v>3598</v>
+        <v>3673</v>
       </c>
       <c r="L7">
-        <v>2874</v>
+        <v>2922</v>
       </c>
       <c r="M7">
-        <v>2563</v>
+        <v>2602</v>
       </c>
     </row>
   </sheetData>
@@ -1192,7 +1192,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -1334,7 +1334,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -1349,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1546,10 +1546,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>9</v>
@@ -1570,13 +1570,13 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>11</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1593,7 +1593,7 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>11</v>
@@ -1634,7 +1634,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1677,13 +1677,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -1695,7 +1695,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>18</v>
@@ -1704,7 +1704,7 @@
         <v>20</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -1718,16 +1718,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -1736,22 +1736,22 @@
         <v>35</v>
       </c>
       <c r="H7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>38</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L7">
         <v>37</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1828,13 +1828,13 @@
         <v>41</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>55</v>
@@ -1843,19 +1843,19 @@
         <v>58</v>
       </c>
       <c r="H2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I2">
         <v>59</v>
       </c>
       <c r="J2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M2">
         <v>55</v>
@@ -1866,22 +1866,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3">
+        <v>64</v>
+      </c>
+      <c r="F3">
         <v>63</v>
       </c>
-      <c r="F3">
-        <v>62</v>
-      </c>
       <c r="G3">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>57</v>
@@ -1890,16 +1890,16 @@
         <v>54</v>
       </c>
       <c r="J3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3">
         <v>63</v>
       </c>
       <c r="L3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1948,7 +1948,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -1957,7 +1957,7 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -1966,7 +1966,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -1989,19 +1989,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C6">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E6">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F6">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>121</v>
@@ -2010,19 +2010,19 @@
         <v>75</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>67</v>
       </c>
       <c r="K6">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2030,40 +2030,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>177</v>
+      </c>
+      <c r="C7">
+        <v>267</v>
+      </c>
+      <c r="D7">
+        <v>296</v>
+      </c>
+      <c r="E7">
+        <v>251</v>
+      </c>
+      <c r="F7">
+        <v>226</v>
+      </c>
+      <c r="G7">
+        <v>281</v>
+      </c>
+      <c r="H7">
+        <v>206</v>
+      </c>
+      <c r="I7">
+        <v>198</v>
+      </c>
+      <c r="J7">
+        <v>239</v>
+      </c>
+      <c r="K7">
+        <v>213</v>
+      </c>
+      <c r="L7">
+        <v>182</v>
+      </c>
+      <c r="M7">
         <v>173</v>
-      </c>
-      <c r="C7">
-        <v>264</v>
-      </c>
-      <c r="D7">
-        <v>290</v>
-      </c>
-      <c r="E7">
-        <v>247</v>
-      </c>
-      <c r="F7">
-        <v>221</v>
-      </c>
-      <c r="G7">
-        <v>280</v>
-      </c>
-      <c r="H7">
-        <v>204</v>
-      </c>
-      <c r="I7">
-        <v>197</v>
-      </c>
-      <c r="J7">
-        <v>235</v>
-      </c>
-      <c r="K7">
-        <v>208</v>
-      </c>
-      <c r="L7">
-        <v>176</v>
-      </c>
-      <c r="M7">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2140,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>23</v>
@@ -2161,7 +2161,7 @@
         <v>24</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2">
         <v>33</v>
@@ -2196,22 +2196,22 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3">
+        <v>29</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>27</v>
-      </c>
-      <c r="K3">
-        <v>19</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2225,7 +2225,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2339,10 +2339,10 @@
         <v>62</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>56</v>
@@ -2354,22 +2354,22 @@
         <v>48</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I7">
+        <v>61</v>
+      </c>
+      <c r="J7">
+        <v>88</v>
+      </c>
+      <c r="K7">
+        <v>64</v>
+      </c>
+      <c r="L7">
+        <v>59</v>
+      </c>
+      <c r="M7">
         <v>60</v>
-      </c>
-      <c r="J7">
-        <v>85</v>
-      </c>
-      <c r="K7">
-        <v>63</v>
-      </c>
-      <c r="L7">
-        <v>58</v>
-      </c>
-      <c r="M7">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2446,7 +2446,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -2461,7 +2461,7 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2">
         <v>33</v>
@@ -2470,10 +2470,10 @@
         <v>35</v>
       </c>
       <c r="K2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2">
         <v>22</v>
@@ -2487,34 +2487,34 @@
         <v>34</v>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>48</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K3">
         <v>56</v>
       </c>
       <c r="L3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M3">
         <v>29</v>
@@ -2546,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -2610,22 +2610,22 @@
         <v>67</v>
       </c>
       <c r="C6">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6">
         <v>62</v>
       </c>
       <c r="G6">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>57</v>
@@ -2651,34 +2651,34 @@
         <v>131</v>
       </c>
       <c r="C7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E7">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M7">
         <v>88</v>
@@ -2761,7 +2761,7 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>13</v>
@@ -2788,7 +2788,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2796,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>12</v>
@@ -2823,13 +2823,13 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2928,7 +2928,7 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -2954,13 +2954,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>45</v>
       </c>
       <c r="D7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7">
         <v>55</v>
@@ -2969,7 +2969,7 @@
         <v>54</v>
       </c>
       <c r="G7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7">
         <v>67</v>
@@ -2981,13 +2981,13 @@
         <v>69</v>
       </c>
       <c r="K7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3079,7 +3079,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2">
         <v>32</v>
@@ -3088,10 +3088,10 @@
         <v>35</v>
       </c>
       <c r="K2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2">
         <v>30</v>
@@ -3114,7 +3114,7 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
         <v>31</v>
@@ -3132,7 +3132,7 @@
         <v>37</v>
       </c>
       <c r="L3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3">
         <v>36</v>
@@ -3143,7 +3143,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>11</v>
@@ -3205,7 +3205,7 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>4</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>45</v>
@@ -3234,7 +3234,7 @@
         <v>30</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>18</v>
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>115</v>
@@ -3272,25 +3272,25 @@
         <v>105</v>
       </c>
       <c r="F7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I7">
         <v>109</v>
       </c>
       <c r="J7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M7">
         <v>101</v>
@@ -3376,10 +3376,10 @@
         <v>18</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>16</v>
@@ -3388,7 +3388,7 @@
         <v>19</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2">
         <v>24</v>
@@ -3397,7 +3397,7 @@
         <v>24</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>21</v>
@@ -3411,13 +3411,13 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>28</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -3435,13 +3435,13 @@
         <v>22</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3">
         <v>17</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3522,10 +3522,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>31</v>
@@ -3546,16 +3546,16 @@
         <v>36</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6">
         <v>52</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3563,19 +3563,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7">
         <v>83</v>
       </c>
       <c r="E7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>54</v>
@@ -3584,19 +3584,19 @@
         <v>53</v>
       </c>
       <c r="I7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M7">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3679,7 +3679,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -3688,7 +3688,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2">
         <v>21</v>
@@ -3711,19 +3711,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>26</v>
@@ -3732,13 +3732,13 @@
         <v>21</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>21</v>
@@ -3782,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -3795,6 +3795,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
       <c r="E5">
         <v>5</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>14</v>
@@ -3849,13 +3852,13 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <v>8</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3863,40 +3866,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>67</v>
       </c>
       <c r="H7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M7">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4029,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -4130,7 +4133,7 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -4219,16 +4222,16 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>17</v>
@@ -4237,16 +4240,16 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -4328,7 +4331,7 @@
         <v>17</v>
       </c>
       <c r="K4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4">
         <v>11</v>
@@ -4360,7 +4363,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>15</v>
@@ -4386,10 +4389,10 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6">
         <v>35</v>
@@ -4398,7 +4401,7 @@
         <v>20</v>
       </c>
       <c r="G6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6">
         <v>19</v>
@@ -4407,7 +4410,7 @@
         <v>26</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K6">
         <v>27</v>
@@ -4427,37 +4430,37 @@
         <v>113</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>110</v>
       </c>
       <c r="G7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I7">
         <v>109</v>
       </c>
       <c r="J7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M7">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4465,40 +4468,40 @@
         <v>14</v>
       </c>
       <c r="B8">
+        <v>177</v>
+      </c>
+      <c r="C8">
+        <v>267</v>
+      </c>
+      <c r="D8">
+        <v>296</v>
+      </c>
+      <c r="E8">
+        <v>251</v>
+      </c>
+      <c r="F8">
+        <v>226</v>
+      </c>
+      <c r="G8">
+        <v>281</v>
+      </c>
+      <c r="H8">
+        <v>206</v>
+      </c>
+      <c r="I8">
+        <v>198</v>
+      </c>
+      <c r="J8">
+        <v>239</v>
+      </c>
+      <c r="K8">
+        <v>213</v>
+      </c>
+      <c r="L8">
+        <v>182</v>
+      </c>
+      <c r="M8">
         <v>173</v>
-      </c>
-      <c r="C8">
-        <v>264</v>
-      </c>
-      <c r="D8">
-        <v>290</v>
-      </c>
-      <c r="E8">
-        <v>247</v>
-      </c>
-      <c r="F8">
-        <v>221</v>
-      </c>
-      <c r="G8">
-        <v>280</v>
-      </c>
-      <c r="H8">
-        <v>204</v>
-      </c>
-      <c r="I8">
-        <v>197</v>
-      </c>
-      <c r="J8">
-        <v>235</v>
-      </c>
-      <c r="K8">
-        <v>208</v>
-      </c>
-      <c r="L8">
-        <v>176</v>
-      </c>
-      <c r="M8">
-        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4515,28 +4518,28 @@
         <v>22</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9">
         <v>19</v>
       </c>
       <c r="I9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K9">
         <v>18</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9">
         <v>16</v>
@@ -4547,7 +4550,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>29</v>
@@ -4559,7 +4562,7 @@
         <v>44</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10">
         <v>30</v>
@@ -4577,7 +4580,7 @@
         <v>22</v>
       </c>
       <c r="L10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10">
         <v>12</v>
@@ -4588,22 +4591,22 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>58</v>
       </c>
       <c r="D11">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E11">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11">
         <v>51</v>
       </c>
       <c r="G11">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H11">
         <v>46</v>
@@ -4615,7 +4618,7 @@
         <v>43</v>
       </c>
       <c r="K11">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L11">
         <v>46</v>
@@ -4632,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -4644,7 +4647,7 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12">
         <v>4</v>
@@ -4688,7 +4691,7 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>7</v>
@@ -4726,7 +4729,7 @@
         <v>16</v>
       </c>
       <c r="I14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14">
         <v>15</v>
@@ -4749,13 +4752,13 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F15">
         <v>27</v>
@@ -4764,22 +4767,22 @@
         <v>21</v>
       </c>
       <c r="H15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15">
         <v>42</v>
       </c>
       <c r="J15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4808,7 +4811,7 @@
         <v>12</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -4834,7 +4837,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -4869,7 +4872,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -4884,13 +4887,13 @@
         <v>12</v>
       </c>
       <c r="H18">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I18">
         <v>28</v>
       </c>
       <c r="J18">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K18">
         <v>28</v>
@@ -4899,7 +4902,7 @@
         <v>22</v>
       </c>
       <c r="M18">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -4907,40 +4910,40 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D19">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F19">
         <v>96</v>
       </c>
       <c r="G19">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H19">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I19">
+        <v>89</v>
+      </c>
+      <c r="J19">
+        <v>124</v>
+      </c>
+      <c r="K19">
+        <v>97</v>
+      </c>
+      <c r="L19">
+        <v>93</v>
+      </c>
+      <c r="M19">
         <v>87</v>
-      </c>
-      <c r="J19">
-        <v>123</v>
-      </c>
-      <c r="K19">
-        <v>94</v>
-      </c>
-      <c r="L19">
-        <v>92</v>
-      </c>
-      <c r="M19">
-        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4948,37 +4951,37 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C20">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F20">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G20">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H20">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I20">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J20">
         <v>81</v>
       </c>
       <c r="K20">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L20">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M20">
         <v>73</v>
@@ -5007,7 +5010,7 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21">
         <v>29</v>
@@ -5019,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -5051,7 +5054,7 @@
         <v>4</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -5074,7 +5077,7 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>48</v>
@@ -5083,7 +5086,7 @@
         <v>39</v>
       </c>
       <c r="F23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23">
         <v>40</v>
@@ -5130,7 +5133,7 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24">
         <v>4</v>
@@ -5142,7 +5145,7 @@
         <v>13</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>11</v>
@@ -5165,16 +5168,16 @@
         <v>17</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25">
         <v>19</v>
@@ -5218,7 +5221,7 @@
         <v>4</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -5235,7 +5238,7 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <v>24</v>
@@ -5244,13 +5247,13 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27">
         <v>22</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H27">
         <v>24</v>
@@ -5265,7 +5268,7 @@
         <v>45</v>
       </c>
       <c r="L27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M27">
         <v>31</v>
@@ -5291,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -5302,40 +5305,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C29">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D29">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E29">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F29">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G29">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H29">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I29">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J29">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K29">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L29">
         <v>137</v>
       </c>
       <c r="M29">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5361,7 +5364,7 @@
         <v>11</v>
       </c>
       <c r="H30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30">
         <v>12</v>
@@ -5399,7 +5402,7 @@
         <v>35</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H31">
         <v>19</v>
@@ -5411,7 +5414,7 @@
         <v>24</v>
       </c>
       <c r="K31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L31">
         <v>30</v>
@@ -5440,13 +5443,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -5469,34 +5472,34 @@
         <v>131</v>
       </c>
       <c r="C33">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D33">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E33">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F33">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G33">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H33">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I33">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J33">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K33">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L33">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M33">
         <v>88</v>
@@ -5534,7 +5537,7 @@
         <v>28</v>
       </c>
       <c r="K34">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L34">
         <v>19</v>
@@ -5563,19 +5566,19 @@
         <v>3</v>
       </c>
       <c r="G35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H35">
         <v>5</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>5</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -5589,31 +5592,31 @@
         <v>42</v>
       </c>
       <c r="B36">
+        <v>40</v>
+      </c>
+      <c r="C36">
         <v>39</v>
-      </c>
-      <c r="C36">
-        <v>38</v>
       </c>
       <c r="D36">
         <v>37</v>
       </c>
       <c r="E36">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H36">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I36">
         <v>44</v>
       </c>
       <c r="J36">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K36">
         <v>43</v>
@@ -5630,7 +5633,7 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C37">
         <v>115</v>
@@ -5642,25 +5645,25 @@
         <v>105</v>
       </c>
       <c r="F37">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G37">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H37">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I37">
         <v>109</v>
       </c>
       <c r="J37">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K37">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L37">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M37">
         <v>101</v>
@@ -5730,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -5759,7 +5762,7 @@
         <v>8</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40">
         <v>8</v>
@@ -5782,13 +5785,13 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F41">
         <v>13</v>
@@ -5820,37 +5823,37 @@
         <v>48</v>
       </c>
       <c r="B42">
+        <v>116</v>
+      </c>
+      <c r="C42">
+        <v>141</v>
+      </c>
+      <c r="D42">
+        <v>164</v>
+      </c>
+      <c r="E42">
+        <v>127</v>
+      </c>
+      <c r="F42">
+        <v>122</v>
+      </c>
+      <c r="G42">
         <v>113</v>
       </c>
-      <c r="C42">
-        <v>138</v>
-      </c>
-      <c r="D42">
-        <v>163</v>
-      </c>
-      <c r="E42">
+      <c r="H42">
         <v>124</v>
       </c>
-      <c r="F42">
-        <v>120</v>
-      </c>
-      <c r="G42">
-        <v>111</v>
-      </c>
-      <c r="H42">
-        <v>121</v>
-      </c>
       <c r="I42">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J42">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K42">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L42">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M42">
         <v>80</v>
@@ -5870,7 +5873,7 @@
         <v>16</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F43">
         <v>25</v>
@@ -5879,10 +5882,10 @@
         <v>29</v>
       </c>
       <c r="H43">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I43">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J43">
         <v>43</v>
@@ -5905,16 +5908,16 @@
         <v>30</v>
       </c>
       <c r="C44">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E44">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G44">
         <v>37</v>
@@ -5923,13 +5926,13 @@
         <v>37</v>
       </c>
       <c r="I44">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J44">
         <v>27</v>
       </c>
       <c r="K44">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L44">
         <v>18</v>
@@ -5984,13 +5987,13 @@
         <v>52</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C46">
         <v>7</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46">
         <v>9</v>
@@ -6008,10 +6011,10 @@
         <v>8</v>
       </c>
       <c r="J46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L46">
         <v>8</v>
@@ -6025,7 +6028,7 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C47">
         <v>22</v>
@@ -6043,13 +6046,13 @@
         <v>14</v>
       </c>
       <c r="H47">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I47">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J47">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K47">
         <v>25</v>
@@ -6075,16 +6078,16 @@
         <v>34</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F48">
         <v>31</v>
       </c>
       <c r="G48">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H48">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I48">
         <v>26</v>
@@ -6093,13 +6096,13 @@
         <v>23</v>
       </c>
       <c r="K48">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L48">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M48">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6119,10 +6122,10 @@
         <v>18</v>
       </c>
       <c r="F49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H49">
         <v>11</v>
@@ -6131,13 +6134,13 @@
         <v>12</v>
       </c>
       <c r="J49">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K49">
         <v>21</v>
       </c>
       <c r="L49">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M49">
         <v>18</v>
@@ -6166,13 +6169,13 @@
         <v>15</v>
       </c>
       <c r="H50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J50">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K50">
         <v>24</v>
@@ -6192,7 +6195,7 @@
         <v>31</v>
       </c>
       <c r="C51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51">
         <v>33</v>
@@ -6201,19 +6204,19 @@
         <v>40</v>
       </c>
       <c r="F51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G51">
         <v>35</v>
       </c>
       <c r="H51">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J51">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K51">
         <v>49</v>
@@ -6222,7 +6225,7 @@
         <v>40</v>
       </c>
       <c r="M51">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6233,13 +6236,13 @@
         <v>44</v>
       </c>
       <c r="C52">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D52">
         <v>94</v>
       </c>
       <c r="E52">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F52">
         <v>64</v>
@@ -6254,16 +6257,16 @@
         <v>67</v>
       </c>
       <c r="J52">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K52">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L52">
         <v>52</v>
       </c>
       <c r="M52">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6271,16 +6274,16 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D53">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E53">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F53">
         <v>30</v>
@@ -6289,22 +6292,22 @@
         <v>35</v>
       </c>
       <c r="H53">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53">
         <v>38</v>
       </c>
       <c r="J53">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K53">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L53">
         <v>37</v>
       </c>
       <c r="M53">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6315,34 +6318,34 @@
         <v>44</v>
       </c>
       <c r="C54">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D54">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E54">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F54">
         <v>59</v>
       </c>
       <c r="G54">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H54">
         <v>32</v>
       </c>
       <c r="I54">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J54">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K54">
         <v>66</v>
       </c>
       <c r="L54">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M54">
         <v>51</v>
@@ -6359,10 +6362,10 @@
         <v>26</v>
       </c>
       <c r="D55">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E55">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55">
         <v>26</v>
@@ -6371,19 +6374,19 @@
         <v>32</v>
       </c>
       <c r="H55">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I55">
         <v>36</v>
       </c>
       <c r="J55">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K55">
         <v>32</v>
       </c>
       <c r="L55">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M55">
         <v>35</v>
@@ -6418,7 +6421,7 @@
         <v>8</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -6435,7 +6438,7 @@
         <v>63</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -6444,7 +6447,7 @@
         <v>11</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57">
         <v>3</v>
@@ -6517,7 +6520,7 @@
         <v>9</v>
       </c>
       <c r="D59">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E59">
         <v>6</v>
@@ -6535,7 +6538,7 @@
         <v>4</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59">
         <v>9</v>
@@ -6555,7 +6558,7 @@
         <v>23</v>
       </c>
       <c r="C60">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D60">
         <v>33</v>
@@ -6564,10 +6567,10 @@
         <v>21</v>
       </c>
       <c r="F60">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G60">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H60">
         <v>25</v>
@@ -6617,7 +6620,7 @@
         <v>4</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K61">
         <v>6</v>
@@ -6660,13 +6663,13 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C63">
         <v>72</v>
       </c>
       <c r="D63">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -6675,7 +6678,7 @@
         <v>59</v>
       </c>
       <c r="G63">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H63">
         <v>45</v>
@@ -6687,13 +6690,13 @@
         <v>48</v>
       </c>
       <c r="K63">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L63">
         <v>13</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6728,13 +6731,13 @@
         <v>20</v>
       </c>
       <c r="K64">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L64">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M64">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6742,19 +6745,19 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C65">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D65">
         <v>83</v>
       </c>
       <c r="E65">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F65">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G65">
         <v>54</v>
@@ -6763,19 +6766,19 @@
         <v>53</v>
       </c>
       <c r="I65">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J65">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K65">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L65">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M65">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6821,40 +6824,40 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C67">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D67">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E67">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F67">
+        <v>125</v>
+      </c>
+      <c r="G67">
+        <v>147</v>
+      </c>
+      <c r="H67">
         <v>122</v>
-      </c>
-      <c r="G67">
-        <v>143</v>
-      </c>
-      <c r="H67">
-        <v>119</v>
       </c>
       <c r="I67">
         <v>126</v>
       </c>
       <c r="J67">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K67">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="L67">
         <v>106</v>
       </c>
       <c r="M67">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6874,7 +6877,7 @@
         <v>6</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G68">
         <v>13</v>
@@ -6883,7 +6886,7 @@
         <v>3</v>
       </c>
       <c r="I68">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J68">
         <v>12</v>
@@ -6915,7 +6918,7 @@
         <v>5</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69">
         <v>7</v>
@@ -6930,7 +6933,7 @@
         <v>8</v>
       </c>
       <c r="K69">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L69">
         <v>7</v>
@@ -6950,7 +6953,7 @@
         <v>4</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70">
         <v>4</v>
@@ -7006,7 +7009,7 @@
         <v>5</v>
       </c>
       <c r="J71">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K71">
         <v>10</v>
@@ -7035,7 +7038,7 @@
         <v>22</v>
       </c>
       <c r="F72">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G72">
         <v>18</v>
@@ -7044,7 +7047,7 @@
         <v>9</v>
       </c>
       <c r="I72">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J72">
         <v>14</v>
@@ -7070,7 +7073,7 @@
         <v>28</v>
       </c>
       <c r="D73">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E73">
         <v>34</v>
@@ -7094,7 +7097,7 @@
         <v>41</v>
       </c>
       <c r="L73">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M73">
         <v>14</v>
@@ -7164,7 +7167,7 @@
         <v>4</v>
       </c>
       <c r="H75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I75">
         <v>8</v>
@@ -7173,10 +7176,10 @@
         <v>16</v>
       </c>
       <c r="K75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M75">
         <v>11</v>
@@ -7190,10 +7193,10 @@
         <v>19</v>
       </c>
       <c r="C76">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D76">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E76">
         <v>36</v>
@@ -7208,16 +7211,16 @@
         <v>29</v>
       </c>
       <c r="I76">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J76">
         <v>60</v>
       </c>
       <c r="K76">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L76">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M76">
         <v>35</v>
@@ -7237,7 +7240,7 @@
         <v>20</v>
       </c>
       <c r="E77">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F77">
         <v>17</v>
@@ -7246,7 +7249,7 @@
         <v>21</v>
       </c>
       <c r="H77">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I77">
         <v>25</v>
@@ -7269,40 +7272,40 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C78">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D78">
         <v>45</v>
       </c>
       <c r="E78">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F78">
         <v>31</v>
       </c>
       <c r="G78">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H78">
         <v>51</v>
       </c>
       <c r="I78">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J78">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K78">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L78">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M78">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7310,37 +7313,37 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C79">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D79">
         <v>102</v>
       </c>
       <c r="E79">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F79">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G79">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H79">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I79">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J79">
         <v>112</v>
       </c>
       <c r="K79">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L79">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M79">
         <v>67</v>
@@ -7419,7 +7422,7 @@
         <v>3</v>
       </c>
       <c r="L81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M81">
         <v>2</v>
@@ -7439,16 +7442,16 @@
         <v>6</v>
       </c>
       <c r="E82">
+        <v>8</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82">
+        <v>5</v>
+      </c>
+      <c r="H82">
         <v>7</v>
-      </c>
-      <c r="F82">
-        <v>6</v>
-      </c>
-      <c r="G82">
-        <v>5</v>
-      </c>
-      <c r="H82">
-        <v>6</v>
       </c>
       <c r="J82">
         <v>7</v>
@@ -7471,10 +7474,10 @@
         <v>62</v>
       </c>
       <c r="C83">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D83">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E83">
         <v>56</v>
@@ -7486,22 +7489,22 @@
         <v>48</v>
       </c>
       <c r="H83">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I83">
+        <v>61</v>
+      </c>
+      <c r="J83">
+        <v>88</v>
+      </c>
+      <c r="K83">
+        <v>64</v>
+      </c>
+      <c r="L83">
+        <v>59</v>
+      </c>
+      <c r="M83">
         <v>60</v>
-      </c>
-      <c r="J83">
-        <v>85</v>
-      </c>
-      <c r="K83">
-        <v>63</v>
-      </c>
-      <c r="L83">
-        <v>58</v>
-      </c>
-      <c r="M83">
-        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7509,25 +7512,25 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D84">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E84">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F84">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G84">
         <v>29</v>
       </c>
       <c r="H84">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I84">
         <v>28</v>
@@ -7539,7 +7542,7 @@
         <v>28</v>
       </c>
       <c r="L84">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M84">
         <v>11</v>
@@ -7553,13 +7556,13 @@
         <v>136</v>
       </c>
       <c r="C85">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D85">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E85">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F85">
         <v>146</v>
@@ -7568,19 +7571,19 @@
         <v>145</v>
       </c>
       <c r="H85">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I85">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J85">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K85">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L85">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M85">
         <v>128</v>
@@ -7600,7 +7603,7 @@
         <v>10</v>
       </c>
       <c r="E86">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F86">
         <v>18</v>
@@ -7618,13 +7621,13 @@
         <v>15</v>
       </c>
       <c r="K86">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L86">
         <v>21</v>
       </c>
       <c r="M86">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7673,13 +7676,13 @@
         <v>94</v>
       </c>
       <c r="B88">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C88">
         <v>41</v>
       </c>
       <c r="D88">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E88">
         <v>38</v>
@@ -7688,13 +7691,13 @@
         <v>38</v>
       </c>
       <c r="G88">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H88">
         <v>32</v>
       </c>
       <c r="I88">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J88">
         <v>28</v>
@@ -7706,7 +7709,7 @@
         <v>42</v>
       </c>
       <c r="M88">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7723,16 +7726,16 @@
         <v>42</v>
       </c>
       <c r="E89">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F89">
         <v>42</v>
       </c>
       <c r="G89">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H89">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I89">
         <v>26</v>
@@ -7744,10 +7747,10 @@
         <v>52</v>
       </c>
       <c r="L89">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M89">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7755,19 +7758,19 @@
         <v>96</v>
       </c>
       <c r="B90">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E90">
         <v>29</v>
       </c>
       <c r="F90">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G90">
         <v>30</v>
@@ -7776,19 +7779,19 @@
         <v>35</v>
       </c>
       <c r="I90">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J90">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K90">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L90">
         <v>24</v>
       </c>
       <c r="M90">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7808,10 +7811,10 @@
         <v>39</v>
       </c>
       <c r="F91">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G91">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H91">
         <v>27</v>
@@ -7820,7 +7823,7 @@
         <v>42</v>
       </c>
       <c r="J91">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K91">
         <v>38</v>
@@ -7864,13 +7867,13 @@
         <v>11</v>
       </c>
       <c r="K92">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L92">
         <v>7</v>
       </c>
       <c r="M92">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7884,7 +7887,7 @@
         <v>23</v>
       </c>
       <c r="D93">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E93">
         <v>17</v>
@@ -7896,7 +7899,7 @@
         <v>22</v>
       </c>
       <c r="H93">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I93">
         <v>15</v>
@@ -7905,7 +7908,7 @@
         <v>17</v>
       </c>
       <c r="K93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L93">
         <v>14</v>
@@ -7919,19 +7922,19 @@
         <v>100</v>
       </c>
       <c r="B94">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C94">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D94">
         <v>27</v>
       </c>
       <c r="E94">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F94">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G94">
         <v>24</v>
@@ -7943,10 +7946,10 @@
         <v>29</v>
       </c>
       <c r="J94">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K94">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L94">
         <v>37</v>
@@ -7960,13 +7963,13 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C95">
         <v>45</v>
       </c>
       <c r="D95">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E95">
         <v>55</v>
@@ -7975,7 +7978,7 @@
         <v>54</v>
       </c>
       <c r="G95">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H95">
         <v>67</v>
@@ -7987,13 +7990,13 @@
         <v>69</v>
       </c>
       <c r="K95">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L95">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M95">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8001,37 +8004,37 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C96">
         <v>36</v>
       </c>
       <c r="D96">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E96">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F96">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G96">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H96">
         <v>25</v>
       </c>
       <c r="I96">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J96">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K96">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L96">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M96">
         <v>23</v>
@@ -8051,7 +8054,7 @@
         <v>34</v>
       </c>
       <c r="E97">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F97">
         <v>20</v>
@@ -8063,19 +8066,19 @@
         <v>22</v>
       </c>
       <c r="I97">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>20</v>
       </c>
       <c r="K97">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L97">
         <v>36</v>
       </c>
       <c r="M97">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8107,7 +8110,7 @@
         <v>22</v>
       </c>
       <c r="J98">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K98">
         <v>21</v>
@@ -8124,40 +8127,40 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C99">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D99">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F99">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G99">
         <v>67</v>
       </c>
       <c r="H99">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I99">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J99">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K99">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L99">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M99">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8206,40 +8209,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2781</v>
+        <v>2829</v>
       </c>
       <c r="C101">
-        <v>3577</v>
+        <v>3628</v>
       </c>
       <c r="D101">
-        <v>3934</v>
+        <v>3988</v>
       </c>
       <c r="E101">
-        <v>3447</v>
+        <v>3529</v>
       </c>
       <c r="F101">
-        <v>3120</v>
+        <v>3161</v>
       </c>
       <c r="G101">
-        <v>3392</v>
+        <v>3439</v>
       </c>
       <c r="H101">
-        <v>3125</v>
+        <v>3179</v>
       </c>
       <c r="I101">
-        <v>3284</v>
+        <v>3328</v>
       </c>
       <c r="J101">
-        <v>3705</v>
+        <v>3770</v>
       </c>
       <c r="K101">
-        <v>3598</v>
+        <v>3673</v>
       </c>
       <c r="L101">
-        <v>2874</v>
+        <v>2922</v>
       </c>
       <c r="M101">
-        <v>2563</v>
+        <v>2602</v>
       </c>
     </row>
   </sheetData>
@@ -8512,7 +8515,7 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -8591,7 +8594,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>13</v>
@@ -8620,7 +8623,7 @@
         <v>35</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7">
         <v>19</v>
@@ -8632,7 +8635,7 @@
         <v>24</v>
       </c>
       <c r="K7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7">
         <v>30</v>
@@ -8712,10 +8715,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>27</v>
@@ -8724,7 +8727,7 @@
         <v>30</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
         <v>38</v>
@@ -8739,7 +8742,7 @@
         <v>28</v>
       </c>
       <c r="K2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2">
         <v>28</v>
@@ -8753,25 +8756,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>58</v>
       </c>
       <c r="D3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>44</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -8780,13 +8783,13 @@
         <v>56</v>
       </c>
       <c r="K3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L3">
         <v>30</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8873,34 +8876,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>62</v>
+      </c>
+      <c r="E6">
+        <v>53</v>
+      </c>
+      <c r="F6">
+        <v>36</v>
+      </c>
+      <c r="G6">
         <v>58</v>
       </c>
-      <c r="D6">
-        <v>61</v>
-      </c>
-      <c r="E6">
-        <v>52</v>
-      </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
-        <v>55</v>
-      </c>
       <c r="H6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6">
         <v>41</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -8914,40 +8917,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F7">
+        <v>125</v>
+      </c>
+      <c r="G7">
+        <v>147</v>
+      </c>
+      <c r="H7">
         <v>122</v>
-      </c>
-      <c r="G7">
-        <v>143</v>
-      </c>
-      <c r="H7">
-        <v>119</v>
       </c>
       <c r="I7">
         <v>126</v>
       </c>
       <c r="J7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="L7">
         <v>106</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -9024,7 +9027,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -9065,22 +9068,22 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>6</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -9152,7 +9155,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>13</v>
@@ -9161,7 +9164,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -9182,7 +9185,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -9193,25 +9196,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>29</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>28</v>
@@ -9223,7 +9226,7 @@
         <v>28</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>11</v>
@@ -9315,7 +9318,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -9359,13 +9362,13 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>4</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -9437,7 +9440,7 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>15</v>
@@ -9478,10 +9481,10 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>11</v>
@@ -9490,13 +9493,13 @@
         <v>12</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>21</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>18</v>
@@ -9576,19 +9579,19 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -9620,7 +9623,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -9644,7 +9647,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3">
         <v>14</v>
@@ -9676,7 +9679,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -9725,7 +9728,7 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6">
         <v>34</v>
@@ -9737,10 +9740,10 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6">
         <v>24</v>
@@ -9760,34 +9763,34 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F7">
         <v>59</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7">
         <v>32</v>
       </c>
       <c r="I7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7">
         <v>66</v>
       </c>
       <c r="L7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M7">
         <v>51</v>
@@ -9864,25 +9867,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>42</v>
       </c>
       <c r="D2">
+        <v>59</v>
+      </c>
+      <c r="E2">
+        <v>52</v>
+      </c>
+      <c r="F2">
+        <v>46</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
         <v>56</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <v>45</v>
-      </c>
-      <c r="G2">
-        <v>49</v>
-      </c>
-      <c r="H2">
-        <v>55</v>
       </c>
       <c r="I2">
         <v>53</v>
@@ -9891,13 +9894,13 @@
         <v>54</v>
       </c>
       <c r="K2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2">
         <v>46</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9908,31 +9911,31 @@
         <v>66</v>
       </c>
       <c r="C3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L3">
         <v>45</v>
@@ -9946,7 +9949,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>14</v>
@@ -10028,31 +10031,31 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I6">
         <v>87</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K6">
         <v>68</v>
@@ -10069,40 +10072,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L7">
         <v>137</v>
       </c>
       <c r="M7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -10209,7 +10212,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10267,7 +10270,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10288,7 +10291,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M4">
         <v>11</v>
@@ -10319,16 +10322,16 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>13</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -10337,7 +10340,7 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <v>17</v>
@@ -10360,16 +10363,16 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>31</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
         <v>26</v>
@@ -10378,13 +10381,13 @@
         <v>23</v>
       </c>
       <c r="K7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -10461,10 +10464,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -10473,7 +10476,7 @@
         <v>26</v>
       </c>
       <c r="G2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>20</v>
@@ -10491,7 +10494,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10499,10 +10502,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>23</v>
@@ -10590,7 +10593,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -10608,7 +10611,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -10622,7 +10625,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>44</v>
@@ -10631,28 +10634,28 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>30</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K6">
         <v>26</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6">
         <v>22</v>
@@ -10663,40 +10666,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F7">
         <v>96</v>
       </c>
       <c r="G7">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H7">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I7">
+        <v>89</v>
+      </c>
+      <c r="J7">
+        <v>124</v>
+      </c>
+      <c r="K7">
+        <v>97</v>
+      </c>
+      <c r="L7">
+        <v>93</v>
+      </c>
+      <c r="M7">
         <v>87</v>
-      </c>
-      <c r="J7">
-        <v>123</v>
-      </c>
-      <c r="K7">
-        <v>94</v>
-      </c>
-      <c r="L7">
-        <v>92</v>
-      </c>
-      <c r="M7">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -10832,13 +10835,13 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -10861,7 +10864,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -10898,6 +10901,9 @@
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -10905,7 +10911,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -10919,16 +10925,16 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>23</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -10960,16 +10966,16 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>37</v>
@@ -10978,13 +10984,13 @@
         <v>37</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7">
         <v>27</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -11067,7 +11073,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -11091,7 +11097,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -11132,10 +11138,10 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>9</v>
@@ -11173,7 +11179,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -11204,7 +11210,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -11219,7 +11225,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <v>34</v>
@@ -11242,10 +11248,10 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>36</v>
@@ -11260,16 +11266,16 @@
         <v>29</v>
       </c>
       <c r="I7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7">
         <v>60</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M7">
         <v>35</v>
@@ -11501,7 +11507,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -11539,7 +11545,7 @@
         <v>16</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7">
         <v>15</v>
@@ -11628,7 +11634,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -11649,7 +11655,7 @@
         <v>11</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>10</v>
@@ -11690,7 +11696,7 @@
         <v>9</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -11747,6 +11753,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -11759,7 +11768,7 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -11768,7 +11777,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -11797,10 +11806,10 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -11809,7 +11818,7 @@
         <v>20</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>19</v>
@@ -11818,7 +11827,7 @@
         <v>26</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K7">
         <v>27</v>
@@ -11910,7 +11919,7 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -11986,7 +11995,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -12038,7 +12047,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -12076,13 +12085,13 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -12183,7 +12192,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>35</v>
@@ -12201,16 +12210,16 @@
         <v>31</v>
       </c>
       <c r="I2">
+        <v>32</v>
+      </c>
+      <c r="J2">
         <v>29</v>
       </c>
-      <c r="J2">
-        <v>28</v>
-      </c>
       <c r="K2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -12221,7 +12230,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -12230,16 +12239,16 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3">
         <v>28</v>
@@ -12289,7 +12298,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -12344,31 +12353,31 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6">
         <v>42</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>25</v>
       </c>
       <c r="J6">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6">
         <v>43</v>
@@ -12382,37 +12391,37 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>116</v>
+      </c>
+      <c r="C7">
+        <v>141</v>
+      </c>
+      <c r="D7">
+        <v>164</v>
+      </c>
+      <c r="E7">
+        <v>127</v>
+      </c>
+      <c r="F7">
+        <v>122</v>
+      </c>
+      <c r="G7">
         <v>113</v>
       </c>
-      <c r="C7">
-        <v>138</v>
-      </c>
-      <c r="D7">
-        <v>163</v>
-      </c>
-      <c r="E7">
+      <c r="H7">
         <v>124</v>
       </c>
-      <c r="F7">
-        <v>120</v>
-      </c>
-      <c r="G7">
-        <v>111</v>
-      </c>
-      <c r="H7">
-        <v>121</v>
-      </c>
       <c r="I7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K7">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M7">
         <v>80</v>
@@ -12570,7 +12579,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -12602,7 +12611,7 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -12715,7 +12724,7 @@
         <v>8</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -12726,7 +12735,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -12738,7 +12747,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -12854,7 +12863,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>29</v>
@@ -12866,7 +12875,7 @@
         <v>44</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>30</v>
@@ -12884,7 +12893,7 @@
         <v>22</v>
       </c>
       <c r="L7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -12991,7 +13000,7 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>10</v>
@@ -13011,7 +13020,7 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -13026,16 +13035,16 @@
         <v>14</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3">
         <v>9</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13064,7 +13073,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -13083,6 +13092,9 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5">
         <v>1</v>
       </c>
@@ -13090,6 +13102,9 @@
         <v>1</v>
       </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
@@ -13101,10 +13116,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -13116,7 +13131,7 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>31</v>
@@ -13131,7 +13146,7 @@
         <v>19</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -13142,40 +13157,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>45</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>31</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7">
         <v>51</v>
       </c>
       <c r="I7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -13279,7 +13294,7 @@
         <v>11</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -13308,13 +13323,13 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>8</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -13334,7 +13349,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -13346,19 +13361,19 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -13401,7 +13416,7 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -13439,10 +13454,10 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>26</v>
@@ -13451,19 +13466,19 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M7">
         <v>35</v>
@@ -13570,7 +13585,7 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -13677,7 +13692,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -13715,7 +13730,7 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -13727,7 +13742,7 @@
         <v>13</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>11</v>
@@ -13860,7 +13875,7 @@
         <v>3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -13920,13 +13935,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -13947,7 +13962,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -13961,13 +13976,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -13985,10 +14000,10 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -14153,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -14217,7 +14232,7 @@
         <v>23</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -14249,7 +14264,7 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>48</v>
@@ -14258,7 +14273,7 @@
         <v>39</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>40</v>
@@ -14368,7 +14383,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -14377,13 +14392,13 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -14456,7 +14471,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -14496,19 +14511,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -14537,37 +14552,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>36</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7">
         <v>25</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7">
         <v>23</v>
@@ -14656,7 +14671,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -14700,7 +14715,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -14709,7 +14724,7 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3">
         <v>12</v>
@@ -14738,7 +14753,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -14837,10 +14852,10 @@
         <v>39</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>27</v>
@@ -14849,7 +14864,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K7">
         <v>38</v>
@@ -14991,7 +15006,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -15042,7 +15057,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>25</v>
@@ -15083,7 +15098,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>29</v>
@@ -15095,7 +15110,7 @@
         <v>13</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -15175,7 +15190,7 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -15187,13 +15202,13 @@
         <v>31</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2">
         <v>31</v>
@@ -15213,7 +15228,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>27</v>
@@ -15225,16 +15240,16 @@
         <v>24</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>35</v>
       </c>
       <c r="I3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3">
         <v>37</v>
@@ -15263,7 +15278,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -15272,16 +15287,16 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>6</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -15295,7 +15310,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -15322,7 +15337,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -15336,19 +15351,19 @@
         <v>47</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>19</v>
       </c>
       <c r="G6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6">
         <v>35</v>
@@ -15363,7 +15378,7 @@
         <v>23</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
         <v>16</v>
@@ -15374,37 +15389,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D7">
         <v>102</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>112</v>
       </c>
       <c r="K7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M7">
         <v>67</v>
@@ -15549,7 +15564,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -15586,6 +15601,9 @@
       <c r="L4">
         <v>5</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -15648,7 +15666,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -15686,13 +15704,13 @@
         <v>20</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -15772,10 +15790,10 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>29</v>
@@ -15784,7 +15802,7 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2">
         <v>22</v>
@@ -15793,7 +15811,7 @@
         <v>20</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L2">
         <v>21</v>
@@ -15810,19 +15828,19 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>20</v>
@@ -15837,7 +15855,7 @@
         <v>26</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <v>22</v>
@@ -15860,7 +15878,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -15927,7 +15945,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -15936,7 +15954,7 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F6">
         <v>41</v>
@@ -15948,7 +15966,7 @@
         <v>19</v>
       </c>
       <c r="I6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>26</v>
@@ -15968,37 +15986,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J7">
         <v>81</v>
       </c>
       <c r="K7">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M7">
         <v>73</v>
@@ -16108,7 +16126,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16119,7 +16137,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -16140,7 +16158,7 @@
         <v>6</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>6</v>
@@ -16149,7 +16167,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16212,7 +16230,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -16238,7 +16256,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -16253,13 +16271,13 @@
         <v>12</v>
       </c>
       <c r="H7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I7">
         <v>28</v>
       </c>
       <c r="J7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K7">
         <v>28</v>
@@ -16268,7 +16286,7 @@
         <v>22</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -16417,6 +16435,9 @@
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
@@ -16479,7 +16500,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -16586,7 +16607,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -16601,7 +16622,7 @@
         <v>9</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K2">
         <v>15</v>
@@ -16618,10 +16639,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -16630,13 +16651,13 @@
         <v>22</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>9</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3">
         <v>9</v>
@@ -16674,7 +16695,7 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -16738,7 +16759,7 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -16770,31 +16791,31 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
         <v>39</v>
-      </c>
-      <c r="C7">
-        <v>38</v>
       </c>
       <c r="D7">
         <v>37</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7">
         <v>44</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K7">
         <v>43</v>
@@ -16904,7 +16925,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -16974,7 +16995,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -17005,7 +17026,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -17046,7 +17067,7 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -17058,7 +17079,7 @@
         <v>22</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>15</v>
@@ -17067,7 +17088,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>14</v>
@@ -17360,10 +17381,10 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -17387,7 +17408,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17404,28 +17425,28 @@
         <v>49</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>28</v>
       </c>
       <c r="G3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3">
         <v>29</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3">
         <v>25</v>
@@ -17454,7 +17475,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -17466,10 +17487,10 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17518,13 +17539,13 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>36</v>
@@ -17539,10 +17560,10 @@
         <v>33</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L6">
         <v>29</v>
@@ -17559,37 +17580,37 @@
         <v>113</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>110</v>
       </c>
       <c r="G7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I7">
         <v>109</v>
       </c>
       <c r="J7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M7">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -17690,7 +17711,7 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -17859,7 +17880,7 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -17938,6 +17959,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>3</v>
       </c>
@@ -17986,10 +18010,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -18004,7 +18028,7 @@
         <v>6</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>9</v>
@@ -18035,6 +18059,9 @@
       <c r="I4">
         <v>2</v>
       </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>4</v>
       </c>
@@ -18064,7 +18091,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -18102,19 +18129,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>27</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>24</v>
@@ -18126,10 +18153,10 @@
         <v>29</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7">
         <v>37</v>
@@ -18227,7 +18254,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -18262,7 +18289,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -18355,7 +18382,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -18384,16 +18411,16 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>19</v>
@@ -18479,7 +18506,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -18503,7 +18530,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -18610,6 +18637,9 @@
       <c r="H5">
         <v>2</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="K5">
         <v>1</v>
       </c>
@@ -18619,7 +18649,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -18637,7 +18667,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -18660,7 +18690,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -18678,13 +18708,13 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7">
         <v>25</v>
@@ -18776,7 +18806,7 @@
         <v>11</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>6</v>
@@ -18785,7 +18815,7 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -18794,13 +18824,13 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18811,10 +18841,10 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -18832,10 +18862,10 @@
         <v>9</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -18919,7 +18949,7 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -18937,13 +18967,13 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18954,13 +18984,13 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F7">
         <v>27</v>
@@ -18969,22 +18999,22 @@
         <v>21</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -19201,7 +19231,7 @@
         <v>17</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K6">
         <v>16</v>
@@ -19242,7 +19272,7 @@
         <v>22</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>21</v>
@@ -19343,10 +19373,13 @@
         <v>5</v>
       </c>
       <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -19387,7 +19420,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -19515,13 +19548,13 @@
         <v>15</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K7">
         <v>24</v>
@@ -19676,7 +19709,7 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -19717,7 +19750,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -19861,6 +19894,9 @@
       <c r="J5">
         <v>4</v>
       </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
@@ -19897,7 +19933,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -20202,7 +20238,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>13</v>
@@ -20211,13 +20247,13 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>9</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>17</v>
@@ -20270,7 +20306,7 @@
         <v>11</v>
       </c>
       <c r="K3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3">
         <v>17</v>
@@ -20299,7 +20335,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -20357,10 +20393,10 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -20378,7 +20414,7 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -20392,22 +20428,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>58</v>
       </c>
       <c r="D7">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7">
         <v>51</v>
       </c>
       <c r="G7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H7">
         <v>46</v>
@@ -20419,7 +20455,7 @@
         <v>43</v>
       </c>
       <c r="K7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L7">
         <v>46</v>
@@ -20505,7 +20541,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -20524,6 +20560,9 @@
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="M3">
         <v>2</v>
       </c>
@@ -20571,7 +20610,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -20603,19 +20642,19 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -20704,7 +20743,7 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -20716,7 +20755,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -20748,7 +20787,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -20757,7 +20796,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -20766,7 +20805,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -20818,7 +20857,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -20859,7 +20898,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -20885,28 +20924,28 @@
         <v>22</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>19</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>18</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7">
         <v>16</v>
@@ -21030,7 +21069,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -21144,7 +21183,7 @@
         <v>17</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -21161,7 +21200,7 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>34</v>
@@ -21185,7 +21224,7 @@
         <v>41</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -21300,7 +21339,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -21378,7 +21417,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -21398,7 +21437,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -21416,7 +21455,7 @@
         <v>4</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -21502,13 +21541,13 @@
         <v>7</v>
       </c>
       <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>7</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -21517,7 +21556,7 @@
         <v>9</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>9</v>
@@ -21526,7 +21565,7 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -21540,7 +21579,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -21549,7 +21588,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -21564,7 +21603,7 @@
         <v>12</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -21633,7 +21672,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -21654,7 +21693,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -21674,16 +21713,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -21692,16 +21731,16 @@
         <v>31</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>17</v>
@@ -21805,13 +21844,13 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21915,7 +21954,7 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -21927,7 +21966,7 @@
         <v>16</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6">
         <v>14</v>
@@ -21956,7 +21995,7 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -21968,19 +22007,19 @@
         <v>22</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
         <v>36</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -22087,7 +22126,7 @@
         <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22185,7 +22224,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -22226,13 +22265,13 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -22394,6 +22433,9 @@
       <c r="C5">
         <v>2</v>
       </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
@@ -22427,7 +22469,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -22558,7 +22600,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22566,13 +22608,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -22683,13 +22725,13 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>17</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -22709,13 +22751,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>41</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>38</v>
@@ -22724,13 +22766,13 @@
         <v>38</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7">
         <v>32</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <v>28</v>
@@ -22742,7 +22784,7 @@
         <v>42</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -22828,7 +22870,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -22894,6 +22936,9 @@
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
@@ -22955,13 +23000,13 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -23062,10 +23107,10 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -23121,7 +23166,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23138,7 +23183,7 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -23162,7 +23207,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23220,7 +23265,7 @@
         <v>17</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -23240,16 +23285,16 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>42</v>
       </c>
       <c r="G7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>26</v>
@@ -23261,10 +23306,10 @@
         <v>52</v>
       </c>
       <c r="L7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -23396,6 +23441,9 @@
       <c r="G3">
         <v>2</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3">
         <v>1</v>
       </c>
@@ -23493,7 +23541,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>15</v>
@@ -23591,7 +23639,7 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -23623,7 +23671,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -23638,7 +23686,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -23731,7 +23779,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>13</v>
@@ -23746,7 +23794,7 @@
         <v>20</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -23757,7 +23805,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -23766,13 +23814,13 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>22</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>24</v>
@@ -23787,7 +23835,7 @@
         <v>45</v>
       </c>
       <c r="L7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M7">
         <v>31</v>
@@ -23926,7 +23974,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -23949,7 +23997,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -23967,13 +24015,13 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4">
         <v>14</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24031,7 +24079,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>18</v>
@@ -24049,13 +24097,13 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>21</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -24144,7 +24192,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -24153,7 +24201,7 @@
         <v>8</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -24197,7 +24245,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -24304,7 +24352,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -24313,10 +24361,10 @@
         <v>16</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M7">
         <v>11</v>
@@ -24396,7 +24444,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -24405,7 +24453,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -24414,19 +24462,19 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2">
         <v>11</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>12</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24539,19 +24587,22 @@
       <c r="L5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>30</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -24569,7 +24620,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -24586,19 +24637,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>29</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>30</v>
@@ -24607,19 +24658,19 @@
         <v>35</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>24</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -24696,7 +24747,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -24726,7 +24777,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24848,19 +24899,19 @@
         <v>15</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>16</v>
@@ -24880,7 +24931,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -24889,19 +24940,19 @@
         <v>40</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>35</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7">
         <v>49</v>
@@ -24910,7 +24961,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -25002,7 +25053,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -25040,7 +25091,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -25106,7 +25157,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -25144,7 +25195,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -25153,7 +25204,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -25245,7 +25296,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -25315,7 +25366,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -25393,7 +25444,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -25402,7 +25453,7 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -25503,7 +25554,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -25556,7 +25607,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -25640,7 +25691,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -25672,7 +25723,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -25681,10 +25732,10 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7">
         <v>25</v>
@@ -25823,7 +25874,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -25919,10 +25970,10 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>28</v>
@@ -25951,7 +26002,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>25</v>
@@ -25960,10 +26011,10 @@
         <v>29</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7">
         <v>43</v>
@@ -26052,13 +26103,13 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>26</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>33</v>
@@ -26067,19 +26118,19 @@
         <v>30</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2">
         <v>38</v>
@@ -26096,10 +26147,10 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F3">
         <v>50</v>
@@ -26108,22 +26159,22 @@
         <v>54</v>
       </c>
       <c r="H3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I3">
+        <v>59</v>
+      </c>
+      <c r="J3">
+        <v>51</v>
+      </c>
+      <c r="K3">
+        <v>59</v>
+      </c>
+      <c r="L3">
+        <v>64</v>
+      </c>
+      <c r="M3">
         <v>58</v>
-      </c>
-      <c r="J3">
-        <v>50</v>
-      </c>
-      <c r="K3">
-        <v>57</v>
-      </c>
-      <c r="L3">
-        <v>63</v>
-      </c>
-      <c r="M3">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26140,7 +26191,7 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -26222,7 +26273,7 @@
         <v>56</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>48</v>
@@ -26231,7 +26282,7 @@
         <v>47</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6">
         <v>52</v>
@@ -26240,13 +26291,13 @@
         <v>44</v>
       </c>
       <c r="K6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26257,13 +26308,13 @@
         <v>136</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E7">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F7">
         <v>146</v>
@@ -26272,19 +26323,19 @@
         <v>145</v>
       </c>
       <c r="H7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M7">
         <v>128</v>
@@ -26495,7 +26546,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -26530,7 +26581,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -26732,7 +26783,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -26773,7 +26824,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -26912,7 +26963,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -26976,7 +27027,7 @@
         <v>14</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -27017,7 +27068,7 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -27026,7 +27077,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>14</v>
@@ -27189,7 +27240,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -27198,7 +27249,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -27224,16 +27275,16 @@
         <v>6</v>
       </c>
       <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
         <v>7</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -27378,7 +27429,7 @@
         <v>5</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -27465,7 +27516,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -27506,7 +27557,7 @@
         <v>20</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -27515,7 +27566,7 @@
         <v>21</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <v>25</v>
@@ -27880,7 +27931,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>4</v>
@@ -27921,7 +27972,7 @@
         <v>8</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -28567,6 +28618,9 @@
       <c r="H6">
         <v>1</v>
       </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
       <c r="J6">
         <v>2</v>
       </c>
@@ -28603,7 +28657,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -28692,13 +28746,13 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>16</v>
@@ -28722,7 +28776,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28754,16 +28808,16 @@
         <v>25</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3">
         <v>15</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28897,13 +28951,13 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7">
         <v>94</v>
       </c>
       <c r="E7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>64</v>
@@ -28918,16 +28972,16 @@
         <v>67</v>
       </c>
       <c r="J7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L7">
         <v>52</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -29022,7 +29076,7 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -29147,7 +29201,7 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>11</v>
@@ -29334,7 +29388,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -29343,7 +29397,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -29372,7 +29426,7 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -29384,7 +29438,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -29737,7 +29791,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -29853,7 +29907,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -30033,7 +30087,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -30071,7 +30125,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -30660,7 +30714,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -30719,6 +30773,9 @@
       <c r="J5">
         <v>2</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
@@ -30752,7 +30809,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -30812,7 +30869,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -30868,7 +30925,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>2</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="107">
   <si>
     <t>crime_category</t>
   </si>
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C2">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="D2">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="E2">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="F2">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="G2">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="I2">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="J2">
-        <v>949</v>
+        <v>971</v>
       </c>
       <c r="K2">
-        <v>1038</v>
+        <v>1055</v>
       </c>
       <c r="L2">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="M2">
-        <v>784</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="C3">
-        <v>938</v>
+        <v>961</v>
       </c>
       <c r="D3">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="E3">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F3">
-        <v>903</v>
+        <v>917</v>
       </c>
       <c r="G3">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="H3">
-        <v>867</v>
+        <v>881</v>
       </c>
       <c r="I3">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="J3">
-        <v>1042</v>
+        <v>1062</v>
       </c>
       <c r="K3">
-        <v>983</v>
+        <v>1006</v>
       </c>
       <c r="L3">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="M3">
-        <v>871</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -953,37 +953,37 @@
         <v>330</v>
       </c>
       <c r="C4">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D4">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E4">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F4">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G4">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="H4">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I4">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J4">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K4">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L4">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M4">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,37 +994,37 @@
         <v>50</v>
       </c>
       <c r="C5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F5">
         <v>47</v>
       </c>
       <c r="G5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I5">
         <v>95</v>
       </c>
       <c r="J5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K5">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L5">
         <v>60</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1206</v>
+        <v>1217</v>
       </c>
       <c r="C6">
-        <v>1652</v>
+        <v>1682</v>
       </c>
       <c r="D6">
-        <v>1792</v>
+        <v>1816</v>
       </c>
       <c r="E6">
-        <v>1485</v>
+        <v>1499</v>
       </c>
       <c r="F6">
-        <v>1102</v>
+        <v>1118</v>
       </c>
       <c r="G6">
-        <v>1289</v>
+        <v>1306</v>
       </c>
       <c r="H6">
-        <v>1159</v>
+        <v>1175</v>
       </c>
       <c r="I6">
-        <v>1241</v>
+        <v>1271</v>
       </c>
       <c r="J6">
-        <v>1418</v>
+        <v>1432</v>
       </c>
       <c r="K6">
-        <v>1322</v>
+        <v>1352</v>
       </c>
       <c r="L6">
-        <v>901</v>
+        <v>917</v>
       </c>
       <c r="M6">
-        <v>647</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2829</v>
+        <v>2855</v>
       </c>
       <c r="C7">
-        <v>3628</v>
+        <v>3698</v>
       </c>
       <c r="D7">
-        <v>3988</v>
+        <v>4048</v>
       </c>
       <c r="E7">
-        <v>3529</v>
+        <v>3576</v>
       </c>
       <c r="F7">
-        <v>3161</v>
+        <v>3206</v>
       </c>
       <c r="G7">
-        <v>3439</v>
+        <v>3493</v>
       </c>
       <c r="H7">
-        <v>3179</v>
+        <v>3239</v>
       </c>
       <c r="I7">
-        <v>3328</v>
+        <v>3394</v>
       </c>
       <c r="J7">
-        <v>3770</v>
+        <v>3829</v>
       </c>
       <c r="K7">
-        <v>3673</v>
+        <v>3747</v>
       </c>
       <c r="L7">
-        <v>2922</v>
+        <v>2969</v>
       </c>
       <c r="M7">
-        <v>2602</v>
+        <v>2651</v>
       </c>
     </row>
   </sheetData>
@@ -1200,6 +1200,9 @@
       <c r="I2">
         <v>3</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
         <v>3</v>
       </c>
@@ -1215,7 +1218,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1305,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -1322,7 +1325,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1346,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>15</v>
@@ -1561,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>5</v>
@@ -1590,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>11</v>
@@ -1608,7 +1611,7 @@
         <v>10</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3">
         <v>11</v>
@@ -1724,7 +1727,7 @@
         <v>53</v>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7">
         <v>45</v>
@@ -1736,13 +1739,13 @@
         <v>35</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>38</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7">
         <v>46</v>
@@ -1825,31 +1828,31 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>49</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2">
         <v>50</v>
       </c>
       <c r="F2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>58</v>
       </c>
       <c r="I2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K2">
         <v>60</v>
@@ -1858,7 +1861,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1869,37 +1872,37 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E3">
         <v>64</v>
       </c>
       <c r="F3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L3">
         <v>57</v>
       </c>
       <c r="M3">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1925,13 +1928,13 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>13</v>
       </c>
       <c r="J4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4">
         <v>14</v>
@@ -1940,7 +1943,7 @@
         <v>14</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1963,7 +1966,7 @@
         <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -1992,7 +1995,7 @@
         <v>81</v>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D6">
         <v>131</v>
@@ -2001,28 +2004,28 @@
         <v>114</v>
       </c>
       <c r="F6">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H6">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J6">
         <v>67</v>
       </c>
       <c r="K6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L6">
         <v>58</v>
       </c>
       <c r="M6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2030,40 +2033,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E7">
         <v>251</v>
       </c>
       <c r="F7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L7">
         <v>182</v>
       </c>
       <c r="M7">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2158,7 +2161,7 @@
         <v>19</v>
       </c>
       <c r="I2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2">
         <v>23</v>
@@ -2170,7 +2173,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2181,13 +2184,13 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -2205,10 +2208,10 @@
         <v>29</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3">
         <v>27</v>
@@ -2322,7 +2325,7 @@
         <v>30</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>15</v>
@@ -2339,13 +2342,13 @@
         <v>62</v>
       </c>
       <c r="C7">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7">
         <v>57</v>
@@ -2357,19 +2360,19 @@
         <v>65</v>
       </c>
       <c r="I7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7">
         <v>88</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2443,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>28</v>
@@ -2452,7 +2455,7 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -2461,7 +2464,7 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2">
         <v>33</v>
@@ -2470,10 +2473,10 @@
         <v>35</v>
       </c>
       <c r="K2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2">
         <v>22</v>
@@ -2487,7 +2490,7 @@
         <v>34</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>48</v>
@@ -2496,25 +2499,25 @@
         <v>69</v>
       </c>
       <c r="F3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3">
         <v>41</v>
       </c>
       <c r="K3">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M3">
         <v>29</v>
@@ -2540,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -2607,37 +2610,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>84</v>
       </c>
       <c r="F6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6">
         <v>70</v>
       </c>
       <c r="K6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M6">
         <v>28</v>
@@ -2648,37 +2651,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J7">
         <v>157</v>
       </c>
       <c r="K7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M7">
         <v>88</v>
@@ -2767,16 +2770,16 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <v>18</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -2788,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2808,10 +2811,10 @@
         <v>16</v>
       </c>
       <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
         <v>20</v>
-      </c>
-      <c r="G3">
-        <v>19</v>
       </c>
       <c r="H3">
         <v>28</v>
@@ -2884,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2934,7 +2937,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>21</v>
@@ -2943,7 +2946,7 @@
         <v>19</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -2963,19 +2966,19 @@
         <v>67</v>
       </c>
       <c r="E7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J7">
         <v>69</v>
@@ -2984,10 +2987,10 @@
         <v>61</v>
       </c>
       <c r="L7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3070,31 +3073,31 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>32</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K2">
         <v>27</v>
       </c>
       <c r="L2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3102,28 +3105,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>37</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3">
         <v>31</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3">
         <v>41</v>
@@ -3170,7 +3173,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -3208,7 +3211,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -3219,25 +3222,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6">
         <v>33</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>27</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6">
         <v>31</v>
@@ -3246,10 +3249,10 @@
         <v>42</v>
       </c>
       <c r="K6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M6">
         <v>27</v>
@@ -3260,40 +3263,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G7">
         <v>94</v>
       </c>
       <c r="H7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3391,10 +3394,10 @@
         <v>15</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L2">
         <v>19</v>
@@ -3411,22 +3414,22 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>28</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3">
         <v>24</v>
@@ -3441,7 +3444,7 @@
         <v>17</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3458,7 +3461,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3470,7 +3473,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -3525,16 +3528,16 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -3543,7 +3546,7 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>42</v>
@@ -3566,37 +3569,37 @@
         <v>52</v>
       </c>
       <c r="C7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>54</v>
       </c>
       <c r="H7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L7">
         <v>60</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3688,7 +3691,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>21</v>
@@ -3720,7 +3723,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -3732,13 +3735,13 @@
         <v>21</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>19</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>21</v>
@@ -3831,7 +3834,7 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6">
         <v>14</v>
@@ -3849,7 +3852,7 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>20</v>
@@ -3872,10 +3875,10 @@
         <v>50</v>
       </c>
       <c r="D7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7">
         <v>62</v>
@@ -3884,16 +3887,16 @@
         <v>67</v>
       </c>
       <c r="H7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7">
         <v>47</v>
@@ -3982,7 +3985,7 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>6</v>
@@ -4124,7 +4127,7 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>15</v>
@@ -4225,7 +4228,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -4240,10 +4243,10 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J2">
         <v>32</v>
@@ -4252,7 +4255,7 @@
         <v>26</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>23</v>
@@ -4310,7 +4313,7 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -4334,10 +4337,10 @@
         <v>15</v>
       </c>
       <c r="L4">
+        <v>12</v>
+      </c>
+      <c r="M4">
         <v>11</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4348,22 +4351,22 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>19</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>15</v>
@@ -4375,10 +4378,10 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4389,10 +4392,10 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>35</v>
@@ -4410,7 +4413,7 @@
         <v>26</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6">
         <v>27</v>
@@ -4419,7 +4422,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4430,37 +4433,37 @@
         <v>113</v>
       </c>
       <c r="C7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G7">
         <v>95</v>
       </c>
       <c r="H7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K7">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4468,40 +4471,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D8">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E8">
         <v>251</v>
       </c>
       <c r="F8">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G8">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H8">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I8">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J8">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L8">
         <v>182</v>
       </c>
       <c r="M8">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4539,10 +4542,10 @@
         <v>18</v>
       </c>
       <c r="L9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4556,7 +4559,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>44</v>
@@ -4577,7 +4580,7 @@
         <v>24</v>
       </c>
       <c r="K10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10">
         <v>15</v>
@@ -4591,7 +4594,7 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>58</v>
@@ -4600,7 +4603,7 @@
         <v>73</v>
       </c>
       <c r="E11">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11">
         <v>51</v>
@@ -4612,13 +4615,13 @@
         <v>46</v>
       </c>
       <c r="I11">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L11">
         <v>46</v>
@@ -4632,7 +4635,7 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -4665,7 +4668,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4679,7 +4682,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -4711,7 +4714,7 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>22</v>
@@ -4749,16 +4752,16 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>43</v>
       </c>
       <c r="D15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>27</v>
@@ -4773,7 +4776,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K15">
         <v>25</v>
@@ -4782,7 +4785,7 @@
         <v>21</v>
       </c>
       <c r="M15">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4831,10 +4834,10 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -4869,7 +4872,7 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>15</v>
@@ -4913,13 +4916,13 @@
         <v>69</v>
       </c>
       <c r="C19">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E19">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19">
         <v>96</v>
@@ -4928,19 +4931,19 @@
         <v>104</v>
       </c>
       <c r="H19">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I19">
         <v>89</v>
       </c>
       <c r="J19">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K19">
         <v>97</v>
       </c>
       <c r="L19">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M19">
         <v>87</v>
@@ -4951,37 +4954,37 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C20">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20">
+        <v>94</v>
+      </c>
+      <c r="E20">
+        <v>128</v>
+      </c>
+      <c r="F20">
+        <v>112</v>
+      </c>
+      <c r="G20">
+        <v>75</v>
+      </c>
+      <c r="H20">
+        <v>87</v>
+      </c>
+      <c r="I20">
         <v>92</v>
       </c>
-      <c r="E20">
-        <v>126</v>
-      </c>
-      <c r="F20">
-        <v>111</v>
-      </c>
-      <c r="G20">
-        <v>73</v>
-      </c>
-      <c r="H20">
+      <c r="J20">
         <v>82</v>
-      </c>
-      <c r="I20">
-        <v>91</v>
-      </c>
-      <c r="J20">
-        <v>81</v>
       </c>
       <c r="K20">
         <v>91</v>
       </c>
       <c r="L20">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M20">
         <v>73</v>
@@ -5013,7 +5016,7 @@
         <v>12</v>
       </c>
       <c r="I21">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -5022,7 +5025,7 @@
         <v>13</v>
       </c>
       <c r="L21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -5042,10 +5045,10 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>11</v>
@@ -5057,7 +5060,7 @@
         <v>7</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>11</v>
@@ -5077,13 +5080,13 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>48</v>
       </c>
       <c r="E23">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F23">
         <v>28</v>
@@ -5092,13 +5095,13 @@
         <v>40</v>
       </c>
       <c r="H23">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I23">
         <v>36</v>
       </c>
       <c r="J23">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K23">
         <v>31</v>
@@ -5121,7 +5124,7 @@
         <v>30</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24">
         <v>11</v>
@@ -5145,7 +5148,7 @@
         <v>13</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>11</v>
@@ -5159,10 +5162,10 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E25">
         <v>17</v>
@@ -5177,13 +5180,13 @@
         <v>11</v>
       </c>
       <c r="I25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25">
         <v>13</v>
@@ -5244,25 +5247,25 @@
         <v>24</v>
       </c>
       <c r="D27">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E27">
         <v>28</v>
       </c>
       <c r="F27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G27">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I27">
         <v>35</v>
       </c>
       <c r="J27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27">
         <v>45</v>
@@ -5271,7 +5274,7 @@
         <v>35</v>
       </c>
       <c r="M27">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5287,6 +5290,9 @@
       <c r="F28">
         <v>1</v>
       </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
       <c r="I28">
         <v>1</v>
       </c>
@@ -5305,37 +5311,37 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C29">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D29">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E29">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F29">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G29">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H29">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I29">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J29">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K29">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="L29">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M29">
         <v>145</v>
@@ -5355,7 +5361,7 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F30">
         <v>15</v>
@@ -5408,13 +5414,13 @@
         <v>19</v>
       </c>
       <c r="I31">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J31">
         <v>24</v>
       </c>
       <c r="K31">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L31">
         <v>30</v>
@@ -5449,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -5469,37 +5475,37 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C33">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D33">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E33">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F33">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G33">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H33">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I33">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J33">
         <v>157</v>
       </c>
       <c r="K33">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L33">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M33">
         <v>88</v>
@@ -5513,10 +5519,10 @@
         <v>11</v>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34">
         <v>10</v>
@@ -5537,7 +5543,7 @@
         <v>28</v>
       </c>
       <c r="K34">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L34">
         <v>19</v>
@@ -5592,10 +5598,10 @@
         <v>42</v>
       </c>
       <c r="B36">
+        <v>41</v>
+      </c>
+      <c r="C36">
         <v>40</v>
-      </c>
-      <c r="C36">
-        <v>39</v>
       </c>
       <c r="D36">
         <v>37</v>
@@ -5604,28 +5610,28 @@
         <v>50</v>
       </c>
       <c r="F36">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H36">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I36">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J36">
         <v>57</v>
       </c>
       <c r="K36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L36">
         <v>52</v>
       </c>
       <c r="M36">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5633,40 +5639,40 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C37">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D37">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E37">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F37">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G37">
         <v>94</v>
       </c>
       <c r="H37">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I37">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J37">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K37">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5756,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>8</v>
@@ -5765,7 +5771,7 @@
         <v>4</v>
       </c>
       <c r="J40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>6</v>
@@ -5774,7 +5780,7 @@
         <v>5</v>
       </c>
       <c r="M40">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -5785,7 +5791,7 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D41">
         <v>24</v>
@@ -5800,22 +5806,22 @@
         <v>19</v>
       </c>
       <c r="H41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41">
         <v>14</v>
       </c>
       <c r="J41">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K41">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L41">
         <v>12</v>
       </c>
       <c r="M41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5823,37 +5829,37 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C42">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D42">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E42">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F42">
         <v>122</v>
       </c>
       <c r="G42">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H42">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I42">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J42">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K42">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L42">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M42">
         <v>80</v>
@@ -5888,7 +5894,7 @@
         <v>33</v>
       </c>
       <c r="J43">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K43">
         <v>34</v>
@@ -5908,7 +5914,7 @@
         <v>30</v>
       </c>
       <c r="C44">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D44">
         <v>35</v>
@@ -5926,13 +5932,13 @@
         <v>37</v>
       </c>
       <c r="I44">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J44">
         <v>27</v>
       </c>
       <c r="K44">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L44">
         <v>18</v>
@@ -5979,7 +5985,7 @@
         <v>2</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -6017,7 +6023,7 @@
         <v>8</v>
       </c>
       <c r="L46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M46">
         <v>9</v>
@@ -6046,19 +6052,19 @@
         <v>14</v>
       </c>
       <c r="H47">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J47">
         <v>36</v>
       </c>
       <c r="K47">
+        <v>27</v>
+      </c>
+      <c r="L47">
         <v>25</v>
-      </c>
-      <c r="L47">
-        <v>24</v>
       </c>
       <c r="M47">
         <v>18</v>
@@ -6072,7 +6078,7 @@
         <v>22</v>
       </c>
       <c r="C48">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D48">
         <v>34</v>
@@ -6084,13 +6090,13 @@
         <v>31</v>
       </c>
       <c r="G48">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H48">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I48">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J48">
         <v>23</v>
@@ -6131,13 +6137,13 @@
         <v>11</v>
       </c>
       <c r="I49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J49">
         <v>22</v>
       </c>
       <c r="K49">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L49">
         <v>19</v>
@@ -6154,16 +6160,16 @@
         <v>11</v>
       </c>
       <c r="C50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D50">
         <v>26</v>
       </c>
       <c r="E50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F50">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G50">
         <v>15</v>
@@ -6178,13 +6184,13 @@
         <v>24</v>
       </c>
       <c r="K50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L50">
         <v>22</v>
       </c>
       <c r="M50">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6192,7 +6198,7 @@
         <v>57</v>
       </c>
       <c r="B51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C51">
         <v>33</v>
@@ -6213,10 +6219,10 @@
         <v>44</v>
       </c>
       <c r="I51">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K51">
         <v>49</v>
@@ -6233,34 +6239,34 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C52">
         <v>106</v>
       </c>
       <c r="D52">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E52">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F52">
+        <v>66</v>
+      </c>
+      <c r="G52">
         <v>64</v>
       </c>
-      <c r="G52">
-        <v>61</v>
-      </c>
       <c r="H52">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I52">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J52">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K52">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L52">
         <v>52</v>
@@ -6280,7 +6286,7 @@
         <v>53</v>
       </c>
       <c r="D53">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E53">
         <v>45</v>
@@ -6292,13 +6298,13 @@
         <v>35</v>
       </c>
       <c r="H53">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I53">
         <v>38</v>
       </c>
       <c r="J53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K53">
         <v>46</v>
@@ -6321,34 +6327,34 @@
         <v>47</v>
       </c>
       <c r="D54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E54">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F54">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G54">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H54">
         <v>32</v>
       </c>
       <c r="I54">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J54">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K54">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L54">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M54">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6359,37 +6365,37 @@
         <v>18</v>
       </c>
       <c r="C55">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D55">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E55">
         <v>37</v>
       </c>
       <c r="F55">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G55">
         <v>32</v>
       </c>
       <c r="H55">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I55">
         <v>36</v>
       </c>
       <c r="J55">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K55">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L55">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M55">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6447,10 +6453,10 @@
         <v>11</v>
       </c>
       <c r="E57">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6468,10 +6474,10 @@
         <v>8</v>
       </c>
       <c r="L57">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M57">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6523,7 +6529,7 @@
         <v>9</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59">
         <v>8</v>
@@ -6532,7 +6538,7 @@
         <v>3</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59">
         <v>4</v>
@@ -6547,7 +6553,7 @@
         <v>3</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -6558,7 +6564,7 @@
         <v>23</v>
       </c>
       <c r="C60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D60">
         <v>33</v>
@@ -6567,7 +6573,7 @@
         <v>21</v>
       </c>
       <c r="F60">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G60">
         <v>22</v>
@@ -6582,7 +6588,7 @@
         <v>20</v>
       </c>
       <c r="K60">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L60">
         <v>18</v>
@@ -6623,7 +6629,7 @@
         <v>8</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L61">
         <v>2</v>
@@ -6678,25 +6684,25 @@
         <v>59</v>
       </c>
       <c r="G63">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H63">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I63">
         <v>40</v>
       </c>
       <c r="J63">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K63">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L63">
         <v>13</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6719,13 +6725,13 @@
         <v>16</v>
       </c>
       <c r="G64">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H64">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I64">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J64">
         <v>20</v>
@@ -6748,37 +6754,37 @@
         <v>52</v>
       </c>
       <c r="C65">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D65">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E65">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F65">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G65">
         <v>54</v>
       </c>
       <c r="H65">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I65">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J65">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K65">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L65">
         <v>60</v>
       </c>
       <c r="M65">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6827,37 +6833,37 @@
         <v>107</v>
       </c>
       <c r="C67">
+        <v>156</v>
+      </c>
+      <c r="D67">
+        <v>162</v>
+      </c>
+      <c r="E67">
+        <v>141</v>
+      </c>
+      <c r="F67">
+        <v>129</v>
+      </c>
+      <c r="G67">
+        <v>151</v>
+      </c>
+      <c r="H67">
+        <v>124</v>
+      </c>
+      <c r="I67">
+        <v>133</v>
+      </c>
+      <c r="J67">
+        <v>136</v>
+      </c>
+      <c r="K67">
         <v>153</v>
       </c>
-      <c r="D67">
-        <v>157</v>
-      </c>
-      <c r="E67">
-        <v>140</v>
-      </c>
-      <c r="F67">
-        <v>125</v>
-      </c>
-      <c r="G67">
-        <v>147</v>
-      </c>
-      <c r="H67">
-        <v>122</v>
-      </c>
-      <c r="I67">
-        <v>126</v>
-      </c>
-      <c r="J67">
-        <v>135</v>
-      </c>
-      <c r="K67">
-        <v>150</v>
-      </c>
       <c r="L67">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M67">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6868,7 +6874,7 @@
         <v>5</v>
       </c>
       <c r="C68">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D68">
         <v>9</v>
@@ -6880,7 +6886,7 @@
         <v>5</v>
       </c>
       <c r="G68">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H68">
         <v>3</v>
@@ -6892,7 +6898,7 @@
         <v>12</v>
       </c>
       <c r="K68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L68">
         <v>7</v>
@@ -6906,7 +6912,7 @@
         <v>75</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -6930,7 +6936,7 @@
         <v>8</v>
       </c>
       <c r="J69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K69">
         <v>15</v>
@@ -6974,7 +6980,7 @@
         <v>9</v>
       </c>
       <c r="L70">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M70">
         <v>4</v>
@@ -6988,7 +6994,7 @@
         <v>2</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <v>7</v>
@@ -7000,16 +7006,16 @@
         <v>8</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H71">
         <v>16</v>
       </c>
       <c r="I71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K71">
         <v>10</v>
@@ -7032,7 +7038,7 @@
         <v>12</v>
       </c>
       <c r="D72">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E72">
         <v>22</v>
@@ -7073,10 +7079,10 @@
         <v>28</v>
       </c>
       <c r="D73">
+        <v>36</v>
+      </c>
+      <c r="E73">
         <v>35</v>
-      </c>
-      <c r="E73">
-        <v>34</v>
       </c>
       <c r="F73">
         <v>33</v>
@@ -7091,13 +7097,13 @@
         <v>34</v>
       </c>
       <c r="J73">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K73">
         <v>41</v>
       </c>
       <c r="L73">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M73">
         <v>14</v>
@@ -7114,7 +7120,7 @@
         <v>3</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -7141,7 +7147,7 @@
         <v>2</v>
       </c>
       <c r="M74">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -7152,7 +7158,7 @@
         <v>8</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D75">
         <v>10</v>
@@ -7161,7 +7167,7 @@
         <v>9</v>
       </c>
       <c r="F75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -7173,10 +7179,10 @@
         <v>8</v>
       </c>
       <c r="J75">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K75">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L75">
         <v>13</v>
@@ -7196,22 +7202,22 @@
         <v>44</v>
       </c>
       <c r="D76">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E76">
         <v>36</v>
       </c>
       <c r="F76">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G76">
         <v>56</v>
       </c>
       <c r="H76">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I76">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J76">
         <v>60</v>
@@ -7223,7 +7229,7 @@
         <v>41</v>
       </c>
       <c r="M76">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7231,7 +7237,7 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C77">
         <v>26</v>
@@ -7258,10 +7264,10 @@
         <v>33</v>
       </c>
       <c r="K77">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L77">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M77">
         <v>25</v>
@@ -7272,22 +7278,22 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C78">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D78">
         <v>45</v>
       </c>
       <c r="E78">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F78">
         <v>31</v>
       </c>
       <c r="G78">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H78">
         <v>51</v>
@@ -7296,7 +7302,7 @@
         <v>51</v>
       </c>
       <c r="J78">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K78">
         <v>56</v>
@@ -7305,7 +7311,7 @@
         <v>41</v>
       </c>
       <c r="M78">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7316,37 +7322,37 @@
         <v>98</v>
       </c>
       <c r="C79">
+        <v>108</v>
+      </c>
+      <c r="D79">
+        <v>103</v>
+      </c>
+      <c r="E79">
+        <v>90</v>
+      </c>
+      <c r="F79">
+        <v>90</v>
+      </c>
+      <c r="G79">
+        <v>111</v>
+      </c>
+      <c r="H79">
+        <v>115</v>
+      </c>
+      <c r="I79">
+        <v>91</v>
+      </c>
+      <c r="J79">
+        <v>114</v>
+      </c>
+      <c r="K79">
         <v>105</v>
       </c>
-      <c r="D79">
-        <v>102</v>
-      </c>
-      <c r="E79">
-        <v>89</v>
-      </c>
-      <c r="F79">
-        <v>89</v>
-      </c>
-      <c r="G79">
-        <v>109</v>
-      </c>
-      <c r="H79">
-        <v>113</v>
-      </c>
-      <c r="I79">
+      <c r="L79">
         <v>90</v>
       </c>
-      <c r="J79">
-        <v>112</v>
-      </c>
-      <c r="K79">
-        <v>103</v>
-      </c>
-      <c r="L79">
-        <v>88</v>
-      </c>
       <c r="M79">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7369,7 +7375,7 @@
         <v>16</v>
       </c>
       <c r="G80">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H80">
         <v>3</v>
@@ -7401,7 +7407,7 @@
         <v>2</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -7474,13 +7480,13 @@
         <v>62</v>
       </c>
       <c r="C83">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D83">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E83">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F83">
         <v>57</v>
@@ -7492,19 +7498,19 @@
         <v>65</v>
       </c>
       <c r="I83">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J83">
         <v>88</v>
       </c>
       <c r="K83">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L83">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M83">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7515,7 +7521,7 @@
         <v>17</v>
       </c>
       <c r="C84">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D84">
         <v>25</v>
@@ -7527,19 +7533,19 @@
         <v>27</v>
       </c>
       <c r="G84">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H84">
         <v>27</v>
       </c>
       <c r="I84">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J84">
         <v>39</v>
       </c>
       <c r="K84">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L84">
         <v>26</v>
@@ -7559,34 +7565,34 @@
         <v>101</v>
       </c>
       <c r="D85">
+        <v>152</v>
+      </c>
+      <c r="E85">
+        <v>124</v>
+      </c>
+      <c r="F85">
+        <v>150</v>
+      </c>
+      <c r="G85">
         <v>151</v>
       </c>
-      <c r="E85">
-        <v>123</v>
-      </c>
-      <c r="F85">
-        <v>146</v>
-      </c>
-      <c r="G85">
-        <v>145</v>
-      </c>
       <c r="H85">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I85">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J85">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K85">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L85">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M85">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7594,7 +7600,7 @@
         <v>92</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C86">
         <v>16</v>
@@ -7603,7 +7609,7 @@
         <v>10</v>
       </c>
       <c r="E86">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F86">
         <v>18</v>
@@ -7612,10 +7618,10 @@
         <v>20</v>
       </c>
       <c r="H86">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I86">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J86">
         <v>15</v>
@@ -7624,7 +7630,7 @@
         <v>26</v>
       </c>
       <c r="L86">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M86">
         <v>19</v>
@@ -7662,7 +7668,7 @@
         <v>15</v>
       </c>
       <c r="K87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87">
         <v>11</v>
@@ -7679,10 +7685,10 @@
         <v>30</v>
       </c>
       <c r="C88">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D88">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E88">
         <v>38</v>
@@ -7694,13 +7700,13 @@
         <v>32</v>
       </c>
       <c r="H88">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I88">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J88">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K88">
         <v>49</v>
@@ -7720,7 +7726,7 @@
         <v>40</v>
       </c>
       <c r="C89">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D89">
         <v>42</v>
@@ -7738,13 +7744,13 @@
         <v>30</v>
       </c>
       <c r="I89">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J89">
         <v>44</v>
       </c>
       <c r="K89">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L89">
         <v>37</v>
@@ -7761,7 +7767,7 @@
         <v>29</v>
       </c>
       <c r="C90">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D90">
         <v>51</v>
@@ -7770,16 +7776,16 @@
         <v>29</v>
       </c>
       <c r="F90">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G90">
         <v>30</v>
       </c>
       <c r="H90">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I90">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J90">
         <v>44</v>
@@ -7788,7 +7794,7 @@
         <v>32</v>
       </c>
       <c r="L90">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M90">
         <v>30</v>
@@ -7799,13 +7805,13 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C91">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E91">
         <v>39</v>
@@ -7814,16 +7820,16 @@
         <v>34</v>
       </c>
       <c r="G91">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H91">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K91">
         <v>38</v>
@@ -7884,7 +7890,7 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D93">
         <v>27</v>
@@ -7899,10 +7905,10 @@
         <v>22</v>
       </c>
       <c r="H93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I93">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J93">
         <v>17</v>
@@ -7911,7 +7917,7 @@
         <v>13</v>
       </c>
       <c r="L93">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M93">
         <v>14</v>
@@ -7925,13 +7931,13 @@
         <v>10</v>
       </c>
       <c r="C94">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D94">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E94">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F94">
         <v>20</v>
@@ -7972,19 +7978,19 @@
         <v>67</v>
       </c>
       <c r="E95">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F95">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G95">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H95">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I95">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J95">
         <v>69</v>
@@ -7993,10 +7999,10 @@
         <v>61</v>
       </c>
       <c r="L95">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M95">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8007,13 +8013,13 @@
         <v>25</v>
       </c>
       <c r="C96">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D96">
         <v>35</v>
       </c>
       <c r="E96">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F96">
         <v>36</v>
@@ -8022,7 +8028,7 @@
         <v>42</v>
       </c>
       <c r="H96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I96">
         <v>37</v>
@@ -8031,7 +8037,7 @@
         <v>48</v>
       </c>
       <c r="K96">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L96">
         <v>27</v>
@@ -8051,7 +8057,7 @@
         <v>31</v>
       </c>
       <c r="D97">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E97">
         <v>24</v>
@@ -8063,10 +8069,10 @@
         <v>16</v>
       </c>
       <c r="H97">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I97">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J97">
         <v>20</v>
@@ -8092,10 +8098,10 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E98">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F98">
         <v>14</v>
@@ -8113,13 +8119,13 @@
         <v>27</v>
       </c>
       <c r="K98">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L98">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M98">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -8133,10 +8139,10 @@
         <v>50</v>
       </c>
       <c r="D99">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E99">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F99">
         <v>62</v>
@@ -8145,16 +8151,16 @@
         <v>67</v>
       </c>
       <c r="H99">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I99">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J99">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K99">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L99">
         <v>47</v>
@@ -8183,10 +8189,10 @@
         <v>3</v>
       </c>
       <c r="G100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -8195,7 +8201,7 @@
         <v>5</v>
       </c>
       <c r="K100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8209,40 +8215,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2829</v>
+        <v>2855</v>
       </c>
       <c r="C101">
-        <v>3628</v>
+        <v>3698</v>
       </c>
       <c r="D101">
-        <v>3988</v>
+        <v>4048</v>
       </c>
       <c r="E101">
-        <v>3529</v>
+        <v>3576</v>
       </c>
       <c r="F101">
-        <v>3161</v>
+        <v>3206</v>
       </c>
       <c r="G101">
-        <v>3439</v>
+        <v>3493</v>
       </c>
       <c r="H101">
-        <v>3179</v>
+        <v>3239</v>
       </c>
       <c r="I101">
-        <v>3328</v>
+        <v>3394</v>
       </c>
       <c r="J101">
-        <v>3770</v>
+        <v>3829</v>
       </c>
       <c r="K101">
-        <v>3673</v>
+        <v>3747</v>
       </c>
       <c r="L101">
-        <v>2922</v>
+        <v>2969</v>
       </c>
       <c r="M101">
-        <v>2602</v>
+        <v>2651</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8451,7 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -8588,7 +8594,7 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -8629,13 +8635,13 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7">
         <v>24</v>
       </c>
       <c r="K7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7">
         <v>30</v>
@@ -8721,7 +8727,7 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -8733,19 +8739,19 @@
         <v>38</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J2">
         <v>28</v>
       </c>
       <c r="K2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2">
         <v>23</v>
@@ -8759,37 +8765,37 @@
         <v>38</v>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3">
         <v>56</v>
       </c>
       <c r="K3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8809,10 +8815,10 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -8844,7 +8850,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -8859,7 +8865,7 @@
         <v>2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -8879,37 +8885,37 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6">
         <v>53</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H6">
         <v>48</v>
       </c>
       <c r="I6">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>42</v>
       </c>
       <c r="K6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8920,37 +8926,37 @@
         <v>107</v>
       </c>
       <c r="C7">
+        <v>156</v>
+      </c>
+      <c r="D7">
+        <v>162</v>
+      </c>
+      <c r="E7">
+        <v>141</v>
+      </c>
+      <c r="F7">
+        <v>129</v>
+      </c>
+      <c r="G7">
+        <v>151</v>
+      </c>
+      <c r="H7">
+        <v>124</v>
+      </c>
+      <c r="I7">
+        <v>133</v>
+      </c>
+      <c r="J7">
+        <v>136</v>
+      </c>
+      <c r="K7">
         <v>153</v>
       </c>
-      <c r="D7">
-        <v>157</v>
-      </c>
-      <c r="E7">
-        <v>140</v>
-      </c>
-      <c r="F7">
-        <v>125</v>
-      </c>
-      <c r="G7">
-        <v>147</v>
-      </c>
-      <c r="H7">
-        <v>122</v>
-      </c>
-      <c r="I7">
-        <v>126</v>
-      </c>
-      <c r="J7">
-        <v>135</v>
-      </c>
-      <c r="K7">
-        <v>150</v>
-      </c>
       <c r="L7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -9051,7 +9057,7 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -9086,7 +9092,7 @@
         <v>14</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>9</v>
@@ -9118,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -9158,7 +9164,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -9176,7 +9182,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>17</v>
@@ -9199,7 +9205,7 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -9211,19 +9217,19 @@
         <v>27</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>27</v>
       </c>
       <c r="I7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <v>39</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>26</v>
@@ -9449,13 +9455,13 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>8</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -9490,13 +9496,13 @@
         <v>11</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <v>22</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -9588,16 +9594,16 @@
         <v>12</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2">
         <v>21</v>
@@ -9606,7 +9612,7 @@
         <v>14</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -9626,13 +9632,13 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -9691,7 +9697,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9725,10 +9731,10 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6">
         <v>34</v>
@@ -9743,16 +9749,16 @@
         <v>36</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>30</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9766,34 +9772,34 @@
         <v>47</v>
       </c>
       <c r="D7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H7">
         <v>32</v>
       </c>
       <c r="I7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M7">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -9870,31 +9876,31 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>59</v>
       </c>
       <c r="E2">
+        <v>54</v>
+      </c>
+      <c r="F2">
+        <v>48</v>
+      </c>
+      <c r="G2">
         <v>52</v>
       </c>
-      <c r="F2">
-        <v>46</v>
-      </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
       <c r="H2">
+        <v>58</v>
+      </c>
+      <c r="I2">
+        <v>55</v>
+      </c>
+      <c r="J2">
         <v>56</v>
       </c>
-      <c r="I2">
-        <v>53</v>
-      </c>
-      <c r="J2">
-        <v>54</v>
-      </c>
       <c r="K2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L2">
         <v>46</v>
@@ -9911,16 +9917,16 @@
         <v>66</v>
       </c>
       <c r="C3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <v>73</v>
@@ -9929,16 +9935,16 @@
         <v>68</v>
       </c>
       <c r="I3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J3">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K3">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M3">
         <v>52</v>
@@ -9952,7 +9958,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>15</v>
@@ -9964,19 +9970,19 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4">
         <v>6</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -10031,22 +10037,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6">
         <v>59</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>50</v>
@@ -10072,37 +10078,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E7">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G7">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K7">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="L7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M7">
         <v>145</v>
@@ -10200,7 +10206,7 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -10316,7 +10322,7 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -10328,10 +10334,10 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -10357,7 +10363,7 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>34</v>
@@ -10369,13 +10375,13 @@
         <v>31</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7">
         <v>23</v>
@@ -10479,13 +10485,13 @@
         <v>24</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>36</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -10508,7 +10514,7 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>19</v>
@@ -10532,7 +10538,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3">
         <v>32</v>
@@ -10628,13 +10634,13 @@
         <v>36</v>
       </c>
       <c r="C6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>34</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>30</v>
@@ -10649,13 +10655,13 @@
         <v>26</v>
       </c>
       <c r="J6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6">
         <v>26</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6">
         <v>22</v>
@@ -10669,13 +10675,13 @@
         <v>69</v>
       </c>
       <c r="C7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -10684,19 +10690,19 @@
         <v>104</v>
       </c>
       <c r="H7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>89</v>
       </c>
       <c r="J7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K7">
         <v>97</v>
       </c>
       <c r="L7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M7">
         <v>87</v>
@@ -10841,13 +10847,13 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10925,7 +10931,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>18</v>
@@ -10943,7 +10949,7 @@
         <v>19</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -10955,7 +10961,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10966,7 +10972,7 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>35</v>
@@ -10984,13 +10990,13 @@
         <v>37</v>
       </c>
       <c r="I7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7">
         <v>27</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -11088,7 +11094,7 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -11117,7 +11123,7 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -11132,7 +11138,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>14</v>
@@ -11182,7 +11188,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -11210,13 +11216,13 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>30</v>
@@ -11225,7 +11231,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J6">
         <v>34</v>
@@ -11237,7 +11243,7 @@
         <v>20</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11251,22 +11257,22 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>56</v>
       </c>
       <c r="H7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J7">
         <v>60</v>
@@ -11278,7 +11284,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -11355,7 +11361,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -11527,7 +11533,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>22</v>
@@ -11634,10 +11640,10 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -11655,7 +11661,7 @@
         <v>11</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2">
         <v>10</v>
@@ -11664,7 +11670,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11765,10 +11771,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -11795,7 +11801,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11806,10 +11812,10 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -11827,7 +11833,7 @@
         <v>26</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
         <v>27</v>
@@ -11836,7 +11842,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -11913,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -11934,7 +11940,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>11</v>
@@ -12059,7 +12065,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -12068,13 +12074,13 @@
         <v>13</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12085,7 +12091,7 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>24</v>
@@ -12100,22 +12106,22 @@
         <v>19</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>14</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L7">
         <v>12</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -12189,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -12198,7 +12204,7 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -12207,19 +12213,19 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>32</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -12236,7 +12242,7 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>36</v>
@@ -12245,13 +12251,13 @@
         <v>33</v>
       </c>
       <c r="G3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>33</v>
       </c>
       <c r="I3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>23</v>
@@ -12350,10 +12356,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>87</v>
@@ -12368,13 +12374,13 @@
         <v>42</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K6">
         <v>49</v>
@@ -12391,37 +12397,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F7">
         <v>122</v>
       </c>
       <c r="G7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M7">
         <v>80</v>
@@ -12503,6 +12509,9 @@
       <c r="C3">
         <v>2</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
@@ -12599,7 +12608,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -12721,7 +12730,7 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -12741,7 +12750,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -12869,7 +12878,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>44</v>
@@ -12890,7 +12899,7 @@
         <v>24</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>15</v>
@@ -12985,7 +12994,7 @@
         <v>8</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -12994,7 +13003,7 @@
         <v>8</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <v>18</v>
@@ -13011,7 +13020,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>12</v>
@@ -13035,7 +13044,7 @@
         <v>14</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <v>14</v>
@@ -13067,7 +13076,7 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -13085,7 +13094,7 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13119,13 +13128,13 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>16</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -13157,22 +13166,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>45</v>
       </c>
       <c r="E7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>31</v>
       </c>
       <c r="G7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H7">
         <v>51</v>
@@ -13181,7 +13190,7 @@
         <v>51</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>56</v>
@@ -13190,7 +13199,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -13282,7 +13291,7 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -13294,7 +13303,7 @@
         <v>11</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -13308,7 +13317,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -13329,7 +13338,7 @@
         <v>8</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -13413,13 +13422,13 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>16</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -13434,13 +13443,13 @@
         <v>27</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13451,37 +13460,37 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>37</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>32</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -13625,6 +13634,9 @@
       <c r="K3">
         <v>5</v>
       </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
       <c r="M3">
         <v>5</v>
       </c>
@@ -13680,7 +13692,7 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -13718,7 +13730,7 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>11</v>
@@ -13742,7 +13754,7 @@
         <v>13</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>11</v>
@@ -13965,7 +13977,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -14006,7 +14018,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -14142,13 +14154,13 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>12</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>6</v>
@@ -14223,13 +14235,13 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>16</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -14264,13 +14276,13 @@
         <v>24</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>48</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>28</v>
@@ -14279,13 +14291,13 @@
         <v>40</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K7">
         <v>31</v>
@@ -14371,7 +14383,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -14514,13 +14526,13 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>16</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -14529,7 +14541,7 @@
         <v>20</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>18</v>
@@ -14538,7 +14550,7 @@
         <v>13</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -14555,13 +14567,13 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>35</v>
       </c>
       <c r="E7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>36</v>
@@ -14570,7 +14582,7 @@
         <v>42</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7">
         <v>37</v>
@@ -14579,7 +14591,7 @@
         <v>48</v>
       </c>
       <c r="K7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7">
         <v>27</v>
@@ -14665,7 +14677,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>11</v>
@@ -14700,10 +14712,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -14715,7 +14727,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -14724,7 +14736,7 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3">
         <v>12</v>
@@ -14750,7 +14762,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -14823,7 +14835,7 @@
         <v>12</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -14840,13 +14852,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>39</v>
@@ -14855,16 +14867,16 @@
         <v>34</v>
       </c>
       <c r="G7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K7">
         <v>38</v>
@@ -15006,7 +15018,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -15060,7 +15072,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -15101,7 +15113,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -15110,7 +15122,7 @@
         <v>13</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -15196,7 +15208,7 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>31</v>
@@ -15217,10 +15229,10 @@
         <v>38</v>
       </c>
       <c r="L2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15231,7 +15243,7 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -15240,25 +15252,25 @@
         <v>24</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3">
         <v>27</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3">
         <v>24</v>
@@ -15351,10 +15363,10 @@
         <v>47</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>36</v>
@@ -15363,16 +15375,16 @@
         <v>19</v>
       </c>
       <c r="G6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>31</v>
+      </c>
+      <c r="J6">
         <v>35</v>
-      </c>
-      <c r="I6">
-        <v>30</v>
-      </c>
-      <c r="J6">
-        <v>34</v>
       </c>
       <c r="K6">
         <v>23</v>
@@ -15392,37 +15404,37 @@
         <v>98</v>
       </c>
       <c r="C7">
+        <v>108</v>
+      </c>
+      <c r="D7">
+        <v>103</v>
+      </c>
+      <c r="E7">
+        <v>90</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7">
+        <v>111</v>
+      </c>
+      <c r="H7">
+        <v>115</v>
+      </c>
+      <c r="I7">
+        <v>91</v>
+      </c>
+      <c r="J7">
+        <v>114</v>
+      </c>
+      <c r="K7">
         <v>105</v>
       </c>
-      <c r="D7">
-        <v>102</v>
-      </c>
-      <c r="E7">
-        <v>89</v>
-      </c>
-      <c r="F7">
-        <v>89</v>
-      </c>
-      <c r="G7">
-        <v>109</v>
-      </c>
-      <c r="H7">
-        <v>113</v>
-      </c>
-      <c r="I7">
+      <c r="L7">
         <v>90</v>
       </c>
-      <c r="J7">
-        <v>112</v>
-      </c>
-      <c r="K7">
-        <v>103</v>
-      </c>
-      <c r="L7">
-        <v>88</v>
-      </c>
       <c r="M7">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -15514,7 +15526,7 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -15552,13 +15564,13 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -15692,13 +15704,13 @@
         <v>16</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>20</v>
@@ -15796,13 +15808,13 @@
         <v>31</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2">
         <v>22</v>
@@ -15825,16 +15837,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>26</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>23</v>
@@ -15843,19 +15855,19 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <v>25</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3">
         <v>26</v>
       </c>
       <c r="L3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3">
         <v>22</v>
@@ -15925,7 +15937,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -15945,16 +15957,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6">
         <v>41</v>
@@ -15963,10 +15975,10 @@
         <v>36</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>26</v>
@@ -15986,37 +15998,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7">
+        <v>94</v>
+      </c>
+      <c r="E7">
+        <v>128</v>
+      </c>
+      <c r="F7">
+        <v>112</v>
+      </c>
+      <c r="G7">
+        <v>75</v>
+      </c>
+      <c r="H7">
+        <v>87</v>
+      </c>
+      <c r="I7">
         <v>92</v>
       </c>
-      <c r="E7">
-        <v>126</v>
-      </c>
-      <c r="F7">
-        <v>111</v>
-      </c>
-      <c r="G7">
-        <v>73</v>
-      </c>
-      <c r="H7">
+      <c r="J7">
         <v>82</v>
-      </c>
-      <c r="I7">
-        <v>91</v>
-      </c>
-      <c r="J7">
-        <v>81</v>
       </c>
       <c r="K7">
         <v>91</v>
       </c>
       <c r="L7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M7">
         <v>73</v>
@@ -16212,7 +16224,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -16253,7 +16265,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -16430,7 +16442,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -16462,7 +16474,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -16494,10 +16506,10 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -16613,10 +16625,10 @@
         <v>15</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>9</v>
@@ -16639,7 +16651,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -16657,10 +16669,10 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -16672,7 +16684,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16683,7 +16695,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -16707,13 +16719,13 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -16762,7 +16774,7 @@
         <v>17</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -16791,10 +16803,10 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>41</v>
+      </c>
+      <c r="C7">
         <v>40</v>
-      </c>
-      <c r="C7">
-        <v>39</v>
       </c>
       <c r="D7">
         <v>37</v>
@@ -16803,28 +16815,28 @@
         <v>50</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J7">
         <v>57</v>
       </c>
       <c r="K7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7">
         <v>52</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -16969,7 +16981,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -17023,7 +17035,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>18</v>
@@ -17038,10 +17050,10 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -17064,7 +17076,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>27</v>
@@ -17079,10 +17091,10 @@
         <v>22</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <v>17</v>
@@ -17091,7 +17103,7 @@
         <v>13</v>
       </c>
       <c r="L7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -17174,7 +17186,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -17199,6 +17211,9 @@
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="J3">
         <v>1</v>
       </c>
@@ -17254,7 +17269,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -17283,10 +17298,10 @@
         <v>3</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -17295,7 +17310,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -17378,28 +17393,28 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>31</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
         <v>21</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>35</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K2">
         <v>42</v>
@@ -17408,7 +17423,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17419,16 +17434,16 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
         <v>33</v>
@@ -17443,13 +17458,13 @@
         <v>38</v>
       </c>
       <c r="K3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17478,7 +17493,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -17490,7 +17505,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17539,13 +17554,13 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>36</v>
@@ -17554,7 +17569,7 @@
         <v>27</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6">
         <v>33</v>
@@ -17563,7 +17578,7 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L6">
         <v>29</v>
@@ -17580,37 +17595,37 @@
         <v>113</v>
       </c>
       <c r="C7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G7">
         <v>95</v>
       </c>
       <c r="H7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K7">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -17687,7 +17702,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -17728,7 +17743,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -17839,7 +17854,7 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -17856,10 +17871,10 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -17880,7 +17895,7 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -18010,7 +18025,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -18091,10 +18106,10 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>21</v>
@@ -18132,13 +18147,13 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -18239,7 +18254,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -18260,10 +18275,10 @@
         <v>4</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -18343,6 +18358,9 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
       <c r="G5">
         <v>2</v>
       </c>
@@ -18382,7 +18400,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -18402,10 +18420,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -18420,13 +18438,13 @@
         <v>11</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -18574,7 +18592,7 @@
         <v>7</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -18615,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -18667,10 +18685,10 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>20</v>
@@ -18679,7 +18697,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -18708,19 +18726,19 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>36</v>
       </c>
       <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
         <v>25</v>
-      </c>
-      <c r="L7">
-        <v>24</v>
       </c>
       <c r="M7">
         <v>18</v>
@@ -18797,13 +18815,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -18847,7 +18865,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>8</v>
@@ -18909,7 +18927,7 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18949,7 +18967,7 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -18964,7 +18982,7 @@
         <v>21</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>14</v>
@@ -18981,16 +18999,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>43</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7">
         <v>27</v>
@@ -19005,7 +19023,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7">
         <v>25</v>
@@ -19014,7 +19032,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -19138,7 +19156,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -19159,10 +19177,10 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19213,7 +19231,7 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -19234,13 +19252,13 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>15</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19254,10 +19272,10 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>14</v>
@@ -19275,13 +19293,13 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -19358,13 +19376,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -19382,7 +19400,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -19429,7 +19447,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19470,7 +19488,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19501,7 +19519,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -19522,7 +19540,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19533,16 +19551,16 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>26</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>15</v>
@@ -19557,13 +19575,13 @@
         <v>24</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7">
         <v>22</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -20265,7 +20283,7 @@
         <v>12</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -20279,7 +20297,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -20306,7 +20324,7 @@
         <v>11</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3">
         <v>17</v>
@@ -20396,7 +20414,7 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -20408,10 +20426,10 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>37</v>
@@ -20428,7 +20446,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>58</v>
@@ -20437,7 +20455,7 @@
         <v>73</v>
       </c>
       <c r="E7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>51</v>
@@ -20449,13 +20467,13 @@
         <v>46</v>
       </c>
       <c r="I7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L7">
         <v>46</v>
@@ -20904,10 +20922,10 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -20945,10 +20963,10 @@
         <v>18</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -21046,7 +21064,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2">
         <v>12</v>
@@ -21069,7 +21087,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -21093,7 +21111,7 @@
         <v>9</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -21162,7 +21180,7 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -21177,7 +21195,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>17</v>
@@ -21200,10 +21218,10 @@
         <v>28</v>
       </c>
       <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
         <v>35</v>
-      </c>
-      <c r="E7">
-        <v>34</v>
       </c>
       <c r="F7">
         <v>33</v>
@@ -21218,13 +21236,13 @@
         <v>34</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K7">
         <v>41</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -21315,6 +21333,9 @@
       <c r="F2">
         <v>5</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="I2">
         <v>2</v>
       </c>
@@ -21328,7 +21349,7 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21342,7 +21363,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -21358,6 +21379,9 @@
       </c>
       <c r="L3">
         <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21440,7 +21464,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -21449,7 +21473,7 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -21464,7 +21488,7 @@
         <v>3</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -21556,10 +21580,10 @@
         <v>9</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -21600,7 +21624,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>11</v>
@@ -21609,7 +21633,7 @@
         <v>9</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>9</v>
@@ -21675,7 +21699,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>22</v>
@@ -21702,7 +21726,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -21716,7 +21740,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>30</v>
@@ -21731,10 +21755,10 @@
         <v>31</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>32</v>
@@ -21743,7 +21767,7 @@
         <v>26</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>23</v>
@@ -21826,7 +21850,7 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -21835,10 +21859,10 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -21992,7 +22016,7 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -22004,10 +22028,10 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>20</v>
@@ -22368,7 +22392,7 @@
         <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -22490,7 +22514,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -22585,10 +22609,10 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -22614,7 +22638,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -22632,7 +22656,7 @@
         <v>9</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>10</v>
@@ -22713,7 +22737,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>26</v>
@@ -22731,7 +22755,7 @@
         <v>17</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -22754,10 +22778,10 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>38</v>
@@ -22769,13 +22793,13 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7">
         <v>49</v>
@@ -22971,7 +22995,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -23006,7 +23030,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -23113,7 +23137,7 @@
         <v>8</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>13</v>
@@ -23177,7 +23201,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -23238,7 +23262,7 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -23262,7 +23286,7 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6">
         <v>11</v>
@@ -23279,7 +23303,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -23297,13 +23321,13 @@
         <v>30</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <v>44</v>
       </c>
       <c r="K7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L7">
         <v>37</v>
@@ -23319,7 +23343,7 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23398,10 +23422,10 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -23457,7 +23481,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23479,84 +23503,92 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>7</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="D6">
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <v>15</v>
       </c>
-      <c r="J6">
+      <c r="J7">
         <v>11</v>
       </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -23654,7 +23686,7 @@
         <v>9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>14</v>
@@ -23686,7 +23718,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -23718,13 +23750,13 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -23745,7 +23777,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23770,7 +23802,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -23782,7 +23814,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -23811,25 +23843,25 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>28</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>35</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>45</v>
@@ -23838,7 +23870,7 @@
         <v>35</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -23912,7 +23944,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -23956,7 +23988,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -24006,10 +24038,10 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -24018,7 +24050,7 @@
         <v>13</v>
       </c>
       <c r="L4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4">
         <v>11</v>
@@ -24070,7 +24102,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -24079,7 +24111,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>18</v>
@@ -24088,10 +24120,10 @@
         <v>20</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -24100,7 +24132,7 @@
         <v>26</v>
       </c>
       <c r="L6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M6">
         <v>19</v>
@@ -24180,13 +24212,13 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -24201,7 +24233,7 @@
         <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -24239,7 +24271,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -24337,7 +24369,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -24346,7 +24378,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -24358,10 +24390,10 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -24444,7 +24476,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -24459,7 +24491,7 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -24485,7 +24517,7 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>18</v>
@@ -24541,7 +24573,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -24608,13 +24640,13 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -24626,7 +24658,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -24640,7 +24672,7 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7">
         <v>51</v>
@@ -24649,16 +24681,16 @@
         <v>29</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>30</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>44</v>
@@ -24667,7 +24699,7 @@
         <v>32</v>
       </c>
       <c r="L7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7">
         <v>30</v>
@@ -24887,7 +24919,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -24908,10 +24940,10 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>16</v>
@@ -24928,7 +24960,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -24949,10 +24981,10 @@
         <v>44</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K7">
         <v>49</v>
@@ -25151,7 +25183,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -25160,7 +25192,7 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -25172,7 +25204,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -25186,7 +25218,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -25198,7 +25230,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -25210,7 +25242,7 @@
         <v>12</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -25299,7 +25331,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -25320,7 +25352,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25355,7 +25387,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -25415,7 +25447,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -25453,10 +25485,10 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -25474,10 +25506,10 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -25595,7 +25627,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -25691,7 +25723,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -25706,7 +25738,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -25723,7 +25755,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -25732,7 +25764,7 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -25747,7 +25779,7 @@
         <v>20</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -25889,7 +25921,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>10</v>
@@ -26017,7 +26049,7 @@
         <v>33</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7">
         <v>34</v>
@@ -26106,22 +26138,22 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>28</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2">
         <v>40</v>
@@ -26130,10 +26162,10 @@
         <v>70</v>
       </c>
       <c r="L2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26150,31 +26182,31 @@
         <v>51</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>54</v>
       </c>
       <c r="H3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26238,7 +26270,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -26276,10 +26308,10 @@
         <v>37</v>
       </c>
       <c r="F6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>45</v>
@@ -26291,13 +26323,13 @@
         <v>44</v>
       </c>
       <c r="K6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L6">
         <v>30</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26311,34 +26343,34 @@
         <v>101</v>
       </c>
       <c r="D7">
+        <v>152</v>
+      </c>
+      <c r="E7">
+        <v>124</v>
+      </c>
+      <c r="F7">
+        <v>150</v>
+      </c>
+      <c r="G7">
         <v>151</v>
       </c>
-      <c r="E7">
-        <v>123</v>
-      </c>
-      <c r="F7">
-        <v>146</v>
-      </c>
-      <c r="G7">
-        <v>145</v>
-      </c>
       <c r="H7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M7">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -26421,10 +26453,10 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -26436,7 +26468,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -26569,10 +26601,10 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -26584,7 +26616,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>11</v>
@@ -26705,7 +26737,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -26762,7 +26794,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -26780,10 +26812,10 @@
         <v>14</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -26803,7 +26835,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -26815,16 +26847,16 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>16</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -26948,7 +26980,7 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -27062,7 +27094,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -27397,7 +27429,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -27411,7 +27443,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>12</v>
@@ -27537,7 +27569,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -27548,7 +27580,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>26</v>
@@ -27575,10 +27607,10 @@
         <v>33</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>25</v>
@@ -27693,7 +27725,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27782,7 +27814,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -28172,7 +28204,7 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -28210,7 +28242,7 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -28565,7 +28597,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28613,7 +28645,7 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -28622,7 +28654,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -28651,7 +28683,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -28660,7 +28692,7 @@
         <v>4</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -28669,7 +28701,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -28749,10 +28781,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>16</v>
@@ -28784,7 +28816,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>29</v>
@@ -28796,13 +28828,13 @@
         <v>25</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3">
         <v>25</v>
@@ -28811,7 +28843,7 @@
         <v>29</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -28840,7 +28872,7 @@
         <v>4</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -28907,7 +28939,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>49</v>
@@ -28928,13 +28960,13 @@
         <v>26</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -28948,34 +28980,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>106</v>
       </c>
       <c r="D7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7">
+        <v>66</v>
+      </c>
+      <c r="G7">
         <v>64</v>
       </c>
-      <c r="G7">
-        <v>61</v>
-      </c>
       <c r="H7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K7">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L7">
         <v>52</v>
@@ -29082,7 +29114,7 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29139,7 +29171,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -29163,7 +29195,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>4</v>
@@ -29180,7 +29212,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -29204,10 +29236,10 @@
         <v>15</v>
       </c>
       <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
         <v>11</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -29340,7 +29372,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29385,7 +29417,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -29423,7 +29455,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -29456,7 +29488,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -29583,7 +29615,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29687,7 +29719,7 @@
         <v>15</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -29794,7 +29826,7 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -29910,7 +29942,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -30238,6 +30270,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
@@ -30277,7 +30312,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -30291,7 +30326,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -30318,7 +30353,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -30698,6 +30733,9 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
@@ -30788,7 +30826,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -30822,7 +30860,7 @@
 
 <file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -30833,9 +30871,10 @@
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -30849,30 +30888,36 @@
         <v>2019</v>
       </c>
       <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
         <v>2022</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2023</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2024</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -30882,14 +30927,14 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -30897,7 +30942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -30905,7 +30950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -30925,9 +30970,12 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
     </row>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>854</v>
       </c>
       <c r="M2">
-        <v>800</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>891</v>
       </c>
       <c r="M3">
-        <v>886</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>247</v>
       </c>
       <c r="M4">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>917</v>
       </c>
       <c r="M6">
-        <v>657</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>2969</v>
       </c>
       <c r="M7">
-        <v>2651</v>
+        <v>2689</v>
       </c>
     </row>
   </sheetData>
@@ -1902,7 +1902,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2025,7 +2025,7 @@
         <v>58</v>
       </c>
       <c r="M6">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2066,7 +2066,7 @@
         <v>182</v>
       </c>
       <c r="M7">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2173,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2372,7 +2372,7 @@
         <v>60</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2479,7 +2479,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2684,7 +2684,7 @@
         <v>130</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3444,7 +3444,7 @@
         <v>17</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3599,7 +3599,7 @@
         <v>60</v>
       </c>
       <c r="M7">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4422,7 +4422,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4504,7 +4504,7 @@
         <v>182</v>
       </c>
       <c r="M8">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4785,7 +4785,7 @@
         <v>21</v>
       </c>
       <c r="M15">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4987,7 +4987,7 @@
         <v>79</v>
       </c>
       <c r="M20">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5028,7 +5028,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5344,7 +5344,7 @@
         <v>140</v>
       </c>
       <c r="M29">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5508,7 +5508,7 @@
         <v>130</v>
       </c>
       <c r="M33">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5549,7 +5549,7 @@
         <v>19</v>
       </c>
       <c r="M34">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -5944,7 +5944,7 @@
         <v>18</v>
       </c>
       <c r="M44">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6149,7 +6149,7 @@
         <v>19</v>
       </c>
       <c r="M49">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6190,7 +6190,7 @@
         <v>22</v>
       </c>
       <c r="M50">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6354,7 +6354,7 @@
         <v>59</v>
       </c>
       <c r="M54">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6395,7 +6395,7 @@
         <v>34</v>
       </c>
       <c r="M55">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6477,7 +6477,7 @@
         <v>17</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6594,7 +6594,7 @@
         <v>18</v>
       </c>
       <c r="M60">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6702,7 +6702,7 @@
         <v>13</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6784,7 +6784,7 @@
         <v>60</v>
       </c>
       <c r="M65">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6863,7 +6863,7 @@
         <v>110</v>
       </c>
       <c r="M67">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7106,7 +7106,7 @@
         <v>21</v>
       </c>
       <c r="M73">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7352,7 +7352,7 @@
         <v>90</v>
       </c>
       <c r="M79">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7510,7 +7510,7 @@
         <v>60</v>
       </c>
       <c r="M83">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7592,7 +7592,7 @@
         <v>144</v>
       </c>
       <c r="M85">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7756,7 +7756,7 @@
         <v>37</v>
       </c>
       <c r="M89">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7838,7 +7838,7 @@
         <v>38</v>
       </c>
       <c r="M91">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7920,7 +7920,7 @@
         <v>15</v>
       </c>
       <c r="M93">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7961,7 +7961,7 @@
         <v>37</v>
       </c>
       <c r="M94">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8084,7 +8084,7 @@
         <v>36</v>
       </c>
       <c r="M97">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8248,7 +8248,7 @@
         <v>2969</v>
       </c>
       <c r="M101">
-        <v>2651</v>
+        <v>2689</v>
       </c>
     </row>
   </sheetData>
@@ -8754,7 +8754,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8795,7 +8795,7 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8956,7 +8956,7 @@
         <v>110</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -9467,7 +9467,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9508,7 +9508,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -9758,7 +9758,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9799,7 +9799,7 @@
         <v>59</v>
       </c>
       <c r="M7">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -9906,7 +9906,7 @@
         <v>46</v>
       </c>
       <c r="M2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9947,7 +9947,7 @@
         <v>48</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10070,7 +10070,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10111,7 +10111,7 @@
         <v>140</v>
       </c>
       <c r="M7">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -10812,7 +10812,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10961,7 +10961,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11002,7 +11002,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -11670,7 +11670,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11842,7 +11842,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -13385,7 +13385,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13490,7 +13490,7 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -14704,7 +14704,7 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14885,7 +14885,7 @@
         <v>38</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -15084,7 +15084,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15125,7 +15125,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15232,7 +15232,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15434,7 +15434,7 @@
         <v>90</v>
       </c>
       <c r="M7">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -15870,7 +15870,7 @@
         <v>22</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16031,7 +16031,7 @@
         <v>79</v>
       </c>
       <c r="M7">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -16943,7 +16943,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17106,7 +17106,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -17860,7 +17860,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17901,7 +17901,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -18136,7 +18136,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18177,7 +18177,7 @@
         <v>37</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -18848,7 +18848,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19032,7 +19032,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -19406,7 +19406,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19581,7 +19581,7 @@
         <v>22</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -21073,7 +21073,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21245,7 +21245,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -21874,7 +21874,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22043,7 +22043,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -23292,7 +23292,7 @@
         <v>11</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23333,7 +23333,7 @@
         <v>37</v>
       </c>
       <c r="M7">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -25470,6 +25470,9 @@
       <c r="L6">
         <v>5</v>
       </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
@@ -25509,7 +25512,7 @@
         <v>17</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -25744,7 +25747,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25785,7 +25788,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -26247,7 +26250,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -26370,7 +26373,7 @@
         <v>144</v>
       </c>
       <c r="M7">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C2">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="D2">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="E2">
-        <v>763</v>
+        <v>781</v>
       </c>
       <c r="F2">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="G2">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="H2">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="I2">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="J2">
-        <v>971</v>
+        <v>990</v>
       </c>
       <c r="K2">
-        <v>1055</v>
+        <v>1083</v>
       </c>
       <c r="L2">
-        <v>854</v>
+        <v>870</v>
       </c>
       <c r="M2">
-        <v>818</v>
+        <v>839</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="C3">
-        <v>961</v>
+        <v>983</v>
       </c>
       <c r="D3">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="E3">
-        <v>912</v>
+        <v>926</v>
       </c>
       <c r="F3">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="G3">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="H3">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="I3">
-        <v>902</v>
+        <v>926</v>
       </c>
       <c r="J3">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="K3">
-        <v>1006</v>
+        <v>1032</v>
       </c>
       <c r="L3">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="M3">
-        <v>894</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -953,37 +953,37 @@
         <v>330</v>
       </c>
       <c r="C4">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D4">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E4">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F4">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G4">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H4">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I4">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="J4">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K4">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="L4">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M4">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,7 +994,7 @@
         <v>50</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5">
         <v>103</v>
@@ -1003,22 +1003,22 @@
         <v>83</v>
       </c>
       <c r="F5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>72</v>
       </c>
       <c r="H5">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J5">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K5">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L5">
         <v>60</v>
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1217</v>
+        <v>1233</v>
       </c>
       <c r="C6">
-        <v>1682</v>
+        <v>1706</v>
       </c>
       <c r="D6">
-        <v>1816</v>
+        <v>1847</v>
       </c>
       <c r="E6">
-        <v>1499</v>
+        <v>1514</v>
       </c>
       <c r="F6">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="G6">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="H6">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="I6">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="J6">
-        <v>1432</v>
+        <v>1455</v>
       </c>
       <c r="K6">
-        <v>1352</v>
+        <v>1365</v>
       </c>
       <c r="L6">
-        <v>917</v>
+        <v>934</v>
       </c>
       <c r="M6">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2855</v>
+        <v>2899</v>
       </c>
       <c r="C7">
-        <v>3698</v>
+        <v>3771</v>
       </c>
       <c r="D7">
-        <v>4048</v>
+        <v>4106</v>
       </c>
       <c r="E7">
-        <v>3576</v>
+        <v>3629</v>
       </c>
       <c r="F7">
-        <v>3206</v>
+        <v>3254</v>
       </c>
       <c r="G7">
-        <v>3493</v>
+        <v>3534</v>
       </c>
       <c r="H7">
-        <v>3239</v>
+        <v>3299</v>
       </c>
       <c r="I7">
-        <v>3394</v>
+        <v>3459</v>
       </c>
       <c r="J7">
-        <v>3829</v>
+        <v>3893</v>
       </c>
       <c r="K7">
-        <v>3747</v>
+        <v>3822</v>
       </c>
       <c r="L7">
-        <v>2969</v>
+        <v>3016</v>
       </c>
       <c r="M7">
-        <v>2689</v>
+        <v>2741</v>
       </c>
     </row>
   </sheetData>
@@ -1264,6 +1264,9 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="I4">
         <v>2</v>
       </c>
@@ -1340,7 +1343,7 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -1421,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1472,7 +1475,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1549,7 +1552,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -1558,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -1602,7 +1605,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1634,7 +1637,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1680,10 +1683,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -1698,7 +1701,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>18</v>
@@ -1710,7 +1713,7 @@
         <v>22</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1721,25 +1724,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7">
         <v>45</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>38</v>
@@ -1751,7 +1754,7 @@
         <v>46</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -1828,40 +1831,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>62</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
+        <v>63</v>
+      </c>
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="H2">
+      <c r="I2">
+        <v>62</v>
+      </c>
+      <c r="J2">
+        <v>77</v>
+      </c>
+      <c r="K2">
+        <v>64</v>
+      </c>
+      <c r="L2">
+        <v>51</v>
+      </c>
+      <c r="M2">
         <v>58</v>
-      </c>
-      <c r="I2">
-        <v>60</v>
-      </c>
-      <c r="J2">
-        <v>76</v>
-      </c>
-      <c r="K2">
-        <v>60</v>
-      </c>
-      <c r="L2">
-        <v>50</v>
-      </c>
-      <c r="M2">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1869,19 +1872,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>79</v>
@@ -1890,19 +1893,19 @@
         <v>59</v>
       </c>
       <c r="I3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J3">
         <v>81</v>
       </c>
       <c r="K3">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L3">
         <v>57</v>
       </c>
       <c r="M3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1913,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -1934,16 +1937,16 @@
         <v>13</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4">
         <v>14</v>
       </c>
       <c r="L4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1992,40 +1995,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C6">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D6">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E6">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F6">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G6">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H6">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6">
         <v>72</v>
       </c>
       <c r="L6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M6">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2033,40 +2036,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C7">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="H7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K7">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="L7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M7">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2149,7 +2152,7 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -2158,22 +2161,22 @@
         <v>15</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>25</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2">
         <v>17</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2196,25 +2199,25 @@
         <v>24</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>23</v>
       </c>
       <c r="I3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J3">
         <v>29</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2304,7 +2307,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>23</v>
@@ -2345,34 +2348,34 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>57</v>
       </c>
       <c r="G7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M7">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2446,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>28</v>
@@ -2461,25 +2464,25 @@
         <v>30</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H2">
         <v>36</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2">
         <v>35</v>
       </c>
       <c r="K2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2">
         <v>30</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2490,10 +2493,10 @@
         <v>34</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E3">
         <v>69</v>
@@ -2505,10 +2508,10 @@
         <v>61</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3">
         <v>41</v>
@@ -2520,7 +2523,7 @@
         <v>46</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2534,7 +2537,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -2558,7 +2561,7 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -2613,19 +2616,19 @@
         <v>68</v>
       </c>
       <c r="C6">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D6">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>84</v>
       </c>
       <c r="F6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H6">
         <v>47</v>
@@ -2637,10 +2640,10 @@
         <v>70</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <v>28</v>
@@ -2651,40 +2654,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E7">
         <v>209</v>
       </c>
       <c r="F7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H7">
+        <v>157</v>
+      </c>
+      <c r="I7">
         <v>155</v>
-      </c>
-      <c r="I7">
-        <v>153</v>
       </c>
       <c r="J7">
         <v>157</v>
       </c>
       <c r="K7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M7">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2782,10 +2785,10 @@
         <v>19</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>16</v>
@@ -2802,13 +2805,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>20</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -2817,7 +2820,7 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3">
         <v>17</v>
@@ -2925,19 +2928,19 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>23</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>21</v>
@@ -2960,31 +2963,31 @@
         <v>38</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>67</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>67</v>
       </c>
       <c r="H7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L7">
         <v>43</v>
@@ -3067,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>29</v>
@@ -3082,7 +3085,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2">
         <v>32</v>
@@ -3094,7 +3097,7 @@
         <v>27</v>
       </c>
       <c r="L2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2">
         <v>32</v>
@@ -3105,7 +3108,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>36</v>
@@ -3117,25 +3120,25 @@
         <v>35</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I3">
         <v>32</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3">
         <v>36</v>
@@ -3225,16 +3228,16 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>27</v>
@@ -3243,16 +3246,16 @@
         <v>19</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K6">
         <v>42</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M6">
         <v>27</v>
@@ -3263,37 +3266,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M7">
         <v>103</v>
@@ -3370,10 +3373,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>18</v>
@@ -3385,13 +3388,13 @@
         <v>15</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>19</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2">
         <v>26</v>
@@ -3400,7 +3403,7 @@
         <v>26</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>21</v>
@@ -3411,7 +3414,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>27</v>
@@ -3423,13 +3426,13 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3">
         <v>24</v>
@@ -3438,7 +3441,7 @@
         <v>22</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3">
         <v>17</v>
@@ -3461,7 +3464,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3476,7 +3479,10 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -3531,10 +3537,10 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>22</v>
@@ -3543,13 +3549,13 @@
         <v>18</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K6">
         <v>52</v>
@@ -3566,37 +3572,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H7">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M7">
         <v>62</v>
@@ -3673,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -3682,7 +3688,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -3706,7 +3712,7 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3723,7 +3729,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -3735,13 +3741,13 @@
         <v>21</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3">
         <v>19</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <v>21</v>
@@ -3814,7 +3820,7 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -3855,13 +3861,13 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6">
         <v>8</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3869,7 +3875,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -3878,7 +3884,7 @@
         <v>83</v>
       </c>
       <c r="E7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>62</v>
@@ -3890,13 +3896,13 @@
         <v>68</v>
       </c>
       <c r="I7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J7">
         <v>51</v>
       </c>
       <c r="K7">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L7">
         <v>47</v>
@@ -4023,7 +4029,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4057,6 +4063,9 @@
       <c r="B4">
         <v>2</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="F4">
         <v>4</v>
       </c>
@@ -4127,7 +4136,7 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>15</v>
@@ -4234,7 +4243,7 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2">
         <v>17</v>
@@ -4243,13 +4252,13 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2">
         <v>26</v>
@@ -4307,7 +4316,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>11</v>
@@ -4322,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -4348,7 +4357,7 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -4375,13 +4384,13 @@
         <v>11</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4392,10 +4401,10 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
         <v>35</v>
@@ -4410,7 +4419,7 @@
         <v>19</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6">
         <v>33</v>
@@ -4433,37 +4442,37 @@
         <v>113</v>
       </c>
       <c r="C7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4471,40 +4480,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C8">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D8">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E8">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F8">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="H8">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I8">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J8">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K8">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="L8">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M8">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4530,7 +4539,7 @@
         <v>16</v>
       </c>
       <c r="H9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9">
         <v>19</v>
@@ -4539,7 +4548,7 @@
         <v>26</v>
       </c>
       <c r="K9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L9">
         <v>19</v>
@@ -4556,10 +4565,10 @@
         <v>30</v>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>44</v>
@@ -4583,7 +4592,7 @@
         <v>23</v>
       </c>
       <c r="L10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M10">
         <v>12</v>
@@ -4594,16 +4603,16 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D11">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>51</v>
@@ -4612,22 +4621,22 @@
         <v>57</v>
       </c>
       <c r="H11">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I11">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J11">
         <v>44</v>
       </c>
       <c r="K11">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L11">
         <v>46</v>
       </c>
       <c r="M11">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4714,7 +4723,7 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>22</v>
@@ -4741,7 +4750,7 @@
         <v>17</v>
       </c>
       <c r="L14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M14">
         <v>12</v>
@@ -4773,7 +4782,7 @@
         <v>31</v>
       </c>
       <c r="I15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J15">
         <v>45</v>
@@ -4872,19 +4881,19 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18">
         <v>15</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18">
         <v>19</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G18">
         <v>12</v>
@@ -4916,37 +4925,37 @@
         <v>69</v>
       </c>
       <c r="C19">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G19">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H19">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I19">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J19">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K19">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L19">
         <v>95</v>
       </c>
       <c r="M19">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4954,40 +4963,40 @@
         <v>26</v>
       </c>
       <c r="B20">
+        <v>79</v>
+      </c>
+      <c r="C20">
+        <v>81</v>
+      </c>
+      <c r="D20">
+        <v>97</v>
+      </c>
+      <c r="E20">
+        <v>130</v>
+      </c>
+      <c r="F20">
+        <v>113</v>
+      </c>
+      <c r="G20">
         <v>77</v>
-      </c>
-      <c r="C20">
-        <v>79</v>
-      </c>
-      <c r="D20">
-        <v>94</v>
-      </c>
-      <c r="E20">
-        <v>128</v>
-      </c>
-      <c r="F20">
-        <v>112</v>
-      </c>
-      <c r="G20">
-        <v>75</v>
       </c>
       <c r="H20">
         <v>87</v>
       </c>
       <c r="I20">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J20">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K20">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L20">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M20">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5010,7 +5019,7 @@
         <v>9</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H21">
         <v>12</v>
@@ -5077,7 +5086,7 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -5089,28 +5098,28 @@
         <v>40</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G23">
         <v>40</v>
       </c>
       <c r="H23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I23">
         <v>36</v>
       </c>
       <c r="J23">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K23">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>30</v>
+      </c>
+      <c r="M23">
         <v>31</v>
-      </c>
-      <c r="L23">
-        <v>28</v>
-      </c>
-      <c r="M23">
-        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5121,10 +5130,10 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>11</v>
@@ -5151,7 +5160,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5250,10 +5259,10 @@
         <v>23</v>
       </c>
       <c r="E27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G27">
         <v>32</v>
@@ -5271,10 +5280,10 @@
         <v>45</v>
       </c>
       <c r="L27">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M27">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5314,37 +5323,37 @@
         <v>187</v>
       </c>
       <c r="C29">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D29">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E29">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F29">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G29">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H29">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I29">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J29">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K29">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L29">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M29">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5361,7 +5370,7 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F30">
         <v>15</v>
@@ -5393,28 +5402,28 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H31">
         <v>19</v>
       </c>
       <c r="I31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J31">
         <v>24</v>
@@ -5423,7 +5432,7 @@
         <v>40</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M31">
         <v>28</v>
@@ -5440,7 +5449,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -5461,7 +5470,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -5475,40 +5484,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C33">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D33">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E33">
         <v>209</v>
       </c>
       <c r="F33">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G33">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H33">
+        <v>157</v>
+      </c>
+      <c r="I33">
         <v>155</v>
-      </c>
-      <c r="I33">
-        <v>153</v>
       </c>
       <c r="J33">
         <v>157</v>
       </c>
       <c r="K33">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L33">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M33">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5534,16 +5543,16 @@
         <v>19</v>
       </c>
       <c r="H34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I34">
         <v>8</v>
       </c>
       <c r="J34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K34">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L34">
         <v>19</v>
@@ -5610,19 +5619,19 @@
         <v>50</v>
       </c>
       <c r="F36">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H36">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I36">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J36">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K36">
         <v>44</v>
@@ -5631,7 +5640,7 @@
         <v>52</v>
       </c>
       <c r="M36">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5639,37 +5648,37 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C37">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D37">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E37">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F37">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G37">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H37">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I37">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J37">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K37">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M37">
         <v>103</v>
@@ -5750,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -5765,7 +5774,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>4</v>
@@ -5788,10 +5797,10 @@
         <v>47</v>
       </c>
       <c r="B41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D41">
         <v>24</v>
@@ -5809,10 +5818,10 @@
         <v>11</v>
       </c>
       <c r="I41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41">
         <v>41</v>
@@ -5829,40 +5838,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C42">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D42">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E42">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F42">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G42">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H42">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I42">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J42">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K42">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L42">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M42">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5870,7 +5879,7 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43">
         <v>14</v>
@@ -5879,7 +5888,7 @@
         <v>16</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F43">
         <v>25</v>
@@ -5894,10 +5903,10 @@
         <v>33</v>
       </c>
       <c r="J43">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K43">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L43">
         <v>20</v>
@@ -5923,7 +5932,7 @@
         <v>42</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G44">
         <v>37</v>
@@ -5938,7 +5947,7 @@
         <v>27</v>
       </c>
       <c r="K44">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L44">
         <v>18</v>
@@ -6046,16 +6055,16 @@
         <v>18</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G47">
         <v>14</v>
       </c>
       <c r="H47">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I47">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J47">
         <v>36</v>
@@ -6084,10 +6093,10 @@
         <v>34</v>
       </c>
       <c r="E48">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F48">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G48">
         <v>33</v>
@@ -6102,10 +6111,10 @@
         <v>23</v>
       </c>
       <c r="K48">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M48">
         <v>40</v>
@@ -6122,7 +6131,7 @@
         <v>21</v>
       </c>
       <c r="D49">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E49">
         <v>18</v>
@@ -6137,13 +6146,13 @@
         <v>11</v>
       </c>
       <c r="I49">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J49">
         <v>22</v>
       </c>
       <c r="K49">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L49">
         <v>19</v>
@@ -6163,7 +6172,7 @@
         <v>25</v>
       </c>
       <c r="D50">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E50">
         <v>20</v>
@@ -6187,10 +6196,10 @@
         <v>25</v>
       </c>
       <c r="L50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M50">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6201,16 +6210,16 @@
         <v>32</v>
       </c>
       <c r="C51">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51">
         <v>33</v>
       </c>
       <c r="E51">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F51">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G51">
         <v>35</v>
@@ -6219,16 +6228,16 @@
         <v>44</v>
       </c>
       <c r="I51">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J51">
         <v>49</v>
       </c>
       <c r="K51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L51">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M51">
         <v>32</v>
@@ -6239,10 +6248,10 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C52">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D52">
         <v>95</v>
@@ -6251,28 +6260,28 @@
         <v>78</v>
       </c>
       <c r="F52">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G52">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H52">
         <v>57</v>
       </c>
       <c r="I52">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J52">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K52">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L52">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M52">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6280,25 +6289,25 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C53">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D53">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E53">
         <v>45</v>
       </c>
       <c r="F53">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G53">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H53">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I53">
         <v>38</v>
@@ -6310,7 +6319,7 @@
         <v>46</v>
       </c>
       <c r="L53">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M53">
         <v>24</v>
@@ -6321,37 +6330,37 @@
         <v>60</v>
       </c>
       <c r="B54">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C54">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D54">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E54">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F54">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G54">
         <v>63</v>
       </c>
       <c r="H54">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I54">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J54">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K54">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L54">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M54">
         <v>55</v>
@@ -6365,13 +6374,13 @@
         <v>18</v>
       </c>
       <c r="C55">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D55">
+        <v>40</v>
+      </c>
+      <c r="E55">
         <v>38</v>
-      </c>
-      <c r="E55">
-        <v>37</v>
       </c>
       <c r="F55">
         <v>27</v>
@@ -6380,16 +6389,16 @@
         <v>32</v>
       </c>
       <c r="H55">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I55">
+        <v>37</v>
+      </c>
+      <c r="J55">
+        <v>47</v>
+      </c>
+      <c r="K55">
         <v>36</v>
-      </c>
-      <c r="J55">
-        <v>46</v>
-      </c>
-      <c r="K55">
-        <v>33</v>
       </c>
       <c r="L55">
         <v>34</v>
@@ -6421,7 +6430,7 @@
         <v>10</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56">
         <v>8</v>
@@ -6462,10 +6471,10 @@
         <v>8</v>
       </c>
       <c r="H57">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I57">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J57">
         <v>14</v>
@@ -6512,7 +6521,7 @@
         <v>3</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -6529,7 +6538,7 @@
         <v>9</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F59">
         <v>8</v>
@@ -6544,7 +6553,7 @@
         <v>4</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K59">
         <v>9</v>
@@ -6585,7 +6594,7 @@
         <v>13</v>
       </c>
       <c r="J60">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K60">
         <v>29</v>
@@ -6661,7 +6670,7 @@
         <v>2</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6672,19 +6681,19 @@
         <v>139</v>
       </c>
       <c r="C63">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D63">
         <v>89</v>
       </c>
       <c r="E63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F63">
         <v>59</v>
       </c>
       <c r="G63">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H63">
         <v>46</v>
@@ -6702,7 +6711,7 @@
         <v>13</v>
       </c>
       <c r="M63">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6719,7 +6728,7 @@
         <v>12</v>
       </c>
       <c r="E64">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F64">
         <v>16</v>
@@ -6731,10 +6740,10 @@
         <v>17</v>
       </c>
       <c r="I64">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J64">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K64">
         <v>24</v>
@@ -6743,7 +6752,7 @@
         <v>26</v>
       </c>
       <c r="M64">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6751,37 +6760,37 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C65">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D65">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E65">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F65">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G65">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H65">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I65">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J65">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K65">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L65">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M65">
         <v>62</v>
@@ -6792,10 +6801,10 @@
         <v>72</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D66">
         <v>15</v>
@@ -6822,7 +6831,7 @@
         <v>16</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6830,37 +6839,37 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C67">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D67">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E67">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F67">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G67">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H67">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I67">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J67">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K67">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L67">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M67">
         <v>86</v>
@@ -6874,7 +6883,7 @@
         <v>5</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D68">
         <v>9</v>
@@ -6892,7 +6901,7 @@
         <v>3</v>
       </c>
       <c r="I68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J68">
         <v>12</v>
@@ -6927,7 +6936,7 @@
         <v>4</v>
       </c>
       <c r="G69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H69">
         <v>4</v>
@@ -6965,7 +6974,7 @@
         <v>4</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -6980,7 +6989,7 @@
         <v>9</v>
       </c>
       <c r="L70">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M70">
         <v>4</v>
@@ -7015,7 +7024,7 @@
         <v>6</v>
       </c>
       <c r="J71">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K71">
         <v>10</v>
@@ -7024,7 +7033,7 @@
         <v>8</v>
       </c>
       <c r="M71">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7041,10 +7050,10 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72">
         <v>18</v>
@@ -7062,7 +7071,7 @@
         <v>14</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M72">
         <v>13</v>
@@ -7073,13 +7082,13 @@
         <v>79</v>
       </c>
       <c r="B73">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C73">
         <v>28</v>
       </c>
       <c r="D73">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E73">
         <v>35</v>
@@ -7091,7 +7100,7 @@
         <v>29</v>
       </c>
       <c r="H73">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I73">
         <v>34</v>
@@ -7103,10 +7112,10 @@
         <v>41</v>
       </c>
       <c r="L73">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M73">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7135,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74">
         <v>5</v>
@@ -7155,7 +7164,7 @@
         <v>81</v>
       </c>
       <c r="B75">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C75">
         <v>13</v>
@@ -7199,25 +7208,25 @@
         <v>19</v>
       </c>
       <c r="C76">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D76">
         <v>38</v>
       </c>
       <c r="E76">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F76">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G76">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H76">
         <v>30</v>
       </c>
       <c r="I76">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J76">
         <v>60</v>
@@ -7229,7 +7238,7 @@
         <v>41</v>
       </c>
       <c r="M76">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7237,7 +7246,7 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C77">
         <v>26</v>
@@ -7264,7 +7273,7 @@
         <v>33</v>
       </c>
       <c r="K77">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L77">
         <v>19</v>
@@ -7281,13 +7290,13 @@
         <v>34</v>
       </c>
       <c r="C78">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D78">
         <v>45</v>
       </c>
       <c r="E78">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F78">
         <v>31</v>
@@ -7296,19 +7305,19 @@
         <v>53</v>
       </c>
       <c r="H78">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I78">
         <v>51</v>
       </c>
       <c r="J78">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K78">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L78">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M78">
         <v>43</v>
@@ -7319,37 +7328,37 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C79">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D79">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E79">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F79">
         <v>90</v>
       </c>
       <c r="G79">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H79">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I79">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J79">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K79">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L79">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M79">
         <v>69</v>
@@ -7375,13 +7384,13 @@
         <v>16</v>
       </c>
       <c r="G80">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I80">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J80">
         <v>10</v>
@@ -7445,7 +7454,7 @@
         <v>10</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E82">
         <v>8</v>
@@ -7483,34 +7492,34 @@
         <v>78</v>
       </c>
       <c r="D83">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E83">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F83">
         <v>57</v>
       </c>
       <c r="G83">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H83">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I83">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J83">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K83">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L83">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M83">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7518,7 +7527,7 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C84">
         <v>30</v>
@@ -7536,7 +7545,7 @@
         <v>30</v>
       </c>
       <c r="H84">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I84">
         <v>30</v>
@@ -7548,10 +7557,10 @@
         <v>29</v>
       </c>
       <c r="L84">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M84">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7559,40 +7568,40 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C85">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D85">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E85">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F85">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G85">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H85">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I85">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J85">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K85">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L85">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M85">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7603,7 +7612,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D86">
         <v>10</v>
@@ -7615,19 +7624,19 @@
         <v>18</v>
       </c>
       <c r="G86">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H86">
         <v>19</v>
       </c>
       <c r="I86">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J86">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K86">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L86">
         <v>22</v>
@@ -7685,7 +7694,7 @@
         <v>30</v>
       </c>
       <c r="C88">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D88">
         <v>44</v>
@@ -7715,7 +7724,7 @@
         <v>42</v>
       </c>
       <c r="M88">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7726,7 +7735,7 @@
         <v>40</v>
       </c>
       <c r="C89">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D89">
         <v>42</v>
@@ -7735,25 +7744,25 @@
         <v>28</v>
       </c>
       <c r="F89">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G89">
         <v>46</v>
       </c>
       <c r="H89">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I89">
         <v>27</v>
       </c>
       <c r="J89">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K89">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L89">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M89">
         <v>36</v>
@@ -7764,40 +7773,40 @@
         <v>96</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C90">
         <v>59</v>
       </c>
       <c r="D90">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E90">
         <v>29</v>
       </c>
       <c r="F90">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G90">
         <v>30</v>
       </c>
       <c r="H90">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I90">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J90">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K90">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L90">
         <v>25</v>
       </c>
       <c r="M90">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7811,13 +7820,13 @@
         <v>49</v>
       </c>
       <c r="D91">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E91">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F91">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G91">
         <v>42</v>
@@ -7826,19 +7835,19 @@
         <v>28</v>
       </c>
       <c r="I91">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J91">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K91">
         <v>38</v>
       </c>
       <c r="L91">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M91">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7864,10 +7873,10 @@
         <v>13</v>
       </c>
       <c r="H92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I92">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J92">
         <v>11</v>
@@ -7876,7 +7885,7 @@
         <v>16</v>
       </c>
       <c r="L92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M92">
         <v>10</v>
@@ -7905,13 +7914,13 @@
         <v>22</v>
       </c>
       <c r="H93">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I93">
         <v>16</v>
       </c>
       <c r="J93">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K93">
         <v>13</v>
@@ -7920,7 +7929,7 @@
         <v>15</v>
       </c>
       <c r="M93">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7934,10 +7943,10 @@
         <v>23</v>
       </c>
       <c r="D94">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E94">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F94">
         <v>20</v>
@@ -7946,22 +7955,22 @@
         <v>24</v>
       </c>
       <c r="H94">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I94">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J94">
         <v>23</v>
       </c>
       <c r="K94">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L94">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M94">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7972,31 +7981,31 @@
         <v>38</v>
       </c>
       <c r="C95">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D95">
         <v>67</v>
       </c>
       <c r="E95">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F95">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G95">
         <v>67</v>
       </c>
       <c r="H95">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I95">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J95">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K95">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L95">
         <v>43</v>
@@ -8013,7 +8022,7 @@
         <v>25</v>
       </c>
       <c r="C96">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D96">
         <v>35</v>
@@ -8022,22 +8031,22 @@
         <v>53</v>
       </c>
       <c r="F96">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G96">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H96">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I96">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J96">
         <v>48</v>
       </c>
       <c r="K96">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L96">
         <v>27</v>
@@ -8054,7 +8063,7 @@
         <v>11</v>
       </c>
       <c r="C97">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D97">
         <v>35</v>
@@ -8066,19 +8075,19 @@
         <v>20</v>
       </c>
       <c r="G97">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H97">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I97">
         <v>37</v>
       </c>
       <c r="J97">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K97">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L97">
         <v>36</v>
@@ -8119,7 +8128,7 @@
         <v>27</v>
       </c>
       <c r="K98">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L98">
         <v>22</v>
@@ -8133,7 +8142,7 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C99">
         <v>50</v>
@@ -8142,7 +8151,7 @@
         <v>83</v>
       </c>
       <c r="E99">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F99">
         <v>62</v>
@@ -8154,13 +8163,13 @@
         <v>68</v>
       </c>
       <c r="I99">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J99">
         <v>51</v>
       </c>
       <c r="K99">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L99">
         <v>47</v>
@@ -8215,40 +8224,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2855</v>
+        <v>2899</v>
       </c>
       <c r="C101">
-        <v>3698</v>
+        <v>3771</v>
       </c>
       <c r="D101">
-        <v>4048</v>
+        <v>4106</v>
       </c>
       <c r="E101">
-        <v>3576</v>
+        <v>3629</v>
       </c>
       <c r="F101">
-        <v>3206</v>
+        <v>3254</v>
       </c>
       <c r="G101">
-        <v>3493</v>
+        <v>3534</v>
       </c>
       <c r="H101">
-        <v>3239</v>
+        <v>3299</v>
       </c>
       <c r="I101">
-        <v>3394</v>
+        <v>3459</v>
       </c>
       <c r="J101">
-        <v>3829</v>
+        <v>3893</v>
       </c>
       <c r="K101">
-        <v>3747</v>
+        <v>3822</v>
       </c>
       <c r="L101">
-        <v>2969</v>
+        <v>3016</v>
       </c>
       <c r="M101">
-        <v>2689</v>
+        <v>2741</v>
       </c>
     </row>
   </sheetData>
@@ -8433,13 +8442,13 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>9</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -8454,7 +8463,7 @@
         <v>19</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <v>8</v>
@@ -8465,10 +8474,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -8486,7 +8495,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -8579,13 +8588,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -8614,28 +8623,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>19</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -8644,7 +8653,7 @@
         <v>40</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7">
         <v>28</v>
@@ -8721,16 +8730,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>29</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -8739,19 +8748,19 @@
         <v>38</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2">
         <v>25</v>
@@ -8765,25 +8774,25 @@
         <v>38</v>
       </c>
       <c r="C3">
+        <v>61</v>
+      </c>
+      <c r="D3">
         <v>60</v>
       </c>
-      <c r="D3">
-        <v>59</v>
-      </c>
       <c r="E3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3">
         <v>56</v>
@@ -8806,13 +8815,13 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -8827,7 +8836,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -8882,19 +8891,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6">
         <v>60</v>
       </c>
       <c r="D6">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6">
         <v>53</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>60</v>
@@ -8909,7 +8918,7 @@
         <v>42</v>
       </c>
       <c r="K6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L6">
         <v>37</v>
@@ -8923,37 +8932,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M7">
         <v>86</v>
@@ -9030,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -9063,7 +9072,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9089,7 +9098,7 @@
         <v>12</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3">
         <v>13</v>
@@ -9191,7 +9200,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -9202,7 +9211,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -9220,7 +9229,7 @@
         <v>30</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>30</v>
@@ -9232,10 +9241,10 @@
         <v>29</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -9315,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -9333,7 +9342,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -9403,7 +9412,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -9455,7 +9464,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -9481,7 +9490,7 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>18</v>
@@ -9496,13 +9505,13 @@
         <v>11</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J7">
         <v>22</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -9612,7 +9621,7 @@
         <v>14</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -9626,16 +9635,16 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>14</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>12</v>
@@ -9676,13 +9685,13 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -9725,16 +9734,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>35</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F6">
         <v>34</v>
@@ -9743,19 +9752,19 @@
         <v>35</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6">
         <v>25</v>
@@ -9766,37 +9775,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>63</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M7">
         <v>55</v>
@@ -9879,34 +9888,34 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>54</v>
       </c>
       <c r="F2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>52</v>
       </c>
       <c r="H2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J2">
         <v>56</v>
       </c>
       <c r="K2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9917,37 +9926,37 @@
         <v>66</v>
       </c>
       <c r="C3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>71</v>
       </c>
       <c r="E3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>74</v>
       </c>
       <c r="G3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3">
         <v>68</v>
       </c>
       <c r="I3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9967,7 +9976,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>15</v>
@@ -9979,7 +9988,7 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -10008,7 +10017,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -10040,10 +10049,10 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D6">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6">
         <v>59</v>
@@ -10055,19 +10064,19 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I6">
         <v>87</v>
       </c>
       <c r="J6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6">
         <v>68</v>
       </c>
       <c r="L6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M6">
         <v>35</v>
@@ -10081,37 +10090,37 @@
         <v>187</v>
       </c>
       <c r="C7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F7">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M7">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -10194,7 +10203,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10212,7 +10221,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -10297,7 +10306,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4">
         <v>11</v>
@@ -10331,7 +10340,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>13</v>
@@ -10346,7 +10355,7 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>17</v>
@@ -10369,10 +10378,10 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>33</v>
@@ -10387,10 +10396,10 @@
         <v>23</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M7">
         <v>40</v>
@@ -10473,7 +10482,7 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -10488,10 +10497,10 @@
         <v>21</v>
       </c>
       <c r="I2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -10500,7 +10509,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10514,34 +10523,34 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>19</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>30</v>
       </c>
       <c r="H3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>36</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3">
         <v>27</v>
       </c>
       <c r="M3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10614,7 +10623,7 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -10634,19 +10643,19 @@
         <v>36</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>30</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6">
         <v>31</v>
@@ -10655,10 +10664,10 @@
         <v>26</v>
       </c>
       <c r="J6">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6">
         <v>33</v>
@@ -10675,37 +10684,37 @@
         <v>69</v>
       </c>
       <c r="C7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J7">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L7">
         <v>95</v>
       </c>
       <c r="M7">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -10832,7 +10841,7 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -10847,7 +10856,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -10981,7 +10990,7 @@
         <v>42</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>37</v>
@@ -10996,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7">
         <v>18</v>
@@ -11079,7 +11088,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -11091,7 +11100,7 @@
         <v>8</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -11109,7 +11118,7 @@
         <v>4</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11219,10 +11228,10 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>30</v>
@@ -11231,7 +11240,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J6">
         <v>34</v>
@@ -11254,25 +11263,25 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7">
         <v>38</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7">
         <v>30</v>
       </c>
       <c r="I7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7">
         <v>60</v>
@@ -11284,7 +11293,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -11361,7 +11370,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -11522,7 +11531,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11533,7 +11542,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>22</v>
@@ -11560,7 +11569,7 @@
         <v>17</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -11640,10 +11649,10 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -11740,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -11812,10 +11821,10 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -11830,7 +11839,7 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <v>33</v>
@@ -11916,7 +11925,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -11937,7 +11946,7 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -11981,7 +11990,7 @@
         <v>4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -12050,7 +12059,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -12088,10 +12097,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>24</v>
@@ -12109,10 +12118,10 @@
         <v>11</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>41</v>
@@ -12198,10 +12207,10 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>27</v>
@@ -12213,13 +12222,13 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2">
         <v>32</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2">
         <v>28</v>
@@ -12236,19 +12245,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>31</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3">
         <v>39</v>
@@ -12257,7 +12266,7 @@
         <v>33</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>23</v>
@@ -12269,7 +12278,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12283,7 +12292,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -12292,7 +12301,7 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -12362,19 +12371,19 @@
         <v>66</v>
       </c>
       <c r="D6">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6">
         <v>58</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>42</v>
       </c>
       <c r="H6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6">
         <v>26</v>
@@ -12383,10 +12392,10 @@
         <v>98</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M6">
         <v>21</v>
@@ -12397,40 +12406,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -12733,7 +12742,7 @@
         <v>9</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -12774,7 +12783,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -12788,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -12837,7 +12846,7 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -12875,10 +12884,10 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>44</v>
@@ -12902,7 +12911,7 @@
         <v>23</v>
       </c>
       <c r="L7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -13006,7 +13015,7 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>13</v>
@@ -13038,7 +13047,7 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -13064,13 +13073,13 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>11</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -13128,7 +13137,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -13149,13 +13158,13 @@
         <v>18</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>19</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -13169,13 +13178,13 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>45</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>31</v>
@@ -13184,19 +13193,19 @@
         <v>53</v>
       </c>
       <c r="H7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I7">
         <v>51</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7">
         <v>43</v>
@@ -13276,7 +13285,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -13300,7 +13309,7 @@
         <v>9</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -13323,7 +13332,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -13332,13 +13341,13 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
         <v>8</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -13355,7 +13364,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -13370,7 +13379,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -13422,7 +13431,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>16</v>
@@ -13460,13 +13469,13 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
         <v>38</v>
-      </c>
-      <c r="E7">
-        <v>37</v>
       </c>
       <c r="F7">
         <v>27</v>
@@ -13475,16 +13484,16 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7">
+        <v>37</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
         <v>36</v>
-      </c>
-      <c r="J7">
-        <v>46</v>
-      </c>
-      <c r="K7">
-        <v>33</v>
       </c>
       <c r="L7">
         <v>34</v>
@@ -13638,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13689,10 +13698,10 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -13727,10 +13736,10 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>11</v>
@@ -13757,7 +13766,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -14107,7 +14116,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -14136,7 +14145,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -14154,7 +14163,7 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -14163,7 +14172,7 @@
         <v>10</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>12</v>
@@ -14256,16 +14265,16 @@
         <v>12</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>8</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14273,7 +14282,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -14285,28 +14294,28 @@
         <v>40</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>40</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7">
+        <v>32</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7">
         <v>31</v>
-      </c>
-      <c r="L7">
-        <v>28</v>
-      </c>
-      <c r="M7">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -14383,7 +14392,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -14392,13 +14401,13 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -14442,7 +14451,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -14514,6 +14523,9 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="M5">
         <v>1</v>
       </c>
@@ -14538,7 +14550,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>12</v>
@@ -14567,7 +14579,7 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>35</v>
@@ -14576,22 +14588,22 @@
         <v>53</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>48</v>
       </c>
       <c r="K7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L7">
         <v>27</v>
@@ -14680,7 +14692,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>8</v>
@@ -14736,16 +14748,16 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3">
         <v>12</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14817,13 +14829,13 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -14832,7 +14844,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -14844,7 +14856,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14858,13 +14870,13 @@
         <v>49</v>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
         <v>42</v>
@@ -14873,19 +14885,19 @@
         <v>28</v>
       </c>
       <c r="I7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7">
         <v>38</v>
       </c>
       <c r="L7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -15066,7 +15078,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -15107,7 +15119,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7">
         <v>12</v>
@@ -15202,19 +15214,19 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>31</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>37</v>
@@ -15223,10 +15235,10 @@
         <v>27</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2">
         <v>29</v>
@@ -15240,7 +15252,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>29</v>
@@ -15258,7 +15270,7 @@
         <v>33</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3">
         <v>27</v>
@@ -15302,7 +15314,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -15339,6 +15351,9 @@
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>3</v>
       </c>
@@ -15360,16 +15375,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>19</v>
@@ -15390,7 +15405,7 @@
         <v>23</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M6">
         <v>16</v>
@@ -15401,37 +15416,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F7">
         <v>90</v>
       </c>
       <c r="G7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M7">
         <v>69</v>
@@ -15517,7 +15532,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -15532,7 +15547,7 @@
         <v>10</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -15541,7 +15556,7 @@
         <v>8</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15573,7 +15588,7 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -15669,10 +15684,10 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -15681,7 +15696,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15698,7 +15713,7 @@
         <v>12</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>16</v>
@@ -15710,10 +15725,10 @@
         <v>17</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K7">
         <v>24</v>
@@ -15722,7 +15737,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -15802,10 +15817,10 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -15817,19 +15832,19 @@
         <v>31</v>
       </c>
       <c r="I2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2">
         <v>20</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15843,13 +15858,13 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>21</v>
@@ -15858,19 +15873,19 @@
         <v>21</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3">
+        <v>29</v>
+      </c>
+      <c r="K3">
         <v>27</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
       </c>
       <c r="L3">
         <v>22</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15881,7 +15896,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -15911,7 +15926,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15957,13 +15972,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>57</v>
@@ -15972,13 +15987,13 @@
         <v>41</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H6">
         <v>21</v>
       </c>
       <c r="I6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6">
         <v>26</v>
@@ -15990,7 +16005,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15998,40 +16013,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>79</v>
+      </c>
+      <c r="C7">
+        <v>81</v>
+      </c>
+      <c r="D7">
+        <v>97</v>
+      </c>
+      <c r="E7">
+        <v>130</v>
+      </c>
+      <c r="F7">
+        <v>113</v>
+      </c>
+      <c r="G7">
         <v>77</v>
-      </c>
-      <c r="C7">
-        <v>79</v>
-      </c>
-      <c r="D7">
-        <v>94</v>
-      </c>
-      <c r="E7">
-        <v>128</v>
-      </c>
-      <c r="F7">
-        <v>112</v>
-      </c>
-      <c r="G7">
-        <v>75</v>
       </c>
       <c r="H7">
         <v>87</v>
       </c>
       <c r="I7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K7">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -16105,7 +16120,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -16158,7 +16173,7 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -16230,13 +16245,13 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -16265,19 +16280,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>15</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>19</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -16622,19 +16637,19 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>19</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>15</v>
@@ -16669,10 +16684,10 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -16684,7 +16699,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16774,7 +16789,7 @@
         <v>17</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -16786,7 +16801,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -16815,19 +16830,19 @@
         <v>50</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K7">
         <v>44</v>
@@ -16836,7 +16851,7 @@
         <v>52</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -16969,13 +16984,13 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>3</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -16984,7 +16999,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17091,13 +17106,13 @@
         <v>22</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I7">
         <v>16</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>13</v>
@@ -17106,7 +17121,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -17396,34 +17411,34 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>35</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2">
         <v>35</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2">
         <v>42</v>
       </c>
       <c r="L2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17434,7 +17449,7 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -17443,7 +17458,7 @@
         <v>38</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>33</v>
@@ -17452,19 +17467,19 @@
         <v>29</v>
       </c>
       <c r="I3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>38</v>
       </c>
       <c r="K3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3">
         <v>35</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17513,7 +17528,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -17554,7 +17569,7 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -17563,10 +17578,10 @@
         <v>47</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6">
         <v>28</v>
@@ -17584,7 +17599,7 @@
         <v>29</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17595,37 +17610,37 @@
         <v>113</v>
       </c>
       <c r="C7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -17723,7 +17738,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -17764,7 +17779,7 @@
         <v>6</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -17845,7 +17860,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -17886,16 +17901,16 @@
         <v>19</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <v>8</v>
       </c>
       <c r="J7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -17996,7 +18011,7 @@
         <v>3</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -18005,7 +18020,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M2">
         <v>10</v>
@@ -18084,7 +18099,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -18109,10 +18124,10 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -18121,7 +18136,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -18130,7 +18145,7 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -18150,10 +18165,10 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -18162,22 +18177,22 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <v>23</v>
       </c>
       <c r="K7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -18542,7 +18557,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -18656,7 +18671,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -18679,7 +18694,7 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -18720,16 +18735,16 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>14</v>
       </c>
       <c r="H7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7">
         <v>36</v>
@@ -18918,7 +18933,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -19020,7 +19035,7 @@
         <v>31</v>
       </c>
       <c r="I7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <v>45</v>
@@ -19252,7 +19267,7 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6">
         <v>15</v>
@@ -19293,7 +19308,7 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>22</v>
@@ -19444,7 +19459,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -19461,7 +19476,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -19540,7 +19555,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19554,7 +19569,7 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -19578,10 +19593,10 @@
         <v>25</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -20021,10 +20036,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -20059,7 +20074,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -20089,7 +20104,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -20152,10 +20167,10 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -20182,7 +20197,7 @@
         <v>16</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -20256,16 +20271,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>9</v>
@@ -20277,13 +20292,13 @@
         <v>17</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <v>12</v>
       </c>
       <c r="K2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -20300,7 +20315,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -20315,7 +20330,7 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -20330,7 +20345,7 @@
         <v>17</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20359,13 +20374,13 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -20405,13 +20420,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>41</v>
@@ -20426,7 +20441,7 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>16</v>
@@ -20446,16 +20461,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7">
         <v>51</v>
@@ -20464,22 +20479,22 @@
         <v>57</v>
       </c>
       <c r="H7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J7">
         <v>44</v>
       </c>
       <c r="K7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L7">
         <v>46</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -20857,6 +20872,9 @@
       <c r="J4">
         <v>1</v>
       </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
       <c r="L4">
         <v>2</v>
       </c>
@@ -20910,7 +20928,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -20951,7 +20969,7 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>19</v>
@@ -20960,7 +20978,7 @@
         <v>26</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -21046,7 +21064,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -21081,7 +21099,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -21111,10 +21129,10 @@
         <v>9</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21189,7 +21207,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -21212,13 +21230,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -21230,7 +21248,7 @@
         <v>29</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7">
         <v>34</v>
@@ -21242,10 +21260,10 @@
         <v>41</v>
       </c>
       <c r="L7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -21328,7 +21346,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -21340,7 +21358,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -21464,7 +21482,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -21479,7 +21497,7 @@
         <v>4</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -21571,7 +21589,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -21583,7 +21601,7 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -21714,13 +21732,13 @@
         <v>12</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>9</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -21746,7 +21764,7 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -21755,13 +21773,13 @@
         <v>31</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
         <v>26</v>
@@ -21858,6 +21876,9 @@
       <c r="F2">
         <v>3</v>
       </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
       <c r="H2">
         <v>3</v>
       </c>
@@ -21874,7 +21895,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21909,7 +21930,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21972,7 +21993,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -21987,16 +22008,16 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>27</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>27</v>
@@ -22013,7 +22034,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>35</v>
@@ -22025,19 +22046,19 @@
         <v>20</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>37</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>36</v>
@@ -22176,7 +22197,7 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -22239,10 +22260,10 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -22280,10 +22301,10 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7">
         <v>11</v>
@@ -22292,7 +22313,7 @@
         <v>16</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -22377,7 +22398,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -22392,7 +22413,7 @@
         <v>2</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -22499,7 +22520,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -22514,7 +22535,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -22624,7 +22645,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22635,7 +22656,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -22778,7 +22799,7 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>44</v>
@@ -22808,7 +22829,7 @@
         <v>42</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -22903,7 +22924,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -22986,7 +23007,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -23015,7 +23036,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -23036,7 +23057,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -23140,13 +23161,13 @@
         <v>7</v>
       </c>
       <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
         <v>13</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>12</v>
       </c>
       <c r="M2">
         <v>7</v>
@@ -23169,7 +23190,7 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -23184,7 +23205,7 @@
         <v>10</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <v>9</v>
@@ -23262,7 +23283,7 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -23277,16 +23298,16 @@
         <v>19</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>8</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>11</v>
@@ -23303,7 +23324,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -23312,25 +23333,25 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7">
         <v>46</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>27</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7">
         <v>36</v>
@@ -23475,13 +23496,13 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23514,7 +23535,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -23555,7 +23576,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -23582,13 +23603,13 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -23736,7 +23757,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23774,7 +23795,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -23805,10 +23826,10 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>13</v>
@@ -23826,7 +23847,7 @@
         <v>20</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -23846,10 +23867,10 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>32</v>
@@ -23867,10 +23888,10 @@
         <v>45</v>
       </c>
       <c r="L7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -23964,6 +23985,9 @@
       <c r="H2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
         <v>3</v>
       </c>
@@ -23994,7 +24018,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -24006,7 +24030,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -24023,7 +24047,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -24035,7 +24059,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -24044,10 +24068,10 @@
         <v>12</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -24105,7 +24129,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -24117,19 +24141,19 @@
         <v>18</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H6">
         <v>19</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L6">
         <v>22</v>
@@ -24209,7 +24233,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -24366,7 +24390,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>13</v>
@@ -24473,25 +24497,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>8</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -24500,7 +24524,7 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L2">
         <v>12</v>
@@ -24514,13 +24538,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>9</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -24535,10 +24559,10 @@
         <v>14</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -24547,7 +24571,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24573,13 +24597,13 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -24634,7 +24658,7 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -24652,7 +24676,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -24669,40 +24693,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>59</v>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7">
         <v>29</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>30</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L7">
         <v>25</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -24820,7 +24844,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -24838,7 +24862,7 @@
         <v>12</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J3">
         <v>17</v>
@@ -24885,7 +24909,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -24928,10 +24952,10 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -24940,16 +24964,16 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>11</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -24963,16 +24987,16 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>33</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
         <v>35</v>
@@ -24981,16 +25005,16 @@
         <v>44</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>49</v>
       </c>
       <c r="K7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -25108,7 +25132,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -25123,7 +25147,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -25218,7 +25242,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -25236,7 +25260,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -25337,7 +25361,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -25378,7 +25402,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -25497,10 +25521,10 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7">
         <v>14</v>
@@ -25610,7 +25634,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -25651,7 +25675,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>11</v>
@@ -25779,7 +25803,7 @@
         <v>13</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>29</v>
@@ -25927,7 +25951,7 @@
         <v>7</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -25987,7 +26011,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -25996,7 +26020,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -26011,7 +26035,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6">
         <v>15</v>
@@ -26028,7 +26052,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -26037,7 +26061,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>25</v>
@@ -26052,10 +26076,10 @@
         <v>33</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -26135,13 +26159,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>28</v>
@@ -26153,19 +26177,19 @@
         <v>32</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I2">
         <v>41</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2">
         <v>39</v>
@@ -26179,16 +26203,16 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>51</v>
       </c>
       <c r="E3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>54</v>
@@ -26197,19 +26221,19 @@
         <v>60</v>
       </c>
       <c r="I3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3">
+        <v>64</v>
+      </c>
+      <c r="L3">
+        <v>66</v>
+      </c>
+      <c r="M3">
         <v>62</v>
-      </c>
-      <c r="L3">
-        <v>65</v>
-      </c>
-      <c r="M3">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26229,7 +26253,7 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -26282,7 +26306,7 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -26299,31 +26323,31 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>58</v>
+      </c>
+      <c r="C6">
+        <v>45</v>
+      </c>
+      <c r="D6">
         <v>57</v>
-      </c>
-      <c r="C6">
-        <v>44</v>
-      </c>
-      <c r="D6">
-        <v>56</v>
       </c>
       <c r="E6">
         <v>37</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K6">
         <v>40</v>
@@ -26340,40 +26364,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M7">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -26749,7 +26773,7 @@
         <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -26758,7 +26782,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26859,7 +26883,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -26868,7 +26892,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -26948,7 +26972,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -26966,7 +26990,7 @@
         <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <v>5</v>
@@ -26986,7 +27010,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -27100,10 +27124,10 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -27121,7 +27145,7 @@
         <v>14</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6">
         <v>13</v>
@@ -27199,6 +27223,9 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>2</v>
       </c>
@@ -27307,7 +27334,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -27432,7 +27459,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -27446,7 +27473,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>12</v>
@@ -27583,7 +27610,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>26</v>
@@ -27610,7 +27637,7 @@
         <v>33</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>19</v>
@@ -27896,6 +27923,9 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="I2">
         <v>2</v>
       </c>
@@ -28001,7 +28031,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -28101,6 +28131,12 @@
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
         <v>1</v>
       </c>
@@ -28207,7 +28243,7 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -28245,13 +28281,13 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -28547,7 +28583,7 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -28636,7 +28672,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -28674,7 +28710,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -28689,7 +28725,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -28799,10 +28835,10 @@
         <v>13</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2">
         <v>22</v>
@@ -28811,7 +28847,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28819,10 +28855,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>22</v>
@@ -28831,7 +28867,7 @@
         <v>25</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -28846,10 +28882,10 @@
         <v>29</v>
       </c>
       <c r="K3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>16</v>
@@ -28957,7 +28993,7 @@
         <v>26</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <v>26</v>
@@ -28969,7 +29005,7 @@
         <v>32</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -28983,10 +29019,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>95</v>
@@ -28995,28 +29031,28 @@
         <v>78</v>
       </c>
       <c r="F7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7">
         <v>57</v>
       </c>
       <c r="I7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -29090,7 +29126,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -29103,6 +29139,9 @@
       </c>
       <c r="F2">
         <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -29209,7 +29248,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -29224,7 +29263,7 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -30276,6 +30315,9 @@
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
@@ -30344,7 +30386,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -30434,7 +30476,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -30514,7 +30556,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C2">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="D2">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="E2">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="F2">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="G2">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="H2">
+        <v>904</v>
+      </c>
+      <c r="I2">
+        <v>893</v>
+      </c>
+      <c r="J2">
+        <v>1012</v>
+      </c>
+      <c r="K2">
+        <v>1115</v>
+      </c>
+      <c r="L2">
         <v>883</v>
       </c>
-      <c r="I2">
-        <v>879</v>
-      </c>
-      <c r="J2">
-        <v>990</v>
-      </c>
-      <c r="K2">
-        <v>1083</v>
-      </c>
-      <c r="L2">
-        <v>870</v>
-      </c>
       <c r="M2">
-        <v>839</v>
+        <v>853</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="C3">
-        <v>983</v>
+        <v>1005</v>
       </c>
       <c r="D3">
-        <v>1005</v>
+        <v>1023</v>
       </c>
       <c r="E3">
+        <v>945</v>
+      </c>
+      <c r="F3">
+        <v>946</v>
+      </c>
+      <c r="G3">
+        <v>1019</v>
+      </c>
+      <c r="H3">
         <v>926</v>
       </c>
-      <c r="F3">
-        <v>931</v>
-      </c>
-      <c r="G3">
-        <v>1003</v>
-      </c>
-      <c r="H3">
-        <v>902</v>
-      </c>
       <c r="I3">
-        <v>926</v>
+        <v>941</v>
       </c>
       <c r="J3">
-        <v>1076</v>
+        <v>1093</v>
       </c>
       <c r="K3">
-        <v>1032</v>
+        <v>1053</v>
       </c>
       <c r="L3">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="M3">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C4">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D4">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E4">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F4">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G4">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H4">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="I4">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="J4">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K4">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="L4">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="M4">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1009,22 +1009,22 @@
         <v>72</v>
       </c>
       <c r="H5">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I5">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1233</v>
+        <v>1254</v>
       </c>
       <c r="C6">
-        <v>1706</v>
+        <v>1729</v>
       </c>
       <c r="D6">
-        <v>1847</v>
+        <v>1863</v>
       </c>
       <c r="E6">
-        <v>1514</v>
+        <v>1533</v>
       </c>
       <c r="F6">
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="G6">
-        <v>1322</v>
+        <v>1342</v>
       </c>
       <c r="H6">
-        <v>1193</v>
+        <v>1207</v>
       </c>
       <c r="I6">
-        <v>1287</v>
+        <v>1302</v>
       </c>
       <c r="J6">
-        <v>1455</v>
+        <v>1473</v>
       </c>
       <c r="K6">
-        <v>1365</v>
+        <v>1379</v>
       </c>
       <c r="L6">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="M6">
-        <v>674</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2899</v>
+        <v>2947</v>
       </c>
       <c r="C7">
-        <v>3771</v>
+        <v>3831</v>
       </c>
       <c r="D7">
-        <v>4106</v>
+        <v>4156</v>
       </c>
       <c r="E7">
-        <v>3629</v>
+        <v>3691</v>
       </c>
       <c r="F7">
-        <v>3254</v>
+        <v>3301</v>
       </c>
       <c r="G7">
-        <v>3534</v>
+        <v>3586</v>
       </c>
       <c r="H7">
-        <v>3299</v>
+        <v>3372</v>
       </c>
       <c r="I7">
-        <v>3459</v>
+        <v>3515</v>
       </c>
       <c r="J7">
-        <v>3893</v>
+        <v>3956</v>
       </c>
       <c r="K7">
-        <v>3822</v>
+        <v>3895</v>
       </c>
       <c r="L7">
-        <v>3016</v>
+        <v>3065</v>
       </c>
       <c r="M7">
-        <v>2741</v>
+        <v>2793</v>
       </c>
     </row>
   </sheetData>
@@ -1192,7 +1192,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1279,6 +1279,9 @@
       <c r="L4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -1293,7 +1296,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1331,7 +1334,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1340,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -1361,7 +1364,7 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1555,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -1564,7 +1567,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -1593,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>14</v>
@@ -1689,13 +1692,13 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6">
         <v>22</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>13</v>
@@ -1704,10 +1707,10 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6">
         <v>22</v>
@@ -1727,28 +1730,28 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7">
         <v>45</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7">
         <v>33</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7">
         <v>46</v>
@@ -1831,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>51</v>
@@ -1840,31 +1843,31 @@
         <v>62</v>
       </c>
       <c r="E2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I2">
         <v>62</v>
       </c>
       <c r="J2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2">
         <v>51</v>
       </c>
       <c r="M2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1878,7 +1881,7 @@
         <v>75</v>
       </c>
       <c r="D3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>65</v>
@@ -1890,7 +1893,7 @@
         <v>79</v>
       </c>
       <c r="H3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I3">
         <v>57</v>
@@ -1905,7 +1908,7 @@
         <v>57</v>
       </c>
       <c r="M3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1928,19 +1931,19 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4">
         <v>7</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J4">
         <v>16</v>
       </c>
       <c r="K4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -1972,13 +1975,13 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -1995,7 +1998,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6">
         <v>125</v>
@@ -2004,31 +2007,31 @@
         <v>133</v>
       </c>
       <c r="E6">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F6">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G6">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H6">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J6">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K6">
         <v>72</v>
       </c>
       <c r="L6">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M6">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2036,40 +2039,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C7">
         <v>280</v>
       </c>
       <c r="D7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H7">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M7">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2146,7 +2149,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>23</v>
@@ -2155,7 +2158,7 @@
         <v>12</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>15</v>
@@ -2167,10 +2170,10 @@
         <v>25</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -2187,7 +2190,7 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>28</v>
@@ -2214,7 +2217,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3">
         <v>30</v>
@@ -2252,7 +2255,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -2316,7 +2319,7 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>16</v>
@@ -2345,7 +2348,7 @@
         <v>62</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -2354,10 +2357,10 @@
         <v>59</v>
       </c>
       <c r="F7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>66</v>
@@ -2366,13 +2369,13 @@
         <v>64</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M7">
         <v>70</v>
@@ -2449,13 +2452,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>28</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2">
         <v>41</v>
@@ -2467,7 +2470,7 @@
         <v>33</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <v>34</v>
@@ -2476,7 +2479,7 @@
         <v>35</v>
       </c>
       <c r="K2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2">
         <v>30</v>
@@ -2490,7 +2493,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>64</v>
@@ -2499,22 +2502,22 @@
         <v>50</v>
       </c>
       <c r="E3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>61</v>
       </c>
       <c r="H3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>53</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3">
         <v>58</v>
@@ -2523,7 +2526,7 @@
         <v>46</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2540,7 +2543,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -2602,7 +2605,7 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -2613,25 +2616,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F6">
         <v>64</v>
       </c>
       <c r="G6">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6">
         <v>58</v>
@@ -2640,13 +2643,13 @@
         <v>70</v>
       </c>
       <c r="K6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2654,40 +2657,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E7">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I7">
         <v>155</v>
       </c>
       <c r="J7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2770,7 +2773,7 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>21</v>
@@ -2785,7 +2788,7 @@
         <v>19</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2">
         <v>22</v>
@@ -2805,13 +2808,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -2829,10 +2832,10 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3">
         <v>13</v>
@@ -2846,7 +2849,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -2919,7 +2922,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -2960,16 +2963,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>59</v>
@@ -2984,13 +2987,13 @@
         <v>57</v>
       </c>
       <c r="J7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7">
         <v>45</v>
@@ -3073,7 +3076,7 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -3085,19 +3088,19 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2">
         <v>32</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2">
         <v>32</v>
@@ -3117,7 +3120,7 @@
         <v>37</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>36</v>
@@ -3129,13 +3132,13 @@
         <v>49</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>42</v>
       </c>
       <c r="K3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L3">
         <v>27</v>
@@ -3170,7 +3173,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -3214,7 +3217,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -3225,10 +3228,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>64</v>
@@ -3237,7 +3240,7 @@
         <v>34</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6">
         <v>27</v>
@@ -3249,10 +3252,10 @@
         <v>32</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6">
         <v>34</v>
@@ -3266,37 +3269,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G7">
         <v>96</v>
       </c>
       <c r="H7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K7">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7">
         <v>103</v>
@@ -3382,25 +3385,25 @@
         <v>18</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>15</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>19</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>26</v>
       </c>
       <c r="K2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2">
         <v>20</v>
@@ -3420,34 +3423,34 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>24</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3">
         <v>24</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3534,16 +3537,16 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>33</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -3575,37 +3578,37 @@
         <v>54</v>
       </c>
       <c r="C7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7">
+        <v>62</v>
+      </c>
+      <c r="G7">
         <v>59</v>
       </c>
-      <c r="G7">
-        <v>56</v>
-      </c>
       <c r="H7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
         <v>61</v>
-      </c>
-      <c r="M7">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3682,13 +3685,13 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>9</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -3729,7 +3732,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -3741,13 +3744,13 @@
         <v>21</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <v>19</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L3">
         <v>21</v>
@@ -3846,7 +3849,7 @@
         <v>14</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -3878,16 +3881,16 @@
         <v>65</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>83</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>67</v>
@@ -3896,13 +3899,13 @@
         <v>68</v>
       </c>
       <c r="I7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J7">
         <v>51</v>
       </c>
       <c r="K7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L7">
         <v>47</v>
@@ -4234,16 +4237,16 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>39</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>17</v>
@@ -4255,19 +4258,19 @@
         <v>33</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4340,7 +4343,7 @@
         <v>15</v>
       </c>
       <c r="J4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4">
         <v>15</v>
@@ -4349,7 +4352,7 @@
         <v>12</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4372,10 +4375,10 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>15</v>
@@ -4390,7 +4393,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4401,13 +4404,13 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>20</v>
@@ -4422,10 +4425,10 @@
         <v>27</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6">
         <v>23</v>
@@ -4439,40 +4442,40 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>135</v>
       </c>
       <c r="F7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L7">
         <v>97</v>
       </c>
       <c r="M7">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4480,40 +4483,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C8">
         <v>280</v>
       </c>
       <c r="D8">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F8">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H8">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I8">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J8">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K8">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L8">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M8">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4524,16 +4527,16 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9">
         <v>16</v>
@@ -4545,16 +4548,16 @@
         <v>19</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9">
         <v>19</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4571,7 +4574,7 @@
         <v>35</v>
       </c>
       <c r="E10">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>21</v>
@@ -4580,19 +4583,19 @@
         <v>30</v>
       </c>
       <c r="H10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10">
         <v>24</v>
       </c>
       <c r="K10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M10">
         <v>12</v>
@@ -4603,40 +4606,40 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F11">
         <v>51</v>
       </c>
       <c r="G11">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H11">
         <v>47</v>
       </c>
       <c r="I11">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K11">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L11">
         <v>46</v>
       </c>
       <c r="M11">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4668,7 +4671,7 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -4697,10 +4700,10 @@
         <v>3</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13">
         <v>6</v>
@@ -4726,7 +4729,7 @@
         <v>21</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>16</v>
@@ -4747,7 +4750,7 @@
         <v>15</v>
       </c>
       <c r="K14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L14">
         <v>11</v>
@@ -4764,7 +4767,7 @@
         <v>31</v>
       </c>
       <c r="C15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15">
         <v>49</v>
@@ -4773,13 +4776,13 @@
         <v>47</v>
       </c>
       <c r="F15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I15">
         <v>43</v>
@@ -4788,7 +4791,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15">
         <v>21</v>
@@ -4814,13 +4817,13 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>11</v>
       </c>
       <c r="I16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16">
         <v>9</v>
@@ -4864,7 +4867,7 @@
         <v>3</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>4</v>
@@ -4887,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18">
         <v>19</v>
@@ -4902,16 +4905,16 @@
         <v>54</v>
       </c>
       <c r="I18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J18">
         <v>59</v>
       </c>
       <c r="K18">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M18">
         <v>20</v>
@@ -4922,40 +4925,40 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19">
         <v>100</v>
       </c>
       <c r="E19">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19">
         <v>97</v>
       </c>
       <c r="G19">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H19">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I19">
+        <v>94</v>
+      </c>
+      <c r="J19">
+        <v>137</v>
+      </c>
+      <c r="K19">
+        <v>101</v>
+      </c>
+      <c r="L19">
+        <v>98</v>
+      </c>
+      <c r="M19">
         <v>91</v>
-      </c>
-      <c r="J19">
-        <v>133</v>
-      </c>
-      <c r="K19">
-        <v>99</v>
-      </c>
-      <c r="L19">
-        <v>95</v>
-      </c>
-      <c r="M19">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4963,13 +4966,13 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>81</v>
       </c>
       <c r="D20">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E20">
         <v>130</v>
@@ -4978,25 +4981,25 @@
         <v>113</v>
       </c>
       <c r="G20">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H20">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I20">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J20">
         <v>84</v>
       </c>
       <c r="K20">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L20">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M20">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5037,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5054,7 +5057,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -5089,34 +5092,34 @@
         <v>25</v>
       </c>
       <c r="C23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>48</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23">
         <v>28</v>
       </c>
       <c r="I23">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J23">
         <v>36</v>
       </c>
       <c r="K23">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L23">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M23">
         <v>31</v>
@@ -5148,7 +5151,7 @@
         <v>17</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>14</v>
@@ -5160,7 +5163,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5180,7 +5183,7 @@
         <v>17</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -5198,7 +5201,7 @@
         <v>18</v>
       </c>
       <c r="L25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -5259,7 +5262,7 @@
         <v>23</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -5274,10 +5277,10 @@
         <v>35</v>
       </c>
       <c r="J27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L27">
         <v>37</v>
@@ -5320,40 +5323,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C29">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D29">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E29">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F29">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G29">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H29">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I29">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J29">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K29">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L29">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M29">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5405,31 +5408,31 @@
         <v>25</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E31">
         <v>22</v>
       </c>
       <c r="F31">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H31">
         <v>19</v>
       </c>
       <c r="I31">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J31">
         <v>24</v>
       </c>
       <c r="K31">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L31">
         <v>31</v>
@@ -5446,7 +5449,7 @@
         <v>3</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>11</v>
@@ -5484,40 +5487,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C33">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D33">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E33">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F33">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G33">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H33">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I33">
         <v>155</v>
       </c>
       <c r="J33">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K33">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L33">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M33">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5572,7 +5575,7 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -5587,7 +5590,7 @@
         <v>5</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -5599,7 +5602,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -5607,40 +5610,40 @@
         <v>42</v>
       </c>
       <c r="B36">
+        <v>44</v>
+      </c>
+      <c r="C36">
         <v>41</v>
-      </c>
-      <c r="C36">
-        <v>40</v>
       </c>
       <c r="D36">
         <v>37</v>
       </c>
       <c r="E36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F36">
         <v>43</v>
       </c>
       <c r="G36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H36">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I36">
         <v>47</v>
       </c>
       <c r="J36">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K36">
         <v>44</v>
       </c>
       <c r="L36">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M36">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5648,37 +5651,37 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D37">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E37">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F37">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G37">
         <v>96</v>
       </c>
       <c r="H37">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I37">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J37">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K37">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L37">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M37">
         <v>103</v>
@@ -5783,7 +5786,7 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -5800,10 +5803,10 @@
         <v>17</v>
       </c>
       <c r="C41">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E41">
         <v>25</v>
@@ -5815,7 +5818,7 @@
         <v>19</v>
       </c>
       <c r="H41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I41">
         <v>15</v>
@@ -5838,40 +5841,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C42">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D42">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E42">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F42">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G42">
         <v>116</v>
       </c>
       <c r="H42">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I42">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J42">
         <v>163</v>
       </c>
       <c r="K42">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L42">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M42">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5882,10 +5885,10 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E43">
         <v>23</v>
@@ -5903,16 +5906,16 @@
         <v>33</v>
       </c>
       <c r="J43">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K43">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M43">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5923,13 +5926,13 @@
         <v>30</v>
       </c>
       <c r="C44">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D44">
         <v>35</v>
       </c>
       <c r="E44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F44">
         <v>21</v>
@@ -5953,7 +5956,7 @@
         <v>18</v>
       </c>
       <c r="M44">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -5988,7 +5991,7 @@
         <v>6</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L45">
         <v>2</v>
@@ -6002,7 +6005,7 @@
         <v>52</v>
       </c>
       <c r="B46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>7</v>
@@ -6035,7 +6038,7 @@
         <v>9</v>
       </c>
       <c r="M46">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -6049,7 +6052,7 @@
         <v>22</v>
       </c>
       <c r="D47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47">
         <v>18</v>
@@ -6061,13 +6064,13 @@
         <v>14</v>
       </c>
       <c r="H47">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J47">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K47">
         <v>27</v>
@@ -6090,13 +6093,13 @@
         <v>52</v>
       </c>
       <c r="D48">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E48">
         <v>37</v>
       </c>
       <c r="F48">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G48">
         <v>33</v>
@@ -6105,10 +6108,10 @@
         <v>39</v>
       </c>
       <c r="I48">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J48">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K48">
         <v>37</v>
@@ -6117,7 +6120,7 @@
         <v>48</v>
       </c>
       <c r="M48">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6134,10 +6137,10 @@
         <v>28</v>
       </c>
       <c r="E49">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G49">
         <v>26</v>
@@ -6158,7 +6161,7 @@
         <v>19</v>
       </c>
       <c r="M49">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6225,7 +6228,7 @@
         <v>35</v>
       </c>
       <c r="H51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I51">
         <v>35</v>
@@ -6251,16 +6254,16 @@
         <v>47</v>
       </c>
       <c r="C52">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D52">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E52">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F52">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G52">
         <v>65</v>
@@ -6272,10 +6275,10 @@
         <v>70</v>
       </c>
       <c r="J52">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K52">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L52">
         <v>53</v>
@@ -6292,28 +6295,28 @@
         <v>43</v>
       </c>
       <c r="C53">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D53">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E53">
         <v>45</v>
       </c>
       <c r="F53">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G53">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H53">
         <v>33</v>
       </c>
       <c r="I53">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J53">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K53">
         <v>46</v>
@@ -6333,22 +6336,22 @@
         <v>45</v>
       </c>
       <c r="C54">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D54">
         <v>58</v>
       </c>
       <c r="E54">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F54">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G54">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H54">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I54">
         <v>77</v>
@@ -6357,13 +6360,13 @@
         <v>80</v>
       </c>
       <c r="K54">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L54">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M54">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6374,10 +6377,10 @@
         <v>18</v>
       </c>
       <c r="C55">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D55">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E55">
         <v>38</v>
@@ -6389,22 +6392,22 @@
         <v>32</v>
       </c>
       <c r="H55">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I55">
+        <v>38</v>
+      </c>
+      <c r="J55">
+        <v>48</v>
+      </c>
+      <c r="K55">
         <v>37</v>
       </c>
-      <c r="J55">
-        <v>47</v>
-      </c>
-      <c r="K55">
+      <c r="L55">
+        <v>35</v>
+      </c>
+      <c r="M55">
         <v>36</v>
-      </c>
-      <c r="L55">
-        <v>34</v>
-      </c>
-      <c r="M55">
-        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6433,7 +6436,7 @@
         <v>3</v>
       </c>
       <c r="I56">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J56">
         <v>3</v>
@@ -6486,7 +6489,7 @@
         <v>17</v>
       </c>
       <c r="M57">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6494,7 +6497,7 @@
         <v>64</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -6532,7 +6535,7 @@
         <v>3</v>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -6570,7 +6573,7 @@
         <v>66</v>
       </c>
       <c r="B60">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C60">
         <v>21</v>
@@ -6579,7 +6582,7 @@
         <v>33</v>
       </c>
       <c r="E60">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F60">
         <v>18</v>
@@ -6594,7 +6597,7 @@
         <v>13</v>
       </c>
       <c r="J60">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K60">
         <v>29</v>
@@ -6684,10 +6687,10 @@
         <v>73</v>
       </c>
       <c r="D63">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E63">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F63">
         <v>59</v>
@@ -6705,13 +6708,13 @@
         <v>49</v>
       </c>
       <c r="K63">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L63">
         <v>13</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6737,7 +6740,7 @@
         <v>24</v>
       </c>
       <c r="H64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I64">
         <v>40</v>
@@ -6749,7 +6752,7 @@
         <v>24</v>
       </c>
       <c r="L64">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M64">
         <v>24</v>
@@ -6763,37 +6766,37 @@
         <v>54</v>
       </c>
       <c r="C65">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D65">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E65">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F65">
+        <v>62</v>
+      </c>
+      <c r="G65">
         <v>59</v>
       </c>
-      <c r="G65">
-        <v>56</v>
-      </c>
       <c r="H65">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I65">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J65">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K65">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L65">
+        <v>63</v>
+      </c>
+      <c r="M65">
         <v>61</v>
-      </c>
-      <c r="M65">
-        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6822,7 +6825,7 @@
         <v>9</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66">
         <v>8</v>
@@ -6830,8 +6833,11 @@
       <c r="K66">
         <v>16</v>
       </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
       <c r="M66">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6839,40 +6845,40 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C67">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D67">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E67">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F67">
+        <v>134</v>
+      </c>
+      <c r="G67">
+        <v>153</v>
+      </c>
+      <c r="H67">
         <v>131</v>
       </c>
-      <c r="G67">
-        <v>152</v>
-      </c>
-      <c r="H67">
-        <v>126</v>
-      </c>
       <c r="I67">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J67">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K67">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L67">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M67">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6924,7 +6930,7 @@
         <v>6</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>6</v>
@@ -6933,7 +6939,7 @@
         <v>5</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G69">
         <v>8</v>
@@ -6954,7 +6960,7 @@
         <v>7</v>
       </c>
       <c r="M69">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6977,7 +6983,7 @@
         <v>3</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I70">
         <v>6</v>
@@ -7000,7 +7006,7 @@
         <v>77</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -7012,13 +7018,13 @@
         <v>4</v>
       </c>
       <c r="F71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G71">
         <v>7</v>
       </c>
       <c r="H71">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I71">
         <v>6</v>
@@ -7044,7 +7050,7 @@
         <v>4</v>
       </c>
       <c r="C72">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D72">
         <v>14</v>
@@ -7065,7 +7071,7 @@
         <v>10</v>
       </c>
       <c r="J72">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K72">
         <v>14</v>
@@ -7094,28 +7100,28 @@
         <v>35</v>
       </c>
       <c r="F73">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G73">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H73">
         <v>35</v>
       </c>
       <c r="I73">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J73">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K73">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L73">
         <v>22</v>
       </c>
       <c r="M73">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7141,7 +7147,7 @@
         <v>7</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I74">
         <v>5</v>
@@ -7191,7 +7197,7 @@
         <v>17</v>
       </c>
       <c r="K75">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L75">
         <v>13</v>
@@ -7208,13 +7214,13 @@
         <v>19</v>
       </c>
       <c r="C76">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D76">
         <v>38</v>
       </c>
       <c r="E76">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F76">
         <v>49</v>
@@ -7226,16 +7232,16 @@
         <v>30</v>
       </c>
       <c r="I76">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J76">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K76">
         <v>52</v>
       </c>
       <c r="L76">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M76">
         <v>40</v>
@@ -7261,10 +7267,10 @@
         <v>17</v>
       </c>
       <c r="G77">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H77">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I77">
         <v>25</v>
@@ -7273,10 +7279,10 @@
         <v>33</v>
       </c>
       <c r="K77">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L77">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M77">
         <v>25</v>
@@ -7287,7 +7293,7 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C78">
         <v>51</v>
@@ -7299,16 +7305,16 @@
         <v>51</v>
       </c>
       <c r="F78">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G78">
         <v>53</v>
       </c>
       <c r="H78">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I78">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J78">
         <v>57</v>
@@ -7317,7 +7323,7 @@
         <v>57</v>
       </c>
       <c r="L78">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M78">
         <v>43</v>
@@ -7328,37 +7334,37 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C79">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D79">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E79">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F79">
         <v>90</v>
       </c>
       <c r="G79">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H79">
         <v>117</v>
       </c>
       <c r="I79">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J79">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K79">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L79">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M79">
         <v>69</v>
@@ -7451,7 +7457,7 @@
         <v>5</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82">
         <v>7</v>
@@ -7489,7 +7495,7 @@
         <v>62</v>
       </c>
       <c r="C83">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D83">
         <v>81</v>
@@ -7498,10 +7504,10 @@
         <v>59</v>
       </c>
       <c r="F83">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G83">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H83">
         <v>66</v>
@@ -7510,13 +7516,13 @@
         <v>64</v>
       </c>
       <c r="J83">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K83">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L83">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M83">
         <v>70</v>
@@ -7533,16 +7539,16 @@
         <v>30</v>
       </c>
       <c r="D84">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E84">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F84">
         <v>27</v>
       </c>
       <c r="G84">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H84">
         <v>28</v>
@@ -7554,13 +7560,13 @@
         <v>39</v>
       </c>
       <c r="K84">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L84">
         <v>27</v>
       </c>
       <c r="M84">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7568,40 +7574,40 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C85">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D85">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E85">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F85">
         <v>154</v>
       </c>
       <c r="G85">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H85">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I85">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J85">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K85">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L85">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M85">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7609,7 +7615,7 @@
         <v>92</v>
       </c>
       <c r="B86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86">
         <v>17</v>
@@ -7621,16 +7627,16 @@
         <v>23</v>
       </c>
       <c r="F86">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G86">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I86">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J86">
         <v>16</v>
@@ -7659,7 +7665,7 @@
         <v>12</v>
       </c>
       <c r="E87">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F87">
         <v>10</v>
@@ -7683,7 +7689,7 @@
         <v>11</v>
       </c>
       <c r="M87">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7706,13 +7712,13 @@
         <v>38</v>
       </c>
       <c r="G88">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H88">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I88">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J88">
         <v>29</v>
@@ -7724,7 +7730,7 @@
         <v>42</v>
       </c>
       <c r="M88">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7732,13 +7738,13 @@
         <v>95</v>
       </c>
       <c r="B89">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C89">
         <v>38</v>
       </c>
       <c r="D89">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E89">
         <v>28</v>
@@ -7750,22 +7756,22 @@
         <v>46</v>
       </c>
       <c r="H89">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I89">
         <v>27</v>
       </c>
       <c r="J89">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K89">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L89">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M89">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7779,31 +7785,31 @@
         <v>59</v>
       </c>
       <c r="D90">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E90">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F90">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G90">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H90">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I90">
         <v>40</v>
       </c>
       <c r="J90">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K90">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L90">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M90">
         <v>31</v>
@@ -7820,16 +7826,16 @@
         <v>49</v>
       </c>
       <c r="D91">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E91">
         <v>41</v>
       </c>
       <c r="F91">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G91">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H91">
         <v>28</v>
@@ -7838,7 +7844,7 @@
         <v>43</v>
       </c>
       <c r="J91">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K91">
         <v>38</v>
@@ -7847,7 +7853,7 @@
         <v>39</v>
       </c>
       <c r="M91">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7867,10 +7873,10 @@
         <v>14</v>
       </c>
       <c r="F92">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G92">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H92">
         <v>8</v>
@@ -7896,7 +7902,7 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C93">
         <v>24</v>
@@ -7905,10 +7911,10 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F93">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G93">
         <v>22</v>
@@ -7929,7 +7935,7 @@
         <v>15</v>
       </c>
       <c r="M93">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7940,7 +7946,7 @@
         <v>10</v>
       </c>
       <c r="C94">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D94">
         <v>31</v>
@@ -7958,16 +7964,16 @@
         <v>19</v>
       </c>
       <c r="I94">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J94">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K94">
         <v>44</v>
       </c>
       <c r="L94">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M94">
         <v>32</v>
@@ -7978,16 +7984,16 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C95">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D95">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E95">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F95">
         <v>59</v>
@@ -8002,13 +8008,13 @@
         <v>57</v>
       </c>
       <c r="J95">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K95">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L95">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M95">
         <v>45</v>
@@ -8019,7 +8025,7 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C96">
         <v>39</v>
@@ -8034,16 +8040,16 @@
         <v>37</v>
       </c>
       <c r="G96">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H96">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I96">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J96">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K96">
         <v>61</v>
@@ -8052,7 +8058,7 @@
         <v>27</v>
       </c>
       <c r="M96">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8060,7 +8066,7 @@
         <v>103</v>
       </c>
       <c r="B97">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C97">
         <v>33</v>
@@ -8081,19 +8087,19 @@
         <v>24</v>
       </c>
       <c r="I97">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J97">
         <v>21</v>
       </c>
       <c r="K97">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L97">
         <v>36</v>
       </c>
       <c r="M97">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8104,25 +8110,25 @@
         <v>16</v>
       </c>
       <c r="C98">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D98">
         <v>30</v>
       </c>
       <c r="E98">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F98">
         <v>14</v>
       </c>
       <c r="G98">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H98">
         <v>18</v>
       </c>
       <c r="I98">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J98">
         <v>27</v>
@@ -8145,16 +8151,16 @@
         <v>65</v>
       </c>
       <c r="C99">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D99">
         <v>83</v>
       </c>
       <c r="E99">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F99">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G99">
         <v>67</v>
@@ -8163,13 +8169,13 @@
         <v>68</v>
       </c>
       <c r="I99">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J99">
         <v>51</v>
       </c>
       <c r="K99">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L99">
         <v>47</v>
@@ -8186,7 +8192,7 @@
         <v>3</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D100">
         <v>5</v>
@@ -8224,40 +8230,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2899</v>
+        <v>2947</v>
       </c>
       <c r="C101">
-        <v>3771</v>
+        <v>3831</v>
       </c>
       <c r="D101">
-        <v>4106</v>
+        <v>4156</v>
       </c>
       <c r="E101">
-        <v>3629</v>
+        <v>3691</v>
       </c>
       <c r="F101">
-        <v>3254</v>
+        <v>3301</v>
       </c>
       <c r="G101">
-        <v>3534</v>
+        <v>3586</v>
       </c>
       <c r="H101">
-        <v>3299</v>
+        <v>3372</v>
       </c>
       <c r="I101">
-        <v>3459</v>
+        <v>3515</v>
       </c>
       <c r="J101">
-        <v>3893</v>
+        <v>3956</v>
       </c>
       <c r="K101">
-        <v>3822</v>
+        <v>3895</v>
       </c>
       <c r="L101">
-        <v>3016</v>
+        <v>3065</v>
       </c>
       <c r="M101">
-        <v>2741</v>
+        <v>2793</v>
       </c>
     </row>
   </sheetData>
@@ -8445,22 +8451,22 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>14</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -8480,7 +8486,7 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -8518,7 +8524,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -8626,31 +8632,31 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>22</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>19</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>24</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7">
         <v>31</v>
@@ -8730,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>32</v>
@@ -8748,22 +8754,22 @@
         <v>38</v>
       </c>
       <c r="H2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I2">
         <v>36</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2">
         <v>46</v>
       </c>
       <c r="L2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8771,31 +8777,31 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>61</v>
       </c>
       <c r="D3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>44</v>
       </c>
       <c r="H3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K3">
         <v>46</v>
@@ -8821,7 +8827,7 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -8894,31 +8900,31 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6">
         <v>48</v>
       </c>
       <c r="I6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J6">
         <v>42</v>
       </c>
       <c r="K6">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L6">
         <v>37</v>
@@ -8932,40 +8938,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F7">
+        <v>134</v>
+      </c>
+      <c r="G7">
+        <v>153</v>
+      </c>
+      <c r="H7">
         <v>131</v>
       </c>
-      <c r="G7">
-        <v>152</v>
-      </c>
-      <c r="H7">
-        <v>126</v>
-      </c>
       <c r="I7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M7">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -9045,7 +9051,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -9072,7 +9078,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9089,13 +9095,13 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -9197,7 +9203,7 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -9217,16 +9223,16 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>27</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>28</v>
@@ -9238,13 +9244,13 @@
         <v>39</v>
       </c>
       <c r="K7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>27</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -9327,10 +9333,10 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -9386,7 +9392,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9424,7 +9430,7 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9476,7 +9482,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9493,10 +9499,10 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>26</v>
@@ -9517,7 +9523,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -9594,7 +9600,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -9618,7 +9624,7 @@
         <v>21</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2">
         <v>19</v>
@@ -9641,16 +9647,16 @@
         <v>10</v>
       </c>
       <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3">
         <v>14</v>
-      </c>
-      <c r="F3">
-        <v>13</v>
       </c>
       <c r="G3">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>16</v>
@@ -9662,10 +9668,10 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9691,7 +9697,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -9743,13 +9749,13 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>34</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6">
         <v>21</v>
@@ -9764,7 +9770,7 @@
         <v>27</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6">
         <v>25</v>
@@ -9778,22 +9784,22 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>58</v>
       </c>
       <c r="E7">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I7">
         <v>77</v>
@@ -9802,13 +9808,13 @@
         <v>80</v>
       </c>
       <c r="K7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L7">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M7">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -9888,34 +9894,34 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2">
         <v>50</v>
       </c>
       <c r="G2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J2">
         <v>56</v>
       </c>
       <c r="K2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9923,37 +9929,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3">
         <v>71</v>
       </c>
       <c r="E3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H3">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M3">
         <v>56</v>
@@ -10029,7 +10035,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -10038,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10046,37 +10052,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>97</v>
       </c>
       <c r="D6">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <v>52</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I6">
         <v>87</v>
       </c>
       <c r="J6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6">
         <v>68</v>
       </c>
       <c r="L6">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M6">
         <v>35</v>
@@ -10087,40 +10093,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H7">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L7">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M7">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -10227,7 +10233,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10247,7 +10253,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -10268,7 +10274,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10282,7 +10288,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -10300,7 +10306,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>6</v>
@@ -10340,7 +10346,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>13</v>
@@ -10349,10 +10355,10 @@
         <v>23</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K6">
         <v>17</v>
@@ -10361,7 +10367,7 @@
         <v>17</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10375,13 +10381,13 @@
         <v>52</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>37</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>33</v>
@@ -10390,10 +10396,10 @@
         <v>39</v>
       </c>
       <c r="I7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>37</v>
@@ -10402,7 +10408,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -10491,19 +10497,19 @@
         <v>26</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2">
         <v>29</v>
@@ -10535,19 +10541,19 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3">
         <v>33</v>
@@ -10576,7 +10582,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -10588,7 +10594,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -10617,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -10629,10 +10635,10 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10640,16 +10646,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>35</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>30</v>
@@ -10658,13 +10664,13 @@
         <v>43</v>
       </c>
       <c r="H6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6">
         <v>26</v>
       </c>
       <c r="J6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6">
         <v>27</v>
@@ -10673,7 +10679,7 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10681,40 +10687,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>100</v>
       </c>
       <c r="E7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>97</v>
       </c>
       <c r="G7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H7">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I7">
+        <v>94</v>
+      </c>
+      <c r="J7">
+        <v>137</v>
+      </c>
+      <c r="K7">
+        <v>101</v>
+      </c>
+      <c r="L7">
+        <v>98</v>
+      </c>
+      <c r="M7">
         <v>91</v>
-      </c>
-      <c r="J7">
-        <v>133</v>
-      </c>
-      <c r="K7">
-        <v>99</v>
-      </c>
-      <c r="L7">
-        <v>95</v>
-      </c>
-      <c r="M7">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -10821,7 +10827,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10832,7 +10838,7 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -10940,13 +10946,13 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>18</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -10981,13 +10987,13 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>35</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>21</v>
@@ -11011,7 +11017,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -11109,7 +11115,7 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
         <v>9</v>
@@ -11129,7 +11135,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -11147,7 +11153,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3">
         <v>14</v>
@@ -11194,7 +11200,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -11210,6 +11216,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="L5">
         <v>1</v>
       </c>
@@ -11228,7 +11237,7 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>26</v>
@@ -11263,13 +11272,13 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>38</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>49</v>
@@ -11281,16 +11290,16 @@
         <v>30</v>
       </c>
       <c r="I7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7">
         <v>52</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7">
         <v>40</v>
@@ -11394,7 +11403,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -11435,7 +11444,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -11507,7 +11516,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -11545,7 +11554,7 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>16</v>
@@ -11566,7 +11575,7 @@
         <v>15</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -11690,7 +11699,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -11711,7 +11720,7 @@
         <v>9</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -11754,6 +11763,9 @@
       <c r="J4">
         <v>1</v>
       </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
       <c r="M4">
         <v>2</v>
       </c>
@@ -11783,10 +11795,10 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -11821,13 +11833,13 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -11842,10 +11854,10 @@
         <v>27</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
         <v>23</v>
@@ -11972,7 +11984,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -12059,7 +12071,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -12074,7 +12086,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -12100,10 +12112,10 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>25</v>
@@ -12115,7 +12127,7 @@
         <v>19</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>15</v>
@@ -12204,25 +12216,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <v>21</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2">
         <v>32</v>
@@ -12231,7 +12243,7 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2">
         <v>24</v>
@@ -12245,13 +12257,13 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>42</v>
+      </c>
+      <c r="D3">
         <v>34</v>
-      </c>
-      <c r="C3">
-        <v>41</v>
-      </c>
-      <c r="D3">
-        <v>31</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -12263,10 +12275,10 @@
         <v>39</v>
       </c>
       <c r="H3">
+        <v>35</v>
+      </c>
+      <c r="I3">
         <v>33</v>
-      </c>
-      <c r="I3">
-        <v>31</v>
       </c>
       <c r="J3">
         <v>23</v>
@@ -12275,10 +12287,10 @@
         <v>37</v>
       </c>
       <c r="L3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12286,19 +12298,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -12307,7 +12319,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -12365,10 +12377,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>88</v>
@@ -12383,7 +12395,7 @@
         <v>42</v>
       </c>
       <c r="H6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6">
         <v>26</v>
@@ -12398,7 +12410,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12406,40 +12418,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G7">
         <v>116</v>
       </c>
       <c r="H7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J7">
         <v>163</v>
       </c>
       <c r="K7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M7">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -12527,6 +12539,9 @@
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>2</v>
       </c>
@@ -12551,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -12623,10 +12638,10 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -12742,7 +12757,7 @@
         <v>9</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -12762,7 +12777,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -12780,7 +12795,7 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -12858,10 +12873,10 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -12890,7 +12905,7 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>21</v>
@@ -12899,19 +12914,19 @@
         <v>30</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>24</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -12988,7 +13003,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -13000,7 +13015,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -13018,7 +13033,7 @@
         <v>19</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2">
         <v>10</v>
@@ -13059,7 +13074,7 @@
         <v>14</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>17</v>
@@ -13152,10 +13167,10 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -13164,7 +13179,7 @@
         <v>19</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -13175,7 +13190,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>51</v>
@@ -13187,16 +13202,16 @@
         <v>51</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>53</v>
       </c>
       <c r="H7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7">
         <v>57</v>
@@ -13205,7 +13220,7 @@
         <v>57</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M7">
         <v>43</v>
@@ -13300,16 +13315,16 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>12</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -13344,7 +13359,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -13356,7 +13371,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13428,10 +13443,10 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>16</v>
@@ -13455,7 +13470,7 @@
         <v>13</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -13469,10 +13484,10 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>38</v>
@@ -13484,22 +13499,22 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7">
+        <v>38</v>
+      </c>
+      <c r="J7">
+        <v>48</v>
+      </c>
+      <c r="K7">
         <v>37</v>
       </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
+      <c r="L7">
+        <v>35</v>
+      </c>
+      <c r="M7">
         <v>36</v>
-      </c>
-      <c r="L7">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -13594,7 +13609,7 @@
         <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -13606,7 +13621,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13754,7 +13769,7 @@
         <v>17</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>14</v>
@@ -13766,7 +13781,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -13956,7 +13971,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -13989,7 +14004,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13997,7 +14012,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -14030,7 +14045,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -14131,10 +14146,10 @@
         <v>10</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <v>5</v>
@@ -14148,7 +14163,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -14157,7 +14172,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -14189,13 +14204,13 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -14256,13 +14271,13 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6">
         <v>9</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -14285,34 +14300,34 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>48</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>28</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>36</v>
       </c>
       <c r="K7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7">
         <v>31</v>
@@ -14389,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -14404,7 +14419,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -14448,13 +14463,13 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>12</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -14556,10 +14571,10 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6">
         <v>32</v>
@@ -14568,7 +14583,7 @@
         <v>3</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14576,7 +14591,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -14591,16 +14606,16 @@
         <v>37</v>
       </c>
       <c r="G7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K7">
         <v>61</v>
@@ -14609,7 +14624,7 @@
         <v>27</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -14689,7 +14704,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>13</v>
@@ -14716,7 +14731,7 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14739,7 +14754,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -14806,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -14829,13 +14844,13 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -14870,16 +14885,16 @@
         <v>49</v>
       </c>
       <c r="D7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E7">
         <v>41</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7">
         <v>28</v>
@@ -14888,7 +14903,7 @@
         <v>43</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7">
         <v>38</v>
@@ -14897,7 +14912,7 @@
         <v>39</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -15096,7 +15111,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15137,7 +15152,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -15211,7 +15226,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>28</v>
@@ -15226,19 +15241,19 @@
         <v>31</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2">
         <v>37</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2">
         <v>33</v>
       </c>
       <c r="K2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L2">
         <v>29</v>
@@ -15255,13 +15270,13 @@
         <v>22</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>19</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>31</v>
@@ -15279,7 +15294,7 @@
         <v>38</v>
       </c>
       <c r="K3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L3">
         <v>31</v>
@@ -15320,7 +15335,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -15375,13 +15390,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>37</v>
@@ -15390,7 +15405,7 @@
         <v>19</v>
       </c>
       <c r="G6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>36</v>
@@ -15399,13 +15414,13 @@
         <v>31</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>16</v>
@@ -15416,37 +15431,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F7">
         <v>90</v>
       </c>
       <c r="G7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H7">
         <v>117</v>
       </c>
       <c r="I7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K7">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7">
         <v>69</v>
@@ -15616,6 +15631,9 @@
       <c r="G4">
         <v>5</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="I4">
         <v>1</v>
       </c>
@@ -15693,7 +15711,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -15722,7 +15740,7 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7">
         <v>40</v>
@@ -15734,7 +15752,7 @@
         <v>24</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -15829,7 +15847,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>23</v>
@@ -15844,7 +15862,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15852,13 +15870,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>24</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>31</v>
@@ -15867,25 +15885,25 @@
         <v>24</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
         <v>21</v>
       </c>
       <c r="I3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>29</v>
       </c>
       <c r="K3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3">
         <v>22</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15964,7 +15982,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15978,7 +15996,7 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>57</v>
@@ -15987,7 +16005,7 @@
         <v>41</v>
       </c>
       <c r="G6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>21</v>
@@ -16002,7 +16020,7 @@
         <v>38</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6">
         <v>15</v>
@@ -16013,13 +16031,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>81</v>
       </c>
       <c r="D7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7">
         <v>130</v>
@@ -16028,25 +16046,25 @@
         <v>113</v>
       </c>
       <c r="G7">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J7">
         <v>84</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M7">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -16126,7 +16144,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -16147,7 +16165,7 @@
         <v>12</v>
       </c>
       <c r="K2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L2">
         <v>9</v>
@@ -16191,7 +16209,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -16213,6 +16231,9 @@
       <c r="H4">
         <v>5</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>3</v>
       </c>
@@ -16286,7 +16307,7 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>19</v>
@@ -16301,16 +16322,16 @@
         <v>54</v>
       </c>
       <c r="I7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7">
         <v>59</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -16501,7 +16522,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -16542,7 +16563,7 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -16643,7 +16664,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -16655,7 +16676,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -16666,16 +16687,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>11</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -16684,19 +16705,19 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>11</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3">
         <v>16</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M3">
         <v>15</v>
@@ -16725,7 +16746,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -16777,7 +16798,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -16792,7 +16813,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>20</v>
@@ -16810,7 +16831,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16818,40 +16839,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>44</v>
+      </c>
+      <c r="C7">
         <v>41</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
       </c>
       <c r="D7">
         <v>37</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>43</v>
       </c>
       <c r="G7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I7">
         <v>47</v>
       </c>
       <c r="J7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K7">
         <v>44</v>
       </c>
       <c r="L7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -16966,7 +16987,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -17007,16 +17028,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -17080,7 +17101,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17088,7 +17109,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -17097,10 +17118,10 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -17121,7 +17142,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -17266,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -17301,7 +17322,7 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -17405,10 +17426,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>38</v>
@@ -17423,16 +17444,16 @@
         <v>22</v>
       </c>
       <c r="H2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2">
         <v>23</v>
@@ -17449,7 +17470,7 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -17458,19 +17479,19 @@
         <v>38</v>
       </c>
       <c r="F3">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>34</v>
+      </c>
+      <c r="H3">
         <v>30</v>
-      </c>
-      <c r="G3">
-        <v>33</v>
-      </c>
-      <c r="H3">
-        <v>29</v>
       </c>
       <c r="I3">
         <v>30</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3">
         <v>31</v>
@@ -17505,10 +17526,10 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -17543,7 +17564,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -17558,7 +17579,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17569,10 +17590,10 @@
         <v>54</v>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>47</v>
@@ -17593,7 +17614,7 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>29</v>
@@ -17607,40 +17628,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>135</v>
       </c>
       <c r="F7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L7">
         <v>97</v>
       </c>
       <c r="M7">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -17993,7 +18014,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -18020,7 +18041,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <v>10</v>
@@ -18139,10 +18160,10 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6">
         <v>19</v>
@@ -18162,7 +18183,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -18180,16 +18201,16 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
         <v>44</v>
       </c>
       <c r="L7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -18296,7 +18317,7 @@
         <v>7</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -18319,7 +18340,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -18444,7 +18465,7 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -18462,7 +18483,7 @@
         <v>18</v>
       </c>
       <c r="L7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -18563,7 +18584,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -18639,7 +18660,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -18671,7 +18692,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -18688,7 +18709,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>11</v>
@@ -18729,7 +18750,7 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>18</v>
@@ -18741,13 +18762,13 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7">
         <v>27</v>
@@ -18842,7 +18863,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -18857,7 +18878,7 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -18886,10 +18907,10 @@
         <v>8</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>9</v>
@@ -18976,7 +18997,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>18</v>
@@ -18991,7 +19012,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>21</v>
@@ -19017,7 +19038,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>49</v>
@@ -19026,13 +19047,13 @@
         <v>47</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I7">
         <v>43</v>
@@ -19041,7 +19062,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>21</v>
@@ -19124,13 +19145,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -19177,13 +19198,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -19261,7 +19282,7 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>14</v>
@@ -19284,25 +19305,25 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>14</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>18</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J7">
         <v>27</v>
@@ -19976,7 +19997,7 @@
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -19991,9 +20012,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20028,10 +20050,13 @@
         <v>2024</v>
       </c>
       <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -20065,11 +20090,11 @@
       <c r="K2">
         <v>5</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -20103,11 +20128,11 @@
       <c r="K3">
         <v>3</v>
       </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -20127,7 +20152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -20152,6 +20177,9 @@
       <c r="H5">
         <v>4</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>4</v>
       </c>
@@ -20161,8 +20189,11 @@
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -20188,7 +20219,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>8</v>
@@ -20197,7 +20228,10 @@
         <v>16</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -20280,7 +20314,7 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>9</v>
@@ -20295,16 +20329,16 @@
         <v>29</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2">
         <v>10</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20315,7 +20349,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -20327,7 +20361,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>14</v>
@@ -20420,13 +20454,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>41</v>
@@ -20435,13 +20469,13 @@
         <v>24</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <v>16</v>
@@ -20461,40 +20495,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>51</v>
       </c>
       <c r="G7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H7">
         <v>47</v>
       </c>
       <c r="I7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L7">
         <v>46</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -20605,7 +20639,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -20643,7 +20677,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -20653,6 +20687,9 @@
       </c>
       <c r="L5">
         <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20666,7 +20703,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -20681,7 +20718,7 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -20693,7 +20730,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -20791,7 +20828,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -20811,10 +20848,10 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -20835,13 +20872,13 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>8</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20913,16 +20950,16 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -20934,7 +20971,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -20954,16 +20991,16 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -20975,16 +21012,16 @@
         <v>19</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <v>19</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -21073,7 +21110,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -21082,7 +21119,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <v>12</v>
@@ -21111,7 +21148,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -21123,10 +21160,10 @@
         <v>13</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -21152,7 +21189,7 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -21161,7 +21198,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -21222,7 +21259,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21242,28 +21279,28 @@
         <v>35</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>35</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7">
         <v>22</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -21375,7 +21412,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -21476,7 +21513,7 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -21601,10 +21638,10 @@
         <v>10</v>
       </c>
       <c r="I2">
+        <v>13</v>
+      </c>
+      <c r="J2">
         <v>12</v>
-      </c>
-      <c r="J2">
-        <v>11</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -21613,7 +21650,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21662,7 +21699,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -21671,7 +21708,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -21708,6 +21745,9 @@
       <c r="J5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -21720,10 +21760,10 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -21741,10 +21781,10 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -21755,16 +21795,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>39</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -21776,19 +21816,19 @@
         <v>33</v>
       </c>
       <c r="I7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -21862,7 +21902,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -21889,7 +21929,7 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -21921,7 +21961,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>5</v>
@@ -21930,7 +21970,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22031,7 +22071,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -22052,19 +22092,19 @@
         <v>24</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>21</v>
       </c>
       <c r="K7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>36</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -22254,10 +22294,10 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -22295,10 +22335,10 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -22430,7 +22470,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -22523,7 +22563,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -22633,7 +22673,7 @@
         <v>8</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -22645,7 +22685,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22668,7 +22708,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -22773,7 +22813,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>15</v>
@@ -22811,13 +22851,13 @@
         <v>38</v>
       </c>
       <c r="G7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <v>29</v>
@@ -22829,7 +22869,7 @@
         <v>42</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -23004,7 +23044,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -23033,7 +23073,7 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -23137,7 +23177,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -23155,13 +23195,13 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>7</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>6</v>
@@ -23202,13 +23242,13 @@
         <v>6</v>
       </c>
       <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3">
         <v>10</v>
-      </c>
-      <c r="K3">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
       </c>
       <c r="M3">
         <v>12</v>
@@ -23219,7 +23259,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -23249,7 +23289,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -23286,7 +23326,7 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -23313,7 +23353,7 @@
         <v>11</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23321,13 +23361,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>38</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -23339,22 +23379,22 @@
         <v>46</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>27</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -23487,7 +23527,7 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -23529,6 +23569,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -23550,7 +23593,7 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -23591,10 +23634,10 @@
         <v>7</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>15</v>
@@ -23609,7 +23652,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -23692,7 +23735,7 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -23710,7 +23753,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -23841,7 +23884,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>20</v>
@@ -23867,7 +23910,7 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>24</v>
@@ -23882,10 +23925,10 @@
         <v>35</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7">
         <v>37</v>
@@ -24044,7 +24087,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -24062,10 +24105,10 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -24097,10 +24140,10 @@
         <v>8</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -24126,7 +24169,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -24138,16 +24181,16 @@
         <v>23</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>16</v>
@@ -24382,7 +24425,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24417,7 +24460,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -24506,13 +24549,13 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -24524,10 +24567,10 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>11</v>
@@ -24547,7 +24590,7 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -24556,7 +24599,7 @@
         <v>13</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -24582,7 +24625,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -24629,7 +24672,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -24661,7 +24704,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -24676,7 +24719,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -24699,31 +24742,31 @@
         <v>59</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I7">
         <v>40</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>31</v>
@@ -24961,7 +25004,7 @@
         <v>16</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>17</v>
@@ -25002,7 +25045,7 @@
         <v>35</v>
       </c>
       <c r="H7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7">
         <v>35</v>
@@ -25414,7 +25457,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25536,7 +25579,7 @@
         <v>17</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -25634,7 +25677,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -25660,7 +25703,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -25738,7 +25781,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -25779,7 +25822,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>21</v>
@@ -25788,7 +25831,7 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>18</v>
@@ -25803,7 +25846,7 @@
         <v>13</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
         <v>29</v>
@@ -25892,7 +25935,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -25957,7 +26000,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25967,6 +26010,9 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
         <v>3</v>
       </c>
@@ -25992,7 +26038,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -26035,10 +26081,10 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -26055,10 +26101,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>23</v>
@@ -26076,16 +26122,16 @@
         <v>33</v>
       </c>
       <c r="J7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -26174,7 +26220,7 @@
         <v>34</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2">
         <v>46</v>
@@ -26183,10 +26229,10 @@
         <v>41</v>
       </c>
       <c r="J2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L2">
         <v>37</v>
@@ -26200,7 +26246,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>32</v>
@@ -26209,31 +26255,31 @@
         <v>51</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>52</v>
       </c>
       <c r="G3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L3">
         <v>66</v>
       </c>
       <c r="M3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26247,10 +26293,10 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>13</v>
@@ -26259,7 +26305,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -26323,10 +26369,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>57</v>
@@ -26341,19 +26387,19 @@
         <v>52</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6">
         <v>53</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -26364,40 +26410,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>154</v>
       </c>
       <c r="G7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -26558,6 +26604,9 @@
       <c r="D4">
         <v>2</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
@@ -26593,7 +26642,7 @@
         <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -26628,7 +26677,7 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -26726,7 +26775,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -26738,6 +26787,9 @@
         <v>2</v>
       </c>
       <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
@@ -26757,6 +26809,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>4</v>
       </c>
@@ -26830,7 +26885,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -26859,7 +26914,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -26871,13 +26926,13 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>7</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -27025,7 +27080,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -27077,7 +27132,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -27118,7 +27173,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>14</v>
@@ -27139,7 +27194,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>14</v>
@@ -27247,7 +27302,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -27331,7 +27386,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -27450,7 +27505,7 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -27459,7 +27514,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -27532,7 +27587,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -27584,7 +27639,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -27625,10 +27680,10 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>25</v>
@@ -27637,10 +27692,10 @@
         <v>33</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>25</v>
@@ -27765,6 +27820,9 @@
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -27838,7 +27896,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -27927,7 +27985,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28034,7 +28092,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -28592,7 +28650,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -28734,7 +28792,7 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -28823,7 +28881,7 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>16</v>
@@ -28838,10 +28896,10 @@
         <v>14</v>
       </c>
       <c r="J2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2">
         <v>18</v>
@@ -28858,16 +28916,16 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -28882,7 +28940,7 @@
         <v>29</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>16</v>
@@ -28902,13 +28960,13 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -28981,7 +29039,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>49</v>
@@ -29005,7 +29063,7 @@
         <v>32</v>
       </c>
       <c r="K6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -29022,16 +29080,16 @@
         <v>47</v>
       </c>
       <c r="C7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>65</v>
@@ -29043,10 +29101,10 @@
         <v>70</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L7">
         <v>53</v>
@@ -29201,6 +29259,9 @@
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
@@ -29240,7 +29301,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29272,7 +29333,7 @@
         <v>15</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>15</v>
@@ -29281,7 +29342,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -29407,6 +29468,9 @@
       <c r="G3">
         <v>2</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -29521,7 +29585,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -29645,7 +29709,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -29658,6 +29722,9 @@
       </c>
       <c r="K3">
         <v>3</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29743,7 +29810,7 @@
         <v>12</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -29767,7 +29834,7 @@
         <v>11</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -30069,7 +30136,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -30158,7 +30225,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -30190,13 +30257,13 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>11</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -30301,6 +30368,9 @@
       <c r="G3">
         <v>2</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="J3">
         <v>2</v>
       </c>
@@ -30383,7 +30453,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -30483,6 +30553,9 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -30529,7 +30602,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>4</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>914</v>
       </c>
       <c r="M2">
-        <v>871</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>945</v>
       </c>
       <c r="M3">
-        <v>951</v>
+        <v>960</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -980,10 +980,10 @@
         <v>301</v>
       </c>
       <c r="L4">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M4">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>65</v>
       </c>
       <c r="M5">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>970</v>
       </c>
       <c r="M6">
-        <v>702</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1103,10 +1103,10 @@
         <v>4112</v>
       </c>
       <c r="L7">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="M7">
-        <v>2849</v>
+        <v>2887</v>
       </c>
     </row>
   </sheetData>
@@ -1661,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1757,7 +1757,7 @@
         <v>55</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -1949,7 +1949,7 @@
         <v>15</v>
       </c>
       <c r="M4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1990,7 +1990,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2031,7 +2031,7 @@
         <v>61</v>
       </c>
       <c r="M6">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2072,7 +2072,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2337,7 +2337,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2378,7 +2378,7 @@
         <v>66</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2526,7 +2526,7 @@
         <v>53</v>
       </c>
       <c r="M3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2567,7 +2567,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2690,7 +2690,7 @@
         <v>141</v>
       </c>
       <c r="M7">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3103,7 +3103,7 @@
         <v>33</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3261,7 +3261,7 @@
         <v>34</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3302,7 +3302,7 @@
         <v>105</v>
       </c>
       <c r="M7">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3450,7 +3450,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3608,7 +3608,7 @@
         <v>66</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4434,7 +4434,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4516,7 +4516,7 @@
         <v>190</v>
       </c>
       <c r="M8">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4598,7 +4598,7 @@
         <v>19</v>
       </c>
       <c r="M10">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4639,7 +4639,7 @@
         <v>51</v>
       </c>
       <c r="M11">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4999,7 +4999,7 @@
         <v>81</v>
       </c>
       <c r="M20">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5040,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5081,7 +5081,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5163,7 +5163,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5204,7 +5204,7 @@
         <v>14</v>
       </c>
       <c r="M25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5356,7 +5356,7 @@
         <v>155</v>
       </c>
       <c r="M29">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5438,7 +5438,7 @@
         <v>33</v>
       </c>
       <c r="M31">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5520,7 +5520,7 @@
         <v>141</v>
       </c>
       <c r="M33">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5643,7 +5643,7 @@
         <v>55</v>
       </c>
       <c r="M36">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5684,7 +5684,7 @@
         <v>105</v>
       </c>
       <c r="M37">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5833,7 +5833,7 @@
         <v>13</v>
       </c>
       <c r="M41">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5915,7 +5915,7 @@
         <v>24</v>
       </c>
       <c r="M43">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="M45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -6243,7 +6243,7 @@
         <v>43</v>
       </c>
       <c r="M51">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6284,7 +6284,7 @@
         <v>54</v>
       </c>
       <c r="M52">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6322,7 +6322,7 @@
         <v>55</v>
       </c>
       <c r="L53">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M53">
         <v>24</v>
@@ -6407,7 +6407,7 @@
         <v>36</v>
       </c>
       <c r="M55">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6714,7 +6714,7 @@
         <v>13</v>
       </c>
       <c r="M63">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6796,7 +6796,7 @@
         <v>66</v>
       </c>
       <c r="M65">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6878,7 +6878,7 @@
         <v>117</v>
       </c>
       <c r="M67">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7121,7 +7121,7 @@
         <v>23</v>
       </c>
       <c r="M73">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7326,7 +7326,7 @@
         <v>48</v>
       </c>
       <c r="M78">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7367,7 +7367,7 @@
         <v>97</v>
       </c>
       <c r="M79">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7408,7 +7408,7 @@
         <v>12</v>
       </c>
       <c r="M80">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7525,7 +7525,7 @@
         <v>66</v>
       </c>
       <c r="M83">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7607,7 +7607,7 @@
         <v>153</v>
       </c>
       <c r="M85">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7648,7 +7648,7 @@
         <v>23</v>
       </c>
       <c r="M86">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7730,7 +7730,7 @@
         <v>42</v>
       </c>
       <c r="M88">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7853,7 +7853,7 @@
         <v>41</v>
       </c>
       <c r="M91">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7976,7 +7976,7 @@
         <v>40</v>
       </c>
       <c r="M94">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8260,10 +8260,10 @@
         <v>4112</v>
       </c>
       <c r="L101">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="M101">
-        <v>2849</v>
+        <v>2887</v>
       </c>
     </row>
   </sheetData>
@@ -8513,7 +8513,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8665,7 +8665,7 @@
         <v>33</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -8813,7 +8813,7 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8974,7 +8974,7 @@
         <v>117</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -9927,7 +9927,7 @@
         <v>51</v>
       </c>
       <c r="M2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10091,7 +10091,7 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10132,7 +10132,7 @@
         <v>155</v>
       </c>
       <c r="M7">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -11828,7 +11828,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11869,7 +11869,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -11976,7 +11976,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12148,7 +12148,7 @@
         <v>13</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -12900,7 +12900,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12941,7 +12941,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -13048,7 +13048,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13130,7 +13130,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13194,7 +13194,7 @@
         <v>17</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13235,7 +13235,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -13383,7 +13383,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13529,7 +13529,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -13636,7 +13636,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13796,7 +13796,7 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -14793,7 +14793,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14936,7 +14936,7 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -15089,7 +15089,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15179,7 +15179,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -15409,7 +15409,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15491,7 +15491,7 @@
         <v>97</v>
       </c>
       <c r="M7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -16053,7 +16053,7 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16094,7 +16094,7 @@
         <v>81</v>
       </c>
       <c r="M7">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -16861,7 +16861,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16902,7 +16902,7 @@
         <v>55</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -18124,7 +18124,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18258,7 +18258,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -18406,7 +18406,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18495,6 +18495,9 @@
       <c r="L6">
         <v>1</v>
       </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
@@ -18534,7 +18537,7 @@
         <v>14</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -20389,7 +20392,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20579,7 +20582,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -21179,7 +21182,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21351,7 +21354,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -22027,7 +22030,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22120,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22786,7 +22789,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22929,7 +22932,7 @@
         <v>42</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -23860,7 +23863,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23953,7 +23956,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24180,7 +24183,7 @@
         <v>16</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24262,7 +24265,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -25082,7 +25085,7 @@
         <v>13</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25123,7 +25126,7 @@
         <v>43</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -26031,7 +26034,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26203,7 +26206,7 @@
         <v>24</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -26310,7 +26313,7 @@
         <v>39</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26515,7 +26518,7 @@
         <v>153</v>
       </c>
       <c r="M7">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -26622,7 +26625,7 @@
         <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26779,7 +26782,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -27891,7 +27894,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27983,7 +27986,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -28403,7 +28406,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -28444,7 +28447,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -29162,7 +29165,7 @@
         <v>13</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -29203,7 +29206,7 @@
         <v>54</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="C2">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="D2">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="E2">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="F2">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="G2">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="H2">
+        <v>952</v>
+      </c>
+      <c r="I2">
         <v>933</v>
       </c>
-      <c r="I2">
-        <v>924</v>
-      </c>
       <c r="J2">
-        <v>1039</v>
+        <v>1059</v>
       </c>
       <c r="K2">
-        <v>1185</v>
+        <v>1217</v>
       </c>
       <c r="L2">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="M2">
-        <v>882</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="C3">
-        <v>1045</v>
+        <v>1060</v>
       </c>
       <c r="D3">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="E3">
-        <v>983</v>
+        <v>1003</v>
       </c>
       <c r="F3">
-        <v>986</v>
+        <v>1001</v>
       </c>
       <c r="G3">
-        <v>1084</v>
+        <v>1099</v>
       </c>
       <c r="H3">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="I3">
-        <v>974</v>
+        <v>993</v>
       </c>
       <c r="J3">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="K3">
-        <v>1105</v>
+        <v>1135</v>
       </c>
       <c r="L3">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="M3">
-        <v>960</v>
+        <v>980</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C4">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D4">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E4">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F4">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="G4">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H4">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I4">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J4">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K4">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="L4">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M4">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -991,22 +991,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>106</v>
       </c>
       <c r="D5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H5">
         <v>95</v>
@@ -1018,7 +1018,7 @@
         <v>86</v>
       </c>
       <c r="K5">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L5">
         <v>65</v>
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1297</v>
+        <v>1315</v>
       </c>
       <c r="C6">
-        <v>1786</v>
+        <v>1808</v>
       </c>
       <c r="D6">
-        <v>1903</v>
+        <v>1927</v>
       </c>
       <c r="E6">
-        <v>1587</v>
+        <v>1607</v>
       </c>
       <c r="F6">
-        <v>1195</v>
+        <v>1210</v>
       </c>
       <c r="G6">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="H6">
-        <v>1240</v>
+        <v>1259</v>
       </c>
       <c r="I6">
-        <v>1338</v>
+        <v>1355</v>
       </c>
       <c r="J6">
-        <v>1511</v>
+        <v>1527</v>
       </c>
       <c r="K6">
-        <v>1452</v>
+        <v>1470</v>
       </c>
       <c r="L6">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="M6">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3061</v>
+        <v>3103</v>
       </c>
       <c r="C7">
-        <v>3995</v>
+        <v>4050</v>
       </c>
       <c r="D7">
-        <v>4259</v>
+        <v>4311</v>
       </c>
       <c r="E7">
-        <v>3841</v>
+        <v>3899</v>
       </c>
       <c r="F7">
-        <v>3418</v>
+        <v>3477</v>
       </c>
       <c r="G7">
-        <v>3773</v>
+        <v>3824</v>
       </c>
       <c r="H7">
-        <v>3479</v>
+        <v>3537</v>
       </c>
       <c r="I7">
-        <v>3636</v>
+        <v>3682</v>
       </c>
       <c r="J7">
-        <v>4072</v>
+        <v>4133</v>
       </c>
       <c r="K7">
-        <v>4112</v>
+        <v>4200</v>
       </c>
       <c r="L7">
-        <v>3164</v>
+        <v>3205</v>
       </c>
       <c r="M7">
-        <v>2887</v>
+        <v>2939</v>
       </c>
     </row>
   </sheetData>
@@ -1579,10 +1579,10 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>10</v>
@@ -1614,13 +1614,13 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>11</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>22</v>
@@ -1748,16 +1748,16 @@
         <v>34</v>
       </c>
       <c r="I7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>37</v>
       </c>
       <c r="K7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -1837,34 +1837,34 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2">
         <v>53</v>
       </c>
       <c r="F2">
+        <v>64</v>
+      </c>
+      <c r="G2">
+        <v>69</v>
+      </c>
+      <c r="H2">
+        <v>69</v>
+      </c>
+      <c r="I2">
         <v>63</v>
       </c>
-      <c r="G2">
-        <v>67</v>
-      </c>
-      <c r="H2">
-        <v>68</v>
-      </c>
-      <c r="I2">
-        <v>62</v>
-      </c>
       <c r="J2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M2">
         <v>61</v>
@@ -1875,16 +1875,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3">
         <v>69</v>
@@ -1893,22 +1893,22 @@
         <v>85</v>
       </c>
       <c r="H3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J3">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1931,7 +1931,7 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -1998,40 +1998,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D6">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6">
         <v>132</v>
       </c>
       <c r="H6">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6">
         <v>69</v>
       </c>
       <c r="K6">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L6">
         <v>61</v>
       </c>
       <c r="M6">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2039,40 +2039,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J7">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M7">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2161,10 +2161,10 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>26</v>
@@ -2190,16 +2190,16 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>19</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -2220,7 +2220,7 @@
         <v>29</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2325,7 +2325,7 @@
         <v>16</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>31</v>
@@ -2348,25 +2348,25 @@
         <v>65</v>
       </c>
       <c r="C7">
+        <v>85</v>
+      </c>
+      <c r="D7">
         <v>84</v>
-      </c>
-      <c r="D7">
-        <v>83</v>
       </c>
       <c r="E7">
         <v>61</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J7">
         <v>92</v>
@@ -2378,7 +2378,7 @@
         <v>66</v>
       </c>
       <c r="M7">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2464,28 +2464,28 @@
         <v>43</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L2">
         <v>30</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2493,7 +2493,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>67</v>
@@ -2502,7 +2502,7 @@
         <v>51</v>
       </c>
       <c r="E3">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F3">
         <v>63</v>
@@ -2511,16 +2511,16 @@
         <v>65</v>
       </c>
       <c r="H3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L3">
         <v>53</v>
@@ -2534,7 +2534,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -2561,13 +2561,13 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2616,16 +2616,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E6">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6">
         <v>68</v>
@@ -2634,13 +2634,13 @@
         <v>96</v>
       </c>
       <c r="H6">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6">
         <v>47</v>
@@ -2649,7 +2649,7 @@
         <v>51</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2657,40 +2657,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F7">
+        <v>174</v>
+      </c>
+      <c r="G7">
+        <v>219</v>
+      </c>
+      <c r="H7">
         <v>173</v>
       </c>
-      <c r="G7">
-        <v>218</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
+        <v>164</v>
+      </c>
+      <c r="J7">
+        <v>165</v>
+      </c>
+      <c r="K7">
         <v>166</v>
       </c>
-      <c r="I7">
-        <v>159</v>
-      </c>
-      <c r="J7">
-        <v>162</v>
-      </c>
-      <c r="K7">
-        <v>161</v>
-      </c>
       <c r="L7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M7">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
         <v>18</v>
@@ -2791,10 +2791,10 @@
         <v>27</v>
       </c>
       <c r="K2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2">
         <v>18</v>
@@ -2823,7 +2823,7 @@
         <v>22</v>
       </c>
       <c r="H3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3">
         <v>17</v>
@@ -2832,10 +2832,10 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3">
         <v>13</v>
@@ -2975,13 +2975,13 @@
         <v>66</v>
       </c>
       <c r="F7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>69</v>
       </c>
       <c r="H7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7">
         <v>58</v>
@@ -2990,10 +2990,10 @@
         <v>71</v>
       </c>
       <c r="K7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M7">
         <v>45</v>
@@ -3079,19 +3079,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>33</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <v>35</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2">
         <v>39</v>
@@ -3100,10 +3100,10 @@
         <v>31</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3138,13 +3138,13 @@
         <v>43</v>
       </c>
       <c r="K3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3">
         <v>27</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3199,7 +3199,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -3217,7 +3217,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -3231,7 +3231,7 @@
         <v>49</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>65</v>
@@ -3246,10 +3246,10 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6">
         <v>49</v>
@@ -3261,7 +3261,7 @@
         <v>34</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3272,37 +3272,37 @@
         <v>107</v>
       </c>
       <c r="C7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D7">
         <v>148</v>
       </c>
       <c r="E7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F7">
         <v>113</v>
       </c>
       <c r="G7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J7">
         <v>139</v>
       </c>
       <c r="K7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M7">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -3379,13 +3379,13 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>19</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -3409,7 +3409,7 @@
         <v>21</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3426,13 +3426,13 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3">
         <v>20</v>
@@ -3441,10 +3441,10 @@
         <v>25</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3">
         <v>19</v>
@@ -3537,7 +3537,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>33</v>
@@ -3552,13 +3552,13 @@
         <v>19</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>38</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6">
         <v>52</v>
@@ -3578,37 +3578,37 @@
         <v>56</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7">
         <v>89</v>
       </c>
       <c r="E7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7">
         <v>88</v>
       </c>
       <c r="J7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L7">
         <v>66</v>
       </c>
       <c r="M7">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -3726,7 +3726,7 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>28</v>
@@ -3738,7 +3738,7 @@
         <v>25</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3">
         <v>22</v>
@@ -3750,13 +3750,13 @@
         <v>19</v>
       </c>
       <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>25</v>
-      </c>
-      <c r="L3">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3852,13 +3852,13 @@
         <v>20</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>24</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>16</v>
@@ -3881,7 +3881,7 @@
         <v>68</v>
       </c>
       <c r="C7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>86</v>
@@ -3893,25 +3893,25 @@
         <v>65</v>
       </c>
       <c r="G7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H7">
         <v>72</v>
       </c>
       <c r="I7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J7">
         <v>51</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4056,7 +4056,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4163,7 +4163,7 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4237,7 +4237,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2">
         <v>39</v>
@@ -4249,10 +4249,10 @@
         <v>43</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H2">
         <v>34</v>
@@ -4290,7 +4290,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -4337,16 +4337,16 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>16</v>
       </c>
       <c r="J4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4">
         <v>12</v>
@@ -4369,7 +4369,7 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -4416,7 +4416,7 @@
         <v>21</v>
       </c>
       <c r="G6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>19</v>
@@ -4442,40 +4442,40 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G7">
         <v>101</v>
       </c>
       <c r="H7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4483,40 +4483,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C8">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D8">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F8">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G8">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J8">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K8">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L8">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M8">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4524,7 +4524,7 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>32</v>
@@ -4533,7 +4533,7 @@
         <v>25</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9">
         <v>21</v>
@@ -4542,7 +4542,7 @@
         <v>16</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I9">
         <v>21</v>
@@ -4557,7 +4557,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4565,22 +4565,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>45</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>29</v>
@@ -4595,7 +4595,7 @@
         <v>25</v>
       </c>
       <c r="L10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M10">
         <v>13</v>
@@ -4609,16 +4609,16 @@
         <v>60</v>
       </c>
       <c r="C11">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11">
+        <v>80</v>
+      </c>
+      <c r="E11">
         <v>79</v>
       </c>
-      <c r="E11">
-        <v>78</v>
-      </c>
       <c r="F11">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>65</v>
@@ -4630,7 +4630,7 @@
         <v>66</v>
       </c>
       <c r="J11">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K11">
         <v>92</v>
@@ -4647,7 +4647,7 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>14</v>
@@ -4694,7 +4694,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -4732,10 +4732,10 @@
         <v>23</v>
       </c>
       <c r="E14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>22</v>
@@ -4744,13 +4744,13 @@
         <v>16</v>
       </c>
       <c r="I14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -4767,37 +4767,37 @@
         <v>34</v>
       </c>
       <c r="C15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>48</v>
       </c>
       <c r="F15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15">
         <v>25</v>
       </c>
       <c r="H15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15">
         <v>44</v>
       </c>
       <c r="J15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L15">
         <v>21</v>
       </c>
       <c r="M15">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4820,13 +4820,13 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16">
         <v>13</v>
       </c>
       <c r="J16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>8</v>
@@ -4896,13 +4896,13 @@
         <v>19</v>
       </c>
       <c r="F18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I18">
         <v>30</v>
@@ -4911,7 +4911,7 @@
         <v>60</v>
       </c>
       <c r="K18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L18">
         <v>24</v>
@@ -4925,10 +4925,10 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19">
         <v>101</v>
@@ -4937,28 +4937,28 @@
         <v>83</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G19">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H19">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19">
         <v>97</v>
       </c>
       <c r="J19">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K19">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4966,40 +4966,40 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D20">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E20">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F20">
         <v>115</v>
       </c>
       <c r="G20">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H20">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J20">
         <v>86</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L20">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M20">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5028,7 +5028,7 @@
         <v>12</v>
       </c>
       <c r="I21">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -5060,7 +5060,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>11</v>
@@ -5081,7 +5081,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5092,13 +5092,13 @@
         <v>27</v>
       </c>
       <c r="C23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E23">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F23">
         <v>31</v>
@@ -5148,16 +5148,16 @@
         <v>15</v>
       </c>
       <c r="H24">
+        <v>18</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
         <v>17</v>
       </c>
-      <c r="I24">
-        <v>5</v>
-      </c>
-      <c r="J24">
-        <v>15</v>
-      </c>
       <c r="K24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -5186,7 +5186,7 @@
         <v>12</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25">
         <v>13</v>
@@ -5195,10 +5195,10 @@
         <v>21</v>
       </c>
       <c r="J25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25">
         <v>14</v>
@@ -5256,7 +5256,7 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D27">
         <v>23</v>
@@ -5274,19 +5274,19 @@
         <v>27</v>
       </c>
       <c r="I27">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J27">
         <v>19</v>
       </c>
       <c r="K27">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L27">
         <v>37</v>
       </c>
       <c r="M27">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5323,40 +5323,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C29">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D29">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E29">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F29">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G29">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H29">
+        <v>206</v>
+      </c>
+      <c r="I29">
+        <v>236</v>
+      </c>
+      <c r="J29">
+        <v>225</v>
+      </c>
+      <c r="K29">
         <v>202</v>
       </c>
-      <c r="I29">
-        <v>234</v>
-      </c>
-      <c r="J29">
-        <v>215</v>
-      </c>
-      <c r="K29">
-        <v>198</v>
-      </c>
       <c r="L29">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M29">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5397,7 +5397,7 @@
         <v>16</v>
       </c>
       <c r="M30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5408,10 +5408,10 @@
         <v>26</v>
       </c>
       <c r="C31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E31">
         <v>23</v>
@@ -5423,22 +5423,22 @@
         <v>33</v>
       </c>
       <c r="H31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I31">
         <v>39</v>
       </c>
       <c r="J31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K31">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L31">
         <v>33</v>
       </c>
       <c r="M31">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5461,7 +5461,7 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -5487,40 +5487,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C33">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D33">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E33">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F33">
+        <v>174</v>
+      </c>
+      <c r="G33">
+        <v>219</v>
+      </c>
+      <c r="H33">
         <v>173</v>
       </c>
-      <c r="G33">
-        <v>218</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
+        <v>164</v>
+      </c>
+      <c r="J33">
+        <v>165</v>
+      </c>
+      <c r="K33">
         <v>166</v>
       </c>
-      <c r="I33">
-        <v>159</v>
-      </c>
-      <c r="J33">
-        <v>162</v>
-      </c>
-      <c r="K33">
-        <v>161</v>
-      </c>
       <c r="L33">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M33">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5549,10 +5549,10 @@
         <v>16</v>
       </c>
       <c r="I34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K34">
         <v>25</v>
@@ -5561,7 +5561,7 @@
         <v>19</v>
       </c>
       <c r="M34">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -5578,7 +5578,7 @@
         <v>7</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -5613,19 +5613,19 @@
         <v>45</v>
       </c>
       <c r="C36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36">
+        <v>42</v>
+      </c>
+      <c r="E36">
+        <v>53</v>
+      </c>
+      <c r="F36">
+        <v>44</v>
+      </c>
+      <c r="G36">
         <v>40</v>
-      </c>
-      <c r="E36">
-        <v>52</v>
-      </c>
-      <c r="F36">
-        <v>43</v>
-      </c>
-      <c r="G36">
-        <v>39</v>
       </c>
       <c r="H36">
         <v>69</v>
@@ -5634,16 +5634,16 @@
         <v>49</v>
       </c>
       <c r="J36">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K36">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L36">
         <v>55</v>
       </c>
       <c r="M36">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5654,37 +5654,37 @@
         <v>107</v>
       </c>
       <c r="C37">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D37">
         <v>148</v>
       </c>
       <c r="E37">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F37">
         <v>113</v>
       </c>
       <c r="G37">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H37">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I37">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J37">
         <v>139</v>
       </c>
       <c r="K37">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L37">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M37">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -5730,7 +5730,7 @@
         <v>2</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -5809,10 +5809,10 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41">
         <v>19</v>
@@ -5833,7 +5833,7 @@
         <v>13</v>
       </c>
       <c r="M41">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5841,40 +5841,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C42">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D42">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E42">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F42">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G42">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H42">
         <v>133</v>
       </c>
       <c r="I42">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J42">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K42">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L42">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M42">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5900,7 +5900,7 @@
         <v>30</v>
       </c>
       <c r="H43">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I43">
         <v>34</v>
@@ -5909,13 +5909,13 @@
         <v>46</v>
       </c>
       <c r="K43">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L43">
+        <v>25</v>
+      </c>
+      <c r="M43">
         <v>24</v>
-      </c>
-      <c r="M43">
-        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5926,13 +5926,13 @@
         <v>34</v>
       </c>
       <c r="C44">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D44">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E44">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F44">
         <v>21</v>
@@ -5944,10 +5944,10 @@
         <v>37</v>
       </c>
       <c r="I44">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J44">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K44">
         <v>41</v>
@@ -5985,7 +5985,7 @@
         <v>3</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45">
         <v>6</v>
@@ -6014,7 +6014,7 @@
         <v>13</v>
       </c>
       <c r="E46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -6023,22 +6023,22 @@
         <v>13</v>
       </c>
       <c r="H46">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J46">
         <v>13</v>
       </c>
       <c r="K46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L46">
         <v>9</v>
       </c>
       <c r="M46">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -6046,7 +6046,7 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47">
         <v>23</v>
@@ -6061,7 +6061,7 @@
         <v>25</v>
       </c>
       <c r="G47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47">
         <v>32</v>
@@ -6070,7 +6070,7 @@
         <v>28</v>
       </c>
       <c r="J47">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K47">
         <v>30</v>
@@ -6087,7 +6087,7 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C48">
         <v>52</v>
@@ -6105,22 +6105,22 @@
         <v>35</v>
       </c>
       <c r="H48">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I48">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J48">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K48">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L48">
         <v>50</v>
       </c>
       <c r="M48">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6175,7 +6175,7 @@
         <v>25</v>
       </c>
       <c r="D50">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E50">
         <v>21</v>
@@ -6184,7 +6184,7 @@
         <v>21</v>
       </c>
       <c r="G50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50">
         <v>15</v>
@@ -6228,7 +6228,7 @@
         <v>37</v>
       </c>
       <c r="H51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I51">
         <v>35</v>
@@ -6240,7 +6240,7 @@
         <v>54</v>
       </c>
       <c r="L51">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M51">
         <v>34</v>
@@ -6257,19 +6257,19 @@
         <v>111</v>
       </c>
       <c r="D52">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F52">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G52">
         <v>69</v>
       </c>
       <c r="H52">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I52">
         <v>71</v>
@@ -6278,13 +6278,13 @@
         <v>92</v>
       </c>
       <c r="K52">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L52">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M52">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6313,16 +6313,16 @@
         <v>34</v>
       </c>
       <c r="I53">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J53">
         <v>37</v>
       </c>
       <c r="K53">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L53">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M53">
         <v>24</v>
@@ -6333,34 +6333,34 @@
         <v>60</v>
       </c>
       <c r="B54">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C54">
         <v>54</v>
       </c>
       <c r="D54">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E54">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F54">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G54">
         <v>65</v>
       </c>
       <c r="H54">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I54">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J54">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K54">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L54">
         <v>66</v>
@@ -6374,25 +6374,25 @@
         <v>61</v>
       </c>
       <c r="B55">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55">
         <v>32</v>
       </c>
       <c r="D55">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F55">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G55">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H55">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I55">
         <v>40</v>
@@ -6401,10 +6401,10 @@
         <v>49</v>
       </c>
       <c r="K55">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L55">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M55">
         <v>40</v>
@@ -6483,7 +6483,7 @@
         <v>15</v>
       </c>
       <c r="K57">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L57">
         <v>17</v>
@@ -6532,10 +6532,10 @@
         <v>65</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -6547,7 +6547,7 @@
         <v>10</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -6565,7 +6565,7 @@
         <v>3</v>
       </c>
       <c r="M59">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -6579,16 +6579,16 @@
         <v>21</v>
       </c>
       <c r="D60">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E60">
         <v>24</v>
       </c>
       <c r="F60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G60">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H60">
         <v>25</v>
@@ -6597,7 +6597,7 @@
         <v>13</v>
       </c>
       <c r="J60">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K60">
         <v>32</v>
@@ -6606,7 +6606,7 @@
         <v>19</v>
       </c>
       <c r="M60">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6684,22 +6684,22 @@
         <v>141</v>
       </c>
       <c r="C63">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D63">
         <v>98</v>
       </c>
       <c r="E63">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G63">
         <v>59</v>
       </c>
       <c r="H63">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I63">
         <v>44</v>
@@ -6714,7 +6714,7 @@
         <v>13</v>
       </c>
       <c r="M63">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6731,7 +6731,7 @@
         <v>13</v>
       </c>
       <c r="E64">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F64">
         <v>17</v>
@@ -6749,7 +6749,7 @@
         <v>23</v>
       </c>
       <c r="K64">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L64">
         <v>28</v>
@@ -6766,37 +6766,37 @@
         <v>56</v>
       </c>
       <c r="C65">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D65">
         <v>89</v>
       </c>
       <c r="E65">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F65">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G65">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H65">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I65">
         <v>88</v>
       </c>
       <c r="J65">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K65">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L65">
         <v>66</v>
       </c>
       <c r="M65">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6834,10 +6834,10 @@
         <v>17</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6848,37 +6848,37 @@
         <v>117</v>
       </c>
       <c r="C67">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D67">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E67">
         <v>155</v>
       </c>
       <c r="F67">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G67">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H67">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I67">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J67">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K67">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L67">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M67">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6913,7 +6913,7 @@
         <v>12</v>
       </c>
       <c r="K68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L68">
         <v>8</v>
@@ -6998,7 +6998,7 @@
         <v>12</v>
       </c>
       <c r="M70">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -7033,13 +7033,13 @@
         <v>17</v>
       </c>
       <c r="K71">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L71">
         <v>9</v>
       </c>
       <c r="M71">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7056,13 +7056,13 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F72">
         <v>19</v>
       </c>
       <c r="G72">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H72">
         <v>9</v>
@@ -7074,13 +7074,13 @@
         <v>17</v>
       </c>
       <c r="K72">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L72">
         <v>13</v>
       </c>
       <c r="M72">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -7088,22 +7088,22 @@
         <v>79</v>
       </c>
       <c r="B73">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C73">
         <v>28</v>
       </c>
       <c r="D73">
+        <v>38</v>
+      </c>
+      <c r="E73">
         <v>37</v>
-      </c>
-      <c r="E73">
-        <v>36</v>
       </c>
       <c r="F73">
         <v>37</v>
       </c>
       <c r="G73">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H73">
         <v>36</v>
@@ -7214,31 +7214,31 @@
         <v>19</v>
       </c>
       <c r="C76">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D76">
         <v>38</v>
       </c>
       <c r="E76">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F76">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G76">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H76">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I76">
+        <v>58</v>
+      </c>
+      <c r="J76">
+        <v>64</v>
+      </c>
+      <c r="K76">
         <v>57</v>
-      </c>
-      <c r="J76">
-        <v>63</v>
-      </c>
-      <c r="K76">
-        <v>56</v>
       </c>
       <c r="L76">
         <v>42</v>
@@ -7261,7 +7261,7 @@
         <v>20</v>
       </c>
       <c r="E77">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F77">
         <v>18</v>
@@ -7270,16 +7270,16 @@
         <v>23</v>
       </c>
       <c r="H77">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I77">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J77">
         <v>33</v>
       </c>
       <c r="K77">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L77">
         <v>20</v>
@@ -7296,7 +7296,7 @@
         <v>35</v>
       </c>
       <c r="C78">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D78">
         <v>46</v>
@@ -7305,10 +7305,10 @@
         <v>52</v>
       </c>
       <c r="F78">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G78">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H78">
         <v>56</v>
@@ -7317,13 +7317,13 @@
         <v>53</v>
       </c>
       <c r="J78">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K78">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L78">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M78">
         <v>48</v>
@@ -7334,31 +7334,31 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C79">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D79">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E79">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F79">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G79">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H79">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I79">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J79">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K79">
         <v>116</v>
@@ -7367,7 +7367,7 @@
         <v>97</v>
       </c>
       <c r="M79">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7384,7 +7384,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F80">
         <v>16</v>
@@ -7495,25 +7495,25 @@
         <v>65</v>
       </c>
       <c r="C83">
+        <v>85</v>
+      </c>
+      <c r="D83">
         <v>84</v>
-      </c>
-      <c r="D83">
-        <v>83</v>
       </c>
       <c r="E83">
         <v>61</v>
       </c>
       <c r="F83">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G83">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H83">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I83">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J83">
         <v>92</v>
@@ -7525,7 +7525,7 @@
         <v>66</v>
       </c>
       <c r="M83">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7539,10 +7539,10 @@
         <v>30</v>
       </c>
       <c r="D84">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E84">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F84">
         <v>30</v>
@@ -7551,7 +7551,7 @@
         <v>32</v>
       </c>
       <c r="H84">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I84">
         <v>30</v>
@@ -7560,7 +7560,7 @@
         <v>40</v>
       </c>
       <c r="K84">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L84">
         <v>27</v>
@@ -7574,40 +7574,40 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C85">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D85">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E85">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F85">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G85">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H85">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I85">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J85">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K85">
         <v>207</v>
       </c>
       <c r="L85">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M85">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7636,7 +7636,7 @@
         <v>20</v>
       </c>
       <c r="I86">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J86">
         <v>17</v>
@@ -7645,7 +7645,7 @@
         <v>28</v>
       </c>
       <c r="L86">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M86">
         <v>20</v>
@@ -7712,25 +7712,25 @@
         <v>42</v>
       </c>
       <c r="G88">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H88">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I88">
         <v>32</v>
       </c>
       <c r="J88">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K88">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L88">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M88">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7744,7 +7744,7 @@
         <v>39</v>
       </c>
       <c r="D89">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E89">
         <v>29</v>
@@ -7753,7 +7753,7 @@
         <v>43</v>
       </c>
       <c r="G89">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H89">
         <v>33</v>
@@ -7765,13 +7765,13 @@
         <v>49</v>
       </c>
       <c r="K89">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L89">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M89">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7785,19 +7785,19 @@
         <v>60</v>
       </c>
       <c r="D90">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E90">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F90">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G90">
         <v>32</v>
       </c>
       <c r="H90">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I90">
         <v>40</v>
@@ -7809,10 +7809,10 @@
         <v>37</v>
       </c>
       <c r="L90">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M90">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7820,25 +7820,25 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C91">
         <v>51</v>
       </c>
       <c r="D91">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E91">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F91">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G91">
         <v>49</v>
       </c>
       <c r="H91">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I91">
         <v>44</v>
@@ -7847,13 +7847,13 @@
         <v>55</v>
       </c>
       <c r="K91">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L91">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M91">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7876,7 +7876,7 @@
         <v>9</v>
       </c>
       <c r="G92">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H92">
         <v>8</v>
@@ -7885,16 +7885,16 @@
         <v>12</v>
       </c>
       <c r="J92">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K92">
         <v>16</v>
       </c>
       <c r="L92">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M92">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7902,22 +7902,22 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93">
         <v>25</v>
       </c>
       <c r="D93">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E93">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F93">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H93">
         <v>16</v>
@@ -7929,13 +7929,13 @@
         <v>18</v>
       </c>
       <c r="K93">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L93">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M93">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7949,16 +7949,16 @@
         <v>25</v>
       </c>
       <c r="D94">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E94">
         <v>35</v>
       </c>
       <c r="F94">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G94">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H94">
         <v>19</v>
@@ -7967,13 +7967,13 @@
         <v>33</v>
       </c>
       <c r="J94">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K94">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L94">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M94">
         <v>34</v>
@@ -7996,13 +7996,13 @@
         <v>66</v>
       </c>
       <c r="F95">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G95">
         <v>69</v>
       </c>
       <c r="H95">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I95">
         <v>58</v>
@@ -8011,10 +8011,10 @@
         <v>71</v>
       </c>
       <c r="K95">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L95">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M95">
         <v>45</v>
@@ -8031,25 +8031,25 @@
         <v>45</v>
       </c>
       <c r="D96">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E96">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F96">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G96">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H96">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I96">
         <v>40</v>
       </c>
       <c r="J96">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K96">
         <v>62</v>
@@ -8075,7 +8075,7 @@
         <v>36</v>
       </c>
       <c r="E97">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F97">
         <v>20</v>
@@ -8087,10 +8087,10 @@
         <v>25</v>
       </c>
       <c r="I97">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J97">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K97">
         <v>30</v>
@@ -8099,7 +8099,7 @@
         <v>36</v>
       </c>
       <c r="M97">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8110,13 +8110,13 @@
         <v>16</v>
       </c>
       <c r="C98">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D98">
         <v>30</v>
       </c>
       <c r="E98">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F98">
         <v>14</v>
@@ -8125,7 +8125,7 @@
         <v>16</v>
       </c>
       <c r="H98">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I98">
         <v>26</v>
@@ -8134,10 +8134,10 @@
         <v>28</v>
       </c>
       <c r="K98">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L98">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M98">
         <v>21</v>
@@ -8151,7 +8151,7 @@
         <v>68</v>
       </c>
       <c r="C99">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D99">
         <v>86</v>
@@ -8163,25 +8163,25 @@
         <v>65</v>
       </c>
       <c r="G99">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H99">
         <v>72</v>
       </c>
       <c r="I99">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J99">
         <v>51</v>
       </c>
       <c r="K99">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L99">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M99">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8198,7 +8198,7 @@
         <v>6</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100">
         <v>3</v>
@@ -8219,7 +8219,7 @@
         <v>7</v>
       </c>
       <c r="L100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M100">
         <v>3</v>
@@ -8230,40 +8230,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>3061</v>
+        <v>3103</v>
       </c>
       <c r="C101">
-        <v>3995</v>
+        <v>4050</v>
       </c>
       <c r="D101">
-        <v>4259</v>
+        <v>4311</v>
       </c>
       <c r="E101">
-        <v>3841</v>
+        <v>3899</v>
       </c>
       <c r="F101">
-        <v>3418</v>
+        <v>3477</v>
       </c>
       <c r="G101">
-        <v>3773</v>
+        <v>3824</v>
       </c>
       <c r="H101">
-        <v>3479</v>
+        <v>3537</v>
       </c>
       <c r="I101">
-        <v>3636</v>
+        <v>3682</v>
       </c>
       <c r="J101">
-        <v>4072</v>
+        <v>4133</v>
       </c>
       <c r="K101">
-        <v>4112</v>
+        <v>4200</v>
       </c>
       <c r="L101">
-        <v>3164</v>
+        <v>3205</v>
       </c>
       <c r="M101">
-        <v>2887</v>
+        <v>2939</v>
       </c>
     </row>
   </sheetData>
@@ -8457,13 +8457,13 @@
         <v>15</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>11</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>21</v>
@@ -8483,7 +8483,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -8498,7 +8498,7 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -8513,7 +8513,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8527,7 +8527,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -8618,7 +8618,7 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6">
         <v>13</v>
@@ -8635,10 +8635,10 @@
         <v>26</v>
       </c>
       <c r="C7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7">
         <v>23</v>
@@ -8650,22 +8650,22 @@
         <v>33</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7">
         <v>39</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7">
         <v>33</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -8745,7 +8745,7 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>34</v>
@@ -8754,10 +8754,10 @@
         <v>34</v>
       </c>
       <c r="G2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>41</v>
@@ -8766,13 +8766,13 @@
         <v>30</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8783,7 +8783,7 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3">
         <v>66</v>
@@ -8792,28 +8792,28 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3">
         <v>34</v>
       </c>
       <c r="I3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J3">
         <v>60</v>
       </c>
       <c r="K3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L3">
         <v>31</v>
       </c>
       <c r="M3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8903,10 +8903,10 @@
         <v>47</v>
       </c>
       <c r="C6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6">
         <v>55</v>
@@ -8915,19 +8915,19 @@
         <v>41</v>
       </c>
       <c r="G6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6">
         <v>50</v>
       </c>
       <c r="I6">
+        <v>49</v>
+      </c>
+      <c r="J6">
         <v>46</v>
       </c>
-      <c r="J6">
-        <v>44</v>
-      </c>
       <c r="K6">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L6">
         <v>39</v>
@@ -8944,37 +8944,37 @@
         <v>117</v>
       </c>
       <c r="C7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E7">
         <v>155</v>
       </c>
       <c r="F7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I7">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -9107,7 +9107,7 @@
         <v>13</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <v>13</v>
@@ -9133,10 +9133,10 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -9151,7 +9151,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9200,7 +9200,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -9229,10 +9229,10 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -9241,7 +9241,7 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>30</v>
@@ -9250,7 +9250,7 @@
         <v>40</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>27</v>
@@ -9603,7 +9603,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -9615,7 +9615,7 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -9671,7 +9671,7 @@
         <v>11</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -9697,7 +9697,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -9752,25 +9752,25 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>37</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>30</v>
@@ -9787,34 +9787,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>54</v>
       </c>
       <c r="D7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>65</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L7">
         <v>66</v>
@@ -9894,40 +9894,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>61</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I2">
         <v>62</v>
       </c>
       <c r="J2">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9935,40 +9935,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3">
         <v>81</v>
       </c>
       <c r="G3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J3">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L3">
         <v>52</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10029,10 +10029,10 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -10058,7 +10058,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>98</v>
@@ -10067,16 +10067,16 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>83</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6">
         <v>90</v>
@@ -10099,40 +10099,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H7">
+        <v>206</v>
+      </c>
+      <c r="I7">
+        <v>236</v>
+      </c>
+      <c r="J7">
+        <v>225</v>
+      </c>
+      <c r="K7">
         <v>202</v>
       </c>
-      <c r="I7">
-        <v>234</v>
-      </c>
-      <c r="J7">
-        <v>215</v>
-      </c>
-      <c r="K7">
-        <v>198</v>
-      </c>
       <c r="L7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M7">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -10224,7 +10224,7 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -10233,7 +10233,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -10268,7 +10268,7 @@
         <v>6</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -10280,7 +10280,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10312,7 +10312,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>6</v>
@@ -10340,7 +10340,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>36</v>
@@ -10381,7 +10381,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>52</v>
@@ -10399,22 +10399,22 @@
         <v>35</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7">
         <v>50</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -10491,7 +10491,7 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>29</v>
@@ -10500,7 +10500,7 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
         <v>27</v>
@@ -10512,16 +10512,16 @@
         <v>39</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L2">
         <v>30</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10529,7 +10529,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -10541,13 +10541,13 @@
         <v>19</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3">
+        <v>32</v>
+      </c>
+      <c r="H3">
         <v>31</v>
-      </c>
-      <c r="H3">
-        <v>30</v>
       </c>
       <c r="I3">
         <v>22</v>
@@ -10556,13 +10556,13 @@
         <v>37</v>
       </c>
       <c r="K3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3">
         <v>29</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10594,7 +10594,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -10652,7 +10652,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>48</v>
@@ -10664,7 +10664,7 @@
         <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>44</v>
@@ -10679,7 +10679,7 @@
         <v>57</v>
       </c>
       <c r="K6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>33</v>
@@ -10693,10 +10693,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7">
         <v>101</v>
@@ -10705,28 +10705,28 @@
         <v>83</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I7">
         <v>97</v>
       </c>
       <c r="J7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K7">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -10809,7 +10809,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -10821,7 +10821,7 @@
         <v>12</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -10865,7 +10865,7 @@
         <v>8</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>15</v>
@@ -10952,13 +10952,13 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -10993,13 +10993,13 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7">
         <v>21</v>
@@ -11011,10 +11011,10 @@
         <v>37</v>
       </c>
       <c r="I7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7">
         <v>41</v>
@@ -11112,13 +11112,13 @@
         <v>8</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>7</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>8</v>
@@ -11147,10 +11147,10 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>12</v>
@@ -11179,7 +11179,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -11243,25 +11243,25 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>31</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>25</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>20</v>
@@ -11278,31 +11278,31 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>38</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
+        <v>58</v>
+      </c>
+      <c r="J7">
+        <v>64</v>
+      </c>
+      <c r="K7">
         <v>57</v>
-      </c>
-      <c r="J7">
-        <v>63</v>
-      </c>
-      <c r="K7">
-        <v>56</v>
       </c>
       <c r="L7">
         <v>42</v>
@@ -11394,7 +11394,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -11409,7 +11409,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -11432,7 +11432,7 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -11475,6 +11475,9 @@
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>2</v>
       </c>
@@ -11537,10 +11540,10 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -11563,10 +11566,10 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -11575,13 +11578,13 @@
         <v>16</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>12</v>
@@ -11676,7 +11679,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -11851,7 +11854,7 @@
         <v>21</v>
       </c>
       <c r="G7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7">
         <v>19</v>
@@ -11955,7 +11958,7 @@
         <v>8</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>6</v>
@@ -11976,7 +11979,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12034,7 +12037,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -12124,10 +12127,10 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>19</v>
@@ -12148,7 +12151,7 @@
         <v>13</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12225,10 +12228,10 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -12263,7 +12266,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>45</v>
@@ -12272,31 +12275,31 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H3">
         <v>35</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L3">
         <v>19</v>
       </c>
       <c r="M3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12316,7 +12319,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -12386,19 +12389,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>46</v>
@@ -12410,13 +12413,13 @@
         <v>26</v>
       </c>
       <c r="J6">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K6">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6">
         <v>24</v>
@@ -12427,40 +12430,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F7">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H7">
         <v>133</v>
       </c>
       <c r="I7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -12612,7 +12615,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -12644,7 +12647,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -12745,16 +12748,16 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -12780,10 +12783,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -12867,7 +12870,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -12897,7 +12900,7 @@
         <v>12</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -12908,22 +12911,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>45</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>29</v>
@@ -12938,7 +12941,7 @@
         <v>25</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>13</v>
@@ -13018,7 +13021,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -13027,7 +13030,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -13042,10 +13045,10 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2">
         <v>11</v>
@@ -13059,7 +13062,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -13080,7 +13083,7 @@
         <v>15</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3">
         <v>16</v>
@@ -13164,7 +13167,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>17</v>
@@ -13176,7 +13179,7 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <v>34</v>
@@ -13185,7 +13188,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>19</v>
@@ -13205,7 +13208,7 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>46</v>
@@ -13214,10 +13217,10 @@
         <v>52</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H7">
         <v>56</v>
@@ -13226,13 +13229,13 @@
         <v>53</v>
       </c>
       <c r="J7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M7">
         <v>48</v>
@@ -13336,7 +13339,7 @@
         <v>11</v>
       </c>
       <c r="K2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -13350,7 +13353,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -13368,7 +13371,7 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -13377,10 +13380,10 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>15</v>
@@ -13400,10 +13403,10 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -13461,10 +13464,10 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -13482,10 +13485,10 @@
         <v>27</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -13496,25 +13499,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
         <v>40</v>
@@ -13523,10 +13526,10 @@
         <v>49</v>
       </c>
       <c r="K7">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M7">
         <v>40</v>
@@ -13627,7 +13630,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -13671,7 +13674,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -13743,13 +13746,13 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -13781,16 +13784,16 @@
         <v>15</v>
       </c>
       <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
         <v>17</v>
       </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
       <c r="K7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -13879,7 +13882,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -13891,13 +13894,13 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -13923,7 +13926,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -14025,7 +14028,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14042,7 +14045,7 @@
         <v>13</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -14051,22 +14054,22 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>13</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>9</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14190,7 +14193,7 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>9</v>
@@ -14228,7 +14231,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -14265,6 +14268,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>2</v>
       </c>
@@ -14280,7 +14286,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>17</v>
@@ -14321,13 +14327,13 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>31</v>
@@ -14440,7 +14446,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -14449,7 +14455,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -14490,7 +14496,7 @@
         <v>12</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -14516,7 +14522,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -14577,19 +14583,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>32</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>21</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>20</v>
@@ -14618,25 +14624,25 @@
         <v>45</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>40</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K7">
         <v>62</v>
@@ -14746,10 +14752,10 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M2">
         <v>13</v>
@@ -14766,19 +14772,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>17</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>26</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>16</v>
@@ -14787,13 +14793,13 @@
         <v>24</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L3">
         <v>11</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14804,7 +14810,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -14862,7 +14868,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -14903,25 +14909,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>51</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
         <v>49</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7">
         <v>44</v>
@@ -14930,13 +14936,13 @@
         <v>55</v>
       </c>
       <c r="K7">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -15126,7 +15132,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -15167,7 +15173,7 @@
         <v>12</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -15256,25 +15262,25 @@
         <v>24</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>26</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>37</v>
       </c>
       <c r="I2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <v>33</v>
@@ -15286,7 +15292,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15294,31 +15300,31 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>35</v>
+      </c>
+      <c r="D3">
         <v>22</v>
       </c>
-      <c r="C3">
-        <v>34</v>
-      </c>
-      <c r="D3">
-        <v>21</v>
-      </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>34</v>
       </c>
       <c r="G3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3">
         <v>38</v>
       </c>
       <c r="I3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3">
         <v>37</v>
@@ -15341,7 +15347,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -15391,7 +15397,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -15417,28 +15423,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E6">
         <v>41</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6">
         <v>38</v>
@@ -15458,31 +15464,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C7">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D7">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G7">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K7">
         <v>116</v>
@@ -15491,7 +15497,7 @@
         <v>97</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -15592,7 +15598,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>9</v>
@@ -15720,7 +15726,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -15761,7 +15767,7 @@
         <v>13</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -15779,7 +15785,7 @@
         <v>23</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>28</v>
@@ -15859,7 +15865,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>18</v>
@@ -15877,7 +15883,7 @@
         <v>13</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2">
         <v>23</v>
@@ -15886,10 +15892,10 @@
         <v>20</v>
       </c>
       <c r="K2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2">
         <v>29</v>
@@ -15909,19 +15915,19 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>24</v>
       </c>
       <c r="G3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>21</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>29</v>
@@ -15930,10 +15936,10 @@
         <v>28</v>
       </c>
       <c r="L3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15941,13 +15947,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -16020,13 +16026,13 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>37</v>
+      </c>
+      <c r="C6">
         <v>36</v>
       </c>
-      <c r="C6">
-        <v>35</v>
-      </c>
       <c r="D6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>59</v>
@@ -16053,7 +16059,7 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16061,40 +16067,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F7">
         <v>115</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J7">
         <v>86</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -16195,7 +16201,7 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>9</v>
@@ -16227,7 +16233,7 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -16255,6 +16261,9 @@
       <c r="E4">
         <v>3</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -16343,13 +16352,13 @@
         <v>19</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>13</v>
       </c>
       <c r="H7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7">
         <v>30</v>
@@ -16358,7 +16367,7 @@
         <v>60</v>
       </c>
       <c r="K7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L7">
         <v>24</v>
@@ -16688,10 +16697,10 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>21</v>
@@ -16703,13 +16712,13 @@
         <v>18</v>
       </c>
       <c r="K2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L2">
         <v>27</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16726,7 +16735,7 @@
         <v>11</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -16741,7 +16750,7 @@
         <v>13</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3">
         <v>17</v>
@@ -16782,10 +16791,10 @@
         <v>4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -16831,10 +16840,10 @@
         <v>21</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -16852,7 +16861,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -16872,19 +16881,19 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>53</v>
+      </c>
+      <c r="F7">
+        <v>44</v>
+      </c>
+      <c r="G7">
         <v>40</v>
-      </c>
-      <c r="E7">
-        <v>52</v>
-      </c>
-      <c r="F7">
-        <v>43</v>
-      </c>
-      <c r="G7">
-        <v>39</v>
       </c>
       <c r="H7">
         <v>69</v>
@@ -16893,16 +16902,16 @@
         <v>49</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L7">
         <v>55</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -16976,7 +16985,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -16988,7 +16997,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>6</v>
@@ -17009,7 +17018,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17026,13 +17035,13 @@
         <v>6</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -17044,7 +17053,7 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -17067,7 +17076,7 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -17107,7 +17116,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -17131,7 +17140,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -17142,22 +17151,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>25</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -17169,13 +17178,13 @@
         <v>18</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -17329,7 +17338,7 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -17344,7 +17353,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -17364,7 +17373,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -17385,7 +17394,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7">
         <v>3</v>
@@ -17462,13 +17471,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>21</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -17483,10 +17492,10 @@
         <v>43</v>
       </c>
       <c r="I2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2">
         <v>45</v>
@@ -17506,37 +17515,37 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>51</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3">
         <v>36</v>
       </c>
       <c r="H3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J3">
         <v>41</v>
       </c>
       <c r="K3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17626,13 +17635,13 @@
         <v>58</v>
       </c>
       <c r="C6">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -17653,7 +17662,7 @@
         <v>33</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6">
         <v>15</v>
@@ -17664,40 +17673,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E7">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G7">
         <v>101</v>
       </c>
       <c r="H7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -17795,7 +17804,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -17876,6 +17885,9 @@
       <c r="L4">
         <v>2</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -17923,7 +17935,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -17964,10 +17976,10 @@
         <v>16</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7">
         <v>25</v>
@@ -17976,7 +17988,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -18062,7 +18074,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -18077,7 +18089,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>12</v>
@@ -18106,7 +18118,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -18153,7 +18165,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -18190,7 +18202,7 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>23</v>
@@ -18208,13 +18220,13 @@
         <v>17</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6">
         <v>20</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -18231,16 +18243,16 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>35</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>19</v>
@@ -18249,13 +18261,13 @@
         <v>33</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7">
         <v>34</v>
@@ -18347,7 +18359,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -18356,7 +18368,7 @@
         <v>4</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -18400,7 +18412,7 @@
         <v>7</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -18519,7 +18531,7 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -18528,10 +18540,10 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7">
         <v>14</v>
@@ -18626,7 +18638,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -18676,7 +18688,7 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>11</v>
@@ -18733,6 +18745,9 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="D5">
         <v>2</v>
       </c>
@@ -18795,7 +18810,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>23</v>
@@ -18810,7 +18825,7 @@
         <v>25</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>32</v>
@@ -18819,7 +18834,7 @@
         <v>28</v>
       </c>
       <c r="J7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -18908,7 +18923,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -18926,7 +18941,7 @@
         <v>8</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -18935,7 +18950,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18955,7 +18970,7 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -18970,7 +18985,7 @@
         <v>13</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -18987,7 +19002,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -19002,7 +19017,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -19092,37 +19107,37 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7">
         <v>48</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>25</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
         <v>44</v>
       </c>
       <c r="J7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>21</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -19205,7 +19220,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -19214,7 +19229,7 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -19226,7 +19241,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -19318,7 +19333,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>16</v>
@@ -19342,7 +19357,7 @@
         <v>14</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>15</v>
@@ -19359,13 +19374,13 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>14</v>
@@ -19374,7 +19389,7 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>26</v>
@@ -19383,10 +19398,10 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
         <v>21</v>
@@ -19560,7 +19575,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -19603,7 +19618,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -19644,7 +19659,7 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>21</v>
@@ -19653,7 +19668,7 @@
         <v>21</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>15</v>
@@ -19956,6 +19971,9 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="I3">
         <v>1</v>
       </c>
@@ -19985,7 +20003,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -20020,7 +20038,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -20145,7 +20163,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20205,6 +20223,9 @@
       <c r="J4">
         <v>1</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -20282,10 +20303,10 @@
         <v>17</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -20371,7 +20392,7 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>13</v>
@@ -20403,7 +20424,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -20514,13 +20535,13 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -20532,7 +20553,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>39</v>
@@ -20552,16 +20573,16 @@
         <v>60</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7">
+        <v>80</v>
+      </c>
+      <c r="E7">
         <v>79</v>
       </c>
-      <c r="E7">
-        <v>78</v>
-      </c>
       <c r="F7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>65</v>
@@ -20573,7 +20594,7 @@
         <v>66</v>
       </c>
       <c r="J7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7">
         <v>92</v>
@@ -20719,7 +20740,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -20760,7 +20781,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -20876,7 +20897,7 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -20891,7 +20912,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20899,7 +20920,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -20908,7 +20929,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -20958,7 +20979,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -21042,7 +21063,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -21051,7 +21072,7 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>21</v>
@@ -21060,7 +21081,7 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I7">
         <v>21</v>
@@ -21075,7 +21096,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -21149,7 +21170,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -21158,13 +21179,13 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>14</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -21196,7 +21217,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -21280,7 +21301,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -21321,22 +21342,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
+        <v>38</v>
+      </c>
+      <c r="E7">
         <v>37</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
       </c>
       <c r="F7">
         <v>37</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7">
         <v>36</v>
@@ -21466,7 +21487,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -21490,7 +21511,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21504,7 +21525,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -21526,7 +21547,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -21564,10 +21585,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -21579,7 +21600,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -21597,7 +21618,7 @@
         <v>3</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -21671,7 +21692,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -21683,10 +21704,10 @@
         <v>8</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>11</v>
@@ -21768,7 +21789,7 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -21852,7 +21873,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -21864,10 +21885,10 @@
         <v>43</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H7">
         <v>34</v>
@@ -21968,7 +21989,7 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -22021,7 +22042,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>5</v>
@@ -22114,7 +22135,7 @@
         <v>28</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>17</v>
@@ -22123,7 +22144,7 @@
         <v>27</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22140,7 +22161,7 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -22152,10 +22173,10 @@
         <v>25</v>
       </c>
       <c r="I7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -22164,7 +22185,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -22262,7 +22283,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -22303,7 +22324,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22360,7 +22381,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -22375,7 +22396,7 @@
         <v>11</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -22401,7 +22422,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -22410,16 +22431,16 @@
         <v>12</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7">
         <v>16</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -22519,7 +22540,7 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -22641,7 +22662,7 @@
         <v>12</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -22730,7 +22751,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -22748,7 +22769,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22774,7 +22795,7 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>9</v>
@@ -22789,7 +22810,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22809,7 +22830,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -22882,13 +22903,13 @@
         <v>15</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6">
         <v>11</v>
@@ -22914,25 +22935,25 @@
         <v>42</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I7">
         <v>32</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -23047,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -23148,7 +23169,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -23246,7 +23267,7 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -23255,7 +23276,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -23267,13 +23288,13 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>13</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23311,7 +23332,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3">
         <v>12</v>
@@ -23328,7 +23349,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -23430,7 +23451,7 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>29</v>
@@ -23439,7 +23460,7 @@
         <v>43</v>
       </c>
       <c r="G7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7">
         <v>33</v>
@@ -23451,13 +23472,13 @@
         <v>49</v>
       </c>
       <c r="K7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -23613,7 +23634,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -23691,7 +23712,7 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -23816,13 +23837,13 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>10</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23851,13 +23872,13 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -23926,7 +23947,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -23944,13 +23965,13 @@
         <v>15</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -23967,7 +23988,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>23</v>
@@ -23985,19 +24006,19 @@
         <v>27</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>19</v>
       </c>
       <c r="K7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L7">
         <v>37</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -24101,7 +24122,7 @@
         <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -24171,7 +24192,7 @@
         <v>11</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -24180,7 +24201,7 @@
         <v>14</v>
       </c>
       <c r="L4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4">
         <v>12</v>
@@ -24253,7 +24274,7 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>17</v>
@@ -24262,7 +24283,7 @@
         <v>28</v>
       </c>
       <c r="L6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>20</v>
@@ -24612,7 +24633,7 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -24624,7 +24645,7 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -24680,7 +24701,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -24697,7 +24718,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -24767,10 +24788,10 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -24791,7 +24812,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -24808,19 +24829,19 @@
         <v>60</v>
       </c>
       <c r="D7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>32</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7">
         <v>40</v>
@@ -24832,10 +24853,10 @@
         <v>37</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -24980,7 +25001,7 @@
         <v>13</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -25009,7 +25030,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -25111,7 +25132,7 @@
         <v>37</v>
       </c>
       <c r="H7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7">
         <v>35</v>
@@ -25123,7 +25144,7 @@
         <v>54</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M7">
         <v>34</v>
@@ -25265,7 +25286,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -25381,7 +25402,7 @@
         <v>12</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -25485,7 +25506,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -25648,7 +25669,7 @@
         <v>15</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>17</v>
@@ -25752,7 +25773,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -25775,7 +25796,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -25816,7 +25837,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -25830,6 +25851,9 @@
       <c r="K4">
         <v>8</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -25868,7 +25892,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -25903,16 +25927,16 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>24</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>25</v>
@@ -25921,7 +25945,7 @@
         <v>13</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
         <v>32</v>
@@ -25930,7 +25954,7 @@
         <v>19</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -26019,7 +26043,7 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -26031,10 +26055,10 @@
         <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26110,7 +26134,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -26159,7 +26183,7 @@
         <v>30</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -26191,7 +26215,7 @@
         <v>30</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>34</v>
@@ -26200,13 +26224,13 @@
         <v>46</v>
       </c>
       <c r="K7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7">
+        <v>25</v>
+      </c>
+      <c r="M7">
         <v>24</v>
-      </c>
-      <c r="M7">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -26280,7 +26304,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>22</v>
@@ -26292,19 +26316,19 @@
         <v>31</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
         <v>34</v>
       </c>
       <c r="H2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2">
         <v>79</v>
@@ -26313,7 +26337,7 @@
         <v>39</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26321,37 +26345,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3">
         <v>55</v>
       </c>
       <c r="F3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H3">
         <v>64</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K3">
         <v>71</v>
       </c>
       <c r="L3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M3">
         <v>67</v>
@@ -26365,7 +26389,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>16</v>
@@ -26409,7 +26433,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -26447,25 +26471,25 @@
         <v>60</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>60</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>54</v>
       </c>
       <c r="H6">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J6">
         <v>47</v>
@@ -26474,7 +26498,7 @@
         <v>43</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -26485,40 +26509,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C7">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K7">
         <v>207</v>
       </c>
       <c r="L7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M7">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -26604,7 +26628,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -26700,6 +26724,9 @@
       <c r="L4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -26761,7 +26788,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -26782,7 +26809,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -26918,7 +26945,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26981,7 +27008,7 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -27022,13 +27049,13 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>9</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -27111,7 +27138,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -27196,7 +27223,7 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -27219,13 +27246,13 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -27243,7 +27270,7 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -27260,13 +27287,13 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>19</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -27278,13 +27305,13 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -27589,7 +27616,7 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -27598,7 +27625,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -27621,7 +27648,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -27633,7 +27660,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -27758,7 +27785,7 @@
         <v>20</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>18</v>
@@ -27767,16 +27794,16 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>33</v>
       </c>
       <c r="K7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -27865,7 +27892,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -27974,7 +28001,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -28385,7 +28412,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -28423,7 +28450,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>16</v>
@@ -28524,7 +28551,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -28624,7 +28651,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -28995,10 +29022,10 @@
         <v>22</v>
       </c>
       <c r="K2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>16</v>
@@ -29021,13 +29048,13 @@
         <v>29</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>22</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>25</v>
@@ -29036,7 +29063,7 @@
         <v>29</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3">
         <v>16</v>
@@ -29118,7 +29145,7 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -29138,13 +29165,13 @@
         <v>50</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -29159,13 +29186,13 @@
         <v>34</v>
       </c>
       <c r="K6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6">
         <v>13</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -29179,19 +29206,19 @@
         <v>111</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7">
         <v>69</v>
       </c>
       <c r="H7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7">
         <v>71</v>
@@ -29200,13 +29227,13 @@
         <v>92</v>
       </c>
       <c r="K7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -29297,6 +29324,9 @@
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="I2">
         <v>7</v>
       </c>
@@ -29304,7 +29334,7 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -29356,7 +29386,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -29423,16 +29453,16 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>16</v>
       </c>
       <c r="J6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -29619,7 +29649,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -29628,6 +29658,9 @@
         <v>5</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
@@ -29657,7 +29690,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -29669,7 +29702,7 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>14</v>
@@ -30241,7 +30274,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -30330,7 +30363,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -30362,13 +30395,13 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7">
         <v>13</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -30825,6 +30858,9 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -30866,7 +30902,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>2</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="C2">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="D2">
-        <v>896</v>
+        <v>913</v>
       </c>
       <c r="E2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="F2">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="G2">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="H2">
-        <v>1031</v>
+        <v>1054</v>
       </c>
       <c r="I2">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="J2">
-        <v>1161</v>
+        <v>1187</v>
       </c>
       <c r="K2">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="L2">
-        <v>1015</v>
+        <v>1032</v>
       </c>
       <c r="M2">
-        <v>944</v>
+        <v>963</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="C3">
-        <v>1155</v>
+        <v>1178</v>
       </c>
       <c r="D3">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="E3">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="F3">
-        <v>1084</v>
+        <v>1111</v>
       </c>
       <c r="G3">
-        <v>1199</v>
+        <v>1218</v>
       </c>
       <c r="H3">
-        <v>1050</v>
+        <v>1083</v>
       </c>
       <c r="I3">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="J3">
-        <v>1243</v>
+        <v>1258</v>
       </c>
       <c r="K3">
-        <v>1228</v>
+        <v>1258</v>
       </c>
       <c r="L3">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="M3">
-        <v>1049</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C4">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D4">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E4">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F4">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G4">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H4">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="I4">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J4">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K4">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L4">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M4">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -991,10 +991,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D5">
         <v>111</v>
@@ -1006,25 +1006,25 @@
         <v>54</v>
       </c>
       <c r="G5">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5">
         <v>103</v>
       </c>
       <c r="I5">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J5">
         <v>96</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M5">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1404</v>
+        <v>1429</v>
       </c>
       <c r="C6">
-        <v>1941</v>
+        <v>1964</v>
       </c>
       <c r="D6">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="E6">
-        <v>1709</v>
+        <v>1734</v>
       </c>
       <c r="F6">
-        <v>1300</v>
+        <v>1319</v>
       </c>
       <c r="G6">
-        <v>1500</v>
+        <v>1518</v>
       </c>
       <c r="H6">
-        <v>1346</v>
+        <v>1366</v>
       </c>
       <c r="I6">
-        <v>1460</v>
+        <v>1477</v>
       </c>
       <c r="J6">
-        <v>1637</v>
+        <v>1654</v>
       </c>
       <c r="K6">
-        <v>1577</v>
+        <v>1597</v>
       </c>
       <c r="L6">
-        <v>1029</v>
+        <v>1045</v>
       </c>
       <c r="M6">
-        <v>766</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3337</v>
+        <v>3400</v>
       </c>
       <c r="C7">
-        <v>4380</v>
+        <v>4454</v>
       </c>
       <c r="D7">
-        <v>4618</v>
+        <v>4671</v>
       </c>
       <c r="E7">
-        <v>4156</v>
+        <v>4207</v>
       </c>
       <c r="F7">
-        <v>3717</v>
+        <v>3782</v>
       </c>
       <c r="G7">
-        <v>4112</v>
+        <v>4165</v>
       </c>
       <c r="H7">
-        <v>3828</v>
+        <v>3909</v>
       </c>
       <c r="I7">
-        <v>3993</v>
+        <v>4039</v>
       </c>
       <c r="J7">
-        <v>4470</v>
+        <v>4535</v>
       </c>
       <c r="K7">
-        <v>4523</v>
+        <v>4595</v>
       </c>
       <c r="L7">
-        <v>3447</v>
+        <v>3510</v>
       </c>
       <c r="M7">
-        <v>3114</v>
+        <v>3165</v>
       </c>
     </row>
   </sheetData>
@@ -1561,7 +1561,7 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>11</v>
@@ -1602,7 +1602,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -1614,7 +1614,7 @@
         <v>11</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -1655,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -1704,7 +1704,7 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -1739,19 +1739,19 @@
         <v>63</v>
       </c>
       <c r="D7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7">
         <v>48</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>41</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I7">
         <v>47</v>
@@ -1843,37 +1843,37 @@
         <v>48</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>64</v>
       </c>
       <c r="F2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>67</v>
       </c>
       <c r="J2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2">
         <v>77</v>
       </c>
       <c r="L2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1881,10 +1881,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3">
         <v>89</v>
@@ -1896,25 +1896,25 @@
         <v>78</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1931,13 +1931,13 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -1996,7 +1996,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2004,28 +2004,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>142</v>
       </c>
       <c r="D6">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E6">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F6">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H6">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J6">
         <v>71</v>
@@ -2045,40 +2045,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M7">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2152,13 +2152,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>14</v>
@@ -2167,7 +2167,7 @@
         <v>15</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -2211,19 +2211,19 @@
         <v>22</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3">
         <v>27</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M3">
         <v>35</v>
@@ -2322,7 +2322,7 @@
         <v>25</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -2351,37 +2351,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7">
         <v>64</v>
       </c>
       <c r="F7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7">
         <v>70</v>
       </c>
       <c r="J7">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7">
         <v>80</v>
@@ -2461,28 +2461,28 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K2">
         <v>54</v>
@@ -2499,40 +2499,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <v>55</v>
       </c>
       <c r="E3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3">
         <v>67</v>
       </c>
       <c r="G3">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H3">
         <v>67</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2611,7 +2611,7 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -2622,10 +2622,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D6">
         <v>88</v>
@@ -2640,19 +2640,19 @@
         <v>103</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K6">
         <v>47</v>
       </c>
       <c r="L6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M6">
         <v>32</v>
@@ -2663,40 +2663,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C7">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>186</v>
       </c>
       <c r="G7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H7">
+        <v>188</v>
+      </c>
+      <c r="I7">
+        <v>181</v>
+      </c>
+      <c r="J7">
+        <v>186</v>
+      </c>
+      <c r="K7">
         <v>184</v>
       </c>
-      <c r="I7">
-        <v>178</v>
-      </c>
-      <c r="J7">
-        <v>182</v>
-      </c>
-      <c r="K7">
-        <v>182</v>
-      </c>
       <c r="L7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M7">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2776,7 +2776,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>19</v>
@@ -2841,10 +2841,10 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2861,7 +2861,7 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -2931,7 +2931,7 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>35</v>
@@ -2943,7 +2943,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <v>12</v>
@@ -2961,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2972,19 +2972,19 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7">
         <v>67</v>
       </c>
       <c r="G7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>80</v>
@@ -2999,10 +2999,10 @@
         <v>78</v>
       </c>
       <c r="L7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3088,19 +3088,19 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
         <v>29</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2">
         <v>32</v>
@@ -3109,7 +3109,7 @@
         <v>39</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3120,7 +3120,7 @@
         <v>34</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -3129,7 +3129,7 @@
         <v>39</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>42</v>
@@ -3144,13 +3144,13 @@
         <v>48</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3176,7 +3176,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>11</v>
@@ -3217,7 +3217,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -3240,10 +3240,10 @@
         <v>62</v>
       </c>
       <c r="D6">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>35</v>
@@ -3252,7 +3252,7 @@
         <v>32</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6">
         <v>36</v>
@@ -3261,7 +3261,7 @@
         <v>49</v>
       </c>
       <c r="K6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L6">
         <v>36</v>
@@ -3278,37 +3278,37 @@
         <v>117</v>
       </c>
       <c r="C7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E7">
+        <v>121</v>
+      </c>
+      <c r="F7">
         <v>120</v>
-      </c>
-      <c r="F7">
-        <v>117</v>
       </c>
       <c r="G7">
         <v>114</v>
       </c>
       <c r="H7">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I7">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K7">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3385,7 +3385,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -3406,13 +3406,13 @@
         <v>24</v>
       </c>
       <c r="J2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2">
         <v>30</v>
       </c>
       <c r="L2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2">
         <v>24</v>
@@ -3423,13 +3423,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>26</v>
@@ -3441,7 +3441,7 @@
         <v>18</v>
       </c>
       <c r="H3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3">
         <v>26</v>
@@ -3473,7 +3473,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -3558,7 +3558,7 @@
         <v>20</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6">
         <v>43</v>
@@ -3581,16 +3581,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7">
         <v>70</v>
@@ -3599,19 +3599,19 @@
         <v>67</v>
       </c>
       <c r="H7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I7">
         <v>102</v>
       </c>
       <c r="J7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K7">
         <v>116</v>
       </c>
       <c r="L7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M7">
         <v>70</v>
@@ -3688,7 +3688,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -3697,7 +3697,7 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -3718,7 +3718,7 @@
         <v>23</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2">
         <v>21</v>
@@ -3735,19 +3735,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>27</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3">
         <v>25</v>
@@ -3785,7 +3785,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3858,7 +3858,7 @@
         <v>14</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>24</v>
@@ -3867,7 +3867,7 @@
         <v>29</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>16</v>
@@ -3887,28 +3887,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7">
         <v>62</v>
       </c>
       <c r="D7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7">
         <v>53</v>
@@ -3917,7 +3917,7 @@
         <v>83</v>
       </c>
       <c r="L7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7">
         <v>69</v>
@@ -4006,7 +4006,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -4027,7 +4027,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4035,7 +4035,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -4050,10 +4050,10 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>4</v>
@@ -4104,7 +4104,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -4142,10 +4142,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>18</v>
@@ -4154,13 +4154,13 @@
         <v>14</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
         <v>13</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
       </c>
       <c r="I7">
         <v>14</v>
@@ -4175,7 +4175,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4249,13 +4249,13 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>45</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -4270,10 +4270,10 @@
         <v>36</v>
       </c>
       <c r="I2">
+        <v>46</v>
+      </c>
+      <c r="J2">
         <v>44</v>
-      </c>
-      <c r="J2">
-        <v>43</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -4282,7 +4282,7 @@
         <v>24</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4337,7 +4337,7 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -4346,7 +4346,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -4390,7 +4390,7 @@
         <v>12</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>17</v>
@@ -4402,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>14</v>
@@ -4419,10 +4419,10 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>22</v>
@@ -4437,10 +4437,10 @@
         <v>31</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L6">
         <v>24</v>
@@ -4454,25 +4454,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E7">
         <v>151</v>
       </c>
       <c r="F7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G7">
         <v>116</v>
       </c>
       <c r="H7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I7">
         <v>129</v>
@@ -4481,13 +4481,13 @@
         <v>128</v>
       </c>
       <c r="K7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M7">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4495,40 +4495,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C8">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D8">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F8">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G8">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H8">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J8">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K8">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M8">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4539,19 +4539,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>29</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H9">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4598,7 +4598,7 @@
         <v>31</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J10">
         <v>29</v>
@@ -4624,34 +4624,34 @@
         <v>71</v>
       </c>
       <c r="D11">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F11">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H11">
         <v>55</v>
       </c>
       <c r="I11">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J11">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K11">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L11">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M11">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4677,7 +4677,7 @@
         <v>14</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -4712,7 +4712,7 @@
         <v>4</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -4735,7 +4735,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>25</v>
@@ -4762,7 +4762,7 @@
         <v>17</v>
       </c>
       <c r="K14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L14">
         <v>13</v>
@@ -4776,16 +4776,16 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15">
         <v>54</v>
       </c>
       <c r="E15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F15">
         <v>35</v>
@@ -4794,7 +4794,7 @@
         <v>28</v>
       </c>
       <c r="H15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15">
         <v>47</v>
@@ -4809,7 +4809,7 @@
         <v>22</v>
       </c>
       <c r="M15">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4841,13 +4841,13 @@
         <v>15</v>
       </c>
       <c r="J16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16">
         <v>9</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>2</v>
@@ -4861,7 +4861,7 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -4870,16 +4870,16 @@
         <v>4</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>12</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17">
         <v>11</v>
@@ -4908,16 +4908,16 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18">
         <v>18</v>
       </c>
       <c r="G18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H18">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I18">
         <v>33</v>
@@ -4926,7 +4926,7 @@
         <v>62</v>
       </c>
       <c r="K18">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L18">
         <v>27</v>
@@ -4940,40 +4940,40 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C19">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E19">
         <v>86</v>
       </c>
       <c r="F19">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G19">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J19">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K19">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L19">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M19">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4984,37 +4984,37 @@
         <v>88</v>
       </c>
       <c r="C20">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D20">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E20">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F20">
         <v>122</v>
       </c>
       <c r="G20">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H20">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I20">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J20">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K20">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L20">
         <v>89</v>
       </c>
       <c r="M20">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5078,10 +5078,10 @@
         <v>11</v>
       </c>
       <c r="G22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -5090,13 +5090,13 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L22">
         <v>10</v>
       </c>
       <c r="M22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5122,19 +5122,19 @@
         <v>44</v>
       </c>
       <c r="H23">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
+        <v>44</v>
+      </c>
+      <c r="K23">
         <v>40</v>
       </c>
-      <c r="K23">
-        <v>39</v>
-      </c>
       <c r="L23">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M23">
         <v>32</v>
@@ -5151,7 +5151,7 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>14</v>
@@ -5166,7 +5166,7 @@
         <v>19</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>17</v>
@@ -5178,7 +5178,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5186,10 +5186,10 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>25</v>
@@ -5219,7 +5219,7 @@
         <v>16</v>
       </c>
       <c r="M25">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5268,7 +5268,7 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -5277,10 +5277,10 @@
         <v>25</v>
       </c>
       <c r="E27">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27">
         <v>33</v>
@@ -5292,10 +5292,10 @@
         <v>39</v>
       </c>
       <c r="J27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K27">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L27">
         <v>41</v>
@@ -5341,40 +5341,40 @@
         <v>35</v>
       </c>
       <c r="B29">
+        <v>224</v>
+      </c>
+      <c r="C29">
+        <v>282</v>
+      </c>
+      <c r="D29">
+        <v>277</v>
+      </c>
+      <c r="E29">
+        <v>220</v>
+      </c>
+      <c r="F29">
+        <v>223</v>
+      </c>
+      <c r="G29">
+        <v>272</v>
+      </c>
+      <c r="H29">
+        <v>238</v>
+      </c>
+      <c r="I29">
+        <v>261</v>
+      </c>
+      <c r="J29">
+        <v>252</v>
+      </c>
+      <c r="K29">
         <v>221</v>
       </c>
-      <c r="C29">
-        <v>277</v>
-      </c>
-      <c r="D29">
-        <v>274</v>
-      </c>
-      <c r="E29">
-        <v>217</v>
-      </c>
-      <c r="F29">
-        <v>220</v>
-      </c>
-      <c r="G29">
-        <v>264</v>
-      </c>
-      <c r="H29">
-        <v>231</v>
-      </c>
-      <c r="I29">
-        <v>257</v>
-      </c>
-      <c r="J29">
-        <v>250</v>
-      </c>
-      <c r="K29">
-        <v>216</v>
-      </c>
       <c r="L29">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M29">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5382,10 +5382,10 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30">
         <v>18</v>
@@ -5394,13 +5394,13 @@
         <v>14</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30">
+        <v>14</v>
+      </c>
+      <c r="H30">
         <v>13</v>
-      </c>
-      <c r="H30">
-        <v>12</v>
       </c>
       <c r="I30">
         <v>14</v>
@@ -5415,7 +5415,7 @@
         <v>20</v>
       </c>
       <c r="M30">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5426,7 +5426,7 @@
         <v>31</v>
       </c>
       <c r="C31">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -5435,13 +5435,13 @@
         <v>30</v>
       </c>
       <c r="F31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I31">
         <v>41</v>
@@ -5453,7 +5453,7 @@
         <v>49</v>
       </c>
       <c r="L31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M31">
         <v>32</v>
@@ -5470,7 +5470,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -5491,10 +5491,10 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>2</v>
@@ -5505,40 +5505,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C33">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D33">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E33">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F33">
         <v>186</v>
       </c>
       <c r="G33">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H33">
+        <v>188</v>
+      </c>
+      <c r="I33">
+        <v>181</v>
+      </c>
+      <c r="J33">
+        <v>186</v>
+      </c>
+      <c r="K33">
         <v>184</v>
       </c>
-      <c r="I33">
-        <v>178</v>
-      </c>
-      <c r="J33">
-        <v>182</v>
-      </c>
-      <c r="K33">
-        <v>182</v>
-      </c>
       <c r="L33">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M33">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5546,7 +5546,7 @@
         <v>40</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34">
         <v>18</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G34">
         <v>22</v>
@@ -5570,13 +5570,13 @@
         <v>13</v>
       </c>
       <c r="J34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K34">
         <v>28</v>
       </c>
       <c r="L34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M34">
         <v>14</v>
@@ -5611,7 +5611,7 @@
         <v>6</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>6</v>
@@ -5631,37 +5631,37 @@
         <v>49</v>
       </c>
       <c r="C36">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E36">
         <v>54</v>
       </c>
       <c r="F36">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G36">
         <v>43</v>
       </c>
       <c r="H36">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I36">
         <v>55</v>
       </c>
       <c r="J36">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L36">
         <v>60</v>
       </c>
       <c r="M36">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5672,37 +5672,37 @@
         <v>117</v>
       </c>
       <c r="C37">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D37">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E37">
+        <v>121</v>
+      </c>
+      <c r="F37">
         <v>120</v>
-      </c>
-      <c r="F37">
-        <v>117</v>
       </c>
       <c r="G37">
         <v>114</v>
       </c>
       <c r="H37">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I37">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J37">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K37">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L37">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M37">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5783,13 +5783,13 @@
         <v>11</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40">
         <v>6</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>7</v>
@@ -5801,7 +5801,7 @@
         <v>4</v>
       </c>
       <c r="J40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K40">
         <v>8</v>
@@ -5818,13 +5818,13 @@
         <v>47</v>
       </c>
       <c r="B41">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C41">
         <v>29</v>
       </c>
       <c r="D41">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E41">
         <v>26</v>
@@ -5845,13 +5845,13 @@
         <v>28</v>
       </c>
       <c r="K41">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L41">
+        <v>14</v>
+      </c>
+      <c r="M41">
         <v>13</v>
-      </c>
-      <c r="M41">
-        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5859,40 +5859,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C42">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D42">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E42">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F42">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G42">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H42">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I42">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J42">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K42">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L42">
         <v>111</v>
       </c>
       <c r="M42">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5903,7 +5903,7 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D43">
         <v>19</v>
@@ -5918,16 +5918,16 @@
         <v>32</v>
       </c>
       <c r="H43">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J43">
         <v>51</v>
       </c>
       <c r="K43">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L43">
         <v>28</v>
@@ -5941,10 +5941,10 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C44">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D44">
         <v>41</v>
@@ -5959,7 +5959,7 @@
         <v>40</v>
       </c>
       <c r="H44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I44">
         <v>32</v>
@@ -6000,7 +6000,7 @@
         <v>6</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>5</v>
@@ -6047,7 +6047,7 @@
         <v>9</v>
       </c>
       <c r="J46">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K46">
         <v>10</v>
@@ -6076,13 +6076,13 @@
         <v>21</v>
       </c>
       <c r="F47">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G47">
         <v>16</v>
       </c>
       <c r="H47">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I47">
         <v>31</v>
@@ -6091,13 +6091,13 @@
         <v>39</v>
       </c>
       <c r="K47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L47">
         <v>29</v>
       </c>
       <c r="M47">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6111,31 +6111,31 @@
         <v>58</v>
       </c>
       <c r="D48">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E48">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F48">
         <v>35</v>
       </c>
       <c r="G48">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H48">
         <v>43</v>
       </c>
       <c r="I48">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J48">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K48">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L48">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M48">
         <v>47</v>
@@ -6155,7 +6155,7 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F49">
         <v>17</v>
@@ -6170,7 +6170,7 @@
         <v>16</v>
       </c>
       <c r="J49">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K49">
         <v>30</v>
@@ -6193,7 +6193,7 @@
         <v>25</v>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E50">
         <v>23</v>
@@ -6234,10 +6234,10 @@
         <v>38</v>
       </c>
       <c r="D51">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E51">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F51">
         <v>43</v>
@@ -6246,10 +6246,10 @@
         <v>42</v>
       </c>
       <c r="H51">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I51">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J51">
         <v>59</v>
@@ -6269,40 +6269,40 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C52">
         <v>116</v>
       </c>
       <c r="D52">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E52">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F52">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G52">
         <v>77</v>
       </c>
       <c r="H52">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I52">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J52">
         <v>98</v>
       </c>
       <c r="K52">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L52">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M52">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6316,19 +6316,19 @@
         <v>63</v>
       </c>
       <c r="D53">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
       <c r="F53">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G53">
         <v>41</v>
       </c>
       <c r="H53">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I53">
         <v>47</v>
@@ -6354,37 +6354,37 @@
         <v>47</v>
       </c>
       <c r="C54">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D54">
         <v>65</v>
       </c>
       <c r="E54">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F54">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G54">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H54">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I54">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J54">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K54">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L54">
         <v>69</v>
       </c>
       <c r="M54">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6392,10 +6392,10 @@
         <v>61</v>
       </c>
       <c r="B55">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D55">
         <v>46</v>
@@ -6410,19 +6410,19 @@
         <v>38</v>
       </c>
       <c r="H55">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I55">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J55">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K55">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M55">
         <v>42</v>
@@ -6457,10 +6457,10 @@
         <v>9</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L56">
         <v>2</v>
@@ -6507,7 +6507,7 @@
         <v>18</v>
       </c>
       <c r="M57">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6556,7 +6556,7 @@
         <v>11</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59">
         <v>8</v>
@@ -6624,7 +6624,7 @@
         <v>20</v>
       </c>
       <c r="M60">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6699,16 +6699,16 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C63">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D63">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E63">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F63">
         <v>65</v>
@@ -6720,13 +6720,13 @@
         <v>55</v>
       </c>
       <c r="I63">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J63">
         <v>57</v>
       </c>
       <c r="K63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L63">
         <v>14</v>
@@ -6740,13 +6740,13 @@
         <v>70</v>
       </c>
       <c r="B64">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C64">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D64">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E64">
         <v>26</v>
@@ -6781,16 +6781,16 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C65">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D65">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E65">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F65">
         <v>70</v>
@@ -6799,19 +6799,19 @@
         <v>67</v>
       </c>
       <c r="H65">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I65">
         <v>102</v>
       </c>
       <c r="J65">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K65">
         <v>116</v>
       </c>
       <c r="L65">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M65">
         <v>70</v>
@@ -6849,7 +6849,7 @@
         <v>9</v>
       </c>
       <c r="K66">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L66">
         <v>3</v>
@@ -6863,40 +6863,40 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C67">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D67">
         <v>189</v>
       </c>
       <c r="E67">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F67">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G67">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H67">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I67">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J67">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K67">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L67">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M67">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6916,7 +6916,7 @@
         <v>7</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G68">
         <v>16</v>
@@ -6934,7 +6934,7 @@
         <v>13</v>
       </c>
       <c r="L68">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M68">
         <v>10</v>
@@ -6989,10 +6989,10 @@
         <v>3</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70">
         <v>6</v>
@@ -7027,16 +7027,16 @@
         <v>5</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71">
         <v>9</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F71">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G71">
         <v>7</v>
@@ -7051,7 +7051,7 @@
         <v>18</v>
       </c>
       <c r="K71">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L71">
         <v>9</v>
@@ -7083,7 +7083,7 @@
         <v>21</v>
       </c>
       <c r="H72">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I72">
         <v>10</v>
@@ -7106,10 +7106,10 @@
         <v>79</v>
       </c>
       <c r="B73">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C73">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>41</v>
@@ -7118,7 +7118,7 @@
         <v>43</v>
       </c>
       <c r="F73">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G73">
         <v>36</v>
@@ -7130,7 +7130,7 @@
         <v>39</v>
       </c>
       <c r="J73">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K73">
         <v>44</v>
@@ -7200,7 +7200,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G75">
         <v>6</v>
@@ -7241,10 +7241,10 @@
         <v>45</v>
       </c>
       <c r="F76">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G76">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H76">
         <v>32</v>
@@ -7253,16 +7253,16 @@
         <v>68</v>
       </c>
       <c r="J76">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K76">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L76">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M76">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7273,7 +7273,7 @@
         <v>21</v>
       </c>
       <c r="C77">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D77">
         <v>22</v>
@@ -7288,13 +7288,13 @@
         <v>25</v>
       </c>
       <c r="H77">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I77">
         <v>27</v>
       </c>
       <c r="J77">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K77">
         <v>33</v>
@@ -7303,7 +7303,7 @@
         <v>20</v>
       </c>
       <c r="M77">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7311,7 +7311,7 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C78">
         <v>59</v>
@@ -7326,7 +7326,7 @@
         <v>36</v>
       </c>
       <c r="G78">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H78">
         <v>59</v>
@@ -7341,10 +7341,10 @@
         <v>64</v>
       </c>
       <c r="L78">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M78">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7352,40 +7352,40 @@
         <v>85</v>
       </c>
       <c r="B79">
+        <v>124</v>
+      </c>
+      <c r="C79">
+        <v>135</v>
+      </c>
+      <c r="D79">
+        <v>123</v>
+      </c>
+      <c r="E79">
+        <v>111</v>
+      </c>
+      <c r="F79">
+        <v>104</v>
+      </c>
+      <c r="G79">
+        <v>130</v>
+      </c>
+      <c r="H79">
+        <v>131</v>
+      </c>
+      <c r="I79">
+        <v>104</v>
+      </c>
+      <c r="J79">
+        <v>132</v>
+      </c>
+      <c r="K79">
         <v>122</v>
       </c>
-      <c r="C79">
-        <v>134</v>
-      </c>
-      <c r="D79">
-        <v>121</v>
-      </c>
-      <c r="E79">
-        <v>110</v>
-      </c>
-      <c r="F79">
-        <v>102</v>
-      </c>
-      <c r="G79">
-        <v>128</v>
-      </c>
-      <c r="H79">
-        <v>130</v>
-      </c>
-      <c r="I79">
-        <v>103</v>
-      </c>
-      <c r="J79">
-        <v>130</v>
-      </c>
-      <c r="K79">
-        <v>120</v>
-      </c>
       <c r="L79">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M79">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7396,7 +7396,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80">
         <v>14</v>
@@ -7405,7 +7405,7 @@
         <v>12</v>
       </c>
       <c r="F80">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G80">
         <v>14</v>
@@ -7423,7 +7423,7 @@
         <v>16</v>
       </c>
       <c r="L80">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M80">
         <v>12</v>
@@ -7513,37 +7513,37 @@
         <v>89</v>
       </c>
       <c r="B83">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D83">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E83">
         <v>64</v>
       </c>
       <c r="F83">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G83">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H83">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I83">
         <v>70</v>
       </c>
       <c r="J83">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K83">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L83">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M83">
         <v>80</v>
@@ -7563,10 +7563,10 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F84">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G84">
         <v>34</v>
@@ -7584,7 +7584,7 @@
         <v>33</v>
       </c>
       <c r="L84">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M84">
         <v>16</v>
@@ -7595,37 +7595,37 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C85">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D85">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E85">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F85">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G85">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H85">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I85">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J85">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K85">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L85">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M85">
         <v>152</v>
@@ -7639,7 +7639,7 @@
         <v>7</v>
       </c>
       <c r="C86">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D86">
         <v>15</v>
@@ -7660,16 +7660,16 @@
         <v>22</v>
       </c>
       <c r="J86">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K86">
         <v>30</v>
       </c>
       <c r="L86">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M86">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7721,13 +7721,13 @@
         <v>33</v>
       </c>
       <c r="C88">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D88">
         <v>47</v>
       </c>
       <c r="E88">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F88">
         <v>48</v>
@@ -7745,7 +7745,7 @@
         <v>34</v>
       </c>
       <c r="K88">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L88">
         <v>48</v>
@@ -7759,7 +7759,7 @@
         <v>95</v>
       </c>
       <c r="B89">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C89">
         <v>42</v>
@@ -7771,19 +7771,19 @@
         <v>33</v>
       </c>
       <c r="F89">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G89">
         <v>57</v>
       </c>
       <c r="H89">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I89">
         <v>32</v>
       </c>
       <c r="J89">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K89">
         <v>61</v>
@@ -7800,28 +7800,28 @@
         <v>96</v>
       </c>
       <c r="B90">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C90">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D90">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E90">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F90">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G90">
         <v>36</v>
       </c>
       <c r="H90">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I90">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J90">
         <v>49</v>
@@ -7847,7 +7847,7 @@
         <v>53</v>
       </c>
       <c r="D91">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E91">
         <v>46</v>
@@ -7856,25 +7856,25 @@
         <v>42</v>
       </c>
       <c r="G91">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H91">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I91">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J91">
         <v>60</v>
       </c>
       <c r="K91">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L91">
         <v>44</v>
       </c>
       <c r="M91">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7923,7 +7923,7 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C93">
         <v>27</v>
@@ -7932,7 +7932,7 @@
         <v>30</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F93">
         <v>20</v>
@@ -7967,16 +7967,16 @@
         <v>12</v>
       </c>
       <c r="C94">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D94">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E94">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F94">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G94">
         <v>28</v>
@@ -7991,7 +7991,7 @@
         <v>29</v>
       </c>
       <c r="K94">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L94">
         <v>44</v>
@@ -8008,19 +8008,19 @@
         <v>43</v>
       </c>
       <c r="C95">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D95">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E95">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F95">
         <v>67</v>
       </c>
       <c r="G95">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H95">
         <v>80</v>
@@ -8035,10 +8035,10 @@
         <v>78</v>
       </c>
       <c r="L95">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M95">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8049,37 +8049,37 @@
         <v>30</v>
       </c>
       <c r="C96">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D96">
+        <v>44</v>
+      </c>
+      <c r="E96">
+        <v>64</v>
+      </c>
+      <c r="F96">
         <v>43</v>
-      </c>
-      <c r="E96">
-        <v>63</v>
-      </c>
-      <c r="F96">
-        <v>42</v>
       </c>
       <c r="G96">
         <v>52</v>
       </c>
       <c r="H96">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I96">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J96">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K96">
         <v>64</v>
       </c>
       <c r="L96">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M96">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8090,7 +8090,7 @@
         <v>15</v>
       </c>
       <c r="C97">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D97">
         <v>39</v>
@@ -8111,13 +8111,13 @@
         <v>42</v>
       </c>
       <c r="J97">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K97">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L97">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M97">
         <v>24</v>
@@ -8128,7 +8128,7 @@
         <v>104</v>
       </c>
       <c r="B98">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C98">
         <v>23</v>
@@ -8140,7 +8140,7 @@
         <v>26</v>
       </c>
       <c r="F98">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G98">
         <v>18</v>
@@ -8152,13 +8152,13 @@
         <v>27</v>
       </c>
       <c r="J98">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K98">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L98">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M98">
         <v>22</v>
@@ -8169,28 +8169,28 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C99">
         <v>62</v>
       </c>
       <c r="D99">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E99">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F99">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G99">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H99">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I99">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J99">
         <v>53</v>
@@ -8199,7 +8199,7 @@
         <v>83</v>
       </c>
       <c r="L99">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M99">
         <v>69</v>
@@ -8251,40 +8251,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>3337</v>
+        <v>3400</v>
       </c>
       <c r="C101">
-        <v>4380</v>
+        <v>4454</v>
       </c>
       <c r="D101">
-        <v>4618</v>
+        <v>4671</v>
       </c>
       <c r="E101">
-        <v>4156</v>
+        <v>4207</v>
       </c>
       <c r="F101">
-        <v>3717</v>
+        <v>3782</v>
       </c>
       <c r="G101">
-        <v>4112</v>
+        <v>4165</v>
       </c>
       <c r="H101">
-        <v>3828</v>
+        <v>3909</v>
       </c>
       <c r="I101">
-        <v>3993</v>
+        <v>4039</v>
       </c>
       <c r="J101">
-        <v>4470</v>
+        <v>4535</v>
       </c>
       <c r="K101">
-        <v>4523</v>
+        <v>4595</v>
       </c>
       <c r="L101">
-        <v>3447</v>
+        <v>3510</v>
       </c>
       <c r="M101">
-        <v>3114</v>
+        <v>3165</v>
       </c>
     </row>
   </sheetData>
@@ -8504,7 +8504,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>14</v>
@@ -8513,13 +8513,13 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -8618,7 +8618,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>23</v>
@@ -8627,10 +8627,10 @@
         <v>16</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -8645,7 +8645,7 @@
         <v>19</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -8659,7 +8659,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7">
         <v>51</v>
@@ -8668,13 +8668,13 @@
         <v>30</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>41</v>
@@ -8686,7 +8686,7 @@
         <v>49</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -8763,7 +8763,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>37</v>
@@ -8778,16 +8778,16 @@
         <v>37</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K2">
         <v>54</v>
@@ -8796,7 +8796,7 @@
         <v>40</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8804,10 +8804,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3">
         <v>71</v>
@@ -8816,19 +8816,19 @@
         <v>52</v>
       </c>
       <c r="F3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3">
         <v>53</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K3">
         <v>55</v>
@@ -8837,7 +8837,7 @@
         <v>33</v>
       </c>
       <c r="M3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8875,7 +8875,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -8910,13 +8910,13 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8924,25 +8924,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6">
         <v>73</v>
       </c>
       <c r="E6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>72</v>
       </c>
       <c r="H6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I6">
         <v>54</v>
@@ -8965,40 +8965,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D7">
         <v>189</v>
       </c>
       <c r="E7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -9102,7 +9102,7 @@
         <v>12</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M2">
         <v>7</v>
@@ -9125,7 +9125,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -9215,7 +9215,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -9256,10 +9256,10 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>34</v>
@@ -9277,7 +9277,7 @@
         <v>33</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M7">
         <v>16</v>
@@ -9375,7 +9375,7 @@
         <v>5</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -9488,7 +9488,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -9529,7 +9529,7 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -9544,7 +9544,7 @@
         <v>16</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -9639,7 +9639,7 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>13</v>
@@ -9651,10 +9651,10 @@
         <v>15</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>22</v>
@@ -9671,7 +9671,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -9686,10 +9686,10 @@
         <v>13</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3">
         <v>13</v>
@@ -9701,7 +9701,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9718,7 +9718,7 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9730,7 +9730,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -9782,10 +9782,10 @@
         <v>68</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>23</v>
@@ -9794,10 +9794,10 @@
         <v>43</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>32</v>
@@ -9814,37 +9814,37 @@
         <v>47</v>
       </c>
       <c r="C7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>65</v>
       </c>
       <c r="E7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L7">
         <v>69</v>
       </c>
       <c r="M7">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -9921,10 +9921,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2">
         <v>65</v>
@@ -9933,22 +9933,22 @@
         <v>56</v>
       </c>
       <c r="G2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>67</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2">
         <v>55</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M2">
         <v>54</v>
@@ -9959,37 +9959,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G3">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M3">
         <v>65</v>
@@ -10018,7 +10018,7 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -10027,7 +10027,7 @@
         <v>13</v>
       </c>
       <c r="K4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -10082,40 +10082,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6">
         <v>57</v>
       </c>
       <c r="G6">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H6">
         <v>56</v>
       </c>
       <c r="I6">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>63</v>
       </c>
       <c r="K6">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10123,40 +10123,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>224</v>
+      </c>
+      <c r="C7">
+        <v>282</v>
+      </c>
+      <c r="D7">
+        <v>277</v>
+      </c>
+      <c r="E7">
+        <v>220</v>
+      </c>
+      <c r="F7">
+        <v>223</v>
+      </c>
+      <c r="G7">
+        <v>272</v>
+      </c>
+      <c r="H7">
+        <v>238</v>
+      </c>
+      <c r="I7">
+        <v>261</v>
+      </c>
+      <c r="J7">
+        <v>252</v>
+      </c>
+      <c r="K7">
         <v>221</v>
       </c>
-      <c r="C7">
-        <v>277</v>
-      </c>
-      <c r="D7">
-        <v>274</v>
-      </c>
-      <c r="E7">
-        <v>217</v>
-      </c>
-      <c r="F7">
-        <v>220</v>
-      </c>
-      <c r="G7">
-        <v>264</v>
-      </c>
-      <c r="H7">
-        <v>231</v>
-      </c>
-      <c r="I7">
-        <v>257</v>
-      </c>
-      <c r="J7">
-        <v>250</v>
-      </c>
-      <c r="K7">
-        <v>216</v>
-      </c>
       <c r="L7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -10236,7 +10236,7 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -10295,10 +10295,10 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3">
         <v>13</v>
@@ -10318,10 +10318,10 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -10373,28 +10373,28 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>15</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6">
         <v>25</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6">
         <v>20</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>19</v>
@@ -10411,31 +10411,31 @@
         <v>58</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>35</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7">
         <v>43</v>
       </c>
       <c r="I7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M7">
         <v>47</v>
@@ -10512,19 +10512,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>18</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>24</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G2">
         <v>31</v>
@@ -10533,16 +10533,16 @@
         <v>23</v>
       </c>
       <c r="I2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2">
         <v>33</v>
@@ -10556,7 +10556,7 @@
         <v>22</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -10565,10 +10565,10 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3">
         <v>34</v>
@@ -10577,16 +10577,16 @@
         <v>24</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3">
         <v>36</v>
       </c>
       <c r="L3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10594,7 +10594,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -10650,7 +10650,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -10676,13 +10676,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>51</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>31</v>
@@ -10691,7 +10691,7 @@
         <v>35</v>
       </c>
       <c r="G6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6">
         <v>34</v>
@@ -10703,7 +10703,7 @@
         <v>64</v>
       </c>
       <c r="K6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>33</v>
@@ -10717,40 +10717,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7">
         <v>86</v>
       </c>
       <c r="F7">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L7">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -10842,7 +10842,7 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -10868,7 +10868,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -10906,7 +10906,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -11014,10 +11014,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -11032,7 +11032,7 @@
         <v>40</v>
       </c>
       <c r="H7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7">
         <v>32</v>
@@ -11133,7 +11133,7 @@
         <v>8</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -11174,7 +11174,7 @@
         <v>14</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -11189,7 +11189,7 @@
         <v>17</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -11224,7 +11224,7 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -11233,7 +11233,7 @@
         <v>11</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -11253,7 +11253,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11273,10 +11273,10 @@
         <v>18</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6">
         <v>14</v>
@@ -11288,13 +11288,13 @@
         <v>42</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6">
         <v>20</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11314,10 +11314,10 @@
         <v>45</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>32</v>
@@ -11326,16 +11326,16 @@
         <v>68</v>
       </c>
       <c r="J7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -11436,7 +11436,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -11491,7 +11491,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -11573,7 +11573,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -11587,7 +11587,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -11614,7 +11614,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -11721,7 +11721,7 @@
         <v>13</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -11782,7 +11782,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -11840,7 +11840,7 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -11855,10 +11855,10 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -11878,10 +11878,10 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>22</v>
@@ -11896,10 +11896,10 @@
         <v>31</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L7">
         <v>24</v>
@@ -11979,7 +11979,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -12006,13 +12006,13 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12020,7 +12020,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -12104,6 +12104,9 @@
       <c r="I5">
         <v>1</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -12116,7 +12119,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -12151,13 +12154,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>29</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>26</v>
@@ -12178,13 +12181,13 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L7">
+        <v>14</v>
+      </c>
+      <c r="M7">
         <v>13</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12258,7 +12261,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>33</v>
@@ -12270,13 +12273,13 @@
         <v>34</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <v>34</v>
@@ -12285,13 +12288,13 @@
         <v>33</v>
       </c>
       <c r="K2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L2">
         <v>28</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12299,25 +12302,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3">
         <v>46</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3">
         <v>51</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -12326,7 +12329,7 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L3">
         <v>25</v>
@@ -12349,7 +12352,7 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>14</v>
@@ -12402,7 +12405,7 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -12422,7 +12425,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>77</v>
@@ -12431,22 +12434,22 @@
         <v>95</v>
       </c>
       <c r="E6">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I6">
         <v>30</v>
       </c>
       <c r="J6">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K6">
         <v>62</v>
@@ -12455,7 +12458,7 @@
         <v>47</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12463,40 +12466,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L7">
         <v>111</v>
       </c>
       <c r="M7">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -12654,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -12686,7 +12689,7 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -12930,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6">
         <v>11</v>
@@ -12971,7 +12974,7 @@
         <v>31</v>
       </c>
       <c r="I7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7">
         <v>29</v>
@@ -13113,7 +13116,7 @@
         <v>7</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3">
         <v>13</v>
@@ -13203,7 +13206,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>29</v>
@@ -13218,7 +13221,7 @@
         <v>15</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>35</v>
@@ -13233,10 +13236,10 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13244,7 +13247,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>59</v>
@@ -13259,7 +13262,7 @@
         <v>36</v>
       </c>
       <c r="G7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H7">
         <v>59</v>
@@ -13274,10 +13277,10 @@
         <v>64</v>
       </c>
       <c r="L7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M7">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -13372,7 +13375,7 @@
         <v>14</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2">
         <v>13</v>
@@ -13395,7 +13398,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -13410,7 +13413,7 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>11</v>
@@ -13419,10 +13422,10 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3">
         <v>15</v>
@@ -13500,7 +13503,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -13518,13 +13521,13 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6">
         <v>16</v>
@@ -13541,10 +13544,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>46</v>
@@ -13559,19 +13562,19 @@
         <v>38</v>
       </c>
       <c r="H7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7">
         <v>42</v>
@@ -13654,7 +13657,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -13681,7 +13684,7 @@
         <v>4</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13710,7 +13713,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -13814,7 +13817,7 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -13829,7 +13832,7 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>17</v>
@@ -13841,7 +13844,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -14064,7 +14067,7 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -14105,7 +14108,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -14212,13 +14215,13 @@
         <v>10</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2">
         <v>15</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M2">
         <v>5</v>
@@ -14247,19 +14250,19 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3">
         <v>14</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3">
         <v>12</v>
@@ -14387,19 +14390,19 @@
         <v>44</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
+        <v>44</v>
+      </c>
+      <c r="K7">
         <v>40</v>
       </c>
-      <c r="K7">
-        <v>39</v>
-      </c>
       <c r="L7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -14494,13 +14497,13 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>6</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <v>21</v>
@@ -14509,7 +14512,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14523,7 +14526,7 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>14</v>
@@ -14538,7 +14541,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>17</v>
@@ -14547,7 +14550,7 @@
         <v>8</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>7</v>
@@ -14570,7 +14573,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -14625,13 +14628,13 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>21</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -14666,37 +14669,37 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>64</v>
+      </c>
+      <c r="F7">
         <v>43</v>
-      </c>
-      <c r="E7">
-        <v>63</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
       </c>
       <c r="G7">
         <v>52</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K7">
         <v>64</v>
       </c>
       <c r="L7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -14803,7 +14806,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14829,7 +14832,7 @@
         <v>27</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>18</v>
@@ -14838,7 +14841,7 @@
         <v>26</v>
       </c>
       <c r="K3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -14861,7 +14864,7 @@
         <v>4</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -14919,7 +14922,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>13</v>
@@ -14934,7 +14937,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>13</v>
@@ -14946,7 +14949,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14960,7 +14963,7 @@
         <v>53</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>46</v>
@@ -14969,25 +14972,25 @@
         <v>42</v>
       </c>
       <c r="G7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>60</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>44</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -15319,19 +15322,19 @@
         <v>32</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2">
         <v>39</v>
       </c>
       <c r="I2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2">
         <v>36</v>
       </c>
       <c r="K2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2">
         <v>34</v>
@@ -15345,19 +15348,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>24</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3">
         <v>38</v>
@@ -15372,13 +15375,13 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15392,7 +15395,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -15410,7 +15413,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -15427,7 +15430,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -15474,19 +15477,19 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6">
         <v>46</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6">
         <v>34</v>
@@ -15509,40 +15512,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>135</v>
+      </c>
+      <c r="D7">
+        <v>123</v>
+      </c>
+      <c r="E7">
+        <v>111</v>
+      </c>
+      <c r="F7">
+        <v>104</v>
+      </c>
+      <c r="G7">
+        <v>130</v>
+      </c>
+      <c r="H7">
+        <v>131</v>
+      </c>
+      <c r="I7">
+        <v>104</v>
+      </c>
+      <c r="J7">
+        <v>132</v>
+      </c>
+      <c r="K7">
         <v>122</v>
       </c>
-      <c r="C7">
-        <v>134</v>
-      </c>
-      <c r="D7">
-        <v>121</v>
-      </c>
-      <c r="E7">
-        <v>110</v>
-      </c>
-      <c r="F7">
-        <v>102</v>
-      </c>
-      <c r="G7">
-        <v>128</v>
-      </c>
-      <c r="H7">
-        <v>130</v>
-      </c>
-      <c r="I7">
-        <v>103</v>
-      </c>
-      <c r="J7">
-        <v>130</v>
-      </c>
-      <c r="K7">
-        <v>120</v>
-      </c>
       <c r="L7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -15616,7 +15619,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -15739,7 +15742,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -15768,7 +15771,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -15803,13 +15806,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>26</v>
@@ -15931,19 +15934,19 @@
         <v>37</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2">
         <v>22</v>
       </c>
       <c r="K2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>27</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15960,19 +15963,19 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>27</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>33</v>
@@ -16016,7 +16019,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -16074,10 +16077,10 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>64</v>
@@ -16089,16 +16092,16 @@
         <v>44</v>
       </c>
       <c r="H6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L6">
         <v>32</v>
@@ -16115,37 +16118,37 @@
         <v>88</v>
       </c>
       <c r="C7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F7">
         <v>122</v>
       </c>
       <c r="G7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H7">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L7">
         <v>89</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -16228,13 +16231,13 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -16275,7 +16278,7 @@
         <v>7</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -16341,6 +16344,9 @@
       <c r="I5">
         <v>1</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -16365,7 +16371,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I6">
         <v>18</v>
@@ -16397,16 +16403,16 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>18</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I7">
         <v>33</v>
@@ -16415,7 +16421,7 @@
         <v>62</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L7">
         <v>27</v>
@@ -16497,6 +16503,9 @@
       <c r="B2">
         <v>2</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
@@ -16504,7 +16513,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -16542,10 +16551,10 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -16629,7 +16638,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -16638,16 +16647,16 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>12</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>11</v>
@@ -16739,7 +16748,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -16757,7 +16766,7 @@
         <v>13</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K2">
         <v>19</v>
@@ -16777,7 +16786,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -16786,7 +16795,7 @@
         <v>24</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -16801,13 +16810,13 @@
         <v>12</v>
       </c>
       <c r="K3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>14</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16833,7 +16842,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -16888,7 +16897,7 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -16903,7 +16912,7 @@
         <v>12</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>20</v>
@@ -16929,37 +16938,37 @@
         <v>49</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>54</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7">
         <v>43</v>
       </c>
       <c r="H7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7">
         <v>55</v>
       </c>
       <c r="J7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L7">
         <v>60</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -17121,7 +17130,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -17161,7 +17170,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -17202,7 +17211,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>27</v>
@@ -17211,7 +17220,7 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -17528,10 +17537,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>44</v>
@@ -17540,13 +17549,13 @@
         <v>35</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>26</v>
       </c>
       <c r="H2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I2">
         <v>40</v>
@@ -17569,19 +17578,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3">
         <v>44</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3">
         <v>43</v>
@@ -17596,10 +17605,10 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3">
         <v>28</v>
@@ -17722,7 +17731,7 @@
         <v>34</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17730,25 +17739,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E7">
         <v>151</v>
       </c>
       <c r="F7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G7">
         <v>116</v>
       </c>
       <c r="H7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I7">
         <v>129</v>
@@ -17757,13 +17766,13 @@
         <v>128</v>
       </c>
       <c r="K7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M7">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -17837,7 +17846,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -17861,13 +17870,13 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
         <v>8</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -17916,7 +17925,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -17989,7 +17998,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -18018,7 +18027,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>18</v>
@@ -18030,7 +18039,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -18042,13 +18051,13 @@
         <v>13</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7">
         <v>28</v>
       </c>
       <c r="L7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -18178,7 +18187,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -18216,7 +18225,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -18231,7 +18240,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -18265,13 +18274,13 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -18306,16 +18315,16 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>28</v>
@@ -18330,7 +18339,7 @@
         <v>29</v>
       </c>
       <c r="K7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L7">
         <v>44</v>
@@ -18413,7 +18422,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -18451,7 +18460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -18484,7 +18493,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18574,7 +18583,7 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18582,10 +18591,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -18615,7 +18624,7 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -18722,7 +18731,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18742,7 +18751,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -18853,7 +18862,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>14</v>
@@ -18862,7 +18871,7 @@
         <v>21</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -18888,13 +18897,13 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>16</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7">
         <v>31</v>
@@ -18903,13 +18912,13 @@
         <v>39</v>
       </c>
       <c r="K7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L7">
         <v>29</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -18983,10 +18992,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -19016,7 +19025,7 @@
         <v>8</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19042,7 +19051,7 @@
         <v>8</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -19138,7 +19147,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -19170,16 +19179,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>54</v>
       </c>
       <c r="E7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>35</v>
@@ -19188,7 +19197,7 @@
         <v>28</v>
       </c>
       <c r="H7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I7">
         <v>47</v>
@@ -19203,7 +19212,7 @@
         <v>22</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -19330,7 +19339,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -19402,7 +19411,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -19426,13 +19435,13 @@
         <v>18</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -19443,7 +19452,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>23</v>
@@ -19455,7 +19464,7 @@
         <v>26</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -19467,13 +19476,13 @@
         <v>27</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M7">
         <v>22</v>
@@ -19690,7 +19699,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -19731,7 +19740,7 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>23</v>
@@ -20349,7 +20358,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -20390,7 +20399,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -20485,13 +20494,13 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>21</v>
       </c>
       <c r="I2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2">
         <v>15</v>
@@ -20500,10 +20509,10 @@
         <v>30</v>
       </c>
       <c r="L2">
+        <v>19</v>
+      </c>
+      <c r="M2">
         <v>17</v>
-      </c>
-      <c r="M2">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20526,7 +20535,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -20538,10 +20547,10 @@
         <v>13</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>11</v>
@@ -20573,13 +20582,13 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -20628,13 +20637,13 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -20643,10 +20652,10 @@
         <v>15</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6">
         <v>41</v>
@@ -20669,34 +20678,34 @@
         <v>71</v>
       </c>
       <c r="D7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H7">
         <v>55</v>
       </c>
       <c r="I7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L7">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -20784,6 +20793,9 @@
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
@@ -20895,7 +20907,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -20981,7 +20993,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -20993,7 +21005,7 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -21022,16 +21034,16 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>9</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -21052,7 +21064,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21133,13 +21145,13 @@
         <v>11</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>16</v>
@@ -21168,19 +21180,19 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>29</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H7">
         <v>28</v>
@@ -21198,7 +21210,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -21272,10 +21284,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>15</v>
@@ -21284,7 +21296,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>15</v>
@@ -21296,7 +21308,7 @@
         <v>13</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2">
         <v>12</v>
@@ -21444,10 +21456,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -21456,7 +21468,7 @@
         <v>43</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>36</v>
@@ -21468,7 +21480,7 @@
         <v>39</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7">
         <v>44</v>
@@ -21658,7 +21670,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -21696,7 +21708,7 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -21797,7 +21809,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -21818,10 +21830,10 @@
         <v>11</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -21871,7 +21883,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21946,7 +21958,7 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>21</v>
@@ -21981,13 +21993,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>45</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>48</v>
@@ -22002,10 +22014,10 @@
         <v>36</v>
       </c>
       <c r="I7">
+        <v>46</v>
+      </c>
+      <c r="J7">
         <v>44</v>
-      </c>
-      <c r="J7">
-        <v>43</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -22014,7 +22026,7 @@
         <v>24</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -22112,7 +22124,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -22204,6 +22216,9 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
@@ -22249,10 +22264,10 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -22266,7 +22281,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>39</v>
@@ -22287,13 +22302,13 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -22624,10 +22639,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -22749,10 +22764,10 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -22853,13 +22868,13 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -22966,6 +22981,9 @@
       <c r="B5">
         <v>2</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5">
         <v>1</v>
       </c>
@@ -23002,7 +23020,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -23020,7 +23038,7 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6">
         <v>22</v>
@@ -23037,13 +23055,13 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>47</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>48</v>
@@ -23061,7 +23079,7 @@
         <v>34</v>
       </c>
       <c r="K7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7">
         <v>48</v>
@@ -23194,10 +23212,10 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -23211,7 +23229,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -23245,7 +23263,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -23274,7 +23292,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -23295,10 +23313,10 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -23393,7 +23411,7 @@
         <v>13</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -23428,13 +23446,13 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>15</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -23481,7 +23499,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>11</v>
@@ -23498,7 +23516,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -23518,7 +23536,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>22</v>
@@ -23559,7 +23577,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C7">
         <v>42</v>
@@ -23571,19 +23589,19 @@
         <v>33</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>57</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7">
         <v>32</v>
       </c>
       <c r="J7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7">
         <v>61</v>
@@ -23725,7 +23743,7 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -23737,7 +23755,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -23835,7 +23853,7 @@
         <v>12</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>17</v>
@@ -23847,7 +23865,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -23948,10 +23966,10 @@
         <v>9</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -24058,7 +24076,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>13</v>
@@ -24067,10 +24085,10 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>13</v>
@@ -24099,7 +24117,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>26</v>
@@ -24108,10 +24126,10 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>33</v>
@@ -24123,10 +24141,10 @@
         <v>39</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L7">
         <v>41</v>
@@ -24268,13 +24286,13 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>5</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -24288,7 +24306,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -24309,7 +24327,7 @@
         <v>16</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>15</v>
@@ -24359,7 +24377,7 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -24370,7 +24388,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -24391,16 +24409,16 @@
         <v>22</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -24611,7 +24629,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -24649,7 +24667,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -24747,7 +24765,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -24762,7 +24780,7 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>16</v>
@@ -24788,16 +24806,16 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>14</v>
@@ -24867,7 +24885,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -24902,16 +24920,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -24923,7 +24941,7 @@
         <v>13</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>23</v>
@@ -24943,28 +24961,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>36</v>
       </c>
       <c r="H7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7">
         <v>49</v>
@@ -25056,7 +25074,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -25100,7 +25118,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -25109,7 +25127,7 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -25214,7 +25232,7 @@
         <v>24</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -25240,10 +25258,10 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7">
         <v>43</v>
@@ -25252,10 +25270,10 @@
         <v>42</v>
       </c>
       <c r="H7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <v>59</v>
@@ -25353,7 +25371,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -25371,7 +25389,7 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -25440,6 +25458,9 @@
       <c r="K4">
         <v>2</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
       <c r="M4">
         <v>2</v>
       </c>
@@ -25484,7 +25505,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -25507,7 +25528,7 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -25525,7 +25546,7 @@
         <v>13</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -25632,7 +25653,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25795,7 +25816,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -25902,7 +25923,7 @@
         <v>8</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26074,7 +26095,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -26166,13 +26187,13 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -26204,7 +26225,7 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -26213,7 +26234,7 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -26230,7 +26251,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -26320,7 +26341,7 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -26335,16 +26356,16 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>51</v>
       </c>
       <c r="K7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>28</v>
@@ -26427,13 +26448,13 @@
         <v>41</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>29</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>36</v>
@@ -26445,13 +26466,13 @@
         <v>54</v>
       </c>
       <c r="I2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L2">
         <v>45</v>
@@ -26465,28 +26486,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3">
         <v>67</v>
@@ -26495,7 +26516,7 @@
         <v>74</v>
       </c>
       <c r="L3">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M3">
         <v>72</v>
@@ -26524,10 +26545,10 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -26536,7 +26557,7 @@
         <v>13</v>
       </c>
       <c r="L4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -26588,7 +26609,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>54</v>
@@ -26609,16 +26630,16 @@
         <v>55</v>
       </c>
       <c r="I6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M6">
         <v>24</v>
@@ -26629,37 +26650,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L7">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M7">
         <v>152</v>
@@ -26763,13 +26784,13 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26876,10 +26897,10 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -26914,10 +26935,10 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -26926,13 +26947,13 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>10</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -27015,7 +27036,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -27030,7 +27051,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -27053,7 +27074,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -27122,7 +27143,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -27163,16 +27184,16 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>9</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -27187,7 +27208,7 @@
         <v>18</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -27279,7 +27300,7 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -27393,7 +27414,7 @@
         <v>12</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -27434,7 +27455,7 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -27757,7 +27778,7 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>9</v>
@@ -27783,7 +27804,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -27836,13 +27857,13 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -27920,7 +27941,7 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>22</v>
@@ -27935,13 +27956,13 @@
         <v>25</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>27</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7">
         <v>33</v>
@@ -27950,7 +27971,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -28030,7 +28051,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -28145,7 +28166,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -28269,7 +28290,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -28315,7 +28336,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -28356,10 +28377,10 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -28556,7 +28577,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -28565,7 +28586,7 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -28580,7 +28601,7 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -28594,7 +28615,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>14</v>
@@ -28603,7 +28624,7 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -28621,7 +28642,7 @@
         <v>16</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -28908,7 +28929,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -28920,7 +28941,7 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -28977,6 +28998,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -29047,13 +29071,13 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -29065,7 +29089,7 @@
         <v>4</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7">
         <v>8</v>
@@ -29154,7 +29178,7 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>25</v>
@@ -29198,16 +29222,16 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>24</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I3">
         <v>30</v>
@@ -29216,13 +29240,13 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29271,7 +29295,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -29312,16 +29336,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>51</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>31</v>
@@ -29333,13 +29357,13 @@
         <v>28</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>38</v>
       </c>
       <c r="K6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6">
         <v>15</v>
@@ -29353,40 +29377,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>116</v>
       </c>
       <c r="D7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7">
         <v>77</v>
       </c>
       <c r="H7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7">
         <v>98</v>
       </c>
       <c r="K7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M7">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -29559,7 +29583,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -29568,7 +29592,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -29600,7 +29624,7 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -29609,7 +29633,7 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -29716,7 +29740,7 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -29826,7 +29850,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -29867,7 +29891,7 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -30532,13 +30556,13 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>7</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -30573,13 +30597,13 @@
         <v>15</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>9</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>2</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="C2">
-        <v>833</v>
+        <v>852</v>
       </c>
       <c r="D2">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="E2">
-        <v>916</v>
+        <v>937</v>
       </c>
       <c r="F2">
-        <v>921</v>
+        <v>937</v>
       </c>
       <c r="G2">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="H2">
-        <v>1054</v>
+        <v>1070</v>
       </c>
       <c r="I2">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="J2">
-        <v>1187</v>
+        <v>1201</v>
       </c>
       <c r="K2">
-        <v>1328</v>
+        <v>1337</v>
       </c>
       <c r="L2">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="M2">
-        <v>963</v>
+        <v>978</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="C3">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="D3">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="E3">
-        <v>1079</v>
+        <v>1101</v>
       </c>
       <c r="F3">
-        <v>1111</v>
+        <v>1128</v>
       </c>
       <c r="G3">
-        <v>1218</v>
+        <v>1233</v>
       </c>
       <c r="H3">
-        <v>1083</v>
+        <v>1109</v>
       </c>
       <c r="I3">
-        <v>1095</v>
+        <v>1112</v>
       </c>
       <c r="J3">
-        <v>1258</v>
+        <v>1275</v>
       </c>
       <c r="K3">
-        <v>1258</v>
+        <v>1282</v>
       </c>
       <c r="L3">
-        <v>1056</v>
+        <v>1073</v>
       </c>
       <c r="M3">
-        <v>1068</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C4">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D4">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E4">
+        <v>391</v>
+      </c>
+      <c r="F4">
         <v>385</v>
       </c>
-      <c r="F4">
-        <v>377</v>
-      </c>
       <c r="G4">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="H4">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I4">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J4">
+        <v>343</v>
+      </c>
+      <c r="K4">
         <v>340</v>
       </c>
-      <c r="K4">
-        <v>332</v>
-      </c>
       <c r="L4">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M4">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,25 +994,25 @@
         <v>61</v>
       </c>
       <c r="C5">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E5">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I5">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J5">
         <v>96</v>
@@ -1021,10 +1021,10 @@
         <v>80</v>
       </c>
       <c r="L5">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1429</v>
+        <v>1446</v>
       </c>
       <c r="C6">
-        <v>1964</v>
+        <v>1987</v>
       </c>
       <c r="D6">
-        <v>2061</v>
+        <v>2086</v>
       </c>
       <c r="E6">
-        <v>1734</v>
+        <v>1766</v>
       </c>
       <c r="F6">
-        <v>1319</v>
+        <v>1333</v>
       </c>
       <c r="G6">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="H6">
-        <v>1366</v>
+        <v>1382</v>
       </c>
       <c r="I6">
-        <v>1477</v>
+        <v>1489</v>
       </c>
       <c r="J6">
-        <v>1654</v>
+        <v>1676</v>
       </c>
       <c r="K6">
-        <v>1597</v>
+        <v>1622</v>
       </c>
       <c r="L6">
-        <v>1045</v>
+        <v>1061</v>
       </c>
       <c r="M6">
-        <v>776</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3400</v>
+        <v>3451</v>
       </c>
       <c r="C7">
-        <v>4454</v>
+        <v>4512</v>
       </c>
       <c r="D7">
-        <v>4671</v>
+        <v>4726</v>
       </c>
       <c r="E7">
-        <v>4207</v>
+        <v>4291</v>
       </c>
       <c r="F7">
-        <v>3782</v>
+        <v>3838</v>
       </c>
       <c r="G7">
-        <v>4165</v>
+        <v>4206</v>
       </c>
       <c r="H7">
-        <v>3909</v>
+        <v>3974</v>
       </c>
       <c r="I7">
-        <v>4039</v>
+        <v>4086</v>
       </c>
       <c r="J7">
-        <v>4535</v>
+        <v>4591</v>
       </c>
       <c r="K7">
-        <v>4595</v>
+        <v>4661</v>
       </c>
       <c r="L7">
-        <v>3510</v>
+        <v>3578</v>
       </c>
       <c r="M7">
-        <v>3165</v>
+        <v>3224</v>
       </c>
     </row>
   </sheetData>
@@ -1220,6 +1220,9 @@
       <c r="B3">
         <v>3</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1337,7 +1340,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1361,7 +1364,7 @@
         <v>12</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1579,7 +1582,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>16</v>
@@ -1614,7 +1617,7 @@
         <v>11</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -1646,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1698,13 +1701,13 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -1719,7 +1722,7 @@
         <v>27</v>
       </c>
       <c r="K6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>16</v>
@@ -1739,28 +1742,28 @@
         <v>63</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
         <v>47</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L7">
         <v>42</v>
@@ -1843,16 +1846,16 @@
         <v>48</v>
       </c>
       <c r="C2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2">
         <v>78</v>
@@ -1864,16 +1867,16 @@
         <v>67</v>
       </c>
       <c r="J2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1884,13 +1887,13 @@
         <v>47</v>
       </c>
       <c r="C3">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -1902,19 +1905,19 @@
         <v>76</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <v>94</v>
       </c>
       <c r="K3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1931,7 +1934,7 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -1943,7 +1946,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4">
         <v>19</v>
@@ -1952,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="L4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4">
         <v>16</v>
@@ -1966,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -1975,7 +1978,7 @@
         <v>12</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1993,7 +1996,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -2004,28 +2007,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D6">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E6">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F6">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G6">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H6">
         <v>88</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J6">
         <v>71</v>
@@ -2034,10 +2037,10 @@
         <v>83</v>
       </c>
       <c r="L6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M6">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2045,40 +2048,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H7">
         <v>265</v>
       </c>
       <c r="I7">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="M7">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2152,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -2164,7 +2167,7 @@
         <v>14</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>18</v>
@@ -2173,7 +2176,7 @@
         <v>25</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2">
         <v>31</v>
@@ -2182,7 +2185,7 @@
         <v>42</v>
       </c>
       <c r="L2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2">
         <v>24</v>
@@ -2193,7 +2196,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -2211,7 +2214,7 @@
         <v>22</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3">
         <v>27</v>
@@ -2220,10 +2223,10 @@
         <v>36</v>
       </c>
       <c r="K3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3">
         <v>35</v>
@@ -2246,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2258,13 +2261,13 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -2316,7 +2319,7 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>25</v>
@@ -2328,16 +2331,16 @@
         <v>12</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>13</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6">
         <v>16</v>
@@ -2351,37 +2354,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>91</v>
       </c>
       <c r="D7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7">
         <v>64</v>
       </c>
       <c r="F7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>57</v>
       </c>
       <c r="H7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M7">
         <v>80</v>
@@ -2464,7 +2467,7 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>49</v>
@@ -2476,10 +2479,10 @@
         <v>35</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2">
         <v>45</v>
@@ -2488,7 +2491,7 @@
         <v>54</v>
       </c>
       <c r="L2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2">
         <v>27</v>
@@ -2499,16 +2502,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>67</v>
@@ -2517,22 +2520,22 @@
         <v>73</v>
       </c>
       <c r="H3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2558,10 +2561,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -2622,28 +2625,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D6">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6">
         <v>103</v>
       </c>
       <c r="H6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I6">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6">
         <v>77</v>
@@ -2655,7 +2658,7 @@
         <v>55</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2663,40 +2666,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G7">
         <v>235</v>
       </c>
       <c r="H7">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M7">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2770,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>16</v>
@@ -2779,7 +2782,7 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>25</v>
@@ -2788,7 +2791,7 @@
         <v>19</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2">
         <v>23</v>
@@ -2800,7 +2803,7 @@
         <v>28</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>18</v>
@@ -2829,7 +2832,7 @@
         <v>23</v>
       </c>
       <c r="H3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3">
         <v>20</v>
@@ -2844,7 +2847,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2934,7 +2937,7 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -2943,7 +2946,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>12</v>
@@ -2969,25 +2972,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>67</v>
       </c>
       <c r="D7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7">
         <v>67</v>
       </c>
       <c r="G7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7">
         <v>65</v>
@@ -2999,10 +3002,10 @@
         <v>78</v>
       </c>
       <c r="L7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3085,19 +3088,19 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>39</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2">
         <v>41</v>
@@ -3117,7 +3120,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>41</v>
@@ -3141,16 +3144,16 @@
         <v>36</v>
       </c>
       <c r="J3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3173,7 +3176,7 @@
         <v>8</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -3226,7 +3229,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3240,7 +3243,7 @@
         <v>62</v>
       </c>
       <c r="D6">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E6">
         <v>39</v>
@@ -3255,13 +3258,13 @@
         <v>27</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6">
         <v>36</v>
@@ -3275,40 +3278,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7">
         <v>145</v>
       </c>
       <c r="D7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F7">
         <v>120</v>
       </c>
       <c r="G7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H7">
         <v>129</v>
       </c>
       <c r="I7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3382,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>19</v>
@@ -3391,10 +3394,10 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -3415,7 +3418,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3432,7 +3435,7 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>23</v>
@@ -3447,16 +3450,16 @@
         <v>26</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3">
         <v>20</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3485,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -3534,16 +3537,19 @@
       <c r="L5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>37</v>
@@ -3558,7 +3564,7 @@
         <v>20</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>43</v>
@@ -3581,40 +3587,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7">
         <v>99</v>
       </c>
       <c r="E7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>67</v>
       </c>
       <c r="H7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7">
         <v>72</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3694,10 +3700,10 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -3706,7 +3712,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2">
         <v>22</v>
@@ -3721,7 +3727,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3729,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -3738,7 +3744,7 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -3753,10 +3759,10 @@
         <v>25</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3">
         <v>26</v>
@@ -3846,10 +3852,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>43</v>
@@ -3879,7 +3885,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3887,16 +3893,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7">
         <v>73</v>
@@ -3905,16 +3911,16 @@
         <v>78</v>
       </c>
       <c r="H7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7">
         <v>75</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L7">
         <v>55</v>
@@ -4107,7 +4113,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4119,7 +4125,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -4148,7 +4154,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -4160,7 +4166,7 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <v>14</v>
@@ -4258,7 +4264,7 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>22</v>
@@ -4279,10 +4285,10 @@
         <v>30</v>
       </c>
       <c r="L2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4302,7 +4308,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -4343,7 +4349,7 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -4352,7 +4358,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4">
         <v>22</v>
@@ -4361,10 +4367,10 @@
         <v>19</v>
       </c>
       <c r="L4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4375,7 +4381,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>19</v>
@@ -4384,13 +4390,13 @@
         <v>12</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>12</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>17</v>
@@ -4413,7 +4419,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -4422,10 +4428,10 @@
         <v>63</v>
       </c>
       <c r="E6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>44</v>
@@ -4446,7 +4452,7 @@
         <v>24</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4454,16 +4460,16 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C7">
+        <v>173</v>
+      </c>
+      <c r="D7">
         <v>170</v>
       </c>
-      <c r="D7">
-        <v>166</v>
-      </c>
       <c r="E7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>130</v>
@@ -4472,19 +4478,19 @@
         <v>116</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J7">
         <v>128</v>
       </c>
       <c r="K7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M7">
         <v>92</v>
@@ -4495,40 +4501,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D8">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E8">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F8">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H8">
         <v>265</v>
       </c>
       <c r="I8">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K8">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L8">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="M8">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4545,7 +4551,7 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>24</v>
@@ -4554,13 +4560,13 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I9">
         <v>25</v>
       </c>
       <c r="J9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K9">
         <v>23</v>
@@ -4569,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4586,10 +4592,10 @@
         <v>42</v>
       </c>
       <c r="E10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>32</v>
@@ -4604,7 +4610,7 @@
         <v>29</v>
       </c>
       <c r="K10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10">
         <v>23</v>
@@ -4618,37 +4624,37 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11">
         <v>87</v>
       </c>
       <c r="E11">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F11">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>70</v>
       </c>
       <c r="H11">
+        <v>57</v>
+      </c>
+      <c r="I11">
+        <v>75</v>
+      </c>
+      <c r="J11">
         <v>55</v>
       </c>
-      <c r="I11">
-        <v>74</v>
-      </c>
-      <c r="J11">
-        <v>53</v>
-      </c>
       <c r="K11">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L11">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M11">
         <v>44</v>
@@ -4718,13 +4724,13 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>8</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>3</v>
@@ -4735,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>25</v>
@@ -4744,7 +4750,7 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -4762,7 +4768,7 @@
         <v>17</v>
       </c>
       <c r="K14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L14">
         <v>13</v>
@@ -4776,10 +4782,10 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15">
         <v>54</v>
@@ -4797,16 +4803,16 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M15">
         <v>36</v>
@@ -4841,13 +4847,13 @@
         <v>15</v>
       </c>
       <c r="J16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
         <v>9</v>
-      </c>
-      <c r="L16">
-        <v>8</v>
       </c>
       <c r="M16">
         <v>2</v>
@@ -4870,13 +4876,13 @@
         <v>4</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>12</v>
       </c>
       <c r="H17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17">
         <v>4</v>
@@ -4908,7 +4914,7 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F18">
         <v>18</v>
@@ -4917,19 +4923,19 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I18">
         <v>33</v>
       </c>
       <c r="J18">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K18">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M18">
         <v>20</v>
@@ -4940,40 +4946,40 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C19">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E19">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F19">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G19">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I19">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J19">
         <v>160</v>
       </c>
       <c r="K19">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L19">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4981,25 +4987,25 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <v>97</v>
       </c>
       <c r="D20">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E20">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F20">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G20">
         <v>97</v>
       </c>
       <c r="H20">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I20">
         <v>116</v>
@@ -5011,7 +5017,7 @@
         <v>110</v>
       </c>
       <c r="L20">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M20">
         <v>90</v>
@@ -5022,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21">
         <v>16</v>
@@ -5107,7 +5113,7 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D23">
         <v>51</v>
@@ -5119,10 +5125,10 @@
         <v>36</v>
       </c>
       <c r="G23">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -5131,7 +5137,7 @@
         <v>44</v>
       </c>
       <c r="K23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L23">
         <v>38</v>
@@ -5151,7 +5157,7 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>14</v>
@@ -5219,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="M25">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5257,7 +5263,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -5283,25 +5289,25 @@
         <v>28</v>
       </c>
       <c r="G27">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <v>39</v>
       </c>
       <c r="J27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K27">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L27">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M27">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5341,40 +5347,40 @@
         <v>35</v>
       </c>
       <c r="B29">
+        <v>229</v>
+      </c>
+      <c r="C29">
+        <v>287</v>
+      </c>
+      <c r="D29">
+        <v>281</v>
+      </c>
+      <c r="E29">
         <v>224</v>
       </c>
-      <c r="C29">
-        <v>282</v>
-      </c>
-      <c r="D29">
-        <v>277</v>
-      </c>
-      <c r="E29">
-        <v>220</v>
-      </c>
       <c r="F29">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="G29">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H29">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I29">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J29">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K29">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L29">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M29">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5388,7 +5394,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30">
         <v>14</v>
@@ -5400,7 +5406,7 @@
         <v>14</v>
       </c>
       <c r="H30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30">
         <v>14</v>
@@ -5423,16 +5429,16 @@
         <v>37</v>
       </c>
       <c r="B31">
+        <v>33</v>
+      </c>
+      <c r="C31">
+        <v>63</v>
+      </c>
+      <c r="D31">
+        <v>52</v>
+      </c>
+      <c r="E31">
         <v>31</v>
-      </c>
-      <c r="C31">
-        <v>62</v>
-      </c>
-      <c r="D31">
-        <v>51</v>
-      </c>
-      <c r="E31">
-        <v>30</v>
       </c>
       <c r="F31">
         <v>42</v>
@@ -5450,10 +5456,10 @@
         <v>28</v>
       </c>
       <c r="K31">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M31">
         <v>32</v>
@@ -5505,40 +5511,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C33">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D33">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E33">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F33">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G33">
         <v>235</v>
       </c>
       <c r="H33">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I33">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J33">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K33">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L33">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M33">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5558,7 +5564,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34">
         <v>22</v>
@@ -5573,7 +5579,7 @@
         <v>32</v>
       </c>
       <c r="K34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L34">
         <v>21</v>
@@ -5628,22 +5634,22 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D36">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E36">
         <v>54</v>
       </c>
       <c r="F36">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H36">
         <v>75</v>
@@ -5655,7 +5661,7 @@
         <v>67</v>
       </c>
       <c r="K36">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L36">
         <v>60</v>
@@ -5669,40 +5675,40 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C37">
         <v>145</v>
       </c>
       <c r="D37">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E37">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F37">
         <v>120</v>
       </c>
       <c r="G37">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H37">
         <v>129</v>
       </c>
       <c r="I37">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J37">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K37">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L37">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M37">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5798,7 +5804,7 @@
         <v>9</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>11</v>
@@ -5833,7 +5839,7 @@
         <v>15</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H41">
         <v>14</v>
@@ -5845,7 +5851,7 @@
         <v>28</v>
       </c>
       <c r="K41">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L41">
         <v>14</v>
@@ -5859,40 +5865,40 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C42">
         <v>178</v>
       </c>
       <c r="D42">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E42">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F42">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G42">
         <v>150</v>
       </c>
       <c r="H42">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I42">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J42">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K42">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L42">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M42">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5903,7 +5909,7 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43">
         <v>19</v>
@@ -5918,7 +5924,7 @@
         <v>32</v>
       </c>
       <c r="H43">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I43">
         <v>36</v>
@@ -5944,19 +5950,19 @@
         <v>39</v>
       </c>
       <c r="C44">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D44">
         <v>41</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F44">
         <v>24</v>
       </c>
       <c r="G44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H44">
         <v>41</v>
@@ -5965,7 +5971,7 @@
         <v>32</v>
       </c>
       <c r="J44">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K44">
         <v>44</v>
@@ -6050,7 +6056,7 @@
         <v>17</v>
       </c>
       <c r="K46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L46">
         <v>9</v>
@@ -6076,10 +6082,10 @@
         <v>21</v>
       </c>
       <c r="F47">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G47">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47">
         <v>34</v>
@@ -6088,13 +6094,13 @@
         <v>31</v>
       </c>
       <c r="J47">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K47">
         <v>34</v>
       </c>
       <c r="L47">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M47">
         <v>20</v>
@@ -6105,7 +6111,7 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C48">
         <v>58</v>
@@ -6114,31 +6120,31 @@
         <v>42</v>
       </c>
       <c r="E48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F48">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G48">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H48">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I48">
         <v>36</v>
       </c>
       <c r="J48">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K48">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L48">
         <v>54</v>
       </c>
       <c r="M48">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6155,7 +6161,7 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F49">
         <v>17</v>
@@ -6170,16 +6176,16 @@
         <v>16</v>
       </c>
       <c r="J49">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K49">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L49">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M49">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6190,16 +6196,16 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D50">
         <v>31</v>
       </c>
       <c r="E50">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F50">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G50">
         <v>18</v>
@@ -6214,13 +6220,13 @@
         <v>24</v>
       </c>
       <c r="K50">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L50">
         <v>24</v>
       </c>
       <c r="M50">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6234,13 +6240,13 @@
         <v>38</v>
       </c>
       <c r="D51">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E51">
         <v>47</v>
       </c>
       <c r="F51">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G51">
         <v>42</v>
@@ -6255,13 +6261,13 @@
         <v>59</v>
       </c>
       <c r="K51">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L51">
         <v>48</v>
       </c>
       <c r="M51">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6269,40 +6275,40 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C52">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D52">
         <v>108</v>
       </c>
       <c r="E52">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F52">
         <v>86</v>
       </c>
       <c r="G52">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H52">
         <v>67</v>
       </c>
       <c r="I52">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J52">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K52">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L52">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M52">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6316,28 +6322,28 @@
         <v>63</v>
       </c>
       <c r="D53">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E53">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F53">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G53">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H53">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I53">
         <v>47</v>
       </c>
       <c r="J53">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K53">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L53">
         <v>42</v>
@@ -6357,34 +6363,34 @@
         <v>64</v>
       </c>
       <c r="D54">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E54">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F54">
         <v>72</v>
       </c>
       <c r="G54">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H54">
         <v>40</v>
       </c>
       <c r="I54">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J54">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K54">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L54">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M54">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6392,16 +6398,16 @@
         <v>61</v>
       </c>
       <c r="B55">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C55">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D55">
         <v>46</v>
       </c>
       <c r="E55">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F55">
         <v>31</v>
@@ -6416,10 +6422,10 @@
         <v>46</v>
       </c>
       <c r="J55">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K55">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L55">
         <v>40</v>
@@ -6474,7 +6480,7 @@
         <v>63</v>
       </c>
       <c r="B57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -6492,7 +6498,7 @@
         <v>9</v>
       </c>
       <c r="H57">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I57">
         <v>13</v>
@@ -6521,7 +6527,7 @@
         <v>4</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58">
         <v>2</v>
@@ -6591,16 +6597,16 @@
         <v>66</v>
       </c>
       <c r="B60">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C60">
         <v>25</v>
       </c>
       <c r="D60">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E60">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F60">
         <v>22</v>
@@ -6624,7 +6630,7 @@
         <v>20</v>
       </c>
       <c r="M60">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6708,13 +6714,13 @@
         <v>99</v>
       </c>
       <c r="E63">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F63">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G63">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H63">
         <v>55</v>
@@ -6732,7 +6738,7 @@
         <v>14</v>
       </c>
       <c r="M63">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6749,13 +6755,13 @@
         <v>15</v>
       </c>
       <c r="E64">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F64">
         <v>19</v>
       </c>
       <c r="G64">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H64">
         <v>19</v>
@@ -6767,7 +6773,7 @@
         <v>26</v>
       </c>
       <c r="K64">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L64">
         <v>29</v>
@@ -6781,40 +6787,40 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C65">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D65">
         <v>99</v>
       </c>
       <c r="E65">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F65">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G65">
         <v>67</v>
       </c>
       <c r="H65">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I65">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J65">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K65">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L65">
         <v>72</v>
       </c>
       <c r="M65">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6822,10 +6828,10 @@
         <v>72</v>
       </c>
       <c r="B66">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C66">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D66">
         <v>15</v>
@@ -6849,10 +6855,10 @@
         <v>9</v>
       </c>
       <c r="K66">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M66">
         <v>6</v>
@@ -6863,40 +6869,40 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C67">
+        <v>196</v>
+      </c>
+      <c r="D67">
         <v>193</v>
       </c>
-      <c r="D67">
-        <v>189</v>
-      </c>
       <c r="E67">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F67">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G67">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H67">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I67">
         <v>161</v>
       </c>
       <c r="J67">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K67">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L67">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M67">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6907,7 +6913,7 @@
         <v>5</v>
       </c>
       <c r="C68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D68">
         <v>11</v>
@@ -6928,7 +6934,7 @@
         <v>14</v>
       </c>
       <c r="J68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K68">
         <v>13</v>
@@ -6948,7 +6954,7 @@
         <v>6</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D69">
         <v>8</v>
@@ -6972,7 +6978,7 @@
         <v>12</v>
       </c>
       <c r="K69">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L69">
         <v>7</v>
@@ -7027,7 +7033,7 @@
         <v>5</v>
       </c>
       <c r="C71">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>9</v>
@@ -7106,13 +7112,13 @@
         <v>79</v>
       </c>
       <c r="B73">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C73">
         <v>33</v>
       </c>
       <c r="D73">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E73">
         <v>43</v>
@@ -7124,7 +7130,7 @@
         <v>36</v>
       </c>
       <c r="H73">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I73">
         <v>39</v>
@@ -7133,7 +7139,7 @@
         <v>41</v>
       </c>
       <c r="K73">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L73">
         <v>24</v>
@@ -7159,7 +7165,7 @@
         <v>4</v>
       </c>
       <c r="F74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G74">
         <v>7</v>
@@ -7188,7 +7194,7 @@
         <v>81</v>
       </c>
       <c r="B75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C75">
         <v>13</v>
@@ -7197,16 +7203,16 @@
         <v>10</v>
       </c>
       <c r="E75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F75">
         <v>13</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H75">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I75">
         <v>10</v>
@@ -7232,37 +7238,37 @@
         <v>20</v>
       </c>
       <c r="C76">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D76">
         <v>41</v>
       </c>
       <c r="E76">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F76">
         <v>64</v>
       </c>
       <c r="G76">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H76">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I76">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J76">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K76">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L76">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M76">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7270,7 +7276,7 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C77">
         <v>30</v>
@@ -7282,7 +7288,7 @@
         <v>29</v>
       </c>
       <c r="F77">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G77">
         <v>25</v>
@@ -7320,7 +7326,7 @@
         <v>48</v>
       </c>
       <c r="E78">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F78">
         <v>36</v>
@@ -7329,16 +7335,16 @@
         <v>59</v>
       </c>
       <c r="H78">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I78">
         <v>56</v>
       </c>
       <c r="J78">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K78">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L78">
         <v>56</v>
@@ -7355,37 +7361,37 @@
         <v>124</v>
       </c>
       <c r="C79">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D79">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E79">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F79">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G79">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H79">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I79">
         <v>104</v>
       </c>
       <c r="J79">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K79">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L79">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M79">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7399,13 +7405,13 @@
         <v>12</v>
       </c>
       <c r="D80">
+        <v>15</v>
+      </c>
+      <c r="E80">
         <v>14</v>
       </c>
-      <c r="E80">
-        <v>12</v>
-      </c>
       <c r="F80">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G80">
         <v>14</v>
@@ -7426,7 +7432,7 @@
         <v>15</v>
       </c>
       <c r="M80">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7478,7 +7484,7 @@
         <v>6</v>
       </c>
       <c r="C82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D82">
         <v>7</v>
@@ -7513,37 +7519,37 @@
         <v>89</v>
       </c>
       <c r="B83">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C83">
         <v>91</v>
       </c>
       <c r="D83">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E83">
         <v>64</v>
       </c>
       <c r="F83">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G83">
         <v>57</v>
       </c>
       <c r="H83">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I83">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J83">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K83">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L83">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M83">
         <v>80</v>
@@ -7566,16 +7572,16 @@
         <v>30</v>
       </c>
       <c r="F84">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G84">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H84">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I84">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J84">
         <v>45</v>
@@ -7584,10 +7590,10 @@
         <v>33</v>
       </c>
       <c r="L84">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M84">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7595,40 +7601,40 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C85">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D85">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E85">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F85">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G85">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H85">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I85">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J85">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K85">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L85">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="M85">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7642,13 +7648,13 @@
         <v>22</v>
       </c>
       <c r="D86">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E86">
         <v>24</v>
       </c>
       <c r="F86">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G86">
         <v>27</v>
@@ -7663,10 +7669,10 @@
         <v>23</v>
       </c>
       <c r="K86">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L86">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M86">
         <v>22</v>
@@ -7721,13 +7727,13 @@
         <v>33</v>
       </c>
       <c r="C88">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D88">
         <v>47</v>
       </c>
       <c r="E88">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F88">
         <v>48</v>
@@ -7742,13 +7748,13 @@
         <v>34</v>
       </c>
       <c r="J88">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K88">
         <v>58</v>
       </c>
       <c r="L88">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M88">
         <v>40</v>
@@ -7765,7 +7771,7 @@
         <v>42</v>
       </c>
       <c r="D89">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E89">
         <v>33</v>
@@ -7777,22 +7783,22 @@
         <v>57</v>
       </c>
       <c r="H89">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I89">
         <v>32</v>
       </c>
       <c r="J89">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K89">
         <v>61</v>
       </c>
       <c r="L89">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M89">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7803,19 +7809,19 @@
         <v>36</v>
       </c>
       <c r="C90">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D90">
         <v>62</v>
       </c>
       <c r="E90">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F90">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G90">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H90">
         <v>51</v>
@@ -7841,37 +7847,37 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C91">
+        <v>54</v>
+      </c>
+      <c r="D91">
+        <v>66</v>
+      </c>
+      <c r="E91">
+        <v>47</v>
+      </c>
+      <c r="F91">
+        <v>43</v>
+      </c>
+      <c r="G91">
         <v>53</v>
       </c>
-      <c r="D91">
-        <v>64</v>
-      </c>
-      <c r="E91">
-        <v>46</v>
-      </c>
-      <c r="F91">
-        <v>42</v>
-      </c>
-      <c r="G91">
-        <v>52</v>
-      </c>
       <c r="H91">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I91">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J91">
         <v>60</v>
       </c>
       <c r="K91">
+        <v>46</v>
+      </c>
+      <c r="L91">
         <v>45</v>
-      </c>
-      <c r="L91">
-        <v>44</v>
       </c>
       <c r="M91">
         <v>49</v>
@@ -7882,7 +7888,7 @@
         <v>98</v>
       </c>
       <c r="B92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -7903,7 +7909,7 @@
         <v>10</v>
       </c>
       <c r="I92">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J92">
         <v>14</v>
@@ -7941,13 +7947,13 @@
         <v>24</v>
       </c>
       <c r="H93">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I93">
         <v>18</v>
       </c>
       <c r="J93">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K93">
         <v>20</v>
@@ -7979,7 +7985,7 @@
         <v>25</v>
       </c>
       <c r="G94">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H94">
         <v>23</v>
@@ -7988,7 +7994,7 @@
         <v>38</v>
       </c>
       <c r="J94">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K94">
         <v>57</v>
@@ -8005,25 +8011,25 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C95">
         <v>67</v>
       </c>
       <c r="D95">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E95">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F95">
         <v>67</v>
       </c>
       <c r="G95">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H95">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I95">
         <v>65</v>
@@ -8035,10 +8041,10 @@
         <v>78</v>
       </c>
       <c r="L95">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M95">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8052,13 +8058,13 @@
         <v>54</v>
       </c>
       <c r="D96">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E96">
         <v>64</v>
       </c>
       <c r="F96">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G96">
         <v>52</v>
@@ -8067,7 +8073,7 @@
         <v>34</v>
       </c>
       <c r="I96">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J96">
         <v>58</v>
@@ -8076,10 +8082,10 @@
         <v>64</v>
       </c>
       <c r="L96">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M96">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8108,16 +8114,16 @@
         <v>28</v>
       </c>
       <c r="I97">
+        <v>43</v>
+      </c>
+      <c r="J97">
+        <v>26</v>
+      </c>
+      <c r="K97">
+        <v>38</v>
+      </c>
+      <c r="L97">
         <v>42</v>
-      </c>
-      <c r="J97">
-        <v>24</v>
-      </c>
-      <c r="K97">
-        <v>37</v>
-      </c>
-      <c r="L97">
-        <v>40</v>
       </c>
       <c r="M97">
         <v>24</v>
@@ -8131,28 +8137,28 @@
         <v>18</v>
       </c>
       <c r="C98">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D98">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E98">
         <v>26</v>
       </c>
       <c r="F98">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G98">
         <v>18</v>
       </c>
       <c r="H98">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I98">
         <v>27</v>
       </c>
       <c r="J98">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K98">
         <v>28</v>
@@ -8161,7 +8167,7 @@
         <v>28</v>
       </c>
       <c r="M98">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -8169,16 +8175,16 @@
         <v>105</v>
       </c>
       <c r="B99">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C99">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D99">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E99">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F99">
         <v>73</v>
@@ -8187,16 +8193,16 @@
         <v>78</v>
       </c>
       <c r="H99">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I99">
         <v>75</v>
       </c>
       <c r="J99">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K99">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L99">
         <v>55</v>
@@ -8251,40 +8257,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>3400</v>
+        <v>3451</v>
       </c>
       <c r="C101">
-        <v>4454</v>
+        <v>4512</v>
       </c>
       <c r="D101">
-        <v>4671</v>
+        <v>4726</v>
       </c>
       <c r="E101">
-        <v>4207</v>
+        <v>4291</v>
       </c>
       <c r="F101">
-        <v>3782</v>
+        <v>3838</v>
       </c>
       <c r="G101">
-        <v>4165</v>
+        <v>4206</v>
       </c>
       <c r="H101">
-        <v>3909</v>
+        <v>3974</v>
       </c>
       <c r="I101">
-        <v>4039</v>
+        <v>4086</v>
       </c>
       <c r="J101">
-        <v>4535</v>
+        <v>4591</v>
       </c>
       <c r="K101">
-        <v>4595</v>
+        <v>4661</v>
       </c>
       <c r="L101">
-        <v>3510</v>
+        <v>3578</v>
       </c>
       <c r="M101">
-        <v>3165</v>
+        <v>3224</v>
       </c>
     </row>
   </sheetData>
@@ -8460,16 +8466,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -8487,7 +8493,7 @@
         <v>15</v>
       </c>
       <c r="K2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2">
         <v>11</v>
@@ -8501,7 +8507,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -8621,7 +8627,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>16</v>
@@ -8642,10 +8648,10 @@
         <v>2</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -8656,16 +8662,16 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>63</v>
+      </c>
+      <c r="D7">
+        <v>52</v>
+      </c>
+      <c r="E7">
         <v>31</v>
-      </c>
-      <c r="C7">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>51</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -8683,10 +8689,10 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -8766,7 +8772,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>32</v>
@@ -8781,7 +8787,7 @@
         <v>41</v>
       </c>
       <c r="H2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I2">
         <v>44</v>
@@ -8793,7 +8799,7 @@
         <v>54</v>
       </c>
       <c r="L2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M2">
         <v>28</v>
@@ -8804,25 +8810,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3">
         <v>53</v>
@@ -8831,13 +8837,13 @@
         <v>68</v>
       </c>
       <c r="K3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3">
         <v>33</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8851,7 +8857,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>14</v>
@@ -8860,7 +8866,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -8872,13 +8878,13 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>13</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -8901,7 +8907,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -8927,10 +8933,10 @@
         <v>51</v>
       </c>
       <c r="C6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>59</v>
@@ -8948,10 +8954,10 @@
         <v>54</v>
       </c>
       <c r="J6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L6">
         <v>39</v>
@@ -8965,40 +8971,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7">
+        <v>196</v>
+      </c>
+      <c r="D7">
         <v>193</v>
       </c>
-      <c r="D7">
-        <v>189</v>
-      </c>
       <c r="E7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I7">
         <v>161</v>
       </c>
       <c r="J7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M7">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -9102,10 +9108,10 @@
         <v>12</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9125,13 +9131,13 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>13</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -9143,7 +9149,7 @@
         <v>10</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -9218,16 +9224,16 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6">
         <v>13</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>18</v>
@@ -9236,10 +9242,10 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9259,16 +9265,16 @@
         <v>30</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7">
         <v>45</v>
@@ -9277,10 +9283,10 @@
         <v>33</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -9363,7 +9369,7 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -9375,7 +9381,7 @@
         <v>5</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -9413,7 +9419,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>6</v>
@@ -9457,7 +9463,7 @@
         <v>2</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -9506,13 +9512,13 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9529,7 +9535,7 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>17</v>
@@ -9544,16 +9550,16 @@
         <v>16</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -9683,7 +9689,7 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -9695,7 +9701,7 @@
         <v>13</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3">
         <v>13</v>
@@ -9718,13 +9724,13 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -9733,13 +9739,13 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -9776,7 +9782,7 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>68</v>
@@ -9785,25 +9791,25 @@
         <v>38</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6">
         <v>23</v>
       </c>
       <c r="I6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K6">
         <v>31</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9817,34 +9823,34 @@
         <v>64</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F7">
         <v>72</v>
       </c>
       <c r="G7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H7">
         <v>40</v>
       </c>
       <c r="I7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M7">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -9921,19 +9927,19 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2">
         <v>65</v>
       </c>
       <c r="F2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H2">
         <v>74</v>
@@ -9948,7 +9954,7 @@
         <v>55</v>
       </c>
       <c r="L2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M2">
         <v>54</v>
@@ -9959,40 +9965,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C3">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H3">
         <v>93</v>
       </c>
       <c r="I3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J3">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K3">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10006,7 +10012,7 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -10030,10 +10036,10 @@
         <v>16</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10074,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10082,40 +10088,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>102</v>
       </c>
       <c r="D6">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F6">
+        <v>58</v>
+      </c>
+      <c r="G6">
+        <v>89</v>
+      </c>
+      <c r="H6">
         <v>57</v>
       </c>
-      <c r="G6">
-        <v>88</v>
-      </c>
-      <c r="H6">
-        <v>56</v>
-      </c>
       <c r="I6">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>63</v>
       </c>
       <c r="K6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6">
         <v>44</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10123,40 +10129,40 @@
         <v>6</v>
       </c>
       <c r="B7">
+        <v>229</v>
+      </c>
+      <c r="C7">
+        <v>287</v>
+      </c>
+      <c r="D7">
+        <v>281</v>
+      </c>
+      <c r="E7">
         <v>224</v>
       </c>
-      <c r="C7">
-        <v>282</v>
-      </c>
-      <c r="D7">
-        <v>277</v>
-      </c>
-      <c r="E7">
-        <v>220</v>
-      </c>
       <c r="F7">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="G7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L7">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M7">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -10254,7 +10260,7 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>13</v>
@@ -10263,7 +10269,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10289,7 +10295,7 @@
         <v>5</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -10324,10 +10330,10 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -10339,7 +10345,7 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>14</v>
@@ -10364,7 +10370,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>39</v>
@@ -10373,7 +10379,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -10388,10 +10394,10 @@
         <v>20</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6">
         <v>20</v>
@@ -10405,7 +10411,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>58</v>
@@ -10414,31 +10420,31 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L7">
         <v>54</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -10530,10 +10536,10 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2">
         <v>38</v>
@@ -10553,7 +10559,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>31</v>
@@ -10562,16 +10568,16 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>37</v>
       </c>
       <c r="H3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I3">
         <v>24</v>
@@ -10580,13 +10586,13 @@
         <v>40</v>
       </c>
       <c r="K3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>34</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10594,7 +10600,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -10612,7 +10618,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -10627,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10650,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -10679,22 +10685,22 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>35</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6">
         <v>30</v>
@@ -10703,10 +10709,10 @@
         <v>64</v>
       </c>
       <c r="K6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M6">
         <v>25</v>
@@ -10717,40 +10723,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7">
         <v>160</v>
       </c>
       <c r="K7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -10827,7 +10833,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>9</v>
@@ -10848,7 +10854,7 @@
         <v>10</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -10880,7 +10886,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -10982,7 +10988,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10997,7 +11003,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>17</v>
@@ -11017,19 +11023,19 @@
         <v>39</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>24</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>41</v>
@@ -11038,7 +11044,7 @@
         <v>32</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7">
         <v>44</v>
@@ -11124,7 +11130,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -11136,7 +11142,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -11221,7 +11227,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -11255,6 +11261,9 @@
       <c r="L5">
         <v>2</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -11264,13 +11273,13 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>17</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>34</v>
@@ -11279,19 +11288,19 @@
         <v>34</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>30</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6">
         <v>23</v>
@@ -11305,37 +11314,37 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>64</v>
       </c>
       <c r="G7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -11409,7 +11418,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -11459,7 +11468,7 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -11500,7 +11509,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -11573,7 +11582,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -11587,7 +11596,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -11596,7 +11605,7 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -11614,7 +11623,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -11694,7 +11703,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -11744,7 +11753,7 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -11788,7 +11797,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -11809,7 +11818,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -11831,7 +11840,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -11840,7 +11849,7 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -11872,7 +11881,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -11881,10 +11890,10 @@
         <v>63</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>44</v>
@@ -11905,7 +11914,7 @@
         <v>24</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -12006,7 +12015,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -12035,7 +12044,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -12169,7 +12178,7 @@
         <v>15</v>
       </c>
       <c r="G7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7">
         <v>14</v>
@@ -12181,7 +12190,7 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L7">
         <v>14</v>
@@ -12267,22 +12276,22 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2">
         <v>33</v>
@@ -12294,7 +12303,7 @@
         <v>28</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12302,7 +12311,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>51</v>
@@ -12311,31 +12320,31 @@
         <v>43</v>
       </c>
       <c r="E3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>51</v>
       </c>
       <c r="H3">
+        <v>39</v>
+      </c>
+      <c r="I3">
+        <v>43</v>
+      </c>
+      <c r="J3">
+        <v>31</v>
+      </c>
+      <c r="K3">
+        <v>46</v>
+      </c>
+      <c r="L3">
+        <v>26</v>
+      </c>
+      <c r="M3">
         <v>38</v>
-      </c>
-      <c r="I3">
-        <v>42</v>
-      </c>
-      <c r="J3">
-        <v>30</v>
-      </c>
-      <c r="K3">
-        <v>45</v>
-      </c>
-      <c r="L3">
-        <v>25</v>
-      </c>
-      <c r="M3">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12343,7 +12352,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -12370,13 +12379,13 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12425,19 +12434,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6">
         <v>77</v>
       </c>
       <c r="D6">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>56</v>
@@ -12466,40 +12475,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C7">
         <v>178</v>
       </c>
       <c r="D7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G7">
         <v>150</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M7">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -12567,7 +12576,13 @@
       <c r="E2">
         <v>2</v>
       </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
     </row>
@@ -12695,13 +12710,13 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>8</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>3</v>
@@ -12884,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -12921,10 +12936,10 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -12962,10 +12977,10 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>32</v>
@@ -12980,7 +12995,7 @@
         <v>29</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>23</v>
@@ -13069,7 +13084,7 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>11</v>
@@ -13087,7 +13102,7 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>18</v>
@@ -13215,7 +13230,7 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -13224,13 +13239,13 @@
         <v>26</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6">
         <v>22</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>21</v>
@@ -13256,7 +13271,7 @@
         <v>48</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>36</v>
@@ -13265,16 +13280,16 @@
         <v>59</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7">
         <v>56</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7">
         <v>56</v>
@@ -13357,7 +13372,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -13378,7 +13393,7 @@
         <v>15</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -13395,7 +13410,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -13404,7 +13419,7 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -13422,7 +13437,7 @@
         <v>9</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -13544,16 +13559,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>46</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>31</v>
@@ -13568,10 +13583,10 @@
         <v>46</v>
       </c>
       <c r="J7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L7">
         <v>40</v>
@@ -13779,7 +13794,7 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -13817,7 +13832,7 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -14070,7 +14085,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -14111,7 +14126,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -14194,7 +14209,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -14206,7 +14221,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -14218,7 +14233,7 @@
         <v>16</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -14319,6 +14334,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="I5">
         <v>2</v>
       </c>
@@ -14334,7 +14352,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>17</v>
@@ -14346,7 +14364,7 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6">
         <v>11</v>
@@ -14375,7 +14393,7 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>51</v>
@@ -14387,10 +14405,10 @@
         <v>36</v>
       </c>
       <c r="G7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -14399,7 +14417,7 @@
         <v>44</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7">
         <v>38</v>
@@ -14485,13 +14503,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>16</v>
@@ -14500,7 +14518,7 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>20</v>
@@ -14509,10 +14527,10 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14553,7 +14571,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14646,7 +14664,7 @@
         <v>15</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -14672,13 +14690,13 @@
         <v>54</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>64</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7">
         <v>52</v>
@@ -14687,7 +14705,7 @@
         <v>34</v>
       </c>
       <c r="I7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J7">
         <v>58</v>
@@ -14696,10 +14714,10 @@
         <v>64</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -14776,7 +14794,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -14785,16 +14803,16 @@
         <v>13</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2">
         <v>14</v>
@@ -14832,7 +14850,7 @@
         <v>27</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>18</v>
@@ -14873,7 +14891,7 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -14889,6 +14907,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
@@ -14916,7 +14937,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>21</v>
@@ -14925,7 +14946,7 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -14946,7 +14967,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -14957,37 +14978,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7">
+        <v>54</v>
+      </c>
+      <c r="D7">
+        <v>66</v>
+      </c>
+      <c r="E7">
+        <v>47</v>
+      </c>
+      <c r="F7">
+        <v>43</v>
+      </c>
+      <c r="G7">
         <v>53</v>
       </c>
-      <c r="D7">
-        <v>64</v>
-      </c>
-      <c r="E7">
-        <v>46</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>52</v>
-      </c>
       <c r="H7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7">
         <v>60</v>
       </c>
       <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
         <v>45</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
       </c>
       <c r="M7">
         <v>49</v>
@@ -15063,6 +15084,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -15200,7 +15224,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -15313,16 +15337,16 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>39</v>
@@ -15366,16 +15390,16 @@
         <v>38</v>
       </c>
       <c r="H3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3">
         <v>29</v>
       </c>
       <c r="J3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3">
         <v>34</v>
@@ -15474,22 +15498,22 @@
         <v>59</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>66</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>44</v>
       </c>
       <c r="H6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6">
         <v>34</v>
@@ -15501,10 +15525,10 @@
         <v>26</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15515,37 +15539,37 @@
         <v>124</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I7">
         <v>104</v>
       </c>
       <c r="J7">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -15634,7 +15658,7 @@
         <v>4</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -15669,7 +15693,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -15792,7 +15816,7 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -15815,13 +15839,13 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>19</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7">
         <v>19</v>
@@ -15833,7 +15857,7 @@
         <v>26</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>29</v>
@@ -15913,7 +15937,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -15922,7 +15946,7 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -15931,7 +15955,7 @@
         <v>15</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>26</v>
@@ -15943,7 +15967,7 @@
         <v>32</v>
       </c>
       <c r="L2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2">
         <v>32</v>
@@ -15963,7 +15987,7 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -15972,7 +15996,7 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3">
         <v>35</v>
@@ -15984,7 +16008,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3">
         <v>27</v>
@@ -15995,7 +16019,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -16007,7 +16031,7 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -16080,10 +16104,10 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6">
         <v>45</v>
@@ -16115,25 +16139,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <v>97</v>
       </c>
       <c r="D7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G7">
         <v>97</v>
       </c>
       <c r="H7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I7">
         <v>116</v>
@@ -16145,7 +16169,7 @@
         <v>110</v>
       </c>
       <c r="L7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M7">
         <v>90</v>
@@ -16272,7 +16296,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -16287,7 +16311,7 @@
         <v>6</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -16328,7 +16352,7 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -16371,7 +16395,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6">
         <v>18</v>
@@ -16380,7 +16404,7 @@
         <v>37</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -16403,7 +16427,7 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>18</v>
@@ -16412,19 +16436,19 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7">
         <v>33</v>
       </c>
       <c r="J7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -16551,7 +16575,7 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -16609,7 +16633,7 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -16647,13 +16671,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>12</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -16742,13 +16766,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -16757,7 +16781,7 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>23</v>
@@ -16795,7 +16819,7 @@
         <v>24</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -16810,7 +16834,7 @@
         <v>12</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -16897,7 +16921,7 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -16935,22 +16959,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>54</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7">
         <v>75</v>
@@ -16962,7 +16986,7 @@
         <v>67</v>
       </c>
       <c r="K7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7">
         <v>60</v>
@@ -17066,7 +17090,7 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -17142,7 +17166,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -17156,7 +17180,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -17229,13 +17253,13 @@
         <v>24</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>18</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -17543,7 +17567,7 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>35</v>
@@ -17564,7 +17588,7 @@
         <v>44</v>
       </c>
       <c r="K2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2">
         <v>25</v>
@@ -17584,10 +17608,10 @@
         <v>52</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>35</v>
@@ -17596,19 +17620,19 @@
         <v>43</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>45</v>
       </c>
       <c r="K3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3">
         <v>28</v>
@@ -17622,10 +17646,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>14</v>
@@ -17663,7 +17687,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -17698,16 +17722,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6">
         <v>57</v>
       </c>
       <c r="E6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6">
         <v>44</v>
@@ -17739,16 +17763,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C7">
+        <v>173</v>
+      </c>
+      <c r="D7">
         <v>170</v>
       </c>
-      <c r="D7">
-        <v>166</v>
-      </c>
       <c r="E7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>130</v>
@@ -17757,19 +17781,19 @@
         <v>116</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J7">
         <v>128</v>
       </c>
       <c r="K7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M7">
         <v>92</v>
@@ -17998,7 +18022,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -18013,7 +18037,7 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -18039,7 +18063,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>22</v>
@@ -18054,7 +18078,7 @@
         <v>32</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>21</v>
@@ -18190,7 +18214,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -18228,7 +18252,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -18295,7 +18319,7 @@
         <v>21</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>25</v>
@@ -18327,7 +18351,7 @@
         <v>25</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>23</v>
@@ -18336,7 +18360,7 @@
         <v>38</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K7">
         <v>57</v>
@@ -18493,7 +18517,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18624,7 +18648,7 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -18754,7 +18778,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -18763,7 +18787,7 @@
         <v>8</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>12</v>
@@ -18810,7 +18834,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -18856,7 +18880,7 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -18868,13 +18892,13 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6">
         <v>10</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -18897,10 +18921,10 @@
         <v>21</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>34</v>
@@ -18909,13 +18933,13 @@
         <v>31</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K7">
         <v>34</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -19013,16 +19037,16 @@
         <v>18</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2">
         <v>9</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2">
         <v>21</v>
@@ -19033,7 +19057,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -19060,7 +19084,7 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>11</v>
@@ -19141,7 +19165,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -19179,10 +19203,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>54</v>
@@ -19200,16 +19224,16 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
         <v>36</v>
@@ -19304,7 +19328,7 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>4</v>
@@ -19319,7 +19343,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19330,16 +19354,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -19429,13 +19453,13 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>18</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>21</v>
@@ -19455,28 +19479,28 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>26</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>18</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I7">
         <v>27</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7">
         <v>28</v>
@@ -19485,7 +19509,7 @@
         <v>28</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -19568,7 +19592,7 @@
         <v>4</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -19586,7 +19610,7 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>10</v>
@@ -19644,7 +19668,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -19653,28 +19677,28 @@
         <v>3</v>
       </c>
       <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>7</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>6</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19702,7 +19726,7 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -19737,16 +19761,16 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>31</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -19761,13 +19785,13 @@
         <v>24</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>24</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -19931,7 +19955,7 @@
         <v>4</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -19972,7 +19996,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -20331,10 +20355,10 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -20358,10 +20382,10 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -20372,10 +20396,10 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -20399,10 +20423,10 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -20482,16 +20506,16 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>25</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>14</v>
@@ -20500,16 +20524,16 @@
         <v>21</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>17</v>
@@ -20520,7 +20544,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>11</v>
@@ -20532,13 +20556,13 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>29</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <v>11</v>
@@ -20640,7 +20664,7 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>27</v>
@@ -20649,7 +20673,7 @@
         <v>16</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6">
         <v>22</v>
@@ -20658,10 +20682,10 @@
         <v>19</v>
       </c>
       <c r="K6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -20672,37 +20696,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>87</v>
       </c>
       <c r="E7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>70</v>
       </c>
       <c r="H7">
+        <v>57</v>
+      </c>
+      <c r="I7">
+        <v>75</v>
+      </c>
+      <c r="J7">
         <v>55</v>
       </c>
-      <c r="I7">
-        <v>74</v>
-      </c>
-      <c r="J7">
-        <v>53</v>
-      </c>
       <c r="K7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M7">
         <v>44</v>
@@ -20999,7 +21023,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -21008,7 +21032,7 @@
         <v>6</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -21055,7 +21079,7 @@
         <v>9</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>9</v>
@@ -21064,7 +21088,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21119,7 +21143,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -21186,7 +21210,7 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>24</v>
@@ -21195,13 +21219,13 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>25</v>
       </c>
       <c r="J7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7">
         <v>23</v>
@@ -21210,7 +21234,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -21384,7 +21408,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -21415,13 +21439,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>16</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -21442,7 +21466,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -21456,13 +21480,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>33</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>43</v>
@@ -21474,7 +21498,7 @@
         <v>36</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7">
         <v>39</v>
@@ -21483,7 +21507,7 @@
         <v>41</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>24</v>
@@ -21880,10 +21904,10 @@
         <v>10</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21961,7 +21985,7 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -22002,7 +22026,7 @@
         <v>37</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>22</v>
@@ -22023,10 +22047,10 @@
         <v>30</v>
       </c>
       <c r="L7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -22130,7 +22154,7 @@
         <v>7</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
         <v>9</v>
@@ -22162,7 +22186,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
         <v>5</v>
@@ -22203,7 +22227,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -22261,13 +22285,13 @@
         <v>28</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K6">
         <v>23</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -22299,16 +22323,16 @@
         <v>28</v>
       </c>
       <c r="I7">
+        <v>43</v>
+      </c>
+      <c r="J7">
+        <v>26</v>
+      </c>
+      <c r="K7">
+        <v>38</v>
+      </c>
+      <c r="L7">
         <v>42</v>
-      </c>
-      <c r="J7">
-        <v>24</v>
-      </c>
-      <c r="K7">
-        <v>37</v>
-      </c>
-      <c r="L7">
-        <v>40</v>
       </c>
       <c r="M7">
         <v>24</v>
@@ -22426,7 +22450,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -22513,7 +22537,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -22533,7 +22557,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -22554,7 +22578,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J7">
         <v>14</v>
@@ -22936,7 +22960,7 @@
         <v>12</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M3">
         <v>11</v>
@@ -22955,6 +22979,9 @@
       <c r="D4">
         <v>4</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="F4">
         <v>3</v>
       </c>
@@ -23014,7 +23041,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>27</v>
@@ -23035,13 +23062,13 @@
         <v>15</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>32</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -23055,13 +23082,13 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>47</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7">
         <v>48</v>
@@ -23076,13 +23103,13 @@
         <v>34</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7">
         <v>58</v>
       </c>
       <c r="L7">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M7">
         <v>40</v>
@@ -23417,16 +23444,16 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2">
         <v>8</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23440,7 +23467,7 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -23452,7 +23479,7 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -23583,7 +23610,7 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7">
         <v>33</v>
@@ -23595,22 +23622,22 @@
         <v>57</v>
       </c>
       <c r="H7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I7">
         <v>32</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7">
         <v>61</v>
       </c>
       <c r="L7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M7">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -23687,7 +23714,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -23696,7 +23723,7 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -23812,7 +23839,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -23838,7 +23865,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -23847,13 +23874,13 @@
         <v>12</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>12</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>17</v>
@@ -23972,7 +23999,7 @@
         <v>19</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <v>12</v>
@@ -23998,7 +24025,7 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -24010,7 +24037,7 @@
         <v>5</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -24057,7 +24084,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24094,13 +24121,13 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>22</v>
@@ -24109,7 +24136,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -24132,25 +24159,25 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>39</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -24292,7 +24319,7 @@
         <v>5</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -24309,13 +24336,13 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -24330,7 +24357,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4">
         <v>17</v>
@@ -24391,13 +24418,13 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>24</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>27</v>
@@ -24412,10 +24439,10 @@
         <v>23</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6">
         <v>22</v>
@@ -24492,7 +24519,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -24542,16 +24569,16 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -24655,7 +24682,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>13</v>
@@ -24664,16 +24691,16 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>13</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -24777,7 +24804,7 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>13</v>
@@ -24806,19 +24833,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>21</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>16</v>
@@ -24893,6 +24920,9 @@
       <c r="D5">
         <v>2</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -24964,19 +24994,19 @@
         <v>36</v>
       </c>
       <c r="C7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>62</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7">
         <v>51</v>
@@ -25101,7 +25131,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25121,7 +25151,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -25136,7 +25166,7 @@
         <v>18</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -25156,7 +25186,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -25258,13 +25288,13 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>47</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7">
         <v>42</v>
@@ -25279,13 +25309,13 @@
         <v>59</v>
       </c>
       <c r="K7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7">
         <v>48</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -25362,7 +25392,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -25499,7 +25529,7 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -25519,7 +25549,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -25540,7 +25570,7 @@
         <v>14</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <v>13</v>
@@ -25622,6 +25652,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>2</v>
       </c>
@@ -25676,7 +25709,7 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -25783,7 +25816,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -25801,7 +25834,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>13</v>
@@ -25890,7 +25923,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -25899,7 +25932,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -26027,7 +26060,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -26054,7 +26087,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26062,16 +26095,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>25</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>22</v>
@@ -26095,7 +26128,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -26172,7 +26205,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -26184,7 +26217,7 @@
         <v>7</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>8</v>
@@ -26341,7 +26374,7 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -26356,7 +26389,7 @@
         <v>32</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>36</v>
@@ -26457,7 +26490,7 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2">
         <v>36</v>
@@ -26466,19 +26499,19 @@
         <v>54</v>
       </c>
       <c r="I2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>86</v>
       </c>
       <c r="L2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26486,40 +26519,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>43</v>
       </c>
       <c r="D3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3">
         <v>57</v>
       </c>
       <c r="F3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I3">
+        <v>79</v>
+      </c>
+      <c r="J3">
+        <v>70</v>
+      </c>
+      <c r="K3">
         <v>75</v>
       </c>
-      <c r="J3">
-        <v>67</v>
-      </c>
-      <c r="K3">
-        <v>74</v>
-      </c>
       <c r="L3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26533,7 +26566,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -26571,7 +26604,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -26589,7 +26622,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -26618,7 +26651,7 @@
         <v>65</v>
       </c>
       <c r="E6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6">
         <v>58</v>
@@ -26627,16 +26660,16 @@
         <v>57</v>
       </c>
       <c r="H6">
+        <v>57</v>
+      </c>
+      <c r="I6">
+        <v>59</v>
+      </c>
+      <c r="J6">
+        <v>52</v>
+      </c>
+      <c r="K6">
         <v>55</v>
-      </c>
-      <c r="I6">
-        <v>58</v>
-      </c>
-      <c r="J6">
-        <v>51</v>
-      </c>
-      <c r="K6">
-        <v>53</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -26650,40 +26683,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H7">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I7">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L7">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="M7">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -27030,7 +27063,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -27184,7 +27217,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -27624,7 +27657,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -27659,7 +27692,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -27760,7 +27793,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -27813,7 +27846,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -27938,7 +27971,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -27950,7 +27983,7 @@
         <v>29</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>25</v>
@@ -28490,7 +28523,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28507,7 +28540,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -28545,7 +28578,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -28580,10 +28613,10 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>13</v>
@@ -28618,13 +28651,13 @@
         <v>12</v>
       </c>
       <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -28645,7 +28678,7 @@
         <v>15</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -28722,7 +28755,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -28822,7 +28855,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -28979,7 +29012,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -29086,7 +29119,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>11</v>
@@ -29172,28 +29205,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>16</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>14</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>23</v>
@@ -29205,7 +29238,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29216,13 +29249,13 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>24</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>28</v>
@@ -29240,13 +29273,13 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3">
         <v>18</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29304,7 +29337,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -29351,7 +29384,7 @@
         <v>31</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>28</v>
@@ -29360,13 +29393,13 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K6">
         <v>58</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -29377,40 +29410,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D7">
         <v>108</v>
       </c>
       <c r="E7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F7">
         <v>86</v>
       </c>
       <c r="G7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H7">
         <v>67</v>
       </c>
       <c r="I7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -29505,7 +29538,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -29514,7 +29547,7 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <v>7</v>
@@ -29574,6 +29607,9 @@
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -29589,7 +29625,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -29630,7 +29666,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -29639,7 +29675,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>22</v>
@@ -29648,10 +29684,10 @@
         <v>19</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -30473,7 +30509,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -30504,6 +30540,9 @@
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
       <c r="M3">
         <v>1</v>
       </c>
@@ -30559,7 +30598,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -30597,13 +30636,13 @@
         <v>15</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
         <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -30697,7 +30736,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -30781,7 +30820,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -31095,6 +31134,9 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
@@ -31121,7 +31163,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -31147,7 +31189,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>2</v>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C2">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="D2">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="E2">
-        <v>937</v>
+        <v>959</v>
       </c>
       <c r="F2">
-        <v>937</v>
+        <v>955</v>
       </c>
       <c r="G2">
-        <v>957</v>
+        <v>974</v>
       </c>
       <c r="H2">
-        <v>1070</v>
+        <v>1085</v>
       </c>
       <c r="I2">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="J2">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="K2">
-        <v>1337</v>
+        <v>1358</v>
       </c>
       <c r="L2">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="M2">
-        <v>978</v>
+        <v>994</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>902</v>
+        <v>918</v>
       </c>
       <c r="C3">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="D3">
-        <v>1162</v>
+        <v>1178</v>
       </c>
       <c r="E3">
-        <v>1101</v>
+        <v>1124</v>
       </c>
       <c r="F3">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="G3">
-        <v>1233</v>
+        <v>1251</v>
       </c>
       <c r="H3">
-        <v>1109</v>
+        <v>1133</v>
       </c>
       <c r="I3">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="J3">
-        <v>1275</v>
+        <v>1297</v>
       </c>
       <c r="K3">
-        <v>1282</v>
+        <v>1294</v>
       </c>
       <c r="L3">
-        <v>1073</v>
+        <v>1088</v>
       </c>
       <c r="M3">
-        <v>1088</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,40 +950,40 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D4">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E4">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F4">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G4">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H4">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I4">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J4">
+        <v>346</v>
+      </c>
+      <c r="K4">
         <v>343</v>
       </c>
-      <c r="K4">
-        <v>340</v>
-      </c>
       <c r="L4">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="M4">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -994,13 +994,13 @@
         <v>61</v>
       </c>
       <c r="C5">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D5">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5">
         <v>55</v>
@@ -1015,13 +1015,13 @@
         <v>112</v>
       </c>
       <c r="J5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K5">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M5">
         <v>67</v>
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1446</v>
+        <v>1463</v>
       </c>
       <c r="C6">
-        <v>1987</v>
+        <v>2007</v>
       </c>
       <c r="D6">
-        <v>2086</v>
+        <v>2107</v>
       </c>
       <c r="E6">
-        <v>1766</v>
+        <v>1790</v>
       </c>
       <c r="F6">
-        <v>1333</v>
+        <v>1353</v>
       </c>
       <c r="G6">
-        <v>1527</v>
+        <v>1539</v>
       </c>
       <c r="H6">
-        <v>1382</v>
+        <v>1399</v>
       </c>
       <c r="I6">
-        <v>1489</v>
+        <v>1507</v>
       </c>
       <c r="J6">
-        <v>1676</v>
+        <v>1693</v>
       </c>
       <c r="K6">
-        <v>1622</v>
+        <v>1646</v>
       </c>
       <c r="L6">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="M6">
-        <v>785</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3451</v>
+        <v>3494</v>
       </c>
       <c r="C7">
-        <v>4512</v>
+        <v>4571</v>
       </c>
       <c r="D7">
-        <v>4726</v>
+        <v>4782</v>
       </c>
       <c r="E7">
-        <v>4291</v>
+        <v>4366</v>
       </c>
       <c r="F7">
-        <v>3838</v>
+        <v>3893</v>
       </c>
       <c r="G7">
-        <v>4206</v>
+        <v>4256</v>
       </c>
       <c r="H7">
-        <v>3974</v>
+        <v>4034</v>
       </c>
       <c r="I7">
-        <v>4086</v>
+        <v>4134</v>
       </c>
       <c r="J7">
-        <v>4591</v>
+        <v>4651</v>
       </c>
       <c r="K7">
-        <v>4661</v>
+        <v>4722</v>
       </c>
       <c r="L7">
-        <v>3578</v>
+        <v>3630</v>
       </c>
       <c r="M7">
-        <v>3224</v>
+        <v>3276</v>
       </c>
     </row>
   </sheetData>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -1623,7 +1623,7 @@
         <v>14</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3">
         <v>14</v>
@@ -1707,7 +1707,7 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -1722,7 +1722,7 @@
         <v>27</v>
       </c>
       <c r="K6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>16</v>
@@ -1742,13 +1742,13 @@
         <v>63</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7">
         <v>51</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>42</v>
@@ -1760,10 +1760,10 @@
         <v>47</v>
       </c>
       <c r="J7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L7">
         <v>42</v>
@@ -1843,22 +1843,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2">
         <v>76</v>
       </c>
       <c r="G2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2">
         <v>79</v>
@@ -1867,16 +1867,16 @@
         <v>67</v>
       </c>
       <c r="J2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2">
         <v>64</v>
       </c>
       <c r="M2">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1884,40 +1884,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L3">
         <v>67</v>
       </c>
       <c r="M3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1940,7 +1940,7 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -1955,10 +1955,10 @@
         <v>16</v>
       </c>
       <c r="L4">
+        <v>18</v>
+      </c>
+      <c r="M4">
         <v>17</v>
-      </c>
-      <c r="M4">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1969,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -1996,7 +1996,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -2007,34 +2007,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C6">
         <v>144</v>
       </c>
       <c r="D6">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E6">
         <v>130</v>
       </c>
       <c r="F6">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G6">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H6">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J6">
         <v>71</v>
       </c>
       <c r="K6">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L6">
         <v>64</v>
@@ -2048,40 +2048,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G7">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="H7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="L7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M7">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2170,19 +2170,19 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2">
         <v>27</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2">
         <v>21</v>
@@ -2199,25 +2199,25 @@
         <v>22</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>33</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>26</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>36</v>
@@ -2229,7 +2229,7 @@
         <v>38</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2246,7 +2246,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2316,10 +2316,10 @@
         <v>25</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>25</v>
@@ -2337,16 +2337,16 @@
         <v>13</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <v>16</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2357,37 +2357,37 @@
         <v>74</v>
       </c>
       <c r="C7">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>66</v>
       </c>
       <c r="G7">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L7">
         <v>79</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2461,16 +2461,16 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>37</v>
+      </c>
+      <c r="C2">
         <v>35</v>
       </c>
-      <c r="C2">
-        <v>34</v>
-      </c>
       <c r="D2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>34</v>
@@ -2479,13 +2479,13 @@
         <v>35</v>
       </c>
       <c r="H2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I2">
         <v>40</v>
       </c>
       <c r="J2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K2">
         <v>54</v>
@@ -2502,13 +2502,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>74</v>
       </c>
       <c r="D3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>80</v>
@@ -2517,16 +2517,16 @@
         <v>67</v>
       </c>
       <c r="G3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3">
         <v>73</v>
@@ -2543,7 +2543,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -2555,7 +2555,7 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>17</v>
@@ -2587,7 +2587,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -2625,19 +2625,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C6">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D6">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6">
         <v>103</v>
@@ -2646,19 +2646,19 @@
         <v>58</v>
       </c>
       <c r="I6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6">
         <v>77</v>
       </c>
       <c r="K6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L6">
         <v>55</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2666,40 +2666,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C7">
+        <v>241</v>
+      </c>
+      <c r="D7">
+        <v>214</v>
+      </c>
+      <c r="E7">
+        <v>258</v>
+      </c>
+      <c r="F7">
+        <v>189</v>
+      </c>
+      <c r="G7">
         <v>236</v>
       </c>
-      <c r="D7">
-        <v>211</v>
-      </c>
-      <c r="E7">
-        <v>255</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
+        <v>196</v>
+      </c>
+      <c r="I7">
         <v>187</v>
       </c>
-      <c r="G7">
-        <v>235</v>
-      </c>
-      <c r="H7">
-        <v>194</v>
-      </c>
-      <c r="I7">
-        <v>186</v>
-      </c>
       <c r="J7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L7">
         <v>156</v>
       </c>
       <c r="M7">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2773,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>16</v>
@@ -2788,7 +2788,7 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>28</v>
@@ -2803,7 +2803,7 @@
         <v>28</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>18</v>
@@ -2829,13 +2829,13 @@
         <v>25</v>
       </c>
       <c r="G3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>21</v>
@@ -2844,7 +2844,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3">
         <v>16</v>
@@ -2931,13 +2931,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>26</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -2949,7 +2949,7 @@
         <v>26</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <v>16</v>
@@ -2972,13 +2972,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>67</v>
       </c>
       <c r="D7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>74</v>
@@ -2987,13 +2987,13 @@
         <v>67</v>
       </c>
       <c r="G7">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J7">
         <v>75</v>
@@ -3002,7 +3002,7 @@
         <v>78</v>
       </c>
       <c r="L7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M7">
         <v>49</v>
@@ -3094,19 +3094,19 @@
         <v>34</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2">
         <v>39</v>
       </c>
       <c r="J2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2">
         <v>39</v>
@@ -3123,28 +3123,28 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I3">
         <v>36</v>
       </c>
       <c r="J3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K3">
         <v>53</v>
@@ -3164,7 +3164,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -3205,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3243,10 +3243,10 @@
         <v>62</v>
       </c>
       <c r="D6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>35</v>
@@ -3261,16 +3261,16 @@
         <v>37</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K6">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6">
         <v>36</v>
       </c>
       <c r="M6">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3281,37 +3281,37 @@
         <v>118</v>
       </c>
       <c r="C7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D7">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F7">
         <v>120</v>
       </c>
       <c r="G7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I7">
         <v>129</v>
       </c>
       <c r="J7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L7">
         <v>121</v>
       </c>
       <c r="M7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3391,7 +3391,7 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>32</v>
@@ -3409,10 +3409,10 @@
         <v>24</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>25</v>
@@ -3438,7 +3438,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>18</v>
@@ -3456,7 +3456,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <v>27</v>
@@ -3558,13 +3558,13 @@
         <v>30</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>20</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>43</v>
@@ -3573,7 +3573,7 @@
         <v>49</v>
       </c>
       <c r="K6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6">
         <v>23</v>
@@ -3593,31 +3593,31 @@
         <v>98</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>99</v>
       </c>
       <c r="F7">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G7">
         <v>67</v>
       </c>
       <c r="H7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I7">
         <v>103</v>
       </c>
       <c r="J7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M7">
         <v>74</v>
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>14</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
         <v>22</v>
@@ -3750,13 +3750,13 @@
         <v>27</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>25</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3">
         <v>21</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3794,7 +3794,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -3905,16 +3905,16 @@
         <v>64</v>
       </c>
       <c r="F7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J7">
         <v>54</v>
@@ -3926,7 +3926,7 @@
         <v>55</v>
       </c>
       <c r="M7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -4110,7 +4110,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -4151,7 +4151,7 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -4258,31 +4258,31 @@
         <v>36</v>
       </c>
       <c r="C2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>40</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2">
         <v>44</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>25</v>
@@ -4296,7 +4296,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -4402,7 +4402,7 @@
         <v>17</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -4419,19 +4419,19 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6">
         <v>45</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>44</v>
@@ -4446,13 +4446,13 @@
         <v>44</v>
       </c>
       <c r="K6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>24</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4463,34 +4463,34 @@
         <v>136</v>
       </c>
       <c r="C7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7">
         <v>116</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M7">
         <v>92</v>
@@ -4501,40 +4501,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G8">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="H8">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K8">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="L8">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M8">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4548,7 +4548,7 @@
         <v>35</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>24</v>
@@ -4560,10 +4560,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J9">
         <v>29</v>
@@ -4575,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="M9">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4586,19 +4586,19 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>42</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F10">
         <v>25</v>
       </c>
       <c r="G10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10">
         <v>31</v>
@@ -4627,31 +4627,31 @@
         <v>64</v>
       </c>
       <c r="C11">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11">
         <v>87</v>
       </c>
       <c r="E11">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>70</v>
       </c>
       <c r="H11">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J11">
         <v>55</v>
       </c>
       <c r="K11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11">
         <v>63</v>
@@ -4689,7 +4689,7 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -4747,7 +4747,7 @@
         <v>25</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>22</v>
@@ -4768,7 +4768,7 @@
         <v>17</v>
       </c>
       <c r="K14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L14">
         <v>13</v>
@@ -4785,7 +4785,7 @@
         <v>40</v>
       </c>
       <c r="C15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15">
         <v>54</v>
@@ -4794,19 +4794,19 @@
         <v>54</v>
       </c>
       <c r="F15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J15">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15">
         <v>40</v>
@@ -4829,7 +4829,7 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -4856,7 +4856,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4879,19 +4879,19 @@
         <v>10</v>
       </c>
       <c r="G17">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17">
         <v>12</v>
       </c>
-      <c r="H17">
-        <v>16</v>
-      </c>
-      <c r="I17">
-        <v>4</v>
-      </c>
-      <c r="J17">
-        <v>11</v>
-      </c>
       <c r="K17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -4908,7 +4908,7 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>28</v>
@@ -4917,16 +4917,16 @@
         <v>23</v>
       </c>
       <c r="F18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J18">
         <v>63</v>
@@ -4946,31 +4946,31 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19">
         <v>110</v>
       </c>
       <c r="E19">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F19">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G19">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H19">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I19">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J19">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K19">
         <v>123</v>
@@ -4979,7 +4979,7 @@
         <v>107</v>
       </c>
       <c r="M19">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4987,7 +4987,7 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20">
         <v>97</v>
@@ -4996,13 +4996,13 @@
         <v>114</v>
       </c>
       <c r="E20">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F20">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G20">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H20">
         <v>110</v>
@@ -5011,7 +5011,7 @@
         <v>116</v>
       </c>
       <c r="J20">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K20">
         <v>110</v>
@@ -5043,13 +5043,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H21">
         <v>12</v>
       </c>
       <c r="I21">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -5061,7 +5061,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5137,7 +5137,7 @@
         <v>44</v>
       </c>
       <c r="K23">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L23">
         <v>38</v>
@@ -5184,7 +5184,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5198,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="D25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25">
         <v>17</v>
@@ -5210,7 +5210,7 @@
         <v>11</v>
       </c>
       <c r="H25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25">
         <v>22</v>
@@ -5225,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="M25">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5274,7 +5274,7 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -5292,10 +5292,10 @@
         <v>34</v>
       </c>
       <c r="H27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I27">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J27">
         <v>24</v>
@@ -5347,40 +5347,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C29">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D29">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E29">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F29">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G29">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="H29">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I29">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J29">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K29">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L29">
         <v>169</v>
       </c>
       <c r="M29">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5391,7 +5391,7 @@
         <v>17</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>19</v>
@@ -5450,19 +5450,19 @@
         <v>27</v>
       </c>
       <c r="I31">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J31">
         <v>28</v>
       </c>
       <c r="K31">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L31">
         <v>39</v>
       </c>
       <c r="M31">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5476,7 +5476,7 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -5503,7 +5503,7 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -5511,40 +5511,40 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C33">
+        <v>241</v>
+      </c>
+      <c r="D33">
+        <v>214</v>
+      </c>
+      <c r="E33">
+        <v>258</v>
+      </c>
+      <c r="F33">
+        <v>189</v>
+      </c>
+      <c r="G33">
         <v>236</v>
       </c>
-      <c r="D33">
-        <v>211</v>
-      </c>
-      <c r="E33">
-        <v>255</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
+        <v>196</v>
+      </c>
+      <c r="I33">
         <v>187</v>
       </c>
-      <c r="G33">
-        <v>235</v>
-      </c>
-      <c r="H33">
-        <v>194</v>
-      </c>
-      <c r="I33">
-        <v>186</v>
-      </c>
       <c r="J33">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K33">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L33">
         <v>156</v>
       </c>
       <c r="M33">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5561,19 +5561,19 @@
         <v>15</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34">
         <v>21</v>
       </c>
       <c r="G34">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34">
         <v>18</v>
       </c>
       <c r="I34">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J34">
         <v>32</v>
@@ -5602,7 +5602,7 @@
         <v>7</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -5643,19 +5643,19 @@
         <v>50</v>
       </c>
       <c r="E36">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F36">
         <v>48</v>
       </c>
       <c r="G36">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H36">
         <v>75</v>
       </c>
       <c r="I36">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J36">
         <v>67</v>
@@ -5667,7 +5667,7 @@
         <v>60</v>
       </c>
       <c r="M36">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5678,37 +5678,37 @@
         <v>118</v>
       </c>
       <c r="C37">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D37">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E37">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F37">
         <v>120</v>
       </c>
       <c r="G37">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H37">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I37">
         <v>129</v>
       </c>
       <c r="J37">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K37">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L37">
         <v>121</v>
       </c>
       <c r="M37">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5727,6 +5727,9 @@
       <c r="F38">
         <v>4</v>
       </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
       <c r="I38">
         <v>2</v>
       </c>
@@ -5738,6 +5741,9 @@
       </c>
       <c r="L38">
         <v>3</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -5786,7 +5792,7 @@
         <v>7</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D40">
         <v>7</v>
@@ -5845,13 +5851,13 @@
         <v>14</v>
       </c>
       <c r="I41">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J41">
         <v>28</v>
       </c>
       <c r="K41">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L41">
         <v>14</v>
@@ -5865,34 +5871,34 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D42">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E42">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F42">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G42">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H42">
         <v>146</v>
       </c>
       <c r="I42">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J42">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K42">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L42">
         <v>113</v>
@@ -5915,10 +5921,10 @@
         <v>19</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F43">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G43">
         <v>32</v>
@@ -5936,7 +5942,7 @@
         <v>45</v>
       </c>
       <c r="L43">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M43">
         <v>27</v>
@@ -5947,7 +5953,7 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C44">
         <v>51</v>
@@ -5956,7 +5962,7 @@
         <v>41</v>
       </c>
       <c r="E44">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F44">
         <v>24</v>
@@ -5968,10 +5974,10 @@
         <v>41</v>
       </c>
       <c r="I44">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J44">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K44">
         <v>44</v>
@@ -6035,13 +6041,13 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E46">
         <v>10</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46">
         <v>13</v>
@@ -6053,7 +6059,7 @@
         <v>9</v>
       </c>
       <c r="J46">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K46">
         <v>11</v>
@@ -6062,7 +6068,7 @@
         <v>9</v>
       </c>
       <c r="M46">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -6070,16 +6076,16 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C47">
         <v>26</v>
       </c>
       <c r="D47">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E47">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F47">
         <v>29</v>
@@ -6094,7 +6100,7 @@
         <v>31</v>
       </c>
       <c r="J47">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K47">
         <v>34</v>
@@ -6103,7 +6109,7 @@
         <v>31</v>
       </c>
       <c r="M47">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6111,16 +6117,16 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48">
         <v>58</v>
       </c>
       <c r="D48">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E48">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F48">
         <v>36</v>
@@ -6144,7 +6150,7 @@
         <v>54</v>
       </c>
       <c r="M48">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6161,10 +6167,10 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49">
         <v>28</v>
@@ -6176,7 +6182,7 @@
         <v>16</v>
       </c>
       <c r="J49">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K49">
         <v>31</v>
@@ -6196,7 +6202,7 @@
         <v>12</v>
       </c>
       <c r="C50">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D50">
         <v>31</v>
@@ -6205,7 +6211,7 @@
         <v>25</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G50">
         <v>18</v>
@@ -6217,7 +6223,7 @@
         <v>12</v>
       </c>
       <c r="J50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K50">
         <v>26</v>
@@ -6237,16 +6243,16 @@
         <v>36</v>
       </c>
       <c r="C51">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E51">
         <v>47</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G51">
         <v>42</v>
@@ -6267,7 +6273,7 @@
         <v>48</v>
       </c>
       <c r="M51">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6278,28 +6284,28 @@
         <v>58</v>
       </c>
       <c r="C52">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D52">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E52">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F52">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G52">
         <v>79</v>
       </c>
       <c r="H52">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I52">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J52">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K52">
         <v>126</v>
@@ -6308,7 +6314,7 @@
         <v>65</v>
       </c>
       <c r="M52">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6322,13 +6328,13 @@
         <v>63</v>
       </c>
       <c r="D53">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53">
         <v>51</v>
       </c>
       <c r="F53">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G53">
         <v>42</v>
@@ -6340,10 +6346,10 @@
         <v>47</v>
       </c>
       <c r="J53">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K53">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L53">
         <v>42</v>
@@ -6363,7 +6369,7 @@
         <v>64</v>
       </c>
       <c r="D54">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E54">
         <v>105</v>
@@ -6381,16 +6387,16 @@
         <v>86</v>
       </c>
       <c r="J54">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K54">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L54">
         <v>71</v>
       </c>
       <c r="M54">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6404,16 +6410,16 @@
         <v>40</v>
       </c>
       <c r="D55">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E55">
         <v>41</v>
       </c>
       <c r="F55">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G55">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H55">
         <v>40</v>
@@ -6425,13 +6431,13 @@
         <v>57</v>
       </c>
       <c r="K55">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L55">
         <v>40</v>
       </c>
       <c r="M55">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6480,7 +6486,7 @@
         <v>63</v>
       </c>
       <c r="B57">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -6504,7 +6510,7 @@
         <v>13</v>
       </c>
       <c r="J57">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K57">
         <v>9</v>
@@ -6571,7 +6577,7 @@
         <v>10</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -6609,7 +6615,7 @@
         <v>28</v>
       </c>
       <c r="F60">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G60">
         <v>28</v>
@@ -6624,13 +6630,13 @@
         <v>28</v>
       </c>
       <c r="K60">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L60">
         <v>20</v>
       </c>
       <c r="M60">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6638,7 +6644,7 @@
         <v>67</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>6</v>
@@ -6665,10 +6671,10 @@
         <v>8</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61">
         <v>3</v>
@@ -6705,28 +6711,28 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C63">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D63">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E63">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F63">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H63">
         <v>55</v>
       </c>
       <c r="I63">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J63">
         <v>57</v>
@@ -6735,10 +6741,10 @@
         <v>35</v>
       </c>
       <c r="L63">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6749,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="C64">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D64">
         <v>15</v>
@@ -6764,7 +6770,7 @@
         <v>28</v>
       </c>
       <c r="H64">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I64">
         <v>45</v>
@@ -6793,31 +6799,31 @@
         <v>98</v>
       </c>
       <c r="D65">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E65">
         <v>99</v>
       </c>
       <c r="F65">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G65">
         <v>67</v>
       </c>
       <c r="H65">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I65">
         <v>103</v>
       </c>
       <c r="J65">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K65">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L65">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M65">
         <v>74</v>
@@ -6846,13 +6852,13 @@
         <v>12</v>
       </c>
       <c r="H66">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J66">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K66">
         <v>20</v>
@@ -6861,7 +6867,7 @@
         <v>4</v>
       </c>
       <c r="M66">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6872,34 +6878,34 @@
         <v>132</v>
       </c>
       <c r="C67">
+        <v>199</v>
+      </c>
+      <c r="D67">
         <v>196</v>
       </c>
-      <c r="D67">
-        <v>193</v>
-      </c>
       <c r="E67">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F67">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G67">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H67">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I67">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J67">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K67">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L67">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M67">
         <v>101</v>
@@ -6913,13 +6919,13 @@
         <v>5</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D68">
         <v>11</v>
       </c>
       <c r="E68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F68">
         <v>7</v>
@@ -7000,6 +7006,9 @@
       <c r="D70">
         <v>5</v>
       </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
       <c r="F70">
         <v>6</v>
       </c>
@@ -7042,13 +7051,13 @@
         <v>6</v>
       </c>
       <c r="F71">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G71">
         <v>7</v>
       </c>
       <c r="H71">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I71">
         <v>6</v>
@@ -7077,7 +7086,7 @@
         <v>13</v>
       </c>
       <c r="D72">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E72">
         <v>26</v>
@@ -7115,13 +7124,13 @@
         <v>29</v>
       </c>
       <c r="C73">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D73">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E73">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F73">
         <v>42</v>
@@ -7139,7 +7148,7 @@
         <v>41</v>
       </c>
       <c r="K73">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L73">
         <v>24</v>
@@ -7209,10 +7218,10 @@
         <v>13</v>
       </c>
       <c r="G75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H75">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I75">
         <v>10</v>
@@ -7221,7 +7230,7 @@
         <v>18</v>
       </c>
       <c r="K75">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L75">
         <v>14</v>
@@ -7235,7 +7244,7 @@
         <v>82</v>
       </c>
       <c r="B76">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76">
         <v>59</v>
@@ -7244,25 +7253,25 @@
         <v>41</v>
       </c>
       <c r="E76">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F76">
         <v>64</v>
       </c>
       <c r="G76">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H76">
         <v>33</v>
       </c>
       <c r="I76">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J76">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K76">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L76">
         <v>44</v>
@@ -7285,7 +7294,7 @@
         <v>22</v>
       </c>
       <c r="E77">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F77">
         <v>20</v>
@@ -7294,7 +7303,7 @@
         <v>25</v>
       </c>
       <c r="H77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I77">
         <v>27</v>
@@ -7329,7 +7338,7 @@
         <v>56</v>
       </c>
       <c r="F78">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G78">
         <v>59</v>
@@ -7341,7 +7350,7 @@
         <v>56</v>
       </c>
       <c r="J78">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K78">
         <v>65</v>
@@ -7358,40 +7367,40 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C79">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D79">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E79">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F79">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G79">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H79">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I79">
         <v>104</v>
       </c>
       <c r="J79">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K79">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L79">
         <v>106</v>
       </c>
       <c r="M79">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7411,7 +7420,7 @@
         <v>14</v>
       </c>
       <c r="F80">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G80">
         <v>14</v>
@@ -7426,13 +7435,13 @@
         <v>11</v>
       </c>
       <c r="K80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L80">
         <v>15</v>
       </c>
       <c r="M80">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7502,7 +7511,7 @@
         <v>7</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K82">
         <v>6</v>
@@ -7522,37 +7531,37 @@
         <v>74</v>
       </c>
       <c r="C83">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D83">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E83">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F83">
         <v>66</v>
       </c>
       <c r="G83">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H83">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I83">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J83">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K83">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L83">
         <v>79</v>
       </c>
       <c r="M83">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7560,7 +7569,7 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C84">
         <v>31</v>
@@ -7569,7 +7578,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F84">
         <v>35</v>
@@ -7578,10 +7587,10 @@
         <v>35</v>
       </c>
       <c r="H84">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I84">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J84">
         <v>45</v>
@@ -7593,7 +7602,7 @@
         <v>36</v>
       </c>
       <c r="M84">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7601,40 +7610,40 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C85">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D85">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E85">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F85">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G85">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H85">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I85">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J85">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K85">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L85">
         <v>182</v>
       </c>
       <c r="M85">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7663,19 +7672,19 @@
         <v>22</v>
       </c>
       <c r="I86">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J86">
         <v>23</v>
       </c>
       <c r="K86">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L86">
         <v>28</v>
       </c>
       <c r="M86">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7695,7 +7704,7 @@
         <v>18</v>
       </c>
       <c r="F87">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G87">
         <v>6</v>
@@ -7727,28 +7736,28 @@
         <v>33</v>
       </c>
       <c r="C88">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D88">
         <v>47</v>
       </c>
       <c r="E88">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F88">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G88">
         <v>39</v>
       </c>
       <c r="H88">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I88">
         <v>34</v>
       </c>
       <c r="J88">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K88">
         <v>58</v>
@@ -7757,7 +7766,7 @@
         <v>51</v>
       </c>
       <c r="M88">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7768,28 +7777,28 @@
         <v>50</v>
       </c>
       <c r="C89">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D89">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E89">
+        <v>34</v>
+      </c>
+      <c r="F89">
+        <v>47</v>
+      </c>
+      <c r="G89">
+        <v>58</v>
+      </c>
+      <c r="H89">
+        <v>44</v>
+      </c>
+      <c r="I89">
         <v>33</v>
       </c>
-      <c r="F89">
-        <v>46</v>
-      </c>
-      <c r="G89">
-        <v>57</v>
-      </c>
-      <c r="H89">
-        <v>43</v>
-      </c>
-      <c r="I89">
-        <v>32</v>
-      </c>
       <c r="J89">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K89">
         <v>61</v>
@@ -7798,7 +7807,7 @@
         <v>48</v>
       </c>
       <c r="M89">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7812,25 +7821,25 @@
         <v>70</v>
       </c>
       <c r="D90">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E90">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F90">
         <v>55</v>
       </c>
       <c r="G90">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H90">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I90">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J90">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K90">
         <v>41</v>
@@ -7850,34 +7859,34 @@
         <v>42</v>
       </c>
       <c r="C91">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D91">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E91">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F91">
         <v>43</v>
       </c>
       <c r="G91">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H91">
         <v>38</v>
       </c>
       <c r="I91">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J91">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K91">
         <v>46</v>
       </c>
       <c r="L91">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M91">
         <v>49</v>
@@ -7894,7 +7903,7 @@
         <v>10</v>
       </c>
       <c r="D92">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E92">
         <v>14</v>
@@ -7915,7 +7924,7 @@
         <v>14</v>
       </c>
       <c r="K92">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L92">
         <v>10</v>
@@ -7929,7 +7938,7 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C93">
         <v>27</v>
@@ -7944,7 +7953,7 @@
         <v>20</v>
       </c>
       <c r="G93">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H93">
         <v>17</v>
@@ -7953,7 +7962,7 @@
         <v>18</v>
       </c>
       <c r="J93">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K93">
         <v>20</v>
@@ -7970,7 +7979,7 @@
         <v>100</v>
       </c>
       <c r="B94">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C94">
         <v>28</v>
@@ -7988,16 +7997,16 @@
         <v>30</v>
       </c>
       <c r="H94">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I94">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J94">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K94">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L94">
         <v>44</v>
@@ -8011,13 +8020,13 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C95">
         <v>67</v>
       </c>
       <c r="D95">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E95">
         <v>74</v>
@@ -8026,13 +8035,13 @@
         <v>67</v>
       </c>
       <c r="G95">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H95">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I95">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J95">
         <v>75</v>
@@ -8041,7 +8050,7 @@
         <v>78</v>
       </c>
       <c r="L95">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M95">
         <v>49</v>
@@ -8052,7 +8061,7 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C96">
         <v>54</v>
@@ -8064,16 +8073,16 @@
         <v>64</v>
       </c>
       <c r="F96">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G96">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H96">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I96">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J96">
         <v>58</v>
@@ -8085,7 +8094,7 @@
         <v>34</v>
       </c>
       <c r="M96">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8096,10 +8105,10 @@
         <v>15</v>
       </c>
       <c r="C97">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D97">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E97">
         <v>28</v>
@@ -8117,10 +8126,10 @@
         <v>43</v>
       </c>
       <c r="J97">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K97">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L97">
         <v>42</v>
@@ -8146,7 +8155,7 @@
         <v>26</v>
       </c>
       <c r="F98">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G98">
         <v>18</v>
@@ -8161,7 +8170,7 @@
         <v>31</v>
       </c>
       <c r="K98">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L98">
         <v>28</v>
@@ -8187,16 +8196,16 @@
         <v>64</v>
       </c>
       <c r="F99">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G99">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H99">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I99">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J99">
         <v>54</v>
@@ -8208,7 +8217,7 @@
         <v>55</v>
       </c>
       <c r="M99">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8257,40 +8266,40 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>3451</v>
+        <v>3494</v>
       </c>
       <c r="C101">
-        <v>4512</v>
+        <v>4571</v>
       </c>
       <c r="D101">
-        <v>4726</v>
+        <v>4782</v>
       </c>
       <c r="E101">
-        <v>4291</v>
+        <v>4366</v>
       </c>
       <c r="F101">
-        <v>3838</v>
+        <v>3893</v>
       </c>
       <c r="G101">
-        <v>4206</v>
+        <v>4256</v>
       </c>
       <c r="H101">
-        <v>3974</v>
+        <v>4034</v>
       </c>
       <c r="I101">
-        <v>4086</v>
+        <v>4134</v>
       </c>
       <c r="J101">
-        <v>4591</v>
+        <v>4651</v>
       </c>
       <c r="K101">
-        <v>4661</v>
+        <v>4722</v>
       </c>
       <c r="L101">
-        <v>3578</v>
+        <v>3630</v>
       </c>
       <c r="M101">
-        <v>3224</v>
+        <v>3276</v>
       </c>
     </row>
   </sheetData>
@@ -8487,13 +8496,13 @@
         <v>9</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2">
         <v>15</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2">
         <v>11</v>
@@ -8540,7 +8549,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8642,7 +8651,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -8683,19 +8692,19 @@
         <v>27</v>
       </c>
       <c r="I7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <v>28</v>
       </c>
       <c r="K7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L7">
         <v>39</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -8775,7 +8784,7 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>35</v>
@@ -8784,7 +8793,7 @@
         <v>37</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>45</v>
@@ -8793,7 +8802,7 @@
         <v>44</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2">
         <v>54</v>
@@ -8813,10 +8822,10 @@
         <v>48</v>
       </c>
       <c r="C3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3">
         <v>53</v>
@@ -8828,13 +8837,13 @@
         <v>61</v>
       </c>
       <c r="H3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I3">
         <v>53</v>
       </c>
       <c r="J3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K3">
         <v>56</v>
@@ -8872,7 +8881,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -8881,7 +8890,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -8933,31 +8942,31 @@
         <v>51</v>
       </c>
       <c r="C6">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6">
         <v>75</v>
       </c>
       <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>51</v>
+      </c>
+      <c r="G6">
+        <v>73</v>
+      </c>
+      <c r="H6">
         <v>59</v>
       </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>72</v>
-      </c>
-      <c r="H6">
-        <v>56</v>
-      </c>
       <c r="I6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J6">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L6">
         <v>39</v>
@@ -8974,34 +8983,34 @@
         <v>132</v>
       </c>
       <c r="C7">
+        <v>199</v>
+      </c>
+      <c r="D7">
         <v>196</v>
       </c>
-      <c r="D7">
-        <v>193</v>
-      </c>
       <c r="E7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H7">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M7">
         <v>101</v>
@@ -9087,7 +9096,7 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -9119,7 +9128,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -9140,7 +9149,7 @@
         <v>17</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -9183,6 +9192,9 @@
       <c r="K4">
         <v>2</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -9230,7 +9242,7 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -9253,7 +9265,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -9262,7 +9274,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>35</v>
@@ -9271,10 +9283,10 @@
         <v>35</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>45</v>
@@ -9286,7 +9298,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -9372,7 +9384,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -9494,7 +9506,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -9509,7 +9521,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>20</v>
@@ -9535,10 +9547,10 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>28</v>
@@ -9550,7 +9562,7 @@
         <v>16</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>31</v>
@@ -9666,7 +9678,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9698,7 +9710,7 @@
         <v>17</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3">
         <v>26</v>
@@ -9707,7 +9719,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9721,7 +9733,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -9742,7 +9754,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -9764,6 +9776,9 @@
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
       <c r="K5">
         <v>2</v>
       </c>
@@ -9782,7 +9797,7 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>68</v>
@@ -9823,7 +9838,7 @@
         <v>64</v>
       </c>
       <c r="D7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7">
         <v>105</v>
@@ -9841,16 +9856,16 @@
         <v>86</v>
       </c>
       <c r="J7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L7">
         <v>71</v>
       </c>
       <c r="M7">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -9924,40 +9939,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2">
         <v>65</v>
       </c>
       <c r="E2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2">
         <v>59</v>
       </c>
       <c r="G2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>74</v>
       </c>
       <c r="I2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2">
         <v>71</v>
       </c>
       <c r="K2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L2">
         <v>58</v>
       </c>
       <c r="M2">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9965,31 +9980,31 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C3">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3">
+        <v>97</v>
+      </c>
+      <c r="H3">
         <v>95</v>
-      </c>
-      <c r="H3">
-        <v>93</v>
       </c>
       <c r="I3">
         <v>85</v>
       </c>
       <c r="J3">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K3">
         <v>72</v>
@@ -9998,7 +10013,7 @@
         <v>55</v>
       </c>
       <c r="M3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10018,7 +10033,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>20</v>
@@ -10050,7 +10065,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -10088,7 +10103,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>102</v>
@@ -10103,16 +10118,16 @@
         <v>58</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J6">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K6">
         <v>76</v>
@@ -10121,7 +10136,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10129,40 +10144,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="H7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L7">
         <v>169</v>
       </c>
       <c r="M7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -10310,7 +10325,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10327,7 +10342,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -10370,16 +10385,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>39</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -10411,16 +10426,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>58</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7">
         <v>36</v>
@@ -10444,7 +10459,7 @@
         <v>54</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -10536,7 +10551,7 @@
         <v>31</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2">
         <v>48</v>
@@ -10574,16 +10589,16 @@
         <v>42</v>
       </c>
       <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
         <v>37</v>
       </c>
-      <c r="H3">
-        <v>36</v>
-      </c>
       <c r="I3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K3">
         <v>37</v>
@@ -10592,7 +10607,7 @@
         <v>34</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10682,19 +10697,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>41</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6">
         <v>48</v>
@@ -10706,7 +10721,7 @@
         <v>30</v>
       </c>
       <c r="J6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K6">
         <v>37</v>
@@ -10723,31 +10738,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7">
         <v>110</v>
       </c>
       <c r="E7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H7">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K7">
         <v>123</v>
@@ -10756,7 +10771,7 @@
         <v>107</v>
       </c>
       <c r="M7">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -10839,7 +10854,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -10851,7 +10866,7 @@
         <v>13</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>13</v>
@@ -10979,7 +10994,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>27</v>
@@ -10988,7 +11003,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -11000,10 +11015,10 @@
         <v>21</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>17</v>
@@ -11020,7 +11035,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>51</v>
@@ -11029,7 +11044,7 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>24</v>
@@ -11041,10 +11056,10 @@
         <v>41</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7">
         <v>44</v>
@@ -11142,7 +11157,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -11154,7 +11169,7 @@
         <v>10</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -11177,7 +11192,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -11189,7 +11204,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3">
         <v>17</v>
@@ -11270,7 +11285,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -11279,7 +11294,7 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>34</v>
@@ -11291,10 +11306,10 @@
         <v>15</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6">
         <v>33</v>
@@ -11311,7 +11326,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>59</v>
@@ -11320,25 +11335,25 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>64</v>
       </c>
       <c r="G7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7">
         <v>33</v>
       </c>
       <c r="I7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7">
         <v>44</v>
@@ -11424,7 +11439,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -11445,7 +11460,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -11602,7 +11617,7 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>22</v>
@@ -11623,7 +11638,7 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>13</v>
@@ -11709,13 +11724,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>13</v>
@@ -11744,7 +11759,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -11771,13 +11786,13 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>8</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11852,7 +11867,7 @@
         <v>28</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -11881,19 +11896,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="D7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>45</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>44</v>
@@ -11908,13 +11923,13 @@
         <v>44</v>
       </c>
       <c r="K7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7">
         <v>24</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -12009,13 +12024,13 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -12184,13 +12199,13 @@
         <v>14</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7">
         <v>28</v>
       </c>
       <c r="K7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L7">
         <v>14</v>
@@ -12276,10 +12291,10 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>37</v>
@@ -12291,10 +12306,10 @@
         <v>39</v>
       </c>
       <c r="I2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2">
         <v>40</v>
@@ -12314,16 +12329,16 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>51</v>
@@ -12335,10 +12350,10 @@
         <v>43</v>
       </c>
       <c r="J3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L3">
         <v>26</v>
@@ -12379,7 +12394,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -12402,7 +12417,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -12434,22 +12449,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D6">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6">
         <v>51</v>
       </c>
       <c r="G6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6">
         <v>54</v>
@@ -12475,34 +12490,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H7">
         <v>146</v>
       </c>
       <c r="I7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L7">
         <v>113</v>
@@ -12796,7 +12811,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -12936,13 +12951,13 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>12</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>16</v>
@@ -12971,19 +12986,19 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>42</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
       <c r="G7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7">
         <v>31</v>
@@ -13087,7 +13102,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>13</v>
@@ -13099,7 +13114,7 @@
         <v>8</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>22</v>
@@ -13128,7 +13143,7 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -13233,7 +13248,7 @@
         <v>28</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>26</v>
@@ -13274,7 +13289,7 @@
         <v>56</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G7">
         <v>59</v>
@@ -13286,7 +13301,7 @@
         <v>56</v>
       </c>
       <c r="J7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7">
         <v>65</v>
@@ -13494,6 +13509,9 @@
       <c r="C5">
         <v>5</v>
       </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
@@ -13504,7 +13522,7 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -13530,10 +13548,10 @@
         <v>17</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <v>13</v>
@@ -13551,7 +13569,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13565,16 +13583,16 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>41</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7">
         <v>40</v>
@@ -13586,13 +13604,13 @@
         <v>57</v>
       </c>
       <c r="K7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L7">
         <v>40</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -13772,7 +13790,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13859,7 +13877,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -13977,13 +13995,13 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -13995,7 +14013,7 @@
         <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -14004,7 +14022,7 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14105,13 +14123,13 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -14123,7 +14141,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>11</v>
@@ -14132,7 +14150,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -14274,7 +14292,7 @@
         <v>12</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -14417,7 +14435,7 @@
         <v>44</v>
       </c>
       <c r="K7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7">
         <v>38</v>
@@ -14509,16 +14527,16 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>20</v>
@@ -14530,7 +14548,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14538,7 +14556,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -14661,10 +14679,10 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -14684,7 +14702,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>54</v>
@@ -14696,16 +14714,16 @@
         <v>64</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J7">
         <v>58</v>
@@ -14717,7 +14735,7 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -14794,19 +14812,19 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>9</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>15</v>
@@ -14815,7 +14833,7 @@
         <v>16</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K2">
         <v>17</v>
@@ -14835,13 +14853,13 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
         <v>19</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
       </c>
       <c r="F3">
         <v>16</v>
@@ -14856,13 +14874,13 @@
         <v>18</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3">
         <v>16</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M3">
         <v>21</v>
@@ -14940,7 +14958,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>35</v>
@@ -14958,7 +14976,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>13</v>
@@ -14981,34 +14999,34 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>43</v>
       </c>
       <c r="G7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H7">
         <v>38</v>
       </c>
       <c r="I7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K7">
         <v>46</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M7">
         <v>49</v>
@@ -15103,7 +15121,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -15198,7 +15216,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -15216,7 +15234,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15239,13 +15257,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7">
         <v>12</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -15257,7 +15275,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -15340,16 +15358,16 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G2">
         <v>42</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>33</v>
@@ -15364,7 +15382,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15381,13 +15399,13 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>44</v>
@@ -15396,16 +15414,16 @@
         <v>29</v>
       </c>
       <c r="J3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3">
         <v>34</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15422,7 +15440,7 @@
         <v>12</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -15460,7 +15478,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -15495,16 +15513,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>66</v>
       </c>
       <c r="E6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -15536,40 +15554,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I7">
         <v>104</v>
       </c>
       <c r="J7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L7">
         <v>106</v>
       </c>
       <c r="M7">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -15646,7 +15664,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -15807,7 +15825,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>21</v>
@@ -15833,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>15</v>
@@ -15848,7 +15866,7 @@
         <v>28</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>45</v>
@@ -15946,7 +15964,7 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -15987,10 +16005,10 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3">
         <v>30</v>
@@ -16098,7 +16116,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -16110,10 +16128,10 @@
         <v>65</v>
       </c>
       <c r="F6">
+        <v>46</v>
+      </c>
+      <c r="G6">
         <v>45</v>
-      </c>
-      <c r="G6">
-        <v>44</v>
       </c>
       <c r="H6">
         <v>25</v>
@@ -16122,7 +16140,7 @@
         <v>44</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6">
         <v>42</v>
@@ -16139,7 +16157,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7">
         <v>97</v>
@@ -16148,13 +16166,13 @@
         <v>114</v>
       </c>
       <c r="E7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7">
         <v>110</v>
@@ -16163,7 +16181,7 @@
         <v>116</v>
       </c>
       <c r="J7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K7">
         <v>110</v>
@@ -16261,13 +16279,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>15</v>
@@ -16299,13 +16317,13 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -16327,6 +16345,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
         <v>1</v>
       </c>
@@ -16389,7 +16410,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -16421,7 +16442,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>28</v>
@@ -16430,16 +16451,16 @@
         <v>23</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7">
         <v>63</v>
@@ -16546,10 +16567,10 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16572,10 +16593,10 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -16674,19 +16695,19 @@
         <v>10</v>
       </c>
       <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="H6">
-        <v>16</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -16822,13 +16843,13 @@
         <v>15</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>18</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -16927,7 +16948,7 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -16939,7 +16960,7 @@
         <v>21</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>29</v>
@@ -16951,7 +16972,7 @@
         <v>15</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16968,19 +16989,19 @@
         <v>50</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7">
         <v>48</v>
       </c>
       <c r="G7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7">
         <v>75</v>
       </c>
       <c r="I7">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J7">
         <v>67</v>
@@ -16992,7 +17013,7 @@
         <v>60</v>
       </c>
       <c r="M7">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -17131,7 +17152,7 @@
         <v>3</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>4</v>
@@ -17148,7 +17169,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -17209,7 +17230,7 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -17235,7 +17256,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>27</v>
@@ -17250,7 +17271,7 @@
         <v>20</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>17</v>
@@ -17259,7 +17280,7 @@
         <v>18</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -17564,13 +17585,13 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>45</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>39</v>
@@ -17579,19 +17600,19 @@
         <v>26</v>
       </c>
       <c r="H2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2">
         <v>44</v>
       </c>
       <c r="K2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2">
         <v>38</v>
@@ -17605,13 +17626,13 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>54</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>35</v>
@@ -17629,7 +17650,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3">
         <v>43</v>
@@ -17711,7 +17732,7 @@
         <v>4</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -17725,16 +17746,16 @@
         <v>63</v>
       </c>
       <c r="C6">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>56</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>33</v>
@@ -17743,13 +17764,13 @@
         <v>32</v>
       </c>
       <c r="I6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L6">
         <v>34</v>
@@ -17766,34 +17787,34 @@
         <v>136</v>
       </c>
       <c r="C7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7">
         <v>116</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M7">
         <v>92</v>
@@ -17879,7 +17900,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -17891,7 +17912,7 @@
         <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>8</v>
@@ -17929,7 +17950,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -18025,13 +18046,13 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>8</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>15</v>
@@ -18060,19 +18081,19 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>21</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7">
         <v>18</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <v>32</v>
@@ -18176,16 +18197,16 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2">
         <v>13</v>
@@ -18261,7 +18282,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>6</v>
@@ -18295,7 +18316,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -18316,10 +18337,10 @@
         <v>14</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K6">
         <v>25</v>
@@ -18336,7 +18357,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>28</v>
@@ -18354,16 +18375,16 @@
         <v>30</v>
       </c>
       <c r="H7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7">
         <v>44</v>
@@ -18449,7 +18470,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -18476,7 +18497,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18502,7 +18523,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -18621,7 +18642,7 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>17</v>
@@ -18633,7 +18654,7 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7">
         <v>22</v>
@@ -18648,7 +18669,7 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -18728,10 +18749,10 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -18755,7 +18776,7 @@
         <v>14</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18763,7 +18784,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -18859,6 +18880,9 @@
       <c r="I5">
         <v>3</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
       <c r="K5">
         <v>1</v>
       </c>
@@ -18909,16 +18933,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>26</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>29</v>
@@ -18933,7 +18957,7 @@
         <v>31</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7">
         <v>34</v>
@@ -18942,7 +18966,7 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -19028,7 +19052,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -19060,7 +19084,7 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -19072,16 +19096,16 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>7</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -19206,7 +19230,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>54</v>
@@ -19215,19 +19239,19 @@
         <v>54</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7">
         <v>40</v>
@@ -19322,7 +19346,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -19462,7 +19486,7 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>18</v>
@@ -19488,7 +19512,7 @@
         <v>26</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -19503,7 +19527,7 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>28</v>
@@ -19627,7 +19651,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -19648,7 +19672,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -19677,7 +19701,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -19761,7 +19785,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -19770,7 +19794,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -19782,7 +19806,7 @@
         <v>12</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7">
         <v>26</v>
@@ -20315,7 +20339,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -20341,12 +20365,15 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -20376,7 +20403,7 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -20414,13 +20441,13 @@
         <v>12</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>20</v>
@@ -20429,7 +20456,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -20521,7 +20548,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2">
         <v>34</v>
@@ -20530,7 +20557,7 @@
         <v>17</v>
       </c>
       <c r="K2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>20</v>
@@ -20556,16 +20583,16 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>29</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>13</v>
@@ -20658,22 +20685,22 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>43</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>16</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>22</v>
@@ -20699,31 +20726,31 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>87</v>
       </c>
       <c r="E7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>70</v>
       </c>
       <c r="H7">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7">
         <v>55</v>
       </c>
       <c r="K7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7">
         <v>63</v>
@@ -20875,7 +20902,7 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -20916,7 +20943,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -21166,7 +21193,7 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -21178,10 +21205,10 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>13</v>
@@ -21193,7 +21220,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -21207,7 +21234,7 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -21219,10 +21246,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>29</v>
@@ -21234,7 +21261,7 @@
         <v>20</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -21311,7 +21338,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>15</v>
@@ -21376,7 +21403,7 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -21399,7 +21426,7 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -21445,7 +21472,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -21483,13 +21510,13 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -21507,7 +21534,7 @@
         <v>41</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7">
         <v>24</v>
@@ -21639,6 +21666,9 @@
       <c r="F3">
         <v>2</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>2</v>
       </c>
@@ -21741,7 +21771,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -21880,7 +21910,7 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>11</v>
@@ -21892,7 +21922,7 @@
         <v>7</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -21901,7 +21931,7 @@
         <v>11</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -21979,16 +22009,16 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>26</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>15</v>
@@ -21997,13 +22027,13 @@
         <v>16</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>11</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -22020,31 +22050,31 @@
         <v>36</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>40</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>44</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L7">
         <v>25</v>
@@ -22168,10 +22198,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -22188,6 +22218,9 @@
       <c r="I3">
         <v>7</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>5</v>
       </c>
@@ -22288,7 +22321,7 @@
         <v>19</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L6">
         <v>31</v>
@@ -22305,10 +22338,10 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>28</v>
@@ -22326,10 +22359,10 @@
         <v>43</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7">
         <v>42</v>
@@ -22415,7 +22448,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -22436,7 +22469,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -22543,7 +22576,7 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -22563,7 +22596,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -22584,7 +22617,7 @@
         <v>14</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -22600,7 +22633,7 @@
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -22615,9 +22648,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22631,31 +22665,34 @@
         <v>2017</v>
       </c>
       <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -22672,7 +22709,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -22681,68 +22718,71 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="G3">
+      <c r="F3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -22755,17 +22795,14 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -22774,13 +22811,16 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -22794,16 +22834,16 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
         <v>8</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -22812,9 +22852,12 @@
         <v>9</v>
       </c>
       <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>13</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5</v>
       </c>
     </row>
@@ -22892,7 +22935,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -22901,7 +22944,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -22922,7 +22965,7 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22948,13 +22991,13 @@
         <v>16</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>11</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3">
         <v>12</v>
@@ -22983,7 +23026,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -23047,7 +23090,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -23062,7 +23105,7 @@
         <v>15</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>32</v>
@@ -23071,7 +23114,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23082,28 +23125,28 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>47</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>39</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7">
         <v>34</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K7">
         <v>58</v>
@@ -23112,7 +23155,7 @@
         <v>51</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -23189,7 +23232,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -23213,7 +23256,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23319,7 +23362,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -23346,7 +23389,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -23432,7 +23475,7 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>13</v>
@@ -23441,10 +23484,10 @@
         <v>13</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -23464,7 +23507,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -23479,7 +23522,7 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -23494,7 +23537,7 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23505,7 +23548,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -23517,7 +23560,7 @@
         <v>8</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -23535,7 +23578,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23569,10 +23612,10 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -23596,7 +23639,7 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23607,28 +23650,28 @@
         <v>50</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>47</v>
+      </c>
+      <c r="G7">
+        <v>58</v>
+      </c>
+      <c r="H7">
+        <v>44</v>
+      </c>
+      <c r="I7">
         <v>33</v>
       </c>
-      <c r="F7">
-        <v>46</v>
-      </c>
-      <c r="G7">
-        <v>57</v>
-      </c>
-      <c r="H7">
-        <v>43</v>
-      </c>
-      <c r="I7">
-        <v>32</v>
-      </c>
       <c r="J7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K7">
         <v>61</v>
@@ -23637,7 +23680,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -23845,7 +23888,7 @@
         <v>12</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -23886,7 +23929,7 @@
         <v>17</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -24010,7 +24053,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -24031,7 +24074,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -24121,7 +24164,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>20</v>
@@ -24144,7 +24187,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>26</v>
@@ -24162,10 +24205,10 @@
         <v>34</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <v>24</v>
@@ -24278,7 +24321,7 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -24351,7 +24394,7 @@
         <v>13</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -24363,7 +24406,7 @@
         <v>17</v>
       </c>
       <c r="M4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24433,19 +24476,19 @@
         <v>22</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6">
         <v>23</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6">
         <v>28</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -24575,7 +24618,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -24613,13 +24656,13 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>2</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -24697,10 +24740,10 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -24709,7 +24752,7 @@
         <v>18</v>
       </c>
       <c r="K7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7">
         <v>14</v>
@@ -24798,7 +24841,7 @@
         <v>11</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -24807,7 +24850,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>16</v>
@@ -24839,7 +24882,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>19</v>
@@ -24848,13 +24891,13 @@
         <v>15</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3">
         <v>10</v>
@@ -24886,13 +24929,13 @@
         <v>4</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -24956,7 +24999,7 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -24997,25 +25040,25 @@
         <v>70</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7">
         <v>55</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7">
         <v>41</v>
@@ -25186,7 +25229,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -25213,7 +25256,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -25244,7 +25287,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -25253,7 +25296,7 @@
         <v>19</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>19</v>
@@ -25285,16 +25328,16 @@
         <v>36</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>47</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7">
         <v>42</v>
@@ -25315,7 +25358,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -25398,7 +25441,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -25511,7 +25554,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -25549,13 +25592,13 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>11</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -25775,7 +25818,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -25799,7 +25842,7 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -25816,7 +25859,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -25840,7 +25883,7 @@
         <v>13</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -25935,7 +25978,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -25956,7 +25999,7 @@
         <v>8</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25991,7 +26034,7 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -26081,7 +26124,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -26107,7 +26150,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>28</v>
@@ -26122,13 +26165,13 @@
         <v>28</v>
       </c>
       <c r="K7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7">
         <v>20</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -26249,10 +26292,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>7</v>
@@ -26270,7 +26313,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <v>9</v>
@@ -26380,10 +26423,10 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>32</v>
@@ -26401,7 +26444,7 @@
         <v>45</v>
       </c>
       <c r="L7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7">
         <v>27</v>
@@ -26487,31 +26530,31 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>37</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L2">
         <v>48</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26519,25 +26562,25 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>45</v>
+      </c>
+      <c r="C3">
         <v>44</v>
-      </c>
-      <c r="C3">
-        <v>43</v>
       </c>
       <c r="D3">
         <v>60</v>
       </c>
       <c r="E3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>70</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I3">
         <v>79</v>
@@ -26546,7 +26589,7 @@
         <v>70</v>
       </c>
       <c r="K3">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L3">
         <v>81</v>
@@ -26645,16 +26688,16 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>57</v>
@@ -26663,13 +26706,13 @@
         <v>57</v>
       </c>
       <c r="I6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J6">
         <v>52</v>
       </c>
       <c r="K6">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -26683,40 +26726,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E7">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L7">
         <v>182</v>
       </c>
       <c r="M7">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -27072,7 +27115,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -27191,7 +27234,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -27226,13 +27269,13 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>7</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -27435,7 +27478,7 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>17</v>
@@ -27476,7 +27519,7 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -27645,6 +27688,9 @@
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>2</v>
       </c>
@@ -27710,7 +27756,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -27811,7 +27857,7 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>9</v>
@@ -27843,7 +27889,7 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -27939,7 +27985,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -27980,7 +28026,7 @@
         <v>22</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -27989,7 +28035,7 @@
         <v>25</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>27</v>
@@ -28504,6 +28550,9 @@
       <c r="E2">
         <v>2</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
       <c r="G2">
         <v>1</v>
       </c>
@@ -28564,7 +28613,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28631,7 +28680,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -28657,7 +28706,7 @@
         <v>14</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>14</v>
@@ -28672,13 +28721,13 @@
         <v>11</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6">
         <v>15</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -28805,7 +28854,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -28843,7 +28892,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -28953,7 +29002,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -29101,7 +29150,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -29211,13 +29260,13 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <v>19</v>
@@ -29229,7 +29278,7 @@
         <v>17</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2">
         <v>29</v>
@@ -29255,7 +29304,7 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>28</v>
@@ -29264,10 +29313,10 @@
         <v>24</v>
       </c>
       <c r="H3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>30</v>
@@ -29279,7 +29328,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29290,7 +29339,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -29375,10 +29424,10 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>31</v>
@@ -29387,7 +29436,7 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -29413,28 +29462,28 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7">
         <v>79</v>
       </c>
       <c r="H7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K7">
         <v>126</v>
@@ -29443,7 +29492,7 @@
         <v>65</v>
       </c>
       <c r="M7">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -29846,7 +29895,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -29933,7 +29982,7 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -30129,7 +30178,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -30167,7 +30216,7 @@
         <v>18</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -30262,7 +30311,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -30289,7 +30338,7 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -30343,6 +30392,9 @@
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -30381,7 +30433,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -30408,10 +30460,10 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -30514,6 +30566,9 @@
       <c r="K2">
         <v>2</v>
       </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
@@ -30580,7 +30635,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -30618,7 +30673,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -30645,7 +30700,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -31220,7 +31275,7 @@
 
 <file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -31232,9 +31287,11 @@
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -31251,33 +31308,39 @@
         <v>2019</v>
       </c>
       <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
         <v>2022</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2024</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -31290,14 +31353,14 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
       <c r="I3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -31310,17 +31373,17 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -31333,11 +31396,17 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -31354,16 +31423,22 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>1071</v>
       </c>
       <c r="M2">
-        <v>994</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>1088</v>
       </c>
       <c r="M3">
-        <v>1103</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>321</v>
       </c>
       <c r="M4">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>76</v>
       </c>
       <c r="M5">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>1074</v>
       </c>
       <c r="M6">
-        <v>800</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>3630</v>
       </c>
       <c r="M7">
-        <v>3276</v>
+        <v>3325</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +1876,7 @@
         <v>64</v>
       </c>
       <c r="M2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1917,7 +1917,7 @@
         <v>67</v>
       </c>
       <c r="M3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1958,7 +1958,7 @@
         <v>18</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1999,7 +1999,7 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2040,7 +2040,7 @@
         <v>64</v>
       </c>
       <c r="M6">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2081,7 +2081,7 @@
         <v>220</v>
       </c>
       <c r="M7">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2229,7 @@
         <v>38</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2387,7 +2387,7 @@
         <v>79</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +2494,7 @@
         <v>33</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2617,7 +2617,7 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2699,7 +2699,7 @@
         <v>156</v>
       </c>
       <c r="M7">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -3194,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3270,7 +3270,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3311,7 +3311,7 @@
         <v>121</v>
       </c>
       <c r="M7">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4370,7 +4370,7 @@
         <v>14</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4493,7 +4493,7 @@
         <v>114</v>
       </c>
       <c r="M7">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4534,7 +4534,7 @@
         <v>220</v>
       </c>
       <c r="M8">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4657,7 +4657,7 @@
         <v>63</v>
       </c>
       <c r="M11">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5020,7 +5020,7 @@
         <v>91</v>
       </c>
       <c r="M20">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5143,7 +5143,7 @@
         <v>38</v>
       </c>
       <c r="M23">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5380,7 +5380,7 @@
         <v>169</v>
       </c>
       <c r="M29">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5462,7 +5462,7 @@
         <v>39</v>
       </c>
       <c r="M31">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5544,7 +5544,7 @@
         <v>156</v>
       </c>
       <c r="M33">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5708,7 +5708,7 @@
         <v>121</v>
       </c>
       <c r="M37">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5904,7 +5904,7 @@
         <v>113</v>
       </c>
       <c r="M42">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5986,7 +5986,7 @@
         <v>23</v>
       </c>
       <c r="M44">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6150,7 +6150,7 @@
         <v>54</v>
       </c>
       <c r="M48">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6232,7 +6232,7 @@
         <v>24</v>
       </c>
       <c r="M50">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6273,7 +6273,7 @@
         <v>48</v>
       </c>
       <c r="M51">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6396,7 +6396,7 @@
         <v>71</v>
       </c>
       <c r="M54">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6437,7 +6437,7 @@
         <v>40</v>
       </c>
       <c r="M55">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6744,7 +6744,7 @@
         <v>54</v>
       </c>
       <c r="M63">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6785,7 +6785,7 @@
         <v>29</v>
       </c>
       <c r="M64">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6867,7 +6867,7 @@
         <v>4</v>
       </c>
       <c r="M66">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6908,7 +6908,7 @@
         <v>134</v>
       </c>
       <c r="M67">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7277,7 +7277,7 @@
         <v>44</v>
       </c>
       <c r="M76">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7400,7 +7400,7 @@
         <v>106</v>
       </c>
       <c r="M79">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7561,7 +7561,7 @@
         <v>79</v>
       </c>
       <c r="M83">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7643,7 +7643,7 @@
         <v>182</v>
       </c>
       <c r="M85">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7807,7 +7807,7 @@
         <v>48</v>
       </c>
       <c r="M89">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7889,7 +7889,7 @@
         <v>47</v>
       </c>
       <c r="M91">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7930,7 +7930,7 @@
         <v>10</v>
       </c>
       <c r="M92">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -8299,7 +8299,7 @@
         <v>3630</v>
       </c>
       <c r="M101">
-        <v>3276</v>
+        <v>3325</v>
       </c>
     </row>
   </sheetData>
@@ -8508,7 +8508,7 @@
         <v>11</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8704,7 +8704,7 @@
         <v>39</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -8811,7 +8811,7 @@
         <v>43</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8852,7 +8852,7 @@
         <v>33</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8972,7 +8972,7 @@
         <v>39</v>
       </c>
       <c r="M6">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9013,7 +9013,7 @@
         <v>134</v>
       </c>
       <c r="M7">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -9824,7 +9824,7 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9865,7 +9865,7 @@
         <v>71</v>
       </c>
       <c r="M7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -9972,7 +9972,7 @@
         <v>58</v>
       </c>
       <c r="M2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10054,7 +10054,7 @@
         <v>11</v>
       </c>
       <c r="M4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10136,7 +10136,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10177,7 +10177,7 @@
         <v>169</v>
       </c>
       <c r="M7">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -10284,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10459,7 +10459,7 @@
         <v>54</v>
       </c>
       <c r="M7">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -10919,7 +10919,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11068,7 +11068,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -11216,7 +11216,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -11359,7 +11359,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -12482,7 +12482,7 @@
         <v>47</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12523,7 +12523,7 @@
         <v>113</v>
       </c>
       <c r="M7">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -13417,7 +13417,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13610,7 +13610,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -14339,7 +14339,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14441,7 +14441,7 @@
         <v>38</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -14842,7 +14842,7 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15029,7 +15029,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -15382,7 +15382,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15546,7 +15546,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15587,7 +15587,7 @@
         <v>106</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -15735,7 +15735,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15773,7 +15773,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15840,7 +15840,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15881,7 +15881,7 @@
         <v>29</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -16149,7 +16149,7 @@
         <v>32</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16190,7 +16190,7 @@
         <v>91</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -17735,7 +17735,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17817,7 +17817,7 @@
         <v>114</v>
       </c>
       <c r="M7">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -19681,7 +19681,7 @@
         <v>7</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19815,7 +19815,7 @@
         <v>24</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -20415,7 +20415,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20456,7 +20456,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -20604,7 +20604,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -20756,7 +20756,7 @@
         <v>63</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -22475,7 +22475,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -22623,7 +22623,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -23578,7 +23578,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -23680,7 +23680,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -24906,7 +24906,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25026,7 +25026,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25174,7 +25174,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25358,7 +25358,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -26554,7 +26554,7 @@
         <v>48</v>
       </c>
       <c r="M2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26718,7 +26718,7 @@
         <v>35</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26759,7 +26759,7 @@
         <v>182</v>
       </c>
       <c r="M7">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -29695,7 +29695,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -29736,7 +29736,7 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>1106</v>
       </c>
       <c r="M2">
-        <v>1017</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>1121</v>
       </c>
       <c r="M3">
-        <v>1133</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,7 +950,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C4">
         <v>384</v>
@@ -983,7 +983,7 @@
         <v>329</v>
       </c>
       <c r="M4">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>78</v>
       </c>
       <c r="M5">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>1110</v>
       </c>
       <c r="M6">
-        <v>824</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,7 +1073,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3603</v>
+        <v>3604</v>
       </c>
       <c r="C7">
         <v>4711</v>
@@ -1106,7 +1106,7 @@
         <v>3744</v>
       </c>
       <c r="M7">
-        <v>3367</v>
+        <v>3431</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +1876,7 @@
         <v>66</v>
       </c>
       <c r="M2">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1917,7 +1917,7 @@
         <v>69</v>
       </c>
       <c r="M3">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2040,7 +2040,7 @@
         <v>69</v>
       </c>
       <c r="M6">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2081,7 +2081,7 @@
         <v>231</v>
       </c>
       <c r="M7">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -2188,7 +2188,7 @@
         <v>23</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2229,7 +2229,7 @@
         <v>39</v>
       </c>
       <c r="M3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2270,7 +2270,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2387,7 +2387,7 @@
         <v>83</v>
       </c>
       <c r="M7">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +2494,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2617,7 +2617,7 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2699,7 +2699,7 @@
         <v>162</v>
       </c>
       <c r="M7">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2806,7 +2806,7 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2847,7 +2847,7 @@
         <v>19</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3005,7 +3005,7 @@
         <v>54</v>
       </c>
       <c r="M7">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3153,7 +3153,7 @@
         <v>33</v>
       </c>
       <c r="M3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3194,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3270,7 +3270,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3311,7 +3311,7 @@
         <v>122</v>
       </c>
       <c r="M7">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3418,7 +3418,7 @@
         <v>25</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3579,7 +3579,7 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3620,7 +3620,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3768,7 +3768,7 @@
         <v>28</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3885,7 +3885,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3926,7 +3926,7 @@
         <v>58</v>
       </c>
       <c r="M7">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -4033,7 +4033,7 @@
         <v>7</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4181,7 +4181,7 @@
         <v>22</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4452,7 +4452,7 @@
         <v>26</v>
       </c>
       <c r="M6">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4534,7 +4534,7 @@
         <v>231</v>
       </c>
       <c r="M8">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4616,7 +4616,7 @@
         <v>23</v>
       </c>
       <c r="M10">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4698,7 +4698,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4815,7 +4815,7 @@
         <v>23</v>
       </c>
       <c r="M15">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5020,7 +5020,7 @@
         <v>97</v>
       </c>
       <c r="M20">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5184,7 +5184,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5225,7 +5225,7 @@
         <v>17</v>
       </c>
       <c r="M25">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5307,7 +5307,7 @@
         <v>44</v>
       </c>
       <c r="M27">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5380,7 +5380,7 @@
         <v>174</v>
       </c>
       <c r="M29">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5421,7 +5421,7 @@
         <v>22</v>
       </c>
       <c r="M30">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5544,7 +5544,7 @@
         <v>162</v>
       </c>
       <c r="M33">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5585,7 +5585,7 @@
         <v>23</v>
       </c>
       <c r="M34">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -5626,7 +5626,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -5708,7 +5708,7 @@
         <v>122</v>
       </c>
       <c r="M37">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6273,7 +6273,7 @@
         <v>49</v>
       </c>
       <c r="M51">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6314,7 +6314,7 @@
         <v>65</v>
       </c>
       <c r="M52">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6396,7 +6396,7 @@
         <v>71</v>
       </c>
       <c r="M54">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6636,7 +6636,7 @@
         <v>21</v>
       </c>
       <c r="M60">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6711,7 +6711,7 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C63">
         <v>83</v>
@@ -6744,7 +6744,7 @@
         <v>62</v>
       </c>
       <c r="M63">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6785,7 +6785,7 @@
         <v>29</v>
       </c>
       <c r="M64">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6826,7 +6826,7 @@
         <v>73</v>
       </c>
       <c r="M65">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6908,7 +6908,7 @@
         <v>137</v>
       </c>
       <c r="M67">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7072,7 +7072,7 @@
         <v>9</v>
       </c>
       <c r="M71">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7154,7 +7154,7 @@
         <v>27</v>
       </c>
       <c r="M73">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7236,7 +7236,7 @@
         <v>15</v>
       </c>
       <c r="M75">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7400,7 +7400,7 @@
         <v>108</v>
       </c>
       <c r="M79">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7561,7 +7561,7 @@
         <v>83</v>
       </c>
       <c r="M83">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7643,7 +7643,7 @@
         <v>186</v>
       </c>
       <c r="M85">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7807,7 +7807,7 @@
         <v>48</v>
       </c>
       <c r="M89">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7848,7 +7848,7 @@
         <v>31</v>
       </c>
       <c r="M90">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7889,7 +7889,7 @@
         <v>49</v>
       </c>
       <c r="M91">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7971,7 +7971,7 @@
         <v>18</v>
       </c>
       <c r="M93">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8012,7 +8012,7 @@
         <v>47</v>
       </c>
       <c r="M94">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8053,7 +8053,7 @@
         <v>54</v>
       </c>
       <c r="M95">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -8135,7 +8135,7 @@
         <v>44</v>
       </c>
       <c r="M97">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -8217,7 +8217,7 @@
         <v>58</v>
       </c>
       <c r="M99">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8266,7 +8266,7 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>3603</v>
+        <v>3604</v>
       </c>
       <c r="C101">
         <v>4711</v>
@@ -8299,7 +8299,7 @@
         <v>3744</v>
       </c>
       <c r="M101">
-        <v>3367</v>
+        <v>3431</v>
       </c>
     </row>
   </sheetData>
@@ -8811,7 +8811,7 @@
         <v>44</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9013,7 +9013,7 @@
         <v>137</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -9678,7 +9678,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9719,7 +9719,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9760,7 +9760,7 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9824,7 +9824,7 @@
         <v>33</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9865,7 +9865,7 @@
         <v>71</v>
       </c>
       <c r="M7">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -10013,7 +10013,7 @@
         <v>55</v>
       </c>
       <c r="M3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10177,7 +10177,7 @@
         <v>174</v>
       </c>
       <c r="M7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -11888,7 +11888,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11929,7 +11929,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -12978,7 +12978,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13019,7 +13019,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -13723,7 +13723,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13883,7 +13883,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -14892,7 +14892,7 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15000,7 +15000,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15041,7 +15041,7 @@
         <v>49</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -15558,7 +15558,7 @@
         <v>24</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15599,7 +15599,7 @@
         <v>108</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -15747,7 +15747,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15893,7 +15893,7 @@
         <v>29</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -16041,7 +16041,7 @@
         <v>27</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16202,7 +16202,7 @@
         <v>97</v>
       </c>
       <c r="M7">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -17176,7 +17176,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17304,7 +17304,7 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -17980,7 +17980,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -18123,7 +18123,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -18230,7 +18230,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18408,7 +18408,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -18515,7 +18515,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18687,7 +18687,7 @@
         <v>17</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -19132,7 +19132,7 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19278,7 +19278,7 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -20877,6 +20877,9 @@
       <c r="J2">
         <v>1</v>
       </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
@@ -20997,7 +21000,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -21398,7 +21401,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21570,7 +21573,7 @@
         <v>27</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -22357,7 +22360,7 @@
         <v>32</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22398,7 +22401,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -23526,7 +23529,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23710,7 +23713,7 @@
         <v>48</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -24075,7 +24078,7 @@
         <v>11</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24253,7 +24256,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -24628,7 +24631,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24791,7 +24794,7 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -24898,7 +24901,7 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24939,7 +24942,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -25100,7 +25103,7 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -25207,7 +25210,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25391,7 +25394,7 @@
         <v>49</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -26122,7 +26125,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -26163,7 +26166,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26204,7 +26207,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -26587,7 +26590,7 @@
         <v>50</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26751,7 +26754,7 @@
         <v>36</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26792,7 +26795,7 @@
         <v>186</v>
       </c>
       <c r="M7">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -27204,7 +27207,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -27323,7 +27326,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -29326,7 +29329,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29367,7 +29370,7 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29531,7 +29534,7 @@
         <v>65</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -29917,7 +29920,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -30036,7 +30039,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>1181</v>
       </c>
       <c r="M2">
-        <v>1090</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>1206</v>
       </c>
       <c r="M3">
-        <v>1215</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -983,7 +983,7 @@
         <v>351</v>
       </c>
       <c r="M4">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,7 +1024,7 @@
         <v>81</v>
       </c>
       <c r="M5">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>1183</v>
       </c>
       <c r="M6">
-        <v>881</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1106,7 +1106,7 @@
         <v>4002</v>
       </c>
       <c r="M7">
-        <v>3610</v>
+        <v>3656</v>
       </c>
     </row>
   </sheetData>
@@ -1886,7 +1886,7 @@
         <v>68</v>
       </c>
       <c r="M2">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1927,7 +1927,7 @@
         <v>75</v>
       </c>
       <c r="M3">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2050,7 +2050,7 @@
         <v>70</v>
       </c>
       <c r="M6">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2091,7 +2091,7 @@
         <v>242</v>
       </c>
       <c r="M7">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2239,7 +2239,7 @@
         <v>41</v>
       </c>
       <c r="M3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2397,7 +2397,7 @@
         <v>90</v>
       </c>
       <c r="M7">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2668,7 +2668,7 @@
         <v>61</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2709,7 +2709,7 @@
         <v>174</v>
       </c>
       <c r="M7">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3589,7 +3589,7 @@
         <v>24</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3630,7 +3630,7 @@
         <v>83</v>
       </c>
       <c r="M7">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3778,7 +3778,7 @@
         <v>30</v>
       </c>
       <c r="M3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3936,7 +3936,7 @@
         <v>63</v>
       </c>
       <c r="M7">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4298,7 +4298,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4503,7 +4503,7 @@
         <v>121</v>
       </c>
       <c r="M7">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4544,7 +4544,7 @@
         <v>242</v>
       </c>
       <c r="M8">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4626,7 +4626,7 @@
         <v>25</v>
       </c>
       <c r="M10">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4708,7 +4708,7 @@
         <v>11</v>
       </c>
       <c r="M12">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4828,7 +4828,7 @@
         <v>26</v>
       </c>
       <c r="M15">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4992,7 +4992,7 @@
         <v>117</v>
       </c>
       <c r="M19">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5238,7 +5238,7 @@
         <v>17</v>
       </c>
       <c r="M25">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5393,7 +5393,7 @@
         <v>191</v>
       </c>
       <c r="M29">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5475,7 +5475,7 @@
         <v>40</v>
       </c>
       <c r="M31">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5557,7 +5557,7 @@
         <v>174</v>
       </c>
       <c r="M33">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5835,7 +5835,7 @@
         <v>6</v>
       </c>
       <c r="M40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -5958,7 +5958,7 @@
         <v>32</v>
       </c>
       <c r="M43">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6163,7 +6163,7 @@
         <v>60</v>
       </c>
       <c r="M48">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6286,7 +6286,7 @@
         <v>49</v>
       </c>
       <c r="M51">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6409,7 +6409,7 @@
         <v>80</v>
       </c>
       <c r="M54">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6763,7 +6763,7 @@
         <v>62</v>
       </c>
       <c r="M63">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6845,7 +6845,7 @@
         <v>83</v>
       </c>
       <c r="M65">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7296,7 +7296,7 @@
         <v>47</v>
       </c>
       <c r="M76">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7378,7 +7378,7 @@
         <v>58</v>
       </c>
       <c r="M78">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7419,7 +7419,7 @@
         <v>111</v>
       </c>
       <c r="M79">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7460,7 +7460,7 @@
         <v>16</v>
       </c>
       <c r="M80">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7580,7 +7580,7 @@
         <v>90</v>
       </c>
       <c r="M83">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7621,7 +7621,7 @@
         <v>40</v>
       </c>
       <c r="M84">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7662,7 +7662,7 @@
         <v>197</v>
       </c>
       <c r="M85">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7703,7 +7703,7 @@
         <v>29</v>
       </c>
       <c r="M86">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7785,7 +7785,7 @@
         <v>52</v>
       </c>
       <c r="M88">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8113,7 +8113,7 @@
         <v>36</v>
       </c>
       <c r="M96">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8236,7 +8236,7 @@
         <v>63</v>
       </c>
       <c r="M99">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8318,7 +8318,7 @@
         <v>4002</v>
       </c>
       <c r="M101">
-        <v>3610</v>
+        <v>3656</v>
       </c>
     </row>
   </sheetData>
@@ -8685,7 +8685,7 @@
         <v>17</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8726,7 +8726,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -9218,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9323,7 +9323,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -9849,7 +9849,7 @@
         <v>39</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9890,7 +9890,7 @@
         <v>80</v>
       </c>
       <c r="M7">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -10161,7 +10161,7 @@
         <v>52</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10202,7 +10202,7 @@
         <v>191</v>
       </c>
       <c r="M7">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -10309,7 +10309,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10484,7 +10484,7 @@
         <v>60</v>
       </c>
       <c r="M7">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -10591,7 +10591,7 @@
         <v>34</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10796,7 +10796,7 @@
         <v>117</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -11349,7 +11349,7 @@
         <v>24</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11390,7 +11390,7 @@
         <v>47</v>
       </c>
       <c r="M7">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -12885,7 +12885,7 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13066,7 +13066,7 @@
         <v>25</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -13280,6 +13280,9 @@
       <c r="L5">
         <v>2</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -13360,7 +13363,7 @@
         <v>58</v>
       </c>
       <c r="M7">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -14607,7 +14610,7 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14797,7 +14800,7 @@
         <v>36</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -15447,7 +15450,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15488,7 +15491,7 @@
         <v>35</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15652,7 +15655,7 @@
         <v>111</v>
       </c>
       <c r="M7">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -17786,7 +17789,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17906,7 +17909,7 @@
         <v>121</v>
       </c>
       <c r="M7">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -18676,7 +18679,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18758,7 +18761,7 @@
         <v>17</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -19162,7 +19165,7 @@
         <v>9</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19352,7 +19355,7 @@
         <v>26</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -22106,7 +22109,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -22211,7 +22214,7 @@
         <v>30</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -23137,7 +23140,7 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23289,7 +23292,7 @@
         <v>52</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -24549,7 +24552,7 @@
         <v>17</v>
       </c>
       <c r="M4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -24631,7 +24634,7 @@
         <v>29</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -25463,7 +25466,7 @@
         <v>15</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25504,7 +25507,7 @@
         <v>49</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -26468,7 +26471,7 @@
         <v>9</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26561,7 +26564,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26602,7 +26605,7 @@
         <v>32</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -26709,7 +26712,7 @@
         <v>54</v>
       </c>
       <c r="M2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -26750,7 +26753,7 @@
         <v>87</v>
       </c>
       <c r="M3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -26873,7 +26876,7 @@
         <v>37</v>
       </c>
       <c r="M6">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26914,7 +26917,7 @@
         <v>197</v>
       </c>
       <c r="M7">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -28829,7 +28832,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -28908,7 +28911,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -29257,7 +29260,7 @@
         <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -29364,7 +29367,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -30036,7 +30039,7 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -30190,7 +30193,7 @@
         <v>11</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -868,40 +868,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="C2">
-        <v>963</v>
+        <v>980</v>
       </c>
       <c r="D2">
-        <v>1021</v>
+        <v>1042</v>
       </c>
       <c r="E2">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="F2">
-        <v>1070</v>
+        <v>1089</v>
       </c>
       <c r="G2">
-        <v>1098</v>
+        <v>1112</v>
       </c>
       <c r="H2">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="I2">
-        <v>1191</v>
+        <v>1209</v>
       </c>
       <c r="J2">
-        <v>1336</v>
+        <v>1358</v>
       </c>
       <c r="K2">
-        <v>1506</v>
+        <v>1524</v>
       </c>
       <c r="L2">
-        <v>1198</v>
+        <v>1216</v>
       </c>
       <c r="M2">
-        <v>1120</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -909,40 +909,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1067</v>
+        <v>1083</v>
       </c>
       <c r="C3">
-        <v>1373</v>
+        <v>1393</v>
       </c>
       <c r="D3">
-        <v>1291</v>
+        <v>1312</v>
       </c>
       <c r="E3">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="F3">
-        <v>1272</v>
+        <v>1292</v>
       </c>
       <c r="G3">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="H3">
-        <v>1269</v>
+        <v>1294</v>
       </c>
       <c r="I3">
-        <v>1263</v>
+        <v>1278</v>
       </c>
       <c r="J3">
-        <v>1427</v>
+        <v>1448</v>
       </c>
       <c r="K3">
-        <v>1438</v>
+        <v>1456</v>
       </c>
       <c r="L3">
-        <v>1228</v>
+        <v>1246</v>
       </c>
       <c r="M3">
-        <v>1238</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -950,37 +950,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C4">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D4">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E4">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F4">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="G4">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H4">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I4">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="J4">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K4">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L4">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M4">
         <v>359</v>
@@ -991,7 +991,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -1009,10 +1009,10 @@
         <v>97</v>
       </c>
       <c r="H5">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I5">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J5">
         <v>106</v>
@@ -1024,7 +1024,7 @@
         <v>84</v>
       </c>
       <c r="M5">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1032,40 +1032,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1617</v>
+        <v>1639</v>
       </c>
       <c r="C6">
-        <v>2184</v>
+        <v>2206</v>
       </c>
       <c r="D6">
-        <v>2269</v>
+        <v>2302</v>
       </c>
       <c r="E6">
-        <v>1951</v>
+        <v>1990</v>
       </c>
       <c r="F6">
-        <v>1456</v>
+        <v>1470</v>
       </c>
       <c r="G6">
-        <v>1664</v>
+        <v>1682</v>
       </c>
       <c r="H6">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="I6">
-        <v>1643</v>
+        <v>1658</v>
       </c>
       <c r="J6">
-        <v>1863</v>
+        <v>1879</v>
       </c>
       <c r="K6">
-        <v>1834</v>
+        <v>1860</v>
       </c>
       <c r="L6">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="M6">
-        <v>906</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1073,40 +1073,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3925</v>
+        <v>3982</v>
       </c>
       <c r="C7">
-        <v>5059</v>
+        <v>5124</v>
       </c>
       <c r="D7">
-        <v>5176</v>
+        <v>5256</v>
       </c>
       <c r="E7">
-        <v>4803</v>
+        <v>4863</v>
       </c>
       <c r="F7">
-        <v>4277</v>
+        <v>4336</v>
       </c>
       <c r="G7">
-        <v>4672</v>
+        <v>4713</v>
       </c>
       <c r="H7">
-        <v>4417</v>
+        <v>4468</v>
       </c>
       <c r="I7">
-        <v>4580</v>
+        <v>4635</v>
       </c>
       <c r="J7">
-        <v>5115</v>
+        <v>5178</v>
       </c>
       <c r="K7">
-        <v>5241</v>
+        <v>5305</v>
       </c>
       <c r="L7">
-        <v>4068</v>
+        <v>4118</v>
       </c>
       <c r="M7">
-        <v>3701</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -1574,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>16</v>
@@ -1601,10 +1601,10 @@
         <v>18</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1659,7 +1659,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1711,10 +1711,10 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -1723,7 +1723,7 @@
         <v>21</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6">
         <v>24</v>
@@ -1752,10 +1752,10 @@
         <v>54</v>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7">
         <v>53</v>
@@ -1764,7 +1764,7 @@
         <v>45</v>
       </c>
       <c r="G7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>45</v>
@@ -1779,10 +1779,10 @@
         <v>83</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1859,22 +1859,22 @@
         <v>55</v>
       </c>
       <c r="C2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G2">
+        <v>87</v>
+      </c>
+      <c r="H2">
         <v>86</v>
-      </c>
-      <c r="H2">
-        <v>84</v>
       </c>
       <c r="I2">
         <v>75</v>
@@ -1886,10 +1886,10 @@
         <v>98</v>
       </c>
       <c r="L2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1897,40 +1897,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3">
         <v>102</v>
       </c>
       <c r="H3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J3">
         <v>104</v>
       </c>
       <c r="K3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1944,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -1956,7 +1956,7 @@
         <v>29</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4">
         <v>19</v>
@@ -1979,7 +1979,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>19</v>
@@ -2020,37 +2020,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6">
+        <v>162</v>
+      </c>
+      <c r="D6">
+        <v>158</v>
+      </c>
+      <c r="E6">
+        <v>145</v>
+      </c>
+      <c r="F6">
+        <v>113</v>
+      </c>
+      <c r="G6">
         <v>161</v>
       </c>
-      <c r="D6">
-        <v>157</v>
-      </c>
-      <c r="E6">
-        <v>144</v>
-      </c>
-      <c r="F6">
-        <v>112</v>
-      </c>
-      <c r="G6">
-        <v>158</v>
-      </c>
       <c r="H6">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I6">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K6">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M6">
         <v>74</v>
@@ -2061,40 +2061,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="L7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M7">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2189,16 +2189,16 @@
         <v>28</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2">
         <v>27</v>
@@ -2209,13 +2209,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>22</v>
@@ -2233,13 +2233,13 @@
         <v>33</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K3">
         <v>35</v>
       </c>
       <c r="L3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3">
         <v>46</v>
@@ -2256,7 +2256,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -2309,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2341,7 +2341,7 @@
         <v>20</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>22</v>
@@ -2356,10 +2356,10 @@
         <v>17</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7">
         <v>73</v>
@@ -2382,25 +2382,25 @@
         <v>74</v>
       </c>
       <c r="G7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>91</v>
       </c>
       <c r="I7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K7">
+        <v>105</v>
+      </c>
+      <c r="L7">
+        <v>93</v>
+      </c>
+      <c r="M7">
         <v>104</v>
-      </c>
-      <c r="L7">
-        <v>90</v>
-      </c>
-      <c r="M7">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2474,34 +2474,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>38</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E2">
         <v>56</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>41</v>
       </c>
       <c r="H2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L2">
         <v>37</v>
@@ -2518,34 +2518,34 @@
         <v>55</v>
       </c>
       <c r="C3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E3">
         <v>86</v>
       </c>
       <c r="F3">
+        <v>75</v>
+      </c>
+      <c r="G3">
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>82</v>
+      </c>
+      <c r="I3">
         <v>74</v>
       </c>
-      <c r="G3">
-        <v>81</v>
-      </c>
-      <c r="H3">
+      <c r="J3">
+        <v>63</v>
+      </c>
+      <c r="K3">
         <v>79</v>
       </c>
-      <c r="I3">
-        <v>71</v>
-      </c>
-      <c r="J3">
-        <v>62</v>
-      </c>
-      <c r="K3">
-        <v>78</v>
-      </c>
       <c r="L3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M3">
         <v>48</v>
@@ -2580,13 +2580,13 @@
         <v>12</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -2615,7 +2615,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -2638,25 +2638,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D6">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6">
+        <v>117</v>
+      </c>
+      <c r="F6">
+        <v>85</v>
+      </c>
+      <c r="G6">
         <v>116</v>
       </c>
-      <c r="F6">
-        <v>84</v>
-      </c>
-      <c r="G6">
-        <v>115</v>
-      </c>
       <c r="H6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I6">
         <v>75</v>
@@ -2665,10 +2665,10 @@
         <v>86</v>
       </c>
       <c r="K6">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M6">
         <v>37</v>
@@ -2679,37 +2679,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D7">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M7">
         <v>134</v>
@@ -2798,13 +2798,13 @@
         <v>25</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2">
         <v>27</v>
@@ -2819,7 +2819,7 @@
         <v>22</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2839,19 +2839,19 @@
         <v>22</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>26</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I3">
         <v>25</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3">
         <v>25</v>
@@ -2944,13 +2944,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>23</v>
@@ -2985,31 +2985,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>82</v>
       </c>
       <c r="F7">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I7">
         <v>77</v>
       </c>
       <c r="J7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7">
         <v>87</v>
@@ -3018,7 +3018,7 @@
         <v>61</v>
       </c>
       <c r="M7">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3092,40 +3092,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>31</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>37</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2">
         <v>49</v>
       </c>
       <c r="I2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2">
         <v>40</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3136,7 +3136,7 @@
         <v>39</v>
       </c>
       <c r="C3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>48</v>
@@ -3145,7 +3145,7 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>50</v>
@@ -3157,13 +3157,13 @@
         <v>43</v>
       </c>
       <c r="J3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3">
         <v>51</v>
@@ -3204,7 +3204,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>12</v>
@@ -3250,13 +3250,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>45</v>
@@ -3271,13 +3271,13 @@
         <v>34</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L6">
         <v>41</v>
@@ -3291,40 +3291,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E7">
         <v>141</v>
       </c>
       <c r="F7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H7">
         <v>157</v>
       </c>
       <c r="I7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M7">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3431,7 +3431,7 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3442,7 +3442,7 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>40</v>
@@ -3451,7 +3451,7 @@
         <v>31</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>19</v>
@@ -3460,7 +3460,7 @@
         <v>25</v>
       </c>
       <c r="I3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>27</v>
@@ -3504,7 +3504,7 @@
         <v>7</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3559,10 +3559,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6">
         <v>38</v>
@@ -3574,10 +3574,10 @@
         <v>28</v>
       </c>
       <c r="G6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>48</v>
@@ -3600,10 +3600,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D7">
         <v>109</v>
@@ -3612,19 +3612,19 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K7">
         <v>129</v>
@@ -3633,7 +3633,7 @@
         <v>84</v>
       </c>
       <c r="M7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3710,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -3719,7 +3719,7 @@
         <v>21</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <v>14</v>
@@ -3734,7 +3734,7 @@
         <v>16</v>
       </c>
       <c r="K2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2">
         <v>14</v>
@@ -3754,7 +3754,7 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>23</v>
@@ -3763,7 +3763,7 @@
         <v>28</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3">
         <v>30</v>
@@ -3781,7 +3781,7 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3868,7 +3868,7 @@
         <v>36</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>46</v>
@@ -3889,7 +3889,7 @@
         <v>19</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6">
         <v>28</v>
@@ -3898,7 +3898,7 @@
         <v>11</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3909,19 +3909,19 @@
         <v>92</v>
       </c>
       <c r="C7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7">
         <v>75</v>
       </c>
       <c r="F7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7">
         <v>97</v>
@@ -3930,16 +3930,16 @@
         <v>82</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7">
         <v>64</v>
       </c>
       <c r="M7">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -4037,7 +4037,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -4072,7 +4072,7 @@
         <v>5</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>4</v>
@@ -4126,7 +4126,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4167,7 +4167,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -4179,13 +4179,13 @@
         <v>15</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <v>15</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>19</v>
@@ -4268,16 +4268,16 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F2">
         <v>25</v>
@@ -4292,7 +4292,7 @@
         <v>51</v>
       </c>
       <c r="J2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K2">
         <v>38</v>
@@ -4301,7 +4301,7 @@
         <v>31</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4356,7 +4356,7 @@
         <v>17</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -4365,7 +4365,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4">
         <v>12</v>
@@ -4394,7 +4394,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -4403,7 +4403,7 @@
         <v>13</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>12</v>
@@ -4432,10 +4432,10 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>65</v>
@@ -4447,7 +4447,7 @@
         <v>26</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>24</v>
@@ -4456,16 +4456,16 @@
         <v>33</v>
       </c>
       <c r="J6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6">
         <v>28</v>
       </c>
       <c r="M6">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4473,37 +4473,37 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H7">
         <v>162</v>
       </c>
       <c r="I7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J7">
         <v>142</v>
       </c>
       <c r="K7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L7">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M7">
         <v>98</v>
@@ -4514,40 +4514,40 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C8">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D8">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E8">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G8">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H8">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K8">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="L8">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M8">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4555,13 +4555,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>37</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>26</v>
@@ -4582,7 +4582,7 @@
         <v>32</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9">
         <v>22</v>
@@ -4602,13 +4602,13 @@
         <v>36</v>
       </c>
       <c r="D10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>57</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10">
         <v>35</v>
@@ -4617,10 +4617,10 @@
         <v>35</v>
       </c>
       <c r="I10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K10">
         <v>35</v>
@@ -4637,13 +4637,13 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E11">
         <v>92</v>
@@ -4655,22 +4655,22 @@
         <v>75</v>
       </c>
       <c r="H11">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J11">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K11">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="L11">
         <v>75</v>
       </c>
       <c r="M11">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4705,13 +4705,13 @@
         <v>15</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>11</v>
       </c>
       <c r="M12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4722,13 +4722,13 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>6</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -4763,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -4790,7 +4790,7 @@
         <v>17</v>
       </c>
       <c r="M14">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4801,19 +4801,19 @@
         <v>48</v>
       </c>
       <c r="C15">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15">
         <v>59</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15">
         <v>39</v>
       </c>
       <c r="G15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15">
         <v>43</v>
@@ -4822,10 +4822,10 @@
         <v>54</v>
       </c>
       <c r="J15">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L15">
         <v>27</v>
@@ -4851,7 +4851,7 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -4924,7 +4924,7 @@
         <v>14</v>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18">
         <v>30</v>
@@ -4933,7 +4933,7 @@
         <v>23</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18">
         <v>24</v>
@@ -4951,7 +4951,7 @@
         <v>41</v>
       </c>
       <c r="L18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M18">
         <v>20</v>
@@ -4962,7 +4962,7 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>117</v>
@@ -4971,25 +4971,25 @@
         <v>117</v>
       </c>
       <c r="E19">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F19">
         <v>127</v>
       </c>
       <c r="G19">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I19">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J19">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K19">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L19">
         <v>119</v>
@@ -5003,40 +5003,40 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C20">
         <v>112</v>
       </c>
       <c r="D20">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F20">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G20">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H20">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I20">
         <v>124</v>
       </c>
       <c r="J20">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K20">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L20">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M20">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5044,13 +5044,13 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21">
         <v>21</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -5118,7 +5118,7 @@
         <v>13</v>
       </c>
       <c r="M22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5126,7 +5126,7 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>46</v>
@@ -5135,7 +5135,7 @@
         <v>51</v>
       </c>
       <c r="E23">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F23">
         <v>40</v>
@@ -5144,7 +5144,7 @@
         <v>50</v>
       </c>
       <c r="H23">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I23">
         <v>44</v>
@@ -5156,7 +5156,7 @@
         <v>52</v>
       </c>
       <c r="L23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M23">
         <v>34</v>
@@ -5170,7 +5170,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -5194,7 +5194,7 @@
         <v>18</v>
       </c>
       <c r="K24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -5217,7 +5217,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F25">
         <v>13</v>
@@ -5226,13 +5226,13 @@
         <v>11</v>
       </c>
       <c r="H25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K25">
         <v>21</v>
@@ -5255,7 +5255,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -5299,10 +5299,10 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27">
         <v>35</v>
@@ -5320,7 +5320,7 @@
         <v>61</v>
       </c>
       <c r="L27">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M27">
         <v>42</v>
@@ -5355,7 +5355,7 @@
         <v>2</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -5363,40 +5363,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C29">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D29">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E29">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F29">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G29">
         <v>317</v>
       </c>
       <c r="H29">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I29">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="J29">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K29">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L29">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="M29">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5410,7 +5410,7 @@
         <v>10</v>
       </c>
       <c r="D30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E30">
         <v>15</v>
@@ -5422,13 +5422,13 @@
         <v>15</v>
       </c>
       <c r="H30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
       <c r="J30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <v>19</v>
@@ -5445,28 +5445,28 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31">
         <v>57</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F31">
         <v>48</v>
       </c>
       <c r="G31">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31">
         <v>30</v>
       </c>
       <c r="I31">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J31">
         <v>34</v>
@@ -5475,7 +5475,7 @@
         <v>62</v>
       </c>
       <c r="L31">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M31">
         <v>35</v>
@@ -5489,7 +5489,7 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D32">
         <v>17</v>
@@ -5516,7 +5516,7 @@
         <v>9</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>4</v>
@@ -5527,37 +5527,37 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C33">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D33">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E33">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F33">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G33">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H33">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I33">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J33">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K33">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L33">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M33">
         <v>134</v>
@@ -5586,13 +5586,13 @@
         <v>27</v>
       </c>
       <c r="H34">
- 